--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5347,31 +5350,115 @@
       <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>24701.18</v>
+      </c>
+      <c r="C58" t="n">
+        <v>24926.24</v>
+      </c>
+      <c r="D58" t="n">
+        <v>24662.11</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>264.13</v>
+      </c>
+      <c r="I58" t="n">
+        <v>23475.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>23554.9</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24258.26</v>
+      </c>
+      <c r="L58" t="n">
+        <v>24961.62</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25353</v>
+      </c>
+      <c r="N58" t="n">
+        <v>25744.38</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26759.72</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>23475.5</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>23554.9</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>24258.26</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>24961.62</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>25353</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>25744.38</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>26759.72</v>
+      <c r="I59" s="14" t="n">
+        <v>24397.98</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>25190.37</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -669,25 +666,25 @@
         <v>578.17</v>
       </c>
       <c r="I2" t="n">
-        <v>23784.84</v>
+        <v>23835.64</v>
       </c>
       <c r="J2" t="n">
-        <v>24278.63</v>
+        <v>24297.68</v>
       </c>
       <c r="K2" t="n">
-        <v>24774.63</v>
+        <v>24787.33</v>
       </c>
       <c r="L2" t="n">
-        <v>25270.62</v>
+        <v>25276.97</v>
       </c>
       <c r="M2" t="n">
-        <v>25765.51</v>
+        <v>25752.81</v>
       </c>
       <c r="N2" t="n">
-        <v>26260.41</v>
+        <v>26228.66</v>
       </c>
       <c r="O2" t="n">
-        <v>26757.51</v>
+        <v>26732.11</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5365,13 +5362,13 @@
         <v>24662.11</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>24917.6</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>111.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0045</v>
       </c>
       <c r="H58" t="n">
         <v>264.13</v>
@@ -5397,10 +5394,8 @@
       <c r="O58" t="n">
         <v>26759.72</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5408,9 +5403,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5429,35 +5424,35 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
+      <c r="I59" s="13" t="n">
         <v>24397.98</v>
       </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
+      <c r="J59" s="13" t="n">
+        <v>24715.18</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>24785.53</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>24855.89</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>25049.67</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>25243.44</v>
+      </c>
+      <c r="O59" s="13" t="n">
         <v>25190.37</v>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5356,22 +5356,22 @@
         <v>24701.18</v>
       </c>
       <c r="C58" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D58" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E58" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F58" t="n">
-        <v>111.97</v>
+        <v>-138.39</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0056</v>
       </c>
       <c r="H58" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I58" t="n">
         <v>23475.5</v>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5435,25 +5435,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -666,25 +666,25 @@
         <v>578.17</v>
       </c>
       <c r="I2" t="n">
-        <v>23835.64</v>
+        <v>24569</v>
       </c>
       <c r="J2" t="n">
-        <v>24297.68</v>
+        <v>24572.69</v>
       </c>
       <c r="K2" t="n">
-        <v>24787.33</v>
+        <v>24970.67</v>
       </c>
       <c r="L2" t="n">
-        <v>25276.97</v>
+        <v>25368.64</v>
       </c>
       <c r="M2" t="n">
-        <v>25752.81</v>
+        <v>25569.47</v>
       </c>
       <c r="N2" t="n">
-        <v>26228.66</v>
+        <v>25770.31</v>
       </c>
       <c r="O2" t="n">
-        <v>26732.11</v>
+        <v>26365.43</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,12 +692,14 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -716,7 +718,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -781,7 +783,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -865,7 +867,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -949,7 +951,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1033,7 +1035,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1115,7 +1117,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1197,7 +1199,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1285,7 +1287,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1373,7 +1375,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1455,7 +1457,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1539,7 +1541,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1625,7 +1627,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1711,7 +1713,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1797,7 +1799,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1875,7 +1877,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1959,7 +1961,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2047,7 +2049,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2129,7 +2131,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2207,7 +2209,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2295,7 +2297,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2383,7 +2385,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2467,7 +2469,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2549,7 +2551,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2631,7 +2633,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2717,7 +2719,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2799,7 +2801,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2883,7 +2885,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2965,7 +2967,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3055,7 +3057,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3135,7 +3137,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3213,7 +3215,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3299,7 +3301,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3377,7 +3379,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3459,7 +3461,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3545,7 +3547,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3633,7 +3635,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3717,7 +3719,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3795,7 +3797,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3881,7 +3883,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3965,7 +3967,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4053,7 +4055,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4135,7 +4137,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4221,7 +4223,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4307,7 +4309,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4393,7 +4395,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4471,7 +4473,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4555,7 +4557,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4643,7 +4645,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4727,7 +4729,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4811,7 +4813,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4895,7 +4897,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4979,7 +4981,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5061,7 +5063,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5151,7 +5153,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5237,7 +5239,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5325,7 +5327,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5356,22 +5358,22 @@
         <v>24701.18</v>
       </c>
       <c r="C58" t="n">
-        <v>24934.06</v>
+        <v>24926.24</v>
       </c>
       <c r="D58" t="n">
-        <v>24657.01</v>
+        <v>24662.11</v>
       </c>
       <c r="E58" t="n">
-        <v>24667.24</v>
+        <v>24917.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-138.39</v>
+        <v>111.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0045</v>
       </c>
       <c r="H58" t="n">
-        <v>277.05</v>
+        <v>264.13</v>
       </c>
       <c r="I58" t="n">
         <v>23475.5</v>
@@ -5403,7 +5405,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5424,7 +5426,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5435,25 +5437,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>24379.96</v>
+        <v>24397.98</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>24326.04</v>
+        <v>24715.18</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>24528.71</v>
+        <v>24785.53</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>24731.39</v>
+        <v>24855.89</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>24805.77</v>
+        <v>25049.67</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>24880.14</v>
+        <v>25243.44</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>25211.11</v>
+        <v>25190.37</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5358,22 +5358,22 @@
         <v>24701.18</v>
       </c>
       <c r="C58" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D58" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E58" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F58" t="n">
-        <v>111.97</v>
+        <v>-138.39</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0056</v>
       </c>
       <c r="H58" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I58" t="n">
         <v>23475.5</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5437,25 +5437,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5361,19 +5361,19 @@
         <v>24934.06</v>
       </c>
       <c r="D58" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E58" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-138.39</v>
+        <v>-91.84999999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0037</v>
       </c>
       <c r="H58" t="n">
-        <v>277.05</v>
+        <v>359.31</v>
       </c>
       <c r="I58" t="n">
         <v>23475.5</v>
@@ -5437,25 +5437,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>24379.96</v>
+        <v>24215.44</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>24326.04</v>
+        <v>24334.16</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>24528.71</v>
+        <v>24534.12</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>24731.39</v>
+        <v>24734.09</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>24805.77</v>
+        <v>24893.43</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>24880.14</v>
+        <v>25052.78</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>25211.11</v>
+        <v>25293.37</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5361,19 +5361,19 @@
         <v>24934.06</v>
       </c>
       <c r="D58" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E58" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F58" t="n">
-        <v>-91.84999999999999</v>
+        <v>-201.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0081</v>
       </c>
       <c r="H58" t="n">
-        <v>359.31</v>
+        <v>576.37</v>
       </c>
       <c r="I58" t="n">
         <v>23475.5</v>
@@ -5402,12 +5402,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5424,11 +5426,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5437,25 +5435,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>24215.44</v>
+        <v>23781.32</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>24334.16</v>
+        <v>24007.12</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>24534.12</v>
+        <v>24316.1</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>24734.09</v>
+        <v>24625.08</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>24893.43</v>
+        <v>24892.47</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>25052.78</v>
+        <v>25159.87</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>25293.37</v>
+        <v>25510.43</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,19 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,31 +659,35 @@
         <v>578.17</v>
       </c>
       <c r="I2" t="n">
-        <v>24569</v>
+        <v>24979.08</v>
       </c>
       <c r="J2" t="n">
-        <v>24572.69</v>
+        <v>25085.29</v>
       </c>
       <c r="K2" t="n">
-        <v>24970.67</v>
+        <v>25175.71</v>
       </c>
       <c r="L2" t="n">
-        <v>25368.64</v>
+        <v>25266.12</v>
       </c>
       <c r="M2" t="n">
-        <v>25569.47</v>
+        <v>25364.43</v>
       </c>
       <c r="N2" t="n">
-        <v>25770.31</v>
+        <v>25462.75</v>
       </c>
       <c r="O2" t="n">
-        <v>26365.43</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>25545.27</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -699,14 +696,18 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -718,7 +719,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -783,7 +784,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -867,7 +868,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -951,7 +952,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1035,7 +1036,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1117,7 +1118,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1199,7 +1200,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1287,7 +1288,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1375,7 +1376,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1457,7 +1458,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1541,7 +1542,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1627,7 +1628,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1713,7 +1714,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1799,7 +1800,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1877,7 +1878,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1961,7 +1962,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2049,7 +2050,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2131,7 +2132,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2209,7 +2210,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2297,7 +2298,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2385,7 +2386,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2469,7 +2470,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2551,7 +2552,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2633,7 +2634,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2719,7 +2720,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2801,7 +2802,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2885,7 +2886,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2967,7 +2968,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3057,7 +3058,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3137,7 +3138,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3215,7 +3216,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3301,7 +3302,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3379,7 +3380,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3461,7 +3462,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3547,7 +3548,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3635,7 +3636,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3719,7 +3720,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3797,7 +3798,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3883,7 +3884,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3967,7 +3968,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4055,7 +4056,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4137,7 +4138,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4223,7 +4224,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4309,7 +4310,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4395,7 +4396,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4473,7 +4474,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4557,7 +4558,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4645,7 +4646,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4729,7 +4730,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4813,7 +4814,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4897,7 +4898,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4981,7 +4982,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5063,7 +5064,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5153,7 +5154,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5239,7 +5240,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5327,7 +5328,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5407,7 +5408,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5427,34 +5428,6 @@
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>23781.32</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>24007.12</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>24316.1</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>24625.08</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>24892.47</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>25159.87</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>25510.43</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,55 +634,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25293.34</v>
+        <v>25606.88</v>
       </c>
       <c r="C2" t="n">
-        <v>25466.1</v>
+        <v>25918.86</v>
       </c>
       <c r="D2" t="n">
-        <v>24887.93</v>
+        <v>24808.78</v>
       </c>
       <c r="E2" t="n">
-        <v>25339.14</v>
+        <v>25077.62</v>
       </c>
       <c r="F2" t="n">
-        <v>69.06999999999999</v>
+        <v>-261.52</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0103</v>
       </c>
       <c r="H2" t="n">
-        <v>578.17</v>
+        <v>1110.08</v>
       </c>
       <c r="I2" t="n">
-        <v>24979.08</v>
+        <v>24309.76</v>
       </c>
       <c r="J2" t="n">
-        <v>25085.29</v>
+        <v>24842.03</v>
       </c>
       <c r="K2" t="n">
-        <v>25175.71</v>
+        <v>25050.06</v>
       </c>
       <c r="L2" t="n">
-        <v>25266.12</v>
+        <v>25258.08</v>
       </c>
       <c r="M2" t="n">
-        <v>25364.43</v>
+        <v>25628.23</v>
       </c>
       <c r="N2" t="n">
-        <v>25462.75</v>
+        <v>25998.37</v>
       </c>
       <c r="O2" t="n">
-        <v>25545.27</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26044.27</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -691,23 +689,21 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -719,74 +715,70 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25606.88</v>
+        <v>25508.21</v>
       </c>
       <c r="C3" t="n">
-        <v>25918.86</v>
+        <v>25789.99</v>
       </c>
       <c r="D3" t="n">
-        <v>24808.78</v>
+        <v>25013.26</v>
       </c>
       <c r="E3" t="n">
-        <v>25077.62</v>
+        <v>25417.98</v>
       </c>
       <c r="F3" t="n">
-        <v>-261.52</v>
+        <v>340.36</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0136</v>
       </c>
       <c r="H3" t="n">
-        <v>1110.08</v>
+        <v>776.73</v>
       </c>
       <c r="I3" t="n">
-        <v>24309.76</v>
+        <v>23698.7</v>
       </c>
       <c r="J3" t="n">
-        <v>24842.03</v>
+        <v>23824.44</v>
       </c>
       <c r="K3" t="n">
-        <v>25050.06</v>
+        <v>24522.58</v>
       </c>
       <c r="L3" t="n">
-        <v>25258.08</v>
+        <v>25220.72</v>
       </c>
       <c r="M3" t="n">
-        <v>25628.23</v>
+        <v>25632.66</v>
       </c>
       <c r="N3" t="n">
-        <v>25998.37</v>
+        <v>26044.6</v>
       </c>
       <c r="O3" t="n">
-        <v>26044.27</v>
+        <v>27028.94</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -807,57 +799,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25508.21</v>
+        <v>25440.01</v>
       </c>
       <c r="C4" t="n">
-        <v>25789.99</v>
+        <v>26585.95</v>
       </c>
       <c r="D4" t="n">
-        <v>25013.26</v>
+        <v>25387.81</v>
       </c>
       <c r="E4" t="n">
-        <v>25417.98</v>
+        <v>26388.16</v>
       </c>
       <c r="F4" t="n">
-        <v>340.36</v>
+        <v>970.1799999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0382</v>
       </c>
       <c r="H4" t="n">
-        <v>776.73</v>
+        <v>1198.14</v>
       </c>
       <c r="I4" t="n">
-        <v>23698.7</v>
+        <v>24236.53</v>
       </c>
       <c r="J4" t="n">
-        <v>23824.44</v>
+        <v>24649.43</v>
       </c>
       <c r="K4" t="n">
-        <v>24522.58</v>
+        <v>25029.62</v>
       </c>
       <c r="L4" t="n">
-        <v>25220.72</v>
+        <v>25409.8</v>
       </c>
       <c r="M4" t="n">
-        <v>25632.66</v>
+        <v>25806.35</v>
       </c>
       <c r="N4" t="n">
-        <v>26044.6</v>
+        <v>26202.89</v>
       </c>
       <c r="O4" t="n">
-        <v>27028.94</v>
+        <v>26566.72</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -868,9 +860,9 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -878,70 +870,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25440.01</v>
+        <v>26308.91</v>
       </c>
       <c r="C5" t="n">
-        <v>26585.95</v>
+        <v>27058.03</v>
       </c>
       <c r="D5" t="n">
-        <v>25387.81</v>
+        <v>26280.23</v>
       </c>
       <c r="E5" t="n">
-        <v>26388.16</v>
+        <v>26545.1</v>
       </c>
       <c r="F5" t="n">
-        <v>970.1799999999999</v>
+        <v>156.94</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.0059</v>
       </c>
       <c r="H5" t="n">
-        <v>1198.14</v>
+        <v>777.8</v>
       </c>
       <c r="I5" t="n">
-        <v>24236.53</v>
+        <v>24189.67</v>
       </c>
       <c r="J5" t="n">
-        <v>24649.43</v>
+        <v>25390.66</v>
       </c>
       <c r="K5" t="n">
-        <v>25029.62</v>
+        <v>25789.09</v>
       </c>
       <c r="L5" t="n">
-        <v>25409.8</v>
+        <v>26187.52</v>
       </c>
       <c r="M5" t="n">
-        <v>25806.35</v>
+        <v>26987.23</v>
       </c>
       <c r="N5" t="n">
-        <v>26202.89</v>
+        <v>27786.94</v>
       </c>
       <c r="O5" t="n">
-        <v>26566.72</v>
+        <v>27784.09</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -952,9 +944,9 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -962,15 +954,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -982,50 +970,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26308.91</v>
+        <v>26459.52</v>
       </c>
       <c r="C6" t="n">
-        <v>27058.03</v>
+        <v>26640.53</v>
       </c>
       <c r="D6" t="n">
-        <v>26280.23</v>
+        <v>26003.67</v>
       </c>
       <c r="E6" t="n">
-        <v>26545.1</v>
+        <v>26128.2</v>
       </c>
       <c r="F6" t="n">
-        <v>156.94</v>
+        <v>-416.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0157</v>
       </c>
       <c r="H6" t="n">
-        <v>777.8</v>
+        <v>636.86</v>
       </c>
       <c r="I6" t="n">
-        <v>24189.67</v>
+        <v>25502.43</v>
       </c>
       <c r="J6" t="n">
-        <v>25390.66</v>
+        <v>25705.29</v>
       </c>
       <c r="K6" t="n">
-        <v>25789.09</v>
+        <v>26156.2</v>
       </c>
       <c r="L6" t="n">
-        <v>26187.52</v>
+        <v>26607.11</v>
       </c>
       <c r="M6" t="n">
-        <v>26987.23</v>
+        <v>26934</v>
       </c>
       <c r="N6" t="n">
-        <v>27786.94</v>
+        <v>27260.88</v>
       </c>
       <c r="O6" t="n">
-        <v>27784.09</v>
+        <v>27835.83</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1033,18 +1021,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1057,55 +1045,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26459.52</v>
+        <v>26321.57</v>
       </c>
       <c r="C7" t="n">
-        <v>26640.53</v>
+        <v>27381.84</v>
       </c>
       <c r="D7" t="n">
-        <v>26003.67</v>
+        <v>26321.57</v>
       </c>
       <c r="E7" t="n">
-        <v>26128.2</v>
+        <v>27140.92</v>
       </c>
       <c r="F7" t="n">
-        <v>-416.9</v>
+        <v>1012.72</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0388</v>
       </c>
       <c r="H7" t="n">
-        <v>636.86</v>
+        <v>1060.27</v>
       </c>
       <c r="I7" t="n">
-        <v>25502.43</v>
+        <v>25366.81</v>
       </c>
       <c r="J7" t="n">
-        <v>25705.29</v>
+        <v>25394.39</v>
       </c>
       <c r="K7" t="n">
-        <v>26156.2</v>
+        <v>25809.77</v>
       </c>
       <c r="L7" t="n">
-        <v>26607.11</v>
+        <v>26225.15</v>
       </c>
       <c r="M7" t="n">
-        <v>26934</v>
+        <v>26446.63</v>
       </c>
       <c r="N7" t="n">
-        <v>27260.88</v>
+        <v>26668.11</v>
       </c>
       <c r="O7" t="n">
-        <v>27835.83</v>
+        <v>27277.39</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1113,170 +1105,174 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26321.57</v>
+        <v>27003.92</v>
       </c>
       <c r="C8" t="n">
-        <v>27381.84</v>
+        <v>27145.17</v>
       </c>
       <c r="D8" t="n">
-        <v>26321.57</v>
+        <v>26247.04</v>
       </c>
       <c r="E8" t="n">
-        <v>27140.92</v>
+        <v>26290.32</v>
       </c>
       <c r="F8" t="n">
-        <v>1012.72</v>
+        <v>-850.6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0388</v>
+        <v>-0.0313</v>
       </c>
       <c r="H8" t="n">
-        <v>1060.27</v>
+        <v>898.13</v>
       </c>
       <c r="I8" t="n">
-        <v>25366.81</v>
+        <v>25261.3</v>
       </c>
       <c r="J8" t="n">
-        <v>25394.39</v>
+        <v>26225.26</v>
       </c>
       <c r="K8" t="n">
-        <v>25809.77</v>
+        <v>26610.79</v>
       </c>
       <c r="L8" t="n">
-        <v>26225.15</v>
+        <v>26996.31</v>
       </c>
       <c r="M8" t="n">
-        <v>26446.63</v>
+        <v>27671.05</v>
       </c>
       <c r="N8" t="n">
-        <v>26668.11</v>
+        <v>28345.8</v>
       </c>
       <c r="O8" t="n">
-        <v>27277.39</v>
+        <v>28442.11</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27003.92</v>
+        <v>25634</v>
       </c>
       <c r="C9" t="n">
-        <v>27145.17</v>
+        <v>26102.68</v>
       </c>
       <c r="D9" t="n">
-        <v>26247.04</v>
+        <v>25145.34</v>
       </c>
       <c r="E9" t="n">
-        <v>26290.32</v>
+        <v>25247.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-850.6</v>
+        <v>-1043.22</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0397</v>
       </c>
       <c r="H9" t="n">
-        <v>898.13</v>
+        <v>957.34</v>
       </c>
       <c r="I9" t="n">
-        <v>25261.3</v>
+        <v>25348.91</v>
       </c>
       <c r="J9" t="n">
-        <v>26225.26</v>
+        <v>25189.3</v>
       </c>
       <c r="K9" t="n">
-        <v>26610.79</v>
+        <v>25841.25</v>
       </c>
       <c r="L9" t="n">
-        <v>26996.31</v>
+        <v>26493.21</v>
       </c>
       <c r="M9" t="n">
-        <v>27671.05</v>
+        <v>26739.39</v>
       </c>
       <c r="N9" t="n">
-        <v>28345.8</v>
+        <v>26985.56</v>
       </c>
       <c r="O9" t="n">
-        <v>28442.11</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
+        <v>28043.3</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
@@ -1288,7 +1284,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1316,77 +1312,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25634</v>
+        <v>25884.46</v>
       </c>
       <c r="C10" t="n">
-        <v>26102.68</v>
+        <v>26367.35</v>
       </c>
       <c r="D10" t="n">
-        <v>25145.34</v>
+        <v>25591.66</v>
       </c>
       <c r="E10" t="n">
-        <v>25247.1</v>
+        <v>26160.15</v>
       </c>
       <c r="F10" t="n">
-        <v>-1043.22</v>
+        <v>913.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0362</v>
       </c>
       <c r="H10" t="n">
-        <v>957.34</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>25348.91</v>
+        <v>24188</v>
       </c>
       <c r="J10" t="n">
-        <v>25189.3</v>
+        <v>24101.3</v>
       </c>
       <c r="K10" t="n">
-        <v>25841.25</v>
+        <v>24768.43</v>
       </c>
       <c r="L10" t="n">
-        <v>26493.21</v>
+        <v>25435.55</v>
       </c>
       <c r="M10" t="n">
-        <v>26739.39</v>
+        <v>25725.77</v>
       </c>
       <c r="N10" t="n">
-        <v>26985.56</v>
+        <v>26015.98</v>
       </c>
       <c r="O10" t="n">
-        <v>28043.3</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
+        <v>27060.02</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1395,59 +1389,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25884.46</v>
+        <v>26495.97</v>
       </c>
       <c r="C11" t="n">
-        <v>26367.35</v>
+        <v>26588.89</v>
       </c>
       <c r="D11" t="n">
-        <v>25591.66</v>
+        <v>25906.65</v>
       </c>
       <c r="E11" t="n">
-        <v>26160.15</v>
+        <v>25906.65</v>
       </c>
       <c r="F11" t="n">
-        <v>913.05</v>
+        <v>-253.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0362</v>
+        <v>-0.0097</v>
       </c>
       <c r="H11" t="n">
-        <v>775.6900000000001</v>
+        <v>682.24</v>
       </c>
       <c r="I11" t="n">
-        <v>24188</v>
+        <v>24815.97</v>
       </c>
       <c r="J11" t="n">
-        <v>24101.3</v>
+        <v>25474.78</v>
       </c>
       <c r="K11" t="n">
-        <v>24768.43</v>
+        <v>25772.31</v>
       </c>
       <c r="L11" t="n">
-        <v>25435.55</v>
+        <v>26069.83</v>
       </c>
       <c r="M11" t="n">
-        <v>25725.77</v>
+        <v>26548</v>
       </c>
       <c r="N11" t="n">
-        <v>26015.98</v>
+        <v>27026.16</v>
       </c>
       <c r="O11" t="n">
-        <v>27060.02</v>
+        <v>27143.04</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1455,12 +1445,14 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -1468,10 +1460,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1481,55 +1471,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26495.97</v>
+        <v>25999.17</v>
       </c>
       <c r="C12" t="n">
-        <v>26588.89</v>
+        <v>26490.71</v>
       </c>
       <c r="D12" t="n">
-        <v>25906.65</v>
+        <v>25496.13</v>
       </c>
       <c r="E12" t="n">
-        <v>25906.65</v>
+        <v>26241.83</v>
       </c>
       <c r="F12" t="n">
-        <v>-253.5</v>
+        <v>335.18</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0129</v>
       </c>
       <c r="H12" t="n">
-        <v>682.24</v>
+        <v>994.58</v>
       </c>
       <c r="I12" t="n">
-        <v>24815.97</v>
+        <v>25224.41</v>
       </c>
       <c r="J12" t="n">
-        <v>25474.78</v>
+        <v>25053.85</v>
       </c>
       <c r="K12" t="n">
-        <v>25772.31</v>
+        <v>25565.53</v>
       </c>
       <c r="L12" t="n">
-        <v>26069.83</v>
+        <v>26077.21</v>
       </c>
       <c r="M12" t="n">
-        <v>26548</v>
+        <v>26247.77</v>
       </c>
       <c r="N12" t="n">
-        <v>27026.16</v>
+        <v>26418.33</v>
       </c>
       <c r="O12" t="n">
-        <v>27143.04</v>
+        <v>27271.13</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1539,21 +1533,23 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1565,57 +1561,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25999.17</v>
+        <v>26319.4</v>
       </c>
       <c r="C13" t="n">
-        <v>26490.71</v>
+        <v>27188.81</v>
       </c>
       <c r="D13" t="n">
-        <v>25496.13</v>
+        <v>26302.93</v>
       </c>
       <c r="E13" t="n">
-        <v>26241.83</v>
+        <v>26572.46</v>
       </c>
       <c r="F13" t="n">
-        <v>335.18</v>
+        <v>330.63</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
       <c r="H13" t="n">
-        <v>994.58</v>
+        <v>885.88</v>
       </c>
       <c r="I13" t="n">
-        <v>25224.41</v>
+        <v>24501.55</v>
       </c>
       <c r="J13" t="n">
-        <v>25053.85</v>
+        <v>25371.45</v>
       </c>
       <c r="K13" t="n">
-        <v>25565.53</v>
+        <v>25744.54</v>
       </c>
       <c r="L13" t="n">
-        <v>26077.21</v>
+        <v>26117.63</v>
       </c>
       <c r="M13" t="n">
-        <v>26247.77</v>
+        <v>26739.12</v>
       </c>
       <c r="N13" t="n">
-        <v>26418.33</v>
+        <v>27360.61</v>
       </c>
       <c r="O13" t="n">
-        <v>27271.13</v>
+        <v>27485.29</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1623,12 +1619,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1638,10 +1632,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1651,78 +1643,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26319.4</v>
+        <v>26441.7</v>
       </c>
       <c r="C14" t="n">
-        <v>27188.81</v>
+        <v>26531.8</v>
       </c>
       <c r="D14" t="n">
-        <v>26302.93</v>
+        <v>25178.63</v>
       </c>
       <c r="E14" t="n">
-        <v>26572.46</v>
+        <v>25220.02</v>
       </c>
       <c r="F14" t="n">
-        <v>330.63</v>
+        <v>-1352.44</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0126</v>
+        <v>-0.0509</v>
       </c>
       <c r="H14" t="n">
-        <v>885.88</v>
+        <v>1353.17</v>
       </c>
       <c r="I14" t="n">
-        <v>24501.55</v>
+        <v>25417.05</v>
       </c>
       <c r="J14" t="n">
-        <v>25371.45</v>
+        <v>25599.88</v>
       </c>
       <c r="K14" t="n">
-        <v>25744.54</v>
+        <v>26129.52</v>
       </c>
       <c r="L14" t="n">
-        <v>26117.63</v>
+        <v>26659.17</v>
       </c>
       <c r="M14" t="n">
-        <v>26739.12</v>
+        <v>27015.4</v>
       </c>
       <c r="N14" t="n">
-        <v>27360.61</v>
+        <v>27371.64</v>
       </c>
       <c r="O14" t="n">
-        <v>27485.29</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>28074.69</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1730,9 +1722,9 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1740,74 +1732,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26441.7</v>
+        <v>25452.87</v>
       </c>
       <c r="C15" t="n">
-        <v>26531.8</v>
+        <v>26136.27</v>
       </c>
       <c r="D15" t="n">
-        <v>25178.63</v>
+        <v>25369.29</v>
       </c>
       <c r="E15" t="n">
-        <v>25220.02</v>
+        <v>25858.89</v>
       </c>
       <c r="F15" t="n">
-        <v>-1352.44</v>
+        <v>638.87</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0509</v>
+        <v>0.0253</v>
       </c>
       <c r="H15" t="n">
-        <v>1353.17</v>
+        <v>766.98</v>
       </c>
       <c r="I15" t="n">
-        <v>25417.05</v>
+        <v>23825.46</v>
       </c>
       <c r="J15" t="n">
-        <v>25599.88</v>
+        <v>23549.25</v>
       </c>
       <c r="K15" t="n">
-        <v>26129.52</v>
+        <v>24543.43</v>
       </c>
       <c r="L15" t="n">
-        <v>26659.17</v>
+        <v>25537.62</v>
       </c>
       <c r="M15" t="n">
-        <v>27015.4</v>
+        <v>25896.6</v>
       </c>
       <c r="N15" t="n">
-        <v>27371.64</v>
+        <v>26255.59</v>
       </c>
       <c r="O15" t="n">
-        <v>28074.69</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>27884.97</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1819,55 +1807,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25452.87</v>
+        <v>25945.87</v>
       </c>
       <c r="C16" t="n">
-        <v>26136.27</v>
+        <v>26264.13</v>
       </c>
       <c r="D16" t="n">
-        <v>25369.29</v>
+        <v>25649.3</v>
       </c>
       <c r="E16" t="n">
-        <v>25858.89</v>
+        <v>26085.08</v>
       </c>
       <c r="F16" t="n">
-        <v>638.87</v>
+        <v>226.19</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0253</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>766.98</v>
+        <v>614.83</v>
       </c>
       <c r="I16" t="n">
-        <v>23825.46</v>
+        <v>24602.31</v>
       </c>
       <c r="J16" t="n">
-        <v>23549.25</v>
+        <v>25144.97</v>
       </c>
       <c r="K16" t="n">
-        <v>24543.43</v>
+        <v>25475.4</v>
       </c>
       <c r="L16" t="n">
-        <v>25537.62</v>
+        <v>25805.83</v>
       </c>
       <c r="M16" t="n">
-        <v>25896.6</v>
+        <v>26242.38</v>
       </c>
       <c r="N16" t="n">
-        <v>26255.59</v>
+        <v>26678.93</v>
       </c>
       <c r="O16" t="n">
-        <v>27884.97</v>
+        <v>26903.25</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1878,7 +1870,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1901,76 +1893,78 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25945.87</v>
+        <v>26067.86</v>
       </c>
       <c r="C17" t="n">
-        <v>26264.13</v>
+        <v>26151.46</v>
       </c>
       <c r="D17" t="n">
-        <v>25649.3</v>
+        <v>25257.61</v>
       </c>
       <c r="E17" t="n">
-        <v>26085.08</v>
+        <v>25976.79</v>
       </c>
       <c r="F17" t="n">
-        <v>226.19</v>
+        <v>-108.29</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0042</v>
       </c>
       <c r="H17" t="n">
-        <v>614.83</v>
+        <v>893.85</v>
       </c>
       <c r="I17" t="n">
-        <v>24602.31</v>
+        <v>25034.47</v>
       </c>
       <c r="J17" t="n">
-        <v>25144.97</v>
+        <v>25534.43</v>
       </c>
       <c r="K17" t="n">
-        <v>25475.4</v>
+        <v>25777.67</v>
       </c>
       <c r="L17" t="n">
-        <v>25805.83</v>
+        <v>26020.9</v>
       </c>
       <c r="M17" t="n">
-        <v>26242.38</v>
+        <v>26392.5</v>
       </c>
       <c r="N17" t="n">
-        <v>26678.93</v>
+        <v>26764.09</v>
       </c>
       <c r="O17" t="n">
-        <v>26903.25</v>
+        <v>26878.96</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1983,59 +1977,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26067.86</v>
+        <v>25718.14</v>
       </c>
       <c r="C18" t="n">
-        <v>26151.46</v>
+        <v>25824.44</v>
       </c>
       <c r="D18" t="n">
-        <v>25257.61</v>
+        <v>25086.54</v>
       </c>
       <c r="E18" t="n">
-        <v>25976.79</v>
+        <v>25690.53</v>
       </c>
       <c r="F18" t="n">
-        <v>-108.29</v>
+        <v>-286.26</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.011</v>
       </c>
       <c r="H18" t="n">
-        <v>893.85</v>
+        <v>737.9</v>
       </c>
       <c r="I18" t="n">
-        <v>25034.47</v>
+        <v>24363.76</v>
       </c>
       <c r="J18" t="n">
-        <v>25534.43</v>
+        <v>25219.06</v>
       </c>
       <c r="K18" t="n">
-        <v>25777.67</v>
+        <v>25529.86</v>
       </c>
       <c r="L18" t="n">
-        <v>26020.9</v>
+        <v>25840.66</v>
       </c>
       <c r="M18" t="n">
-        <v>26392.5</v>
+        <v>26423.71</v>
       </c>
       <c r="N18" t="n">
-        <v>26764.09</v>
+        <v>27006.77</v>
       </c>
       <c r="O18" t="n">
-        <v>26878.96</v>
+        <v>27045.31</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2050,7 +2040,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2074,71 +2064,69 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25718.14</v>
+        <v>25795.94</v>
       </c>
       <c r="C19" t="n">
-        <v>25824.44</v>
+        <v>25927.66</v>
       </c>
       <c r="D19" t="n">
-        <v>25086.54</v>
+        <v>25671.33</v>
       </c>
       <c r="E19" t="n">
-        <v>25690.53</v>
+        <v>25818.93</v>
       </c>
       <c r="F19" t="n">
-        <v>-286.26</v>
+        <v>128.4</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H19" t="n">
-        <v>737.9</v>
+        <v>256.33</v>
       </c>
       <c r="I19" t="n">
-        <v>24363.76</v>
+        <v>24348.64</v>
       </c>
       <c r="J19" t="n">
-        <v>25219.06</v>
+        <v>25070.15</v>
       </c>
       <c r="K19" t="n">
-        <v>25529.86</v>
+        <v>25321.58</v>
       </c>
       <c r="L19" t="n">
-        <v>25840.66</v>
+        <v>25573.01</v>
       </c>
       <c r="M19" t="n">
-        <v>26423.71</v>
+        <v>26059.48</v>
       </c>
       <c r="N19" t="n">
-        <v>27006.77</v>
+        <v>26545.95</v>
       </c>
       <c r="O19" t="n">
-        <v>27045.31</v>
+        <v>26562.34</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2151,156 +2139,164 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25795.94</v>
+        <v>25928.89</v>
       </c>
       <c r="C20" t="n">
-        <v>25927.66</v>
+        <v>26345.63</v>
       </c>
       <c r="D20" t="n">
-        <v>25671.33</v>
+        <v>25554.31</v>
       </c>
       <c r="E20" t="n">
-        <v>25818.93</v>
+        <v>26338.47</v>
       </c>
       <c r="F20" t="n">
-        <v>128.4</v>
+        <v>519.54</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0201</v>
       </c>
       <c r="H20" t="n">
-        <v>256.33</v>
+        <v>791.3200000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>24348.64</v>
+        <v>25415</v>
       </c>
       <c r="J20" t="n">
-        <v>25070.15</v>
+        <v>25572.32</v>
       </c>
       <c r="K20" t="n">
-        <v>25321.58</v>
+        <v>25690.76</v>
       </c>
       <c r="L20" t="n">
-        <v>25573.01</v>
+        <v>25809.21</v>
       </c>
       <c r="M20" t="n">
-        <v>26059.48</v>
+        <v>25947.09</v>
       </c>
       <c r="N20" t="n">
-        <v>26545.95</v>
+        <v>26084.98</v>
       </c>
       <c r="O20" t="n">
-        <v>26562.34</v>
+        <v>26183.99</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25928.89</v>
+        <v>26361.44</v>
       </c>
       <c r="C21" t="n">
-        <v>26345.63</v>
+        <v>26858.13</v>
       </c>
       <c r="D21" t="n">
-        <v>25554.31</v>
+        <v>25960.34</v>
       </c>
       <c r="E21" t="n">
-        <v>26338.47</v>
+        <v>26231.79</v>
       </c>
       <c r="F21" t="n">
-        <v>519.54</v>
+        <v>-106.68</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.0041</v>
       </c>
       <c r="H21" t="n">
-        <v>791.3200000000001</v>
+        <v>897.79</v>
       </c>
       <c r="I21" t="n">
-        <v>25415</v>
+        <v>24762.99</v>
       </c>
       <c r="J21" t="n">
-        <v>25572.32</v>
+        <v>25741.4</v>
       </c>
       <c r="K21" t="n">
-        <v>25690.76</v>
+        <v>25942.81</v>
       </c>
       <c r="L21" t="n">
-        <v>25809.21</v>
+        <v>26144.22</v>
       </c>
       <c r="M21" t="n">
-        <v>25947.09</v>
+        <v>26734.13</v>
       </c>
       <c r="N21" t="n">
-        <v>26084.98</v>
+        <v>27324.04</v>
       </c>
       <c r="O21" t="n">
-        <v>26183.99</v>
+        <v>27136.95</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2308,15 +2304,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2332,50 +2324,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26361.44</v>
+        <v>26376.84</v>
       </c>
       <c r="C22" t="n">
-        <v>26858.13</v>
+        <v>27206.84</v>
       </c>
       <c r="D22" t="n">
-        <v>25960.34</v>
+        <v>26187.76</v>
       </c>
       <c r="E22" t="n">
-        <v>26231.79</v>
+        <v>26844.96</v>
       </c>
       <c r="F22" t="n">
-        <v>-106.68</v>
+        <v>613.17</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0234</v>
       </c>
       <c r="H22" t="n">
-        <v>897.79</v>
+        <v>1019.08</v>
       </c>
       <c r="I22" t="n">
-        <v>24762.99</v>
+        <v>25062.55</v>
       </c>
       <c r="J22" t="n">
-        <v>25741.4</v>
+        <v>25245.27</v>
       </c>
       <c r="K22" t="n">
-        <v>25942.81</v>
+        <v>25782.89</v>
       </c>
       <c r="L22" t="n">
-        <v>26144.22</v>
+        <v>26320.51</v>
       </c>
       <c r="M22" t="n">
-        <v>26734.13</v>
+        <v>26680.68</v>
       </c>
       <c r="N22" t="n">
-        <v>27324.04</v>
+        <v>27040.86</v>
       </c>
       <c r="O22" t="n">
-        <v>27136.95</v>
+        <v>27755.92</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2386,18 +2378,20 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2407,59 +2401,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26376.84</v>
+        <v>26641.6</v>
       </c>
       <c r="C23" t="n">
-        <v>27206.84</v>
+        <v>26895.94</v>
       </c>
       <c r="D23" t="n">
-        <v>26187.76</v>
+        <v>26363.86</v>
       </c>
       <c r="E23" t="n">
-        <v>26844.96</v>
+        <v>26749.51</v>
       </c>
       <c r="F23" t="n">
-        <v>613.17</v>
+        <v>-95.45</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0234</v>
+        <v>-0.0036</v>
       </c>
       <c r="H23" t="n">
-        <v>1019.08</v>
+        <v>532.08</v>
       </c>
       <c r="I23" t="n">
-        <v>25062.55</v>
+        <v>25168.68</v>
       </c>
       <c r="J23" t="n">
-        <v>25245.27</v>
+        <v>25899.71</v>
       </c>
       <c r="K23" t="n">
-        <v>25782.89</v>
+        <v>26335.42</v>
       </c>
       <c r="L23" t="n">
-        <v>26320.51</v>
+        <v>26771.13</v>
       </c>
       <c r="M23" t="n">
-        <v>26680.68</v>
+        <v>27354.5</v>
       </c>
       <c r="N23" t="n">
-        <v>27040.86</v>
+        <v>27937.87</v>
       </c>
       <c r="O23" t="n">
-        <v>27755.92</v>
+        <v>28225.92</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2472,18 +2462,14 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2493,55 +2479,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26641.6</v>
+        <v>26844.04</v>
       </c>
       <c r="C24" t="n">
-        <v>26895.94</v>
+        <v>28056.1</v>
       </c>
       <c r="D24" t="n">
-        <v>26363.86</v>
+        <v>26619.83</v>
       </c>
       <c r="E24" t="n">
-        <v>26749.51</v>
+        <v>27387.11</v>
       </c>
       <c r="F24" t="n">
-        <v>-95.45</v>
+        <v>637.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0238</v>
       </c>
       <c r="H24" t="n">
-        <v>532.08</v>
+        <v>1436.27</v>
       </c>
       <c r="I24" t="n">
-        <v>25168.68</v>
+        <v>25831.78</v>
       </c>
       <c r="J24" t="n">
-        <v>25899.71</v>
+        <v>26277.23</v>
       </c>
       <c r="K24" t="n">
-        <v>26335.42</v>
+        <v>26483.47</v>
       </c>
       <c r="L24" t="n">
-        <v>26771.13</v>
+        <v>26689.7</v>
       </c>
       <c r="M24" t="n">
-        <v>27354.5</v>
+        <v>27015.55</v>
       </c>
       <c r="N24" t="n">
-        <v>27937.87</v>
+        <v>27341.4</v>
       </c>
       <c r="O24" t="n">
-        <v>28225.92</v>
+        <v>27428.02</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2554,76 +2544,78 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26844.04</v>
+        <v>27097.34</v>
       </c>
       <c r="C25" t="n">
-        <v>28056.1</v>
+        <v>27126.48</v>
       </c>
       <c r="D25" t="n">
-        <v>26619.83</v>
+        <v>26295.03</v>
       </c>
       <c r="E25" t="n">
-        <v>27387.11</v>
+        <v>26559.95</v>
       </c>
       <c r="F25" t="n">
-        <v>637.6</v>
+        <v>-827.16</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0238</v>
+        <v>-0.0302</v>
       </c>
       <c r="H25" t="n">
-        <v>1436.27</v>
+        <v>831.45</v>
       </c>
       <c r="I25" t="n">
-        <v>25831.78</v>
+        <v>25183.56</v>
       </c>
       <c r="J25" t="n">
-        <v>26277.23</v>
+        <v>25975.41</v>
       </c>
       <c r="K25" t="n">
-        <v>26483.47</v>
+        <v>26668.97</v>
       </c>
       <c r="L25" t="n">
-        <v>26689.7</v>
+        <v>27362.54</v>
       </c>
       <c r="M25" t="n">
-        <v>27015.55</v>
+        <v>28105.24</v>
       </c>
       <c r="N25" t="n">
-        <v>27341.4</v>
+        <v>28847.95</v>
       </c>
       <c r="O25" t="n">
-        <v>27428.02</v>
+        <v>29492.37</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2631,83 +2623,83 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27097.34</v>
+        <v>26982.49</v>
       </c>
       <c r="C26" t="n">
-        <v>27126.48</v>
+        <v>27397.65</v>
       </c>
       <c r="D26" t="n">
-        <v>26295.03</v>
+        <v>26444.46</v>
       </c>
       <c r="E26" t="n">
-        <v>26559.95</v>
+        <v>26567.12</v>
       </c>
       <c r="F26" t="n">
-        <v>-827.16</v>
+        <v>7.17</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0003</v>
       </c>
       <c r="H26" t="n">
-        <v>831.45</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>25183.56</v>
+        <v>25463.58</v>
       </c>
       <c r="J26" t="n">
-        <v>25975.41</v>
+        <v>25653.1</v>
       </c>
       <c r="K26" t="n">
-        <v>26668.97</v>
+        <v>26144.22</v>
       </c>
       <c r="L26" t="n">
-        <v>27362.54</v>
+        <v>26635.35</v>
       </c>
       <c r="M26" t="n">
-        <v>28105.24</v>
+        <v>26975.67</v>
       </c>
       <c r="N26" t="n">
-        <v>28847.95</v>
+        <v>27316</v>
       </c>
       <c r="O26" t="n">
-        <v>29492.37</v>
+        <v>27957.93</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2715,21 +2707,23 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2739,59 +2733,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26982.49</v>
+        <v>26501.2</v>
       </c>
       <c r="C27" t="n">
-        <v>27397.65</v>
+        <v>26734.41</v>
       </c>
       <c r="D27" t="n">
-        <v>26444.46</v>
+        <v>26356.96</v>
       </c>
       <c r="E27" t="n">
-        <v>26567.12</v>
+        <v>26413.35</v>
       </c>
       <c r="F27" t="n">
-        <v>7.17</v>
+        <v>-153.77</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0058</v>
       </c>
       <c r="H27" t="n">
-        <v>953.1900000000001</v>
+        <v>377.45</v>
       </c>
       <c r="I27" t="n">
-        <v>25463.58</v>
+        <v>25491.27</v>
       </c>
       <c r="J27" t="n">
-        <v>25653.1</v>
+        <v>25436.96</v>
       </c>
       <c r="K27" t="n">
-        <v>26144.22</v>
+        <v>26090.52</v>
       </c>
       <c r="L27" t="n">
-        <v>26635.35</v>
+        <v>26744.09</v>
       </c>
       <c r="M27" t="n">
-        <v>26975.67</v>
+        <v>27043.71</v>
       </c>
       <c r="N27" t="n">
-        <v>27316</v>
+        <v>27343.34</v>
       </c>
       <c r="O27" t="n">
-        <v>27957.93</v>
+        <v>28350.84</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2799,23 +2789,21 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2825,55 +2813,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26501.2</v>
+        <v>26798.97</v>
       </c>
       <c r="C28" t="n">
-        <v>26734.41</v>
+        <v>27156.28</v>
       </c>
       <c r="D28" t="n">
-        <v>26356.96</v>
+        <v>26373.01</v>
       </c>
       <c r="E28" t="n">
-        <v>26413.35</v>
+        <v>26630.54</v>
       </c>
       <c r="F28" t="n">
-        <v>-153.77</v>
+        <v>217.19</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>377.45</v>
+        <v>783.27</v>
       </c>
       <c r="I28" t="n">
-        <v>25491.27</v>
+        <v>25979.51</v>
       </c>
       <c r="J28" t="n">
-        <v>25436.96</v>
+        <v>25969.73</v>
       </c>
       <c r="K28" t="n">
-        <v>26090.52</v>
+        <v>26224.62</v>
       </c>
       <c r="L28" t="n">
-        <v>26744.09</v>
+        <v>26479.52</v>
       </c>
       <c r="M28" t="n">
-        <v>27043.71</v>
+        <v>26602.07</v>
       </c>
       <c r="N28" t="n">
-        <v>27343.34</v>
+        <v>26724.63</v>
       </c>
       <c r="O28" t="n">
-        <v>28350.84</v>
+        <v>27111.86</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2881,116 +2873,116 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26798.97</v>
+        <v>26305.58</v>
       </c>
       <c r="C29" t="n">
-        <v>27156.28</v>
+        <v>26403.85</v>
       </c>
       <c r="D29" t="n">
-        <v>26373.01</v>
+        <v>24958.43</v>
       </c>
       <c r="E29" t="n">
-        <v>26630.54</v>
+        <v>25757.29</v>
       </c>
       <c r="F29" t="n">
-        <v>217.19</v>
+        <v>-873.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="H29" t="n">
-        <v>783.27</v>
+        <v>1445.42</v>
       </c>
       <c r="I29" t="n">
-        <v>25979.51</v>
+        <v>25589.74</v>
       </c>
       <c r="J29" t="n">
-        <v>25969.73</v>
+        <v>25780.22</v>
       </c>
       <c r="K29" t="n">
-        <v>26224.62</v>
+        <v>26238.9</v>
       </c>
       <c r="L29" t="n">
-        <v>26479.52</v>
+        <v>26697.59</v>
       </c>
       <c r="M29" t="n">
-        <v>26602.07</v>
+        <v>27022.17</v>
       </c>
       <c r="N29" t="n">
-        <v>26724.63</v>
+        <v>27346.76</v>
       </c>
       <c r="O29" t="n">
-        <v>27111.86</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>27939.55</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2998,69 +2990,65 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26305.58</v>
+        <v>25075.74</v>
       </c>
       <c r="C30" t="n">
-        <v>26403.85</v>
+        <v>26149.64</v>
       </c>
       <c r="D30" t="n">
-        <v>24958.43</v>
+        <v>24906</v>
       </c>
       <c r="E30" t="n">
-        <v>25757.29</v>
+        <v>25465.6</v>
       </c>
       <c r="F30" t="n">
-        <v>-873.25</v>
+        <v>-291.69</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0328</v>
+        <v>-0.0113</v>
       </c>
       <c r="H30" t="n">
-        <v>1445.42</v>
+        <v>1243.64</v>
       </c>
       <c r="I30" t="n">
-        <v>25589.74</v>
+        <v>23513.01</v>
       </c>
       <c r="J30" t="n">
-        <v>25780.22</v>
+        <v>24349.94</v>
       </c>
       <c r="K30" t="n">
-        <v>26238.9</v>
+        <v>25034.58</v>
       </c>
       <c r="L30" t="n">
-        <v>26697.59</v>
+        <v>25719.21</v>
       </c>
       <c r="M30" t="n">
-        <v>27022.17</v>
+        <v>26480</v>
       </c>
       <c r="N30" t="n">
-        <v>27346.76</v>
+        <v>27240.78</v>
       </c>
       <c r="O30" t="n">
-        <v>27939.55</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27849.27</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3082,50 +3070,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25075.74</v>
+        <v>25436.27</v>
       </c>
       <c r="C31" t="n">
-        <v>26149.64</v>
+        <v>26250.14</v>
       </c>
       <c r="D31" t="n">
-        <v>24906</v>
+        <v>25121.46</v>
       </c>
       <c r="E31" t="n">
-        <v>25465.6</v>
+        <v>25277.32</v>
       </c>
       <c r="F31" t="n">
-        <v>-291.69</v>
+        <v>-188.28</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.0074</v>
       </c>
       <c r="H31" t="n">
-        <v>1243.64</v>
+        <v>1128.68</v>
       </c>
       <c r="I31" t="n">
-        <v>23513.01</v>
+        <v>23662.36</v>
       </c>
       <c r="J31" t="n">
-        <v>24349.94</v>
+        <v>24190.85</v>
       </c>
       <c r="K31" t="n">
-        <v>25034.58</v>
+        <v>24843.78</v>
       </c>
       <c r="L31" t="n">
-        <v>25719.21</v>
+        <v>25496.71</v>
       </c>
       <c r="M31" t="n">
-        <v>26480</v>
+        <v>26087.42</v>
       </c>
       <c r="N31" t="n">
-        <v>27240.78</v>
+        <v>26678.13</v>
       </c>
       <c r="O31" t="n">
-        <v>27849.27</v>
+        <v>27393.28</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3133,18 +3121,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3157,55 +3145,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25436.27</v>
+        <v>24789.14</v>
       </c>
       <c r="C32" t="n">
-        <v>26250.14</v>
+        <v>25390.3</v>
       </c>
       <c r="D32" t="n">
-        <v>25121.46</v>
+        <v>24203.54</v>
       </c>
       <c r="E32" t="n">
-        <v>25277.32</v>
+        <v>24951.88</v>
       </c>
       <c r="F32" t="n">
-        <v>-188.28</v>
+        <v>-325.44</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0129</v>
       </c>
       <c r="H32" t="n">
-        <v>1128.68</v>
+        <v>1186.76</v>
       </c>
       <c r="I32" t="n">
-        <v>23662.36</v>
+        <v>23992.78</v>
       </c>
       <c r="J32" t="n">
-        <v>24190.85</v>
+        <v>23944.4</v>
       </c>
       <c r="K32" t="n">
-        <v>24843.78</v>
+        <v>24712.98</v>
       </c>
       <c r="L32" t="n">
-        <v>25496.71</v>
+        <v>25481.56</v>
       </c>
       <c r="M32" t="n">
-        <v>26087.42</v>
+        <v>25841.66</v>
       </c>
       <c r="N32" t="n">
-        <v>26678.13</v>
+        <v>26201.76</v>
       </c>
       <c r="O32" t="n">
-        <v>27393.28</v>
+        <v>27378.82</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3213,18 +3205,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3237,59 +3229,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24789.14</v>
+        <v>24532.85</v>
       </c>
       <c r="C33" t="n">
-        <v>25390.3</v>
+        <v>25429.76</v>
       </c>
       <c r="D33" t="n">
-        <v>24203.54</v>
+        <v>24409.57</v>
       </c>
       <c r="E33" t="n">
-        <v>24951.88</v>
+        <v>25116.53</v>
       </c>
       <c r="F33" t="n">
-        <v>-325.44</v>
+        <v>164.65</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0066</v>
       </c>
       <c r="H33" t="n">
-        <v>1186.76</v>
+        <v>1020.19</v>
       </c>
       <c r="I33" t="n">
-        <v>23992.78</v>
+        <v>23016.78</v>
       </c>
       <c r="J33" t="n">
-        <v>23944.4</v>
+        <v>23842.6</v>
       </c>
       <c r="K33" t="n">
-        <v>24712.98</v>
+        <v>24358.5</v>
       </c>
       <c r="L33" t="n">
-        <v>25481.56</v>
+        <v>24874.4</v>
       </c>
       <c r="M33" t="n">
-        <v>25841.66</v>
+        <v>25545.26</v>
       </c>
       <c r="N33" t="n">
-        <v>26201.76</v>
+        <v>26216.12</v>
       </c>
       <c r="O33" t="n">
-        <v>27378.82</v>
+        <v>26577.06</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3297,14 +3285,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3321,55 +3307,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24532.85</v>
+        <v>25772.56</v>
       </c>
       <c r="C34" t="n">
-        <v>25429.76</v>
+        <v>26073.97</v>
       </c>
       <c r="D34" t="n">
-        <v>24409.57</v>
+        <v>25653.63</v>
       </c>
       <c r="E34" t="n">
-        <v>25116.53</v>
+        <v>25893.54</v>
       </c>
       <c r="F34" t="n">
-        <v>164.65</v>
+        <v>777.01</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0309</v>
       </c>
       <c r="H34" t="n">
-        <v>1020.19</v>
+        <v>420.34</v>
       </c>
       <c r="I34" t="n">
-        <v>23016.78</v>
+        <v>23389.38</v>
       </c>
       <c r="J34" t="n">
-        <v>23842.6</v>
+        <v>24194.77</v>
       </c>
       <c r="K34" t="n">
-        <v>24358.5</v>
+        <v>24606.43</v>
       </c>
       <c r="L34" t="n">
-        <v>24874.4</v>
+        <v>25018.1</v>
       </c>
       <c r="M34" t="n">
-        <v>25545.26</v>
+        <v>25626.62</v>
       </c>
       <c r="N34" t="n">
-        <v>26216.12</v>
+        <v>26235.15</v>
       </c>
       <c r="O34" t="n">
-        <v>26577.06</v>
+        <v>26449.95</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3380,13 +3370,15 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3408,50 +3400,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25772.56</v>
+        <v>25708.64</v>
       </c>
       <c r="C35" t="n">
-        <v>26073.97</v>
+        <v>26403.07</v>
       </c>
       <c r="D35" t="n">
-        <v>25653.63</v>
+        <v>25508.53</v>
       </c>
       <c r="E35" t="n">
-        <v>25893.54</v>
+        <v>26160.33</v>
       </c>
       <c r="F35" t="n">
-        <v>777.01</v>
+        <v>266.79</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.0103</v>
       </c>
       <c r="H35" t="n">
-        <v>420.34</v>
+        <v>894.54</v>
       </c>
       <c r="I35" t="n">
-        <v>23389.38</v>
+        <v>25233.29</v>
       </c>
       <c r="J35" t="n">
-        <v>24194.77</v>
+        <v>25488.07</v>
       </c>
       <c r="K35" t="n">
-        <v>24606.43</v>
+        <v>25683.37</v>
       </c>
       <c r="L35" t="n">
-        <v>25018.1</v>
+        <v>25878.67</v>
       </c>
       <c r="M35" t="n">
-        <v>25626.62</v>
+        <v>26103.71</v>
       </c>
       <c r="N35" t="n">
-        <v>26235.15</v>
+        <v>26328.75</v>
       </c>
       <c r="O35" t="n">
-        <v>26449.95</v>
+        <v>26494.31</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3459,10 +3451,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3472,8 +3466,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3485,57 +3481,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25708.64</v>
+        <v>26204.61</v>
       </c>
       <c r="C36" t="n">
-        <v>26403.07</v>
+        <v>26529.49</v>
       </c>
       <c r="D36" t="n">
-        <v>25508.53</v>
+        <v>25639.26</v>
       </c>
       <c r="E36" t="n">
-        <v>26160.33</v>
+        <v>25978.07</v>
       </c>
       <c r="F36" t="n">
-        <v>266.79</v>
+        <v>-182.26</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.007</v>
       </c>
       <c r="H36" t="n">
-        <v>894.54</v>
+        <v>890.23</v>
       </c>
       <c r="I36" t="n">
-        <v>25233.29</v>
+        <v>24613.99</v>
       </c>
       <c r="J36" t="n">
-        <v>25488.07</v>
+        <v>25368.05</v>
       </c>
       <c r="K36" t="n">
-        <v>25683.37</v>
+        <v>25713.06</v>
       </c>
       <c r="L36" t="n">
-        <v>25878.67</v>
+        <v>26058.06</v>
       </c>
       <c r="M36" t="n">
-        <v>26103.71</v>
+        <v>26607.6</v>
       </c>
       <c r="N36" t="n">
-        <v>26328.75</v>
+        <v>27157.14</v>
       </c>
       <c r="O36" t="n">
-        <v>26494.31</v>
+        <v>27297.61</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3550,18 +3546,14 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3580,50 +3572,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26204.61</v>
+        <v>25976.97</v>
       </c>
       <c r="C37" t="n">
-        <v>26529.49</v>
+        <v>26132.94</v>
       </c>
       <c r="D37" t="n">
-        <v>25639.26</v>
+        <v>25609.61</v>
       </c>
       <c r="E37" t="n">
-        <v>25978.07</v>
+        <v>25776.53</v>
       </c>
       <c r="F37" t="n">
-        <v>-182.26</v>
+        <v>-201.54</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0078</v>
       </c>
       <c r="H37" t="n">
-        <v>890.23</v>
+        <v>523.33</v>
       </c>
       <c r="I37" t="n">
-        <v>24613.99</v>
+        <v>24749.03</v>
       </c>
       <c r="J37" t="n">
-        <v>25368.05</v>
+        <v>25034.69</v>
       </c>
       <c r="K37" t="n">
-        <v>25713.06</v>
+        <v>25532.96</v>
       </c>
       <c r="L37" t="n">
-        <v>26058.06</v>
+        <v>26031.22</v>
       </c>
       <c r="M37" t="n">
-        <v>26607.6</v>
+        <v>26423.19</v>
       </c>
       <c r="N37" t="n">
-        <v>27157.14</v>
+        <v>26815.15</v>
       </c>
       <c r="O37" t="n">
-        <v>27297.61</v>
+        <v>27419.72</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3633,12 +3625,12 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3655,59 +3647,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25976.97</v>
+        <v>26138.34</v>
       </c>
       <c r="C38" t="n">
-        <v>26132.94</v>
+        <v>26669.26</v>
       </c>
       <c r="D38" t="n">
-        <v>25609.61</v>
+        <v>25690.36</v>
       </c>
       <c r="E38" t="n">
-        <v>25776.53</v>
+        <v>26393.71</v>
       </c>
       <c r="F38" t="n">
-        <v>-201.54</v>
+        <v>617.1799999999999</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0239</v>
       </c>
       <c r="H38" t="n">
-        <v>523.33</v>
+        <v>978.9</v>
       </c>
       <c r="I38" t="n">
-        <v>24749.03</v>
+        <v>25086.28</v>
       </c>
       <c r="J38" t="n">
-        <v>25034.69</v>
+        <v>25205.83</v>
       </c>
       <c r="K38" t="n">
-        <v>25532.96</v>
+        <v>25514.86</v>
       </c>
       <c r="L38" t="n">
-        <v>26031.22</v>
+        <v>25823.9</v>
       </c>
       <c r="M38" t="n">
-        <v>26423.19</v>
+        <v>26038.19</v>
       </c>
       <c r="N38" t="n">
-        <v>26815.15</v>
+        <v>26252.49</v>
       </c>
       <c r="O38" t="n">
-        <v>27419.72</v>
+        <v>26656.27</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3715,28 +3703,32 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3744,50 +3736,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26138.34</v>
+        <v>26310.87</v>
       </c>
       <c r="C39" t="n">
-        <v>26669.26</v>
+        <v>26844.8</v>
       </c>
       <c r="D39" t="n">
-        <v>25690.36</v>
+        <v>25847.15</v>
       </c>
       <c r="E39" t="n">
-        <v>26393.71</v>
+        <v>25962.73</v>
       </c>
       <c r="F39" t="n">
-        <v>617.1799999999999</v>
+        <v>-430.98</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0163</v>
       </c>
       <c r="H39" t="n">
-        <v>978.9</v>
+        <v>997.65</v>
       </c>
       <c r="I39" t="n">
-        <v>25086.28</v>
+        <v>24711.46</v>
       </c>
       <c r="J39" t="n">
-        <v>25205.83</v>
+        <v>25521.76</v>
       </c>
       <c r="K39" t="n">
-        <v>25514.86</v>
+        <v>25904.26</v>
       </c>
       <c r="L39" t="n">
-        <v>25823.9</v>
+        <v>26286.76</v>
       </c>
       <c r="M39" t="n">
-        <v>26038.19</v>
+        <v>26883.16</v>
       </c>
       <c r="N39" t="n">
-        <v>26252.49</v>
+        <v>27479.56</v>
       </c>
       <c r="O39" t="n">
-        <v>26656.27</v>
+        <v>27648.16</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3795,83 +3787,83 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26310.87</v>
+        <v>25838.96</v>
       </c>
       <c r="C40" t="n">
-        <v>26844.8</v>
+        <v>25845.46</v>
       </c>
       <c r="D40" t="n">
-        <v>25847.15</v>
+        <v>25341.73</v>
       </c>
       <c r="E40" t="n">
-        <v>25962.73</v>
+        <v>25606.03</v>
       </c>
       <c r="F40" t="n">
-        <v>-430.98</v>
+        <v>-356.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0137</v>
       </c>
       <c r="H40" t="n">
-        <v>997.65</v>
+        <v>503.73</v>
       </c>
       <c r="I40" t="n">
-        <v>24711.46</v>
+        <v>24849.5</v>
       </c>
       <c r="J40" t="n">
-        <v>25521.76</v>
+        <v>24773.46</v>
       </c>
       <c r="K40" t="n">
-        <v>25904.26</v>
+        <v>25463.91</v>
       </c>
       <c r="L40" t="n">
-        <v>26286.76</v>
+        <v>26154.35</v>
       </c>
       <c r="M40" t="n">
-        <v>26883.16</v>
+        <v>26461.56</v>
       </c>
       <c r="N40" t="n">
-        <v>27479.56</v>
+        <v>26768.76</v>
       </c>
       <c r="O40" t="n">
-        <v>27648.16</v>
+        <v>27842.45</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3884,7 +3876,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3905,70 +3897,74 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25838.96</v>
+        <v>25622.36</v>
       </c>
       <c r="C41" t="n">
-        <v>25845.46</v>
+        <v>25768.38</v>
       </c>
       <c r="D41" t="n">
-        <v>25341.73</v>
+        <v>24727.26</v>
       </c>
       <c r="E41" t="n">
-        <v>25606.03</v>
+        <v>25182.39</v>
       </c>
       <c r="F41" t="n">
-        <v>-356.7</v>
+        <v>-423.64</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0165</v>
       </c>
       <c r="H41" t="n">
-        <v>503.73</v>
+        <v>1041.12</v>
       </c>
       <c r="I41" t="n">
-        <v>24849.5</v>
+        <v>24838</v>
       </c>
       <c r="J41" t="n">
-        <v>24773.46</v>
+        <v>25108.52</v>
       </c>
       <c r="K41" t="n">
-        <v>25463.91</v>
+        <v>25354.16</v>
       </c>
       <c r="L41" t="n">
-        <v>26154.35</v>
+        <v>25599.81</v>
       </c>
       <c r="M41" t="n">
-        <v>26461.56</v>
+        <v>25857.89</v>
       </c>
       <c r="N41" t="n">
-        <v>26768.76</v>
+        <v>26115.98</v>
       </c>
       <c r="O41" t="n">
-        <v>27842.45</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>26349.19</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3996,73 +3992,69 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25622.36</v>
+        <v>25180.05</v>
       </c>
       <c r="C42" t="n">
-        <v>25768.38</v>
+        <v>26045.07</v>
       </c>
       <c r="D42" t="n">
-        <v>24727.26</v>
+        <v>24928.14</v>
       </c>
       <c r="E42" t="n">
-        <v>25182.39</v>
+        <v>24961.95</v>
       </c>
       <c r="F42" t="n">
-        <v>-423.64</v>
+        <v>-220.44</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0165</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>1041.12</v>
+        <v>1116.93</v>
       </c>
       <c r="I42" t="n">
-        <v>24838</v>
+        <v>23686.14</v>
       </c>
       <c r="J42" t="n">
-        <v>25108.52</v>
+        <v>24108.55</v>
       </c>
       <c r="K42" t="n">
-        <v>25354.16</v>
+        <v>24661.83</v>
       </c>
       <c r="L42" t="n">
-        <v>25599.81</v>
+        <v>25215.11</v>
       </c>
       <c r="M42" t="n">
-        <v>25857.89</v>
+        <v>25702.95</v>
       </c>
       <c r="N42" t="n">
-        <v>26115.98</v>
+        <v>26190.8</v>
       </c>
       <c r="O42" t="n">
-        <v>26349.19</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+        <v>26809.5</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4077,57 +4069,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25180.05</v>
+        <v>24582.91</v>
       </c>
       <c r="C43" t="n">
-        <v>26045.07</v>
+        <v>24837.98</v>
       </c>
       <c r="D43" t="n">
-        <v>24928.14</v>
+        <v>23999.67</v>
       </c>
       <c r="E43" t="n">
-        <v>24961.95</v>
+        <v>24718.1</v>
       </c>
       <c r="F43" t="n">
-        <v>-220.44</v>
+        <v>-243.85</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="H43" t="n">
-        <v>1116.93</v>
+        <v>838.3099999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>23686.14</v>
+        <v>23811.21</v>
       </c>
       <c r="J43" t="n">
-        <v>24108.55</v>
+        <v>23582.69</v>
       </c>
       <c r="K43" t="n">
-        <v>24661.83</v>
+        <v>24403.48</v>
       </c>
       <c r="L43" t="n">
-        <v>25215.11</v>
+        <v>25224.28</v>
       </c>
       <c r="M43" t="n">
-        <v>25702.95</v>
+        <v>25520.41</v>
       </c>
       <c r="N43" t="n">
-        <v>26190.8</v>
+        <v>25816.55</v>
       </c>
       <c r="O43" t="n">
-        <v>26809.5</v>
+        <v>27162</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4135,18 +4127,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4161,70 +4153,72 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24582.91</v>
+        <v>25001.42</v>
       </c>
       <c r="C44" t="n">
-        <v>24837.98</v>
+        <v>25047.9</v>
       </c>
       <c r="D44" t="n">
-        <v>23999.67</v>
+        <v>23749.99</v>
       </c>
       <c r="E44" t="n">
-        <v>24718.1</v>
+        <v>23924.81</v>
       </c>
       <c r="F44" t="n">
-        <v>-243.85</v>
+        <v>-793.29</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0321</v>
       </c>
       <c r="H44" t="n">
-        <v>838.3099999999999</v>
+        <v>1297.91</v>
       </c>
       <c r="I44" t="n">
-        <v>23811.21</v>
+        <v>23161.36</v>
       </c>
       <c r="J44" t="n">
-        <v>23582.69</v>
+        <v>24029.43</v>
       </c>
       <c r="K44" t="n">
-        <v>24403.48</v>
+        <v>24298.94</v>
       </c>
       <c r="L44" t="n">
-        <v>25224.28</v>
+        <v>24568.46</v>
       </c>
       <c r="M44" t="n">
-        <v>25520.41</v>
+        <v>25137.25</v>
       </c>
       <c r="N44" t="n">
-        <v>25816.55</v>
+        <v>25706.05</v>
       </c>
       <c r="O44" t="n">
-        <v>27162</v>
+        <v>25676.29</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4238,79 +4232,79 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25001.42</v>
+        <v>23811.76</v>
       </c>
       <c r="C45" t="n">
-        <v>25047.9</v>
+        <v>23863.71</v>
       </c>
       <c r="D45" t="n">
-        <v>23749.99</v>
+        <v>22518</v>
       </c>
       <c r="E45" t="n">
-        <v>23924.81</v>
+        <v>22671.86</v>
       </c>
       <c r="F45" t="n">
-        <v>-793.29</v>
+        <v>-1252.95</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0524</v>
       </c>
       <c r="H45" t="n">
-        <v>1297.91</v>
+        <v>1345.71</v>
       </c>
       <c r="I45" t="n">
-        <v>23161.36</v>
+        <v>22452.08</v>
       </c>
       <c r="J45" t="n">
-        <v>24029.43</v>
+        <v>22389.83</v>
       </c>
       <c r="K45" t="n">
-        <v>24298.94</v>
+        <v>23275.86</v>
       </c>
       <c r="L45" t="n">
-        <v>24568.46</v>
+        <v>24161.88</v>
       </c>
       <c r="M45" t="n">
-        <v>25137.25</v>
+        <v>24573.77</v>
       </c>
       <c r="N45" t="n">
-        <v>25706.05</v>
+        <v>24985.65</v>
       </c>
       <c r="O45" t="n">
-        <v>25676.29</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>26345.81</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4329,81 +4323,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23811.76</v>
+        <v>22827.65</v>
       </c>
       <c r="C46" t="n">
-        <v>23863.71</v>
+        <v>23516.7</v>
       </c>
       <c r="D46" t="n">
-        <v>22518</v>
+        <v>22685.14</v>
       </c>
       <c r="E46" t="n">
-        <v>22671.86</v>
+        <v>23350.03</v>
       </c>
       <c r="F46" t="n">
-        <v>-1252.95</v>
+        <v>678.17</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0524</v>
+        <v>0.0299</v>
       </c>
       <c r="H46" t="n">
-        <v>1345.71</v>
+        <v>831.5599999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>22452.08</v>
+        <v>21172.29</v>
       </c>
       <c r="J46" t="n">
-        <v>22389.83</v>
+        <v>21066.65</v>
       </c>
       <c r="K46" t="n">
-        <v>23275.86</v>
+        <v>21999</v>
       </c>
       <c r="L46" t="n">
-        <v>24161.88</v>
+        <v>22931.36</v>
       </c>
       <c r="M46" t="n">
-        <v>24573.77</v>
+        <v>23344.71</v>
       </c>
       <c r="N46" t="n">
-        <v>24985.65</v>
+        <v>23758.07</v>
       </c>
       <c r="O46" t="n">
-        <v>26345.81</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
+        <v>25209.42</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4415,55 +4403,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22827.65</v>
+        <v>23404.61</v>
       </c>
       <c r="C47" t="n">
-        <v>23516.7</v>
+        <v>24499.63</v>
       </c>
       <c r="D47" t="n">
-        <v>22685.14</v>
+        <v>23229.38</v>
       </c>
       <c r="E47" t="n">
-        <v>23350.03</v>
+        <v>24175.12</v>
       </c>
       <c r="F47" t="n">
-        <v>678.17</v>
+        <v>825.09</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0353</v>
       </c>
       <c r="H47" t="n">
-        <v>831.5599999999999</v>
+        <v>1270.25</v>
       </c>
       <c r="I47" t="n">
-        <v>21172.29</v>
+        <v>21853.58</v>
       </c>
       <c r="J47" t="n">
-        <v>21066.65</v>
+        <v>22643.03</v>
       </c>
       <c r="K47" t="n">
-        <v>21999</v>
+        <v>22934.25</v>
       </c>
       <c r="L47" t="n">
-        <v>22931.36</v>
+        <v>23225.47</v>
       </c>
       <c r="M47" t="n">
-        <v>23344.71</v>
+        <v>23765.81</v>
       </c>
       <c r="N47" t="n">
-        <v>23758.07</v>
+        <v>24306.14</v>
       </c>
       <c r="O47" t="n">
-        <v>25209.42</v>
+        <v>24348.26</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4474,21 +4466,25 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
@@ -4497,57 +4493,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>23404.61</v>
+        <v>24157.65</v>
       </c>
       <c r="C48" t="n">
-        <v>24499.63</v>
+        <v>25221.44</v>
       </c>
       <c r="D48" t="n">
-        <v>23229.38</v>
+        <v>23902.05</v>
       </c>
       <c r="E48" t="n">
-        <v>24175.12</v>
+        <v>24562.24</v>
       </c>
       <c r="F48" t="n">
-        <v>825.09</v>
+        <v>387.12</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.016</v>
       </c>
       <c r="H48" t="n">
-        <v>1270.25</v>
+        <v>1319.39</v>
       </c>
       <c r="I48" t="n">
-        <v>21853.58</v>
+        <v>21959.13</v>
       </c>
       <c r="J48" t="n">
-        <v>22643.03</v>
+        <v>23060.18</v>
       </c>
       <c r="K48" t="n">
-        <v>22934.25</v>
+        <v>23539.99</v>
       </c>
       <c r="L48" t="n">
-        <v>23225.47</v>
+        <v>24019.81</v>
       </c>
       <c r="M48" t="n">
-        <v>23765.81</v>
+        <v>24810.24</v>
       </c>
       <c r="N48" t="n">
-        <v>24306.14</v>
+        <v>25600.68</v>
       </c>
       <c r="O48" t="n">
-        <v>24348.26</v>
+        <v>25769.88</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4558,25 +4554,21 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
@@ -4592,50 +4584,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24157.65</v>
+        <v>24835.03</v>
       </c>
       <c r="C49" t="n">
-        <v>25221.44</v>
+        <v>25267.39</v>
       </c>
       <c r="D49" t="n">
-        <v>23902.05</v>
+        <v>24756.36</v>
       </c>
       <c r="E49" t="n">
-        <v>24562.24</v>
+        <v>24963.23</v>
       </c>
       <c r="F49" t="n">
-        <v>387.12</v>
+        <v>400.99</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
       </c>
       <c r="H49" t="n">
-        <v>1319.39</v>
+        <v>511.03</v>
       </c>
       <c r="I49" t="n">
-        <v>21959.13</v>
+        <v>22582.66</v>
       </c>
       <c r="J49" t="n">
-        <v>23060.18</v>
+        <v>23243.1</v>
       </c>
       <c r="K49" t="n">
-        <v>23539.99</v>
+        <v>23902.55</v>
       </c>
       <c r="L49" t="n">
-        <v>24019.81</v>
+        <v>24561.99</v>
       </c>
       <c r="M49" t="n">
-        <v>24810.24</v>
+        <v>25221.93</v>
       </c>
       <c r="N49" t="n">
-        <v>25600.68</v>
+        <v>25881.88</v>
       </c>
       <c r="O49" t="n">
-        <v>25769.88</v>
+        <v>26540.83</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4646,7 +4638,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4676,50 +4668,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24835.03</v>
+        <v>24993.77</v>
       </c>
       <c r="C50" t="n">
-        <v>25267.39</v>
+        <v>25971.63</v>
       </c>
       <c r="D50" t="n">
-        <v>24756.36</v>
+        <v>24938.34</v>
       </c>
       <c r="E50" t="n">
-        <v>24963.23</v>
+        <v>25884.43</v>
       </c>
       <c r="F50" t="n">
-        <v>400.99</v>
+        <v>921.2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0369</v>
       </c>
       <c r="H50" t="n">
-        <v>511.03</v>
+        <v>1033.29</v>
       </c>
       <c r="I50" t="n">
-        <v>22582.66</v>
+        <v>24245.33</v>
       </c>
       <c r="J50" t="n">
-        <v>23243.1</v>
+        <v>24427.88</v>
       </c>
       <c r="K50" t="n">
-        <v>23902.55</v>
+        <v>24707.71</v>
       </c>
       <c r="L50" t="n">
-        <v>24561.99</v>
+        <v>24987.55</v>
       </c>
       <c r="M50" t="n">
-        <v>25221.93</v>
+        <v>25218.75</v>
       </c>
       <c r="N50" t="n">
-        <v>25881.88</v>
+        <v>25449.94</v>
       </c>
       <c r="O50" t="n">
-        <v>26540.83</v>
+        <v>25778.42</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4730,80 +4722,80 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>24993.77</v>
+        <v>25987.31</v>
       </c>
       <c r="C51" t="n">
-        <v>25971.63</v>
+        <v>26187.57</v>
       </c>
       <c r="D51" t="n">
-        <v>24938.34</v>
+        <v>25389.42</v>
       </c>
       <c r="E51" t="n">
-        <v>25884.43</v>
+        <v>25668.03</v>
       </c>
       <c r="F51" t="n">
-        <v>921.2</v>
+        <v>-216.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0369</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>1033.29</v>
+        <v>798.15</v>
       </c>
       <c r="I51" t="n">
-        <v>24245.33</v>
+        <v>23905.05</v>
       </c>
       <c r="J51" t="n">
-        <v>24427.88</v>
+        <v>25065.86</v>
       </c>
       <c r="K51" t="n">
-        <v>24707.71</v>
+        <v>25367.78</v>
       </c>
       <c r="L51" t="n">
-        <v>24987.55</v>
+        <v>25669.71</v>
       </c>
       <c r="M51" t="n">
-        <v>25218.75</v>
+        <v>26401.08</v>
       </c>
       <c r="N51" t="n">
-        <v>25449.94</v>
+        <v>27132.44</v>
       </c>
       <c r="O51" t="n">
-        <v>25778.42</v>
+        <v>27004.92</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4816,78 +4808,76 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25987.31</v>
+        <v>25805.18</v>
       </c>
       <c r="C52" t="n">
-        <v>26187.57</v>
+        <v>26060.32</v>
       </c>
       <c r="D52" t="n">
-        <v>25389.42</v>
+        <v>25089.14</v>
       </c>
       <c r="E52" t="n">
-        <v>25668.03</v>
+        <v>25116.85</v>
       </c>
       <c r="F52" t="n">
-        <v>-216.4</v>
+        <v>-551.1799999999999</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0215</v>
       </c>
       <c r="H52" t="n">
-        <v>798.15</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>23905.05</v>
+        <v>24591.27</v>
       </c>
       <c r="J52" t="n">
-        <v>25065.86</v>
+        <v>24809.65</v>
       </c>
       <c r="K52" t="n">
-        <v>25367.78</v>
+        <v>25268.95</v>
       </c>
       <c r="L52" t="n">
-        <v>25669.71</v>
+        <v>25728.26</v>
       </c>
       <c r="M52" t="n">
-        <v>26401.08</v>
+        <v>26067.1</v>
       </c>
       <c r="N52" t="n">
-        <v>27132.44</v>
+        <v>26405.95</v>
       </c>
       <c r="O52" t="n">
-        <v>27004.92</v>
+        <v>26985.72</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4895,12 +4885,14 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4919,57 +4911,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25805.18</v>
+        <v>25303.41</v>
       </c>
       <c r="C53" t="n">
-        <v>26060.32</v>
+        <v>26009.46</v>
       </c>
       <c r="D53" t="n">
-        <v>25089.14</v>
+        <v>25240.62</v>
       </c>
       <c r="E53" t="n">
-        <v>25116.85</v>
+        <v>26009.46</v>
       </c>
       <c r="F53" t="n">
-        <v>-551.1799999999999</v>
+        <v>892.61</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0215</v>
+        <v>0.0355</v>
       </c>
       <c r="H53" t="n">
-        <v>971.1799999999999</v>
+        <v>768.84</v>
       </c>
       <c r="I53" t="n">
-        <v>24591.27</v>
+        <v>24117.96</v>
       </c>
       <c r="J53" t="n">
-        <v>24809.65</v>
+        <v>23916.73</v>
       </c>
       <c r="K53" t="n">
-        <v>25268.95</v>
+        <v>24631.26</v>
       </c>
       <c r="L53" t="n">
-        <v>25728.26</v>
+        <v>25345.79</v>
       </c>
       <c r="M53" t="n">
-        <v>26067.1</v>
+        <v>25602.44</v>
       </c>
       <c r="N53" t="n">
-        <v>26405.95</v>
+        <v>25859.09</v>
       </c>
       <c r="O53" t="n">
-        <v>26985.72</v>
+        <v>27031.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4977,22 +4969,24 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -5003,81 +4997,81 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25303.41</v>
+        <v>25780.12</v>
       </c>
       <c r="C54" t="n">
-        <v>26009.46</v>
+        <v>25800.22</v>
       </c>
       <c r="D54" t="n">
-        <v>25240.62</v>
+        <v>25403.44</v>
       </c>
       <c r="E54" t="n">
-        <v>26009.46</v>
+        <v>25584.79</v>
       </c>
       <c r="F54" t="n">
-        <v>892.61</v>
+        <v>-424.67</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0355</v>
+        <v>-0.0163</v>
       </c>
       <c r="H54" t="n">
-        <v>768.84</v>
+        <v>396.78</v>
       </c>
       <c r="I54" t="n">
-        <v>24117.96</v>
+        <v>24471.78</v>
       </c>
       <c r="J54" t="n">
-        <v>23916.73</v>
+        <v>25432.83</v>
       </c>
       <c r="K54" t="n">
-        <v>24631.26</v>
+        <v>25625.04</v>
       </c>
       <c r="L54" t="n">
-        <v>25345.79</v>
+        <v>25817.25</v>
       </c>
       <c r="M54" t="n">
-        <v>25602.44</v>
+        <v>26393.88</v>
       </c>
       <c r="N54" t="n">
-        <v>25859.09</v>
+        <v>26970.51</v>
       </c>
       <c r="O54" t="n">
-        <v>27031.5</v>
+        <v>26778.3</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5089,57 +5083,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25780.12</v>
+        <v>25420.63</v>
       </c>
       <c r="C55" t="n">
-        <v>25800.22</v>
+        <v>25791.38</v>
       </c>
       <c r="D55" t="n">
-        <v>25403.44</v>
+        <v>25008.87</v>
       </c>
       <c r="E55" t="n">
-        <v>25584.79</v>
+        <v>25650.87</v>
       </c>
       <c r="F55" t="n">
-        <v>-424.67</v>
+        <v>66.08</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0163</v>
+        <v>0.0026</v>
       </c>
       <c r="H55" t="n">
-        <v>396.78</v>
+        <v>782.51</v>
       </c>
       <c r="I55" t="n">
-        <v>24471.78</v>
+        <v>25006.66</v>
       </c>
       <c r="J55" t="n">
-        <v>25432.83</v>
+        <v>25179.49</v>
       </c>
       <c r="K55" t="n">
-        <v>25625.04</v>
+        <v>25386.4</v>
       </c>
       <c r="L55" t="n">
-        <v>25817.25</v>
+        <v>25593.31</v>
       </c>
       <c r="M55" t="n">
-        <v>26393.88</v>
+        <v>25783.18</v>
       </c>
       <c r="N55" t="n">
-        <v>26970.51</v>
+        <v>25973.05</v>
       </c>
       <c r="O55" t="n">
-        <v>26778.3</v>
+        <v>26197</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5151,16 +5145,18 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5182,57 +5178,57 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25420.63</v>
+        <v>25652.97</v>
       </c>
       <c r="C56" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D56" t="n">
-        <v>25008.87</v>
+        <v>24570.24</v>
       </c>
       <c r="E56" t="n">
-        <v>25650.87</v>
+        <v>24805.63</v>
       </c>
       <c r="F56" t="n">
-        <v>66.08</v>
+        <v>-845.24</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.033</v>
       </c>
       <c r="H56" t="n">
-        <v>782.51</v>
+        <v>1094.74</v>
       </c>
       <c r="I56" t="n">
-        <v>25006.66</v>
+        <v>24226.36</v>
       </c>
       <c r="J56" t="n">
-        <v>25179.49</v>
+        <v>24993.73</v>
       </c>
       <c r="K56" t="n">
-        <v>25386.4</v>
+        <v>25259.61</v>
       </c>
       <c r="L56" t="n">
-        <v>25593.31</v>
+        <v>25525.5</v>
       </c>
       <c r="M56" t="n">
-        <v>25783.18</v>
+        <v>26042.12</v>
       </c>
       <c r="N56" t="n">
-        <v>25973.05</v>
+        <v>26558.75</v>
       </c>
       <c r="O56" t="n">
-        <v>26197</v>
+        <v>26573.89</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -5242,13 +5238,11 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5256,81 +5250,73 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25652.97</v>
+        <v>24701.18</v>
       </c>
       <c r="C57" t="n">
-        <v>25664.98</v>
+        <v>24934.06</v>
       </c>
       <c r="D57" t="n">
-        <v>24570.24</v>
+        <v>24357.69</v>
       </c>
       <c r="E57" t="n">
-        <v>24805.63</v>
+        <v>24750.78</v>
       </c>
       <c r="F57" t="n">
-        <v>-845.24</v>
+        <v>-54.85</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.0022</v>
       </c>
       <c r="H57" t="n">
-        <v>1094.74</v>
+        <v>576.37</v>
       </c>
       <c r="I57" t="n">
-        <v>24226.36</v>
+        <v>23475.5</v>
       </c>
       <c r="J57" t="n">
-        <v>24993.73</v>
+        <v>23554.9</v>
       </c>
       <c r="K57" t="n">
-        <v>25259.61</v>
+        <v>24258.26</v>
       </c>
       <c r="L57" t="n">
-        <v>25525.5</v>
+        <v>24961.62</v>
       </c>
       <c r="M57" t="n">
-        <v>26042.12</v>
+        <v>25353</v>
       </c>
       <c r="N57" t="n">
-        <v>26558.75</v>
+        <v>25744.38</v>
       </c>
       <c r="O57" t="n">
-        <v>26573.89</v>
+        <v>26759.72</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5348,86 +5334,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>24701.18</v>
-      </c>
-      <c r="C58" t="n">
-        <v>24934.06</v>
-      </c>
-      <c r="D58" t="n">
-        <v>24357.69</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24604.29</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-201.34</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0081</v>
-      </c>
-      <c r="H58" t="n">
-        <v>576.37</v>
-      </c>
-      <c r="I58" t="n">
-        <v>23475.5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>23554.9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>24258.26</v>
-      </c>
-      <c r="L58" t="n">
-        <v>24961.62</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25353</v>
-      </c>
-      <c r="N58" t="n">
-        <v>25744.38</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26759.72</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5335,6 +5338,92 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>24748.45</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25042.71</v>
+      </c>
+      <c r="D58" t="n">
+        <v>24736.92</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>305.79</v>
+      </c>
+      <c r="I58" t="n">
+        <v>23781.32</v>
+      </c>
+      <c r="J58" t="n">
+        <v>24226.86</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24462.59</v>
+      </c>
+      <c r="L58" t="n">
+        <v>24698.33</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25038.96</v>
+      </c>
+      <c r="N58" t="n">
+        <v>25379.6</v>
+      </c>
+      <c r="O58" t="n">
+        <v>25510.43</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>1110.08</v>
       </c>
       <c r="I2" t="n">
-        <v>24309.76</v>
+        <v>24426.78</v>
       </c>
       <c r="J2" t="n">
-        <v>24842.03</v>
+        <v>24988.31</v>
       </c>
       <c r="K2" t="n">
-        <v>25050.06</v>
+        <v>25108.57</v>
       </c>
       <c r="L2" t="n">
-        <v>25258.08</v>
+        <v>25228.82</v>
       </c>
       <c r="M2" t="n">
-        <v>25628.23</v>
+        <v>25569.72</v>
       </c>
       <c r="N2" t="n">
-        <v>25998.37</v>
+        <v>25910.61</v>
       </c>
       <c r="O2" t="n">
-        <v>26044.27</v>
+        <v>25810.23</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -705,11 +702,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5354,13 +5355,13 @@
         <v>24736.92</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>25042.71</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>291.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0118</v>
       </c>
       <c r="H58" t="n">
         <v>305.79</v>
@@ -5386,27 +5387,25 @@
       <c r="O58" t="n">
         <v>25510.43</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5420,7 +5419,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5349,22 +5349,22 @@
         <v>24748.45</v>
       </c>
       <c r="C58" t="n">
-        <v>25042.71</v>
+        <v>25254.11</v>
       </c>
       <c r="D58" t="n">
         <v>24736.92</v>
       </c>
       <c r="E58" t="n">
-        <v>25042.71</v>
+        <v>25087.75</v>
       </c>
       <c r="F58" t="n">
-        <v>291.93</v>
+        <v>336.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0136</v>
       </c>
       <c r="H58" t="n">
-        <v>305.79</v>
+        <v>517.1900000000001</v>
       </c>
       <c r="I58" t="n">
         <v>23781.32</v>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5349,22 +5349,22 @@
         <v>24748.45</v>
       </c>
       <c r="C58" t="n">
-        <v>25254.11</v>
+        <v>25042.71</v>
       </c>
       <c r="D58" t="n">
         <v>24736.92</v>
       </c>
       <c r="E58" t="n">
-        <v>25087.75</v>
+        <v>25042.71</v>
       </c>
       <c r="F58" t="n">
-        <v>336.97</v>
+        <v>291.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0118</v>
       </c>
       <c r="H58" t="n">
-        <v>517.1900000000001</v>
+        <v>305.79</v>
       </c>
       <c r="I58" t="n">
         <v>23781.32</v>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5349,22 +5349,22 @@
         <v>24748.45</v>
       </c>
       <c r="C58" t="n">
-        <v>25042.71</v>
+        <v>25072.25</v>
       </c>
       <c r="D58" t="n">
         <v>24736.92</v>
       </c>
       <c r="E58" t="n">
-        <v>25042.71</v>
+        <v>24834.12</v>
       </c>
       <c r="F58" t="n">
-        <v>291.93</v>
+        <v>83.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0034</v>
       </c>
       <c r="H58" t="n">
-        <v>305.79</v>
+        <v>335.33</v>
       </c>
       <c r="I58" t="n">
         <v>23781.32</v>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,37 +659,37 @@
         <v>1110.08</v>
       </c>
       <c r="I2" t="n">
-        <v>24426.78</v>
+        <v>24652.62</v>
       </c>
       <c r="J2" t="n">
-        <v>24988.31</v>
+        <v>25073</v>
       </c>
       <c r="K2" t="n">
-        <v>25108.57</v>
+        <v>25165.03</v>
       </c>
       <c r="L2" t="n">
-        <v>25228.82</v>
+        <v>25257.05</v>
       </c>
       <c r="M2" t="n">
-        <v>25569.72</v>
+        <v>25513.26</v>
       </c>
       <c r="N2" t="n">
-        <v>25910.61</v>
+        <v>25769.46</v>
       </c>
       <c r="O2" t="n">
-        <v>25810.23</v>
+        <v>25697.31</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -5352,19 +5352,19 @@
         <v>25072.25</v>
       </c>
       <c r="D58" t="n">
-        <v>24736.92</v>
+        <v>24648.29</v>
       </c>
       <c r="E58" t="n">
-        <v>24834.12</v>
+        <v>24761.13</v>
       </c>
       <c r="F58" t="n">
-        <v>83.34</v>
+        <v>10.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0034</v>
+        <v>0.0004</v>
       </c>
       <c r="H58" t="n">
-        <v>335.33</v>
+        <v>423.96</v>
       </c>
       <c r="I58" t="n">
         <v>23781.32</v>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,67 +634,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25606.88</v>
+        <v>25508.21</v>
       </c>
       <c r="C2" t="n">
-        <v>25918.86</v>
+        <v>25789.99</v>
       </c>
       <c r="D2" t="n">
-        <v>24808.78</v>
+        <v>25013.26</v>
       </c>
       <c r="E2" t="n">
-        <v>25077.62</v>
+        <v>25417.98</v>
       </c>
       <c r="F2" t="n">
-        <v>-261.52</v>
+        <v>340.36</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0136</v>
       </c>
       <c r="H2" t="n">
-        <v>1110.08</v>
+        <v>776.73</v>
       </c>
       <c r="I2" t="n">
-        <v>24652.62</v>
+        <v>23698.7</v>
       </c>
       <c r="J2" t="n">
-        <v>25073</v>
+        <v>23824.44</v>
       </c>
       <c r="K2" t="n">
-        <v>25165.03</v>
+        <v>24522.58</v>
       </c>
       <c r="L2" t="n">
-        <v>25257.05</v>
+        <v>25220.72</v>
       </c>
       <c r="M2" t="n">
-        <v>25513.26</v>
+        <v>25632.66</v>
       </c>
       <c r="N2" t="n">
-        <v>25769.46</v>
+        <v>26044.6</v>
       </c>
       <c r="O2" t="n">
-        <v>25697.31</v>
+        <v>27028.94</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -702,15 +698,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -719,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25508.21</v>
+        <v>25440.01</v>
       </c>
       <c r="C3" t="n">
-        <v>25789.99</v>
+        <v>26585.95</v>
       </c>
       <c r="D3" t="n">
-        <v>25013.26</v>
+        <v>25387.81</v>
       </c>
       <c r="E3" t="n">
-        <v>25417.98</v>
+        <v>26388.16</v>
       </c>
       <c r="F3" t="n">
-        <v>340.36</v>
+        <v>970.1799999999999</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0382</v>
       </c>
       <c r="H3" t="n">
-        <v>776.73</v>
+        <v>1198.14</v>
       </c>
       <c r="I3" t="n">
-        <v>23698.7</v>
+        <v>24236.53</v>
       </c>
       <c r="J3" t="n">
-        <v>23824.44</v>
+        <v>24649.43</v>
       </c>
       <c r="K3" t="n">
-        <v>24522.58</v>
+        <v>25029.62</v>
       </c>
       <c r="L3" t="n">
-        <v>25220.72</v>
+        <v>25409.8</v>
       </c>
       <c r="M3" t="n">
-        <v>25632.66</v>
+        <v>25806.35</v>
       </c>
       <c r="N3" t="n">
-        <v>26044.6</v>
+        <v>26202.89</v>
       </c>
       <c r="O3" t="n">
-        <v>27028.94</v>
+        <v>26566.72</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,9 +772,9 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -790,70 +782,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25440.01</v>
+        <v>26308.91</v>
       </c>
       <c r="C4" t="n">
-        <v>26585.95</v>
+        <v>27058.03</v>
       </c>
       <c r="D4" t="n">
-        <v>25387.81</v>
+        <v>26280.23</v>
       </c>
       <c r="E4" t="n">
-        <v>26388.16</v>
+        <v>26545.1</v>
       </c>
       <c r="F4" t="n">
-        <v>970.1799999999999</v>
+        <v>156.94</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.0059</v>
       </c>
       <c r="H4" t="n">
-        <v>1198.14</v>
+        <v>777.8</v>
       </c>
       <c r="I4" t="n">
-        <v>24236.53</v>
+        <v>24189.67</v>
       </c>
       <c r="J4" t="n">
-        <v>24649.43</v>
+        <v>25390.66</v>
       </c>
       <c r="K4" t="n">
-        <v>25029.62</v>
+        <v>25789.09</v>
       </c>
       <c r="L4" t="n">
-        <v>25409.8</v>
+        <v>26187.52</v>
       </c>
       <c r="M4" t="n">
-        <v>25806.35</v>
+        <v>26987.23</v>
       </c>
       <c r="N4" t="n">
-        <v>26202.89</v>
+        <v>27786.94</v>
       </c>
       <c r="O4" t="n">
-        <v>26566.72</v>
+        <v>27784.09</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -864,9 +856,9 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -874,15 +866,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -894,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26308.91</v>
+        <v>26459.52</v>
       </c>
       <c r="C5" t="n">
-        <v>27058.03</v>
+        <v>26640.53</v>
       </c>
       <c r="D5" t="n">
-        <v>26280.23</v>
+        <v>26003.67</v>
       </c>
       <c r="E5" t="n">
-        <v>26545.1</v>
+        <v>26128.2</v>
       </c>
       <c r="F5" t="n">
-        <v>156.94</v>
+        <v>-416.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0157</v>
       </c>
       <c r="H5" t="n">
-        <v>777.8</v>
+        <v>636.86</v>
       </c>
       <c r="I5" t="n">
-        <v>24189.67</v>
+        <v>25502.43</v>
       </c>
       <c r="J5" t="n">
-        <v>25390.66</v>
+        <v>25705.29</v>
       </c>
       <c r="K5" t="n">
-        <v>25789.09</v>
+        <v>26156.2</v>
       </c>
       <c r="L5" t="n">
-        <v>26187.52</v>
+        <v>26607.11</v>
       </c>
       <c r="M5" t="n">
-        <v>26987.23</v>
+        <v>26934</v>
       </c>
       <c r="N5" t="n">
-        <v>27786.94</v>
+        <v>27260.88</v>
       </c>
       <c r="O5" t="n">
-        <v>27784.09</v>
+        <v>27835.83</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,18 +933,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -969,55 +957,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26459.52</v>
+        <v>26321.57</v>
       </c>
       <c r="C6" t="n">
-        <v>26640.53</v>
+        <v>27381.84</v>
       </c>
       <c r="D6" t="n">
-        <v>26003.67</v>
+        <v>26321.57</v>
       </c>
       <c r="E6" t="n">
-        <v>26128.2</v>
+        <v>27140.92</v>
       </c>
       <c r="F6" t="n">
-        <v>-416.9</v>
+        <v>1012.72</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0388</v>
       </c>
       <c r="H6" t="n">
-        <v>636.86</v>
+        <v>1060.27</v>
       </c>
       <c r="I6" t="n">
-        <v>25502.43</v>
+        <v>25366.81</v>
       </c>
       <c r="J6" t="n">
-        <v>25705.29</v>
+        <v>25394.39</v>
       </c>
       <c r="K6" t="n">
-        <v>26156.2</v>
+        <v>25809.77</v>
       </c>
       <c r="L6" t="n">
-        <v>26607.11</v>
+        <v>26225.15</v>
       </c>
       <c r="M6" t="n">
-        <v>26934</v>
+        <v>26446.63</v>
       </c>
       <c r="N6" t="n">
-        <v>27260.88</v>
+        <v>26668.11</v>
       </c>
       <c r="O6" t="n">
-        <v>27835.83</v>
+        <v>27277.39</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,170 +1017,174 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26321.57</v>
+        <v>27003.92</v>
       </c>
       <c r="C7" t="n">
-        <v>27381.84</v>
+        <v>27145.17</v>
       </c>
       <c r="D7" t="n">
-        <v>26321.57</v>
+        <v>26247.04</v>
       </c>
       <c r="E7" t="n">
-        <v>27140.92</v>
+        <v>26290.32</v>
       </c>
       <c r="F7" t="n">
-        <v>1012.72</v>
+        <v>-850.6</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0388</v>
+        <v>-0.0313</v>
       </c>
       <c r="H7" t="n">
-        <v>1060.27</v>
+        <v>898.13</v>
       </c>
       <c r="I7" t="n">
-        <v>25366.81</v>
+        <v>25261.3</v>
       </c>
       <c r="J7" t="n">
-        <v>25394.39</v>
+        <v>26225.26</v>
       </c>
       <c r="K7" t="n">
-        <v>25809.77</v>
+        <v>26610.79</v>
       </c>
       <c r="L7" t="n">
-        <v>26225.15</v>
+        <v>26996.31</v>
       </c>
       <c r="M7" t="n">
-        <v>26446.63</v>
+        <v>27671.05</v>
       </c>
       <c r="N7" t="n">
-        <v>26668.11</v>
+        <v>28345.8</v>
       </c>
       <c r="O7" t="n">
-        <v>27277.39</v>
+        <v>28442.11</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27003.92</v>
+        <v>25634</v>
       </c>
       <c r="C8" t="n">
-        <v>27145.17</v>
+        <v>26102.68</v>
       </c>
       <c r="D8" t="n">
-        <v>26247.04</v>
+        <v>25145.34</v>
       </c>
       <c r="E8" t="n">
-        <v>26290.32</v>
+        <v>25247.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-850.6</v>
+        <v>-1043.22</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0397</v>
       </c>
       <c r="H8" t="n">
-        <v>898.13</v>
+        <v>957.34</v>
       </c>
       <c r="I8" t="n">
-        <v>25261.3</v>
+        <v>25348.91</v>
       </c>
       <c r="J8" t="n">
-        <v>26225.26</v>
+        <v>25189.3</v>
       </c>
       <c r="K8" t="n">
-        <v>26610.79</v>
+        <v>25841.25</v>
       </c>
       <c r="L8" t="n">
-        <v>26996.31</v>
+        <v>26493.21</v>
       </c>
       <c r="M8" t="n">
-        <v>27671.05</v>
+        <v>26739.39</v>
       </c>
       <c r="N8" t="n">
-        <v>28345.8</v>
+        <v>26985.56</v>
       </c>
       <c r="O8" t="n">
-        <v>28442.11</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
+        <v>28043.3</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
@@ -1200,7 +1196,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1228,77 +1224,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25634</v>
+        <v>25884.46</v>
       </c>
       <c r="C9" t="n">
-        <v>26102.68</v>
+        <v>26367.35</v>
       </c>
       <c r="D9" t="n">
-        <v>25145.34</v>
+        <v>25591.66</v>
       </c>
       <c r="E9" t="n">
-        <v>25247.1</v>
+        <v>26160.15</v>
       </c>
       <c r="F9" t="n">
-        <v>-1043.22</v>
+        <v>913.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0362</v>
       </c>
       <c r="H9" t="n">
-        <v>957.34</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>25348.91</v>
+        <v>24188</v>
       </c>
       <c r="J9" t="n">
-        <v>25189.3</v>
+        <v>24101.3</v>
       </c>
       <c r="K9" t="n">
-        <v>25841.25</v>
+        <v>24768.43</v>
       </c>
       <c r="L9" t="n">
-        <v>26493.21</v>
+        <v>25435.55</v>
       </c>
       <c r="M9" t="n">
-        <v>26739.39</v>
+        <v>25725.77</v>
       </c>
       <c r="N9" t="n">
-        <v>26985.56</v>
+        <v>26015.98</v>
       </c>
       <c r="O9" t="n">
-        <v>28043.3</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+        <v>27060.02</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1307,59 +1301,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25884.46</v>
+        <v>26495.97</v>
       </c>
       <c r="C10" t="n">
-        <v>26367.35</v>
+        <v>26588.89</v>
       </c>
       <c r="D10" t="n">
-        <v>25591.66</v>
+        <v>25906.65</v>
       </c>
       <c r="E10" t="n">
-        <v>26160.15</v>
+        <v>25906.65</v>
       </c>
       <c r="F10" t="n">
-        <v>913.05</v>
+        <v>-253.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0362</v>
+        <v>-0.0097</v>
       </c>
       <c r="H10" t="n">
-        <v>775.6900000000001</v>
+        <v>682.24</v>
       </c>
       <c r="I10" t="n">
-        <v>24188</v>
+        <v>24815.97</v>
       </c>
       <c r="J10" t="n">
-        <v>24101.3</v>
+        <v>25474.78</v>
       </c>
       <c r="K10" t="n">
-        <v>24768.43</v>
+        <v>25772.31</v>
       </c>
       <c r="L10" t="n">
-        <v>25435.55</v>
+        <v>26069.83</v>
       </c>
       <c r="M10" t="n">
-        <v>25725.77</v>
+        <v>26548</v>
       </c>
       <c r="N10" t="n">
-        <v>26015.98</v>
+        <v>27026.16</v>
       </c>
       <c r="O10" t="n">
-        <v>27060.02</v>
+        <v>27143.04</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1367,12 +1357,14 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
@@ -1380,10 +1372,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1393,55 +1383,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26495.97</v>
+        <v>25999.17</v>
       </c>
       <c r="C11" t="n">
-        <v>26588.89</v>
+        <v>26490.71</v>
       </c>
       <c r="D11" t="n">
-        <v>25906.65</v>
+        <v>25496.13</v>
       </c>
       <c r="E11" t="n">
-        <v>25906.65</v>
+        <v>26241.83</v>
       </c>
       <c r="F11" t="n">
-        <v>-253.5</v>
+        <v>335.18</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0129</v>
       </c>
       <c r="H11" t="n">
-        <v>682.24</v>
+        <v>994.58</v>
       </c>
       <c r="I11" t="n">
-        <v>24815.97</v>
+        <v>25224.41</v>
       </c>
       <c r="J11" t="n">
-        <v>25474.78</v>
+        <v>25053.85</v>
       </c>
       <c r="K11" t="n">
-        <v>25772.31</v>
+        <v>25565.53</v>
       </c>
       <c r="L11" t="n">
-        <v>26069.83</v>
+        <v>26077.21</v>
       </c>
       <c r="M11" t="n">
-        <v>26548</v>
+        <v>26247.77</v>
       </c>
       <c r="N11" t="n">
-        <v>27026.16</v>
+        <v>26418.33</v>
       </c>
       <c r="O11" t="n">
-        <v>27143.04</v>
+        <v>27271.13</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1451,21 +1445,23 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1477,57 +1473,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25999.17</v>
+        <v>26319.4</v>
       </c>
       <c r="C12" t="n">
-        <v>26490.71</v>
+        <v>27188.81</v>
       </c>
       <c r="D12" t="n">
-        <v>25496.13</v>
+        <v>26302.93</v>
       </c>
       <c r="E12" t="n">
-        <v>26241.83</v>
+        <v>26572.46</v>
       </c>
       <c r="F12" t="n">
-        <v>335.18</v>
+        <v>330.63</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
       <c r="H12" t="n">
-        <v>994.58</v>
+        <v>885.88</v>
       </c>
       <c r="I12" t="n">
-        <v>25224.41</v>
+        <v>24501.55</v>
       </c>
       <c r="J12" t="n">
-        <v>25053.85</v>
+        <v>25371.45</v>
       </c>
       <c r="K12" t="n">
-        <v>25565.53</v>
+        <v>25744.54</v>
       </c>
       <c r="L12" t="n">
-        <v>26077.21</v>
+        <v>26117.63</v>
       </c>
       <c r="M12" t="n">
-        <v>26247.77</v>
+        <v>26739.12</v>
       </c>
       <c r="N12" t="n">
-        <v>26418.33</v>
+        <v>27360.61</v>
       </c>
       <c r="O12" t="n">
-        <v>27271.13</v>
+        <v>27485.29</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1535,12 +1531,10 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1550,10 +1544,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1563,78 +1555,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26319.4</v>
+        <v>26441.7</v>
       </c>
       <c r="C13" t="n">
-        <v>27188.81</v>
+        <v>26531.8</v>
       </c>
       <c r="D13" t="n">
-        <v>26302.93</v>
+        <v>25178.63</v>
       </c>
       <c r="E13" t="n">
-        <v>26572.46</v>
+        <v>25220.02</v>
       </c>
       <c r="F13" t="n">
-        <v>330.63</v>
+        <v>-1352.44</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0126</v>
+        <v>-0.0509</v>
       </c>
       <c r="H13" t="n">
-        <v>885.88</v>
+        <v>1353.17</v>
       </c>
       <c r="I13" t="n">
-        <v>24501.55</v>
+        <v>25417.05</v>
       </c>
       <c r="J13" t="n">
-        <v>25371.45</v>
+        <v>25599.88</v>
       </c>
       <c r="K13" t="n">
-        <v>25744.54</v>
+        <v>26129.52</v>
       </c>
       <c r="L13" t="n">
-        <v>26117.63</v>
+        <v>26659.17</v>
       </c>
       <c r="M13" t="n">
-        <v>26739.12</v>
+        <v>27015.4</v>
       </c>
       <c r="N13" t="n">
-        <v>27360.61</v>
+        <v>27371.64</v>
       </c>
       <c r="O13" t="n">
-        <v>27485.29</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>28074.69</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1642,9 +1634,9 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1652,74 +1644,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26441.7</v>
+        <v>25452.87</v>
       </c>
       <c r="C14" t="n">
-        <v>26531.8</v>
+        <v>26136.27</v>
       </c>
       <c r="D14" t="n">
-        <v>25178.63</v>
+        <v>25369.29</v>
       </c>
       <c r="E14" t="n">
-        <v>25220.02</v>
+        <v>25858.89</v>
       </c>
       <c r="F14" t="n">
-        <v>-1352.44</v>
+        <v>638.87</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0509</v>
+        <v>0.0253</v>
       </c>
       <c r="H14" t="n">
-        <v>1353.17</v>
+        <v>766.98</v>
       </c>
       <c r="I14" t="n">
-        <v>25417.05</v>
+        <v>23825.46</v>
       </c>
       <c r="J14" t="n">
-        <v>25599.88</v>
+        <v>23549.25</v>
       </c>
       <c r="K14" t="n">
-        <v>26129.52</v>
+        <v>24543.43</v>
       </c>
       <c r="L14" t="n">
-        <v>26659.17</v>
+        <v>25537.62</v>
       </c>
       <c r="M14" t="n">
-        <v>27015.4</v>
+        <v>25896.6</v>
       </c>
       <c r="N14" t="n">
-        <v>27371.64</v>
+        <v>26255.59</v>
       </c>
       <c r="O14" t="n">
-        <v>28074.69</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>27884.97</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1731,55 +1719,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25452.87</v>
+        <v>25945.87</v>
       </c>
       <c r="C15" t="n">
-        <v>26136.27</v>
+        <v>26264.13</v>
       </c>
       <c r="D15" t="n">
-        <v>25369.29</v>
+        <v>25649.3</v>
       </c>
       <c r="E15" t="n">
-        <v>25858.89</v>
+        <v>26085.08</v>
       </c>
       <c r="F15" t="n">
-        <v>638.87</v>
+        <v>226.19</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0253</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>766.98</v>
+        <v>614.83</v>
       </c>
       <c r="I15" t="n">
-        <v>23825.46</v>
+        <v>24602.31</v>
       </c>
       <c r="J15" t="n">
-        <v>23549.25</v>
+        <v>25144.97</v>
       </c>
       <c r="K15" t="n">
-        <v>24543.43</v>
+        <v>25475.4</v>
       </c>
       <c r="L15" t="n">
-        <v>25537.62</v>
+        <v>25805.83</v>
       </c>
       <c r="M15" t="n">
-        <v>25896.6</v>
+        <v>26242.38</v>
       </c>
       <c r="N15" t="n">
-        <v>26255.59</v>
+        <v>26678.93</v>
       </c>
       <c r="O15" t="n">
-        <v>27884.97</v>
+        <v>26903.25</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1790,7 +1782,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1813,76 +1805,78 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25945.87</v>
+        <v>26067.86</v>
       </c>
       <c r="C16" t="n">
-        <v>26264.13</v>
+        <v>26151.46</v>
       </c>
       <c r="D16" t="n">
-        <v>25649.3</v>
+        <v>25257.61</v>
       </c>
       <c r="E16" t="n">
-        <v>26085.08</v>
+        <v>25976.79</v>
       </c>
       <c r="F16" t="n">
-        <v>226.19</v>
+        <v>-108.29</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0042</v>
       </c>
       <c r="H16" t="n">
-        <v>614.83</v>
+        <v>893.85</v>
       </c>
       <c r="I16" t="n">
-        <v>24602.31</v>
+        <v>25034.47</v>
       </c>
       <c r="J16" t="n">
-        <v>25144.97</v>
+        <v>25534.43</v>
       </c>
       <c r="K16" t="n">
-        <v>25475.4</v>
+        <v>25777.67</v>
       </c>
       <c r="L16" t="n">
-        <v>25805.83</v>
+        <v>26020.9</v>
       </c>
       <c r="M16" t="n">
-        <v>26242.38</v>
+        <v>26392.5</v>
       </c>
       <c r="N16" t="n">
-        <v>26678.93</v>
+        <v>26764.09</v>
       </c>
       <c r="O16" t="n">
-        <v>26903.25</v>
+        <v>26878.96</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1895,59 +1889,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26067.86</v>
+        <v>25718.14</v>
       </c>
       <c r="C17" t="n">
-        <v>26151.46</v>
+        <v>25824.44</v>
       </c>
       <c r="D17" t="n">
-        <v>25257.61</v>
+        <v>25086.54</v>
       </c>
       <c r="E17" t="n">
-        <v>25976.79</v>
+        <v>25690.53</v>
       </c>
       <c r="F17" t="n">
-        <v>-108.29</v>
+        <v>-286.26</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.011</v>
       </c>
       <c r="H17" t="n">
-        <v>893.85</v>
+        <v>737.9</v>
       </c>
       <c r="I17" t="n">
-        <v>25034.47</v>
+        <v>24363.76</v>
       </c>
       <c r="J17" t="n">
-        <v>25534.43</v>
+        <v>25219.06</v>
       </c>
       <c r="K17" t="n">
-        <v>25777.67</v>
+        <v>25529.86</v>
       </c>
       <c r="L17" t="n">
-        <v>26020.9</v>
+        <v>25840.66</v>
       </c>
       <c r="M17" t="n">
-        <v>26392.5</v>
+        <v>26423.71</v>
       </c>
       <c r="N17" t="n">
-        <v>26764.09</v>
+        <v>27006.77</v>
       </c>
       <c r="O17" t="n">
-        <v>26878.96</v>
+        <v>27045.31</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1962,7 +1952,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1986,71 +1976,69 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25718.14</v>
+        <v>25795.94</v>
       </c>
       <c r="C18" t="n">
-        <v>25824.44</v>
+        <v>25927.66</v>
       </c>
       <c r="D18" t="n">
-        <v>25086.54</v>
+        <v>25671.33</v>
       </c>
       <c r="E18" t="n">
-        <v>25690.53</v>
+        <v>25818.93</v>
       </c>
       <c r="F18" t="n">
-        <v>-286.26</v>
+        <v>128.4</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H18" t="n">
-        <v>737.9</v>
+        <v>256.33</v>
       </c>
       <c r="I18" t="n">
-        <v>24363.76</v>
+        <v>24348.64</v>
       </c>
       <c r="J18" t="n">
-        <v>25219.06</v>
+        <v>25070.15</v>
       </c>
       <c r="K18" t="n">
-        <v>25529.86</v>
+        <v>25321.58</v>
       </c>
       <c r="L18" t="n">
-        <v>25840.66</v>
+        <v>25573.01</v>
       </c>
       <c r="M18" t="n">
-        <v>26423.71</v>
+        <v>26059.48</v>
       </c>
       <c r="N18" t="n">
-        <v>27006.77</v>
+        <v>26545.95</v>
       </c>
       <c r="O18" t="n">
-        <v>27045.31</v>
+        <v>26562.34</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2063,156 +2051,164 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25795.94</v>
+        <v>25928.89</v>
       </c>
       <c r="C19" t="n">
-        <v>25927.66</v>
+        <v>26345.63</v>
       </c>
       <c r="D19" t="n">
-        <v>25671.33</v>
+        <v>25554.31</v>
       </c>
       <c r="E19" t="n">
-        <v>25818.93</v>
+        <v>26338.47</v>
       </c>
       <c r="F19" t="n">
-        <v>128.4</v>
+        <v>519.54</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0201</v>
       </c>
       <c r="H19" t="n">
-        <v>256.33</v>
+        <v>791.3200000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>24348.64</v>
+        <v>25415</v>
       </c>
       <c r="J19" t="n">
-        <v>25070.15</v>
+        <v>25572.32</v>
       </c>
       <c r="K19" t="n">
-        <v>25321.58</v>
+        <v>25690.76</v>
       </c>
       <c r="L19" t="n">
-        <v>25573.01</v>
+        <v>25809.21</v>
       </c>
       <c r="M19" t="n">
-        <v>26059.48</v>
+        <v>25947.09</v>
       </c>
       <c r="N19" t="n">
-        <v>26545.95</v>
+        <v>26084.98</v>
       </c>
       <c r="O19" t="n">
-        <v>26562.34</v>
+        <v>26183.99</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25928.89</v>
+        <v>26361.44</v>
       </c>
       <c r="C20" t="n">
-        <v>26345.63</v>
+        <v>26858.13</v>
       </c>
       <c r="D20" t="n">
-        <v>25554.31</v>
+        <v>25960.34</v>
       </c>
       <c r="E20" t="n">
-        <v>26338.47</v>
+        <v>26231.79</v>
       </c>
       <c r="F20" t="n">
-        <v>519.54</v>
+        <v>-106.68</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.0041</v>
       </c>
       <c r="H20" t="n">
-        <v>791.3200000000001</v>
+        <v>897.79</v>
       </c>
       <c r="I20" t="n">
-        <v>25415</v>
+        <v>24762.99</v>
       </c>
       <c r="J20" t="n">
-        <v>25572.32</v>
+        <v>25741.4</v>
       </c>
       <c r="K20" t="n">
-        <v>25690.76</v>
+        <v>25942.81</v>
       </c>
       <c r="L20" t="n">
-        <v>25809.21</v>
+        <v>26144.22</v>
       </c>
       <c r="M20" t="n">
-        <v>25947.09</v>
+        <v>26734.13</v>
       </c>
       <c r="N20" t="n">
-        <v>26084.98</v>
+        <v>27324.04</v>
       </c>
       <c r="O20" t="n">
-        <v>26183.99</v>
+        <v>27136.95</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2220,15 +2216,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2244,50 +2236,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26361.44</v>
+        <v>26376.84</v>
       </c>
       <c r="C21" t="n">
-        <v>26858.13</v>
+        <v>27206.84</v>
       </c>
       <c r="D21" t="n">
-        <v>25960.34</v>
+        <v>26187.76</v>
       </c>
       <c r="E21" t="n">
-        <v>26231.79</v>
+        <v>26844.96</v>
       </c>
       <c r="F21" t="n">
-        <v>-106.68</v>
+        <v>613.17</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0234</v>
       </c>
       <c r="H21" t="n">
-        <v>897.79</v>
+        <v>1019.08</v>
       </c>
       <c r="I21" t="n">
-        <v>24762.99</v>
+        <v>25062.55</v>
       </c>
       <c r="J21" t="n">
-        <v>25741.4</v>
+        <v>25245.27</v>
       </c>
       <c r="K21" t="n">
-        <v>25942.81</v>
+        <v>25782.89</v>
       </c>
       <c r="L21" t="n">
-        <v>26144.22</v>
+        <v>26320.51</v>
       </c>
       <c r="M21" t="n">
-        <v>26734.13</v>
+        <v>26680.68</v>
       </c>
       <c r="N21" t="n">
-        <v>27324.04</v>
+        <v>27040.86</v>
       </c>
       <c r="O21" t="n">
-        <v>27136.95</v>
+        <v>27755.92</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2298,18 +2290,20 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2319,59 +2313,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26376.84</v>
+        <v>26641.6</v>
       </c>
       <c r="C22" t="n">
-        <v>27206.84</v>
+        <v>26895.94</v>
       </c>
       <c r="D22" t="n">
-        <v>26187.76</v>
+        <v>26363.86</v>
       </c>
       <c r="E22" t="n">
-        <v>26844.96</v>
+        <v>26749.51</v>
       </c>
       <c r="F22" t="n">
-        <v>613.17</v>
+        <v>-95.45</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0234</v>
+        <v>-0.0036</v>
       </c>
       <c r="H22" t="n">
-        <v>1019.08</v>
+        <v>532.08</v>
       </c>
       <c r="I22" t="n">
-        <v>25062.55</v>
+        <v>25168.68</v>
       </c>
       <c r="J22" t="n">
-        <v>25245.27</v>
+        <v>25899.71</v>
       </c>
       <c r="K22" t="n">
-        <v>25782.89</v>
+        <v>26335.42</v>
       </c>
       <c r="L22" t="n">
-        <v>26320.51</v>
+        <v>26771.13</v>
       </c>
       <c r="M22" t="n">
-        <v>26680.68</v>
+        <v>27354.5</v>
       </c>
       <c r="N22" t="n">
-        <v>27040.86</v>
+        <v>27937.87</v>
       </c>
       <c r="O22" t="n">
-        <v>27755.92</v>
+        <v>28225.92</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2384,18 +2374,14 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2405,55 +2391,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26641.6</v>
+        <v>26844.04</v>
       </c>
       <c r="C23" t="n">
-        <v>26895.94</v>
+        <v>28056.1</v>
       </c>
       <c r="D23" t="n">
-        <v>26363.86</v>
+        <v>26619.83</v>
       </c>
       <c r="E23" t="n">
-        <v>26749.51</v>
+        <v>27387.11</v>
       </c>
       <c r="F23" t="n">
-        <v>-95.45</v>
+        <v>637.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0238</v>
       </c>
       <c r="H23" t="n">
-        <v>532.08</v>
+        <v>1436.27</v>
       </c>
       <c r="I23" t="n">
-        <v>25168.68</v>
+        <v>25831.78</v>
       </c>
       <c r="J23" t="n">
-        <v>25899.71</v>
+        <v>26277.23</v>
       </c>
       <c r="K23" t="n">
-        <v>26335.42</v>
+        <v>26483.47</v>
       </c>
       <c r="L23" t="n">
-        <v>26771.13</v>
+        <v>26689.7</v>
       </c>
       <c r="M23" t="n">
-        <v>27354.5</v>
+        <v>27015.55</v>
       </c>
       <c r="N23" t="n">
-        <v>27937.87</v>
+        <v>27341.4</v>
       </c>
       <c r="O23" t="n">
-        <v>28225.92</v>
+        <v>27428.02</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2466,76 +2456,78 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26844.04</v>
+        <v>27097.34</v>
       </c>
       <c r="C24" t="n">
-        <v>28056.1</v>
+        <v>27126.48</v>
       </c>
       <c r="D24" t="n">
-        <v>26619.83</v>
+        <v>26295.03</v>
       </c>
       <c r="E24" t="n">
-        <v>27387.11</v>
+        <v>26559.95</v>
       </c>
       <c r="F24" t="n">
-        <v>637.6</v>
+        <v>-827.16</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0238</v>
+        <v>-0.0302</v>
       </c>
       <c r="H24" t="n">
-        <v>1436.27</v>
+        <v>831.45</v>
       </c>
       <c r="I24" t="n">
-        <v>25831.78</v>
+        <v>25183.56</v>
       </c>
       <c r="J24" t="n">
-        <v>26277.23</v>
+        <v>25975.41</v>
       </c>
       <c r="K24" t="n">
-        <v>26483.47</v>
+        <v>26668.97</v>
       </c>
       <c r="L24" t="n">
-        <v>26689.7</v>
+        <v>27362.54</v>
       </c>
       <c r="M24" t="n">
-        <v>27015.55</v>
+        <v>28105.24</v>
       </c>
       <c r="N24" t="n">
-        <v>27341.4</v>
+        <v>28847.95</v>
       </c>
       <c r="O24" t="n">
-        <v>27428.02</v>
+        <v>29492.37</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2543,83 +2535,83 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27097.34</v>
+        <v>26982.49</v>
       </c>
       <c r="C25" t="n">
-        <v>27126.48</v>
+        <v>27397.65</v>
       </c>
       <c r="D25" t="n">
-        <v>26295.03</v>
+        <v>26444.46</v>
       </c>
       <c r="E25" t="n">
-        <v>26559.95</v>
+        <v>26567.12</v>
       </c>
       <c r="F25" t="n">
-        <v>-827.16</v>
+        <v>7.17</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0003</v>
       </c>
       <c r="H25" t="n">
-        <v>831.45</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>25183.56</v>
+        <v>25463.58</v>
       </c>
       <c r="J25" t="n">
-        <v>25975.41</v>
+        <v>25653.1</v>
       </c>
       <c r="K25" t="n">
-        <v>26668.97</v>
+        <v>26144.22</v>
       </c>
       <c r="L25" t="n">
-        <v>27362.54</v>
+        <v>26635.35</v>
       </c>
       <c r="M25" t="n">
-        <v>28105.24</v>
+        <v>26975.67</v>
       </c>
       <c r="N25" t="n">
-        <v>28847.95</v>
+        <v>27316</v>
       </c>
       <c r="O25" t="n">
-        <v>29492.37</v>
+        <v>27957.93</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2627,21 +2619,23 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2651,59 +2645,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26982.49</v>
+        <v>26501.2</v>
       </c>
       <c r="C26" t="n">
-        <v>27397.65</v>
+        <v>26734.41</v>
       </c>
       <c r="D26" t="n">
-        <v>26444.46</v>
+        <v>26356.96</v>
       </c>
       <c r="E26" t="n">
-        <v>26567.12</v>
+        <v>26413.35</v>
       </c>
       <c r="F26" t="n">
-        <v>7.17</v>
+        <v>-153.77</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0058</v>
       </c>
       <c r="H26" t="n">
-        <v>953.1900000000001</v>
+        <v>377.45</v>
       </c>
       <c r="I26" t="n">
-        <v>25463.58</v>
+        <v>25491.27</v>
       </c>
       <c r="J26" t="n">
-        <v>25653.1</v>
+        <v>25436.96</v>
       </c>
       <c r="K26" t="n">
-        <v>26144.22</v>
+        <v>26090.52</v>
       </c>
       <c r="L26" t="n">
-        <v>26635.35</v>
+        <v>26744.09</v>
       </c>
       <c r="M26" t="n">
-        <v>26975.67</v>
+        <v>27043.71</v>
       </c>
       <c r="N26" t="n">
-        <v>27316</v>
+        <v>27343.34</v>
       </c>
       <c r="O26" t="n">
-        <v>27957.93</v>
+        <v>28350.84</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2711,23 +2701,21 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2737,55 +2725,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26501.2</v>
+        <v>26798.97</v>
       </c>
       <c r="C27" t="n">
-        <v>26734.41</v>
+        <v>27156.28</v>
       </c>
       <c r="D27" t="n">
-        <v>26356.96</v>
+        <v>26373.01</v>
       </c>
       <c r="E27" t="n">
-        <v>26413.35</v>
+        <v>26630.54</v>
       </c>
       <c r="F27" t="n">
-        <v>-153.77</v>
+        <v>217.19</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>377.45</v>
+        <v>783.27</v>
       </c>
       <c r="I27" t="n">
-        <v>25491.27</v>
+        <v>25979.51</v>
       </c>
       <c r="J27" t="n">
-        <v>25436.96</v>
+        <v>25969.73</v>
       </c>
       <c r="K27" t="n">
-        <v>26090.52</v>
+        <v>26224.62</v>
       </c>
       <c r="L27" t="n">
-        <v>26744.09</v>
+        <v>26479.52</v>
       </c>
       <c r="M27" t="n">
-        <v>27043.71</v>
+        <v>26602.07</v>
       </c>
       <c r="N27" t="n">
-        <v>27343.34</v>
+        <v>26724.63</v>
       </c>
       <c r="O27" t="n">
-        <v>28350.84</v>
+        <v>27111.86</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2793,116 +2785,116 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26798.97</v>
+        <v>26305.58</v>
       </c>
       <c r="C28" t="n">
-        <v>27156.28</v>
+        <v>26403.85</v>
       </c>
       <c r="D28" t="n">
-        <v>26373.01</v>
+        <v>24958.43</v>
       </c>
       <c r="E28" t="n">
-        <v>26630.54</v>
+        <v>25757.29</v>
       </c>
       <c r="F28" t="n">
-        <v>217.19</v>
+        <v>-873.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="H28" t="n">
-        <v>783.27</v>
+        <v>1445.42</v>
       </c>
       <c r="I28" t="n">
-        <v>25979.51</v>
+        <v>25589.74</v>
       </c>
       <c r="J28" t="n">
-        <v>25969.73</v>
+        <v>25780.22</v>
       </c>
       <c r="K28" t="n">
-        <v>26224.62</v>
+        <v>26238.9</v>
       </c>
       <c r="L28" t="n">
-        <v>26479.52</v>
+        <v>26697.59</v>
       </c>
       <c r="M28" t="n">
-        <v>26602.07</v>
+        <v>27022.17</v>
       </c>
       <c r="N28" t="n">
-        <v>26724.63</v>
+        <v>27346.76</v>
       </c>
       <c r="O28" t="n">
-        <v>27111.86</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>27939.55</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2910,69 +2902,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26305.58</v>
+        <v>25075.74</v>
       </c>
       <c r="C29" t="n">
-        <v>26403.85</v>
+        <v>26149.64</v>
       </c>
       <c r="D29" t="n">
-        <v>24958.43</v>
+        <v>24906</v>
       </c>
       <c r="E29" t="n">
-        <v>25757.29</v>
+        <v>25465.6</v>
       </c>
       <c r="F29" t="n">
-        <v>-873.25</v>
+        <v>-291.69</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0328</v>
+        <v>-0.0113</v>
       </c>
       <c r="H29" t="n">
-        <v>1445.42</v>
+        <v>1243.64</v>
       </c>
       <c r="I29" t="n">
-        <v>25589.74</v>
+        <v>23513.01</v>
       </c>
       <c r="J29" t="n">
-        <v>25780.22</v>
+        <v>24349.94</v>
       </c>
       <c r="K29" t="n">
-        <v>26238.9</v>
+        <v>25034.58</v>
       </c>
       <c r="L29" t="n">
-        <v>26697.59</v>
+        <v>25719.21</v>
       </c>
       <c r="M29" t="n">
-        <v>27022.17</v>
+        <v>26480</v>
       </c>
       <c r="N29" t="n">
-        <v>27346.76</v>
+        <v>27240.78</v>
       </c>
       <c r="O29" t="n">
-        <v>27939.55</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27849.27</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2994,50 +2982,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25075.74</v>
+        <v>25436.27</v>
       </c>
       <c r="C30" t="n">
-        <v>26149.64</v>
+        <v>26250.14</v>
       </c>
       <c r="D30" t="n">
-        <v>24906</v>
+        <v>25121.46</v>
       </c>
       <c r="E30" t="n">
-        <v>25465.6</v>
+        <v>25277.32</v>
       </c>
       <c r="F30" t="n">
-        <v>-291.69</v>
+        <v>-188.28</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.0074</v>
       </c>
       <c r="H30" t="n">
-        <v>1243.64</v>
+        <v>1128.68</v>
       </c>
       <c r="I30" t="n">
-        <v>23513.01</v>
+        <v>23662.36</v>
       </c>
       <c r="J30" t="n">
-        <v>24349.94</v>
+        <v>24190.85</v>
       </c>
       <c r="K30" t="n">
-        <v>25034.58</v>
+        <v>24843.78</v>
       </c>
       <c r="L30" t="n">
-        <v>25719.21</v>
+        <v>25496.71</v>
       </c>
       <c r="M30" t="n">
-        <v>26480</v>
+        <v>26087.42</v>
       </c>
       <c r="N30" t="n">
-        <v>27240.78</v>
+        <v>26678.13</v>
       </c>
       <c r="O30" t="n">
-        <v>27849.27</v>
+        <v>27393.28</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3045,18 +3033,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3069,55 +3057,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25436.27</v>
+        <v>24789.14</v>
       </c>
       <c r="C31" t="n">
-        <v>26250.14</v>
+        <v>25390.3</v>
       </c>
       <c r="D31" t="n">
-        <v>25121.46</v>
+        <v>24203.54</v>
       </c>
       <c r="E31" t="n">
-        <v>25277.32</v>
+        <v>24951.88</v>
       </c>
       <c r="F31" t="n">
-        <v>-188.28</v>
+        <v>-325.44</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0129</v>
       </c>
       <c r="H31" t="n">
-        <v>1128.68</v>
+        <v>1186.76</v>
       </c>
       <c r="I31" t="n">
-        <v>23662.36</v>
+        <v>23992.78</v>
       </c>
       <c r="J31" t="n">
-        <v>24190.85</v>
+        <v>23944.4</v>
       </c>
       <c r="K31" t="n">
-        <v>24843.78</v>
+        <v>24712.98</v>
       </c>
       <c r="L31" t="n">
-        <v>25496.71</v>
+        <v>25481.56</v>
       </c>
       <c r="M31" t="n">
-        <v>26087.42</v>
+        <v>25841.66</v>
       </c>
       <c r="N31" t="n">
-        <v>26678.13</v>
+        <v>26201.76</v>
       </c>
       <c r="O31" t="n">
-        <v>27393.28</v>
+        <v>27378.82</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3125,18 +3117,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3149,59 +3141,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24789.14</v>
+        <v>24532.85</v>
       </c>
       <c r="C32" t="n">
-        <v>25390.3</v>
+        <v>25429.76</v>
       </c>
       <c r="D32" t="n">
-        <v>24203.54</v>
+        <v>24409.57</v>
       </c>
       <c r="E32" t="n">
-        <v>24951.88</v>
+        <v>25116.53</v>
       </c>
       <c r="F32" t="n">
-        <v>-325.44</v>
+        <v>164.65</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0066</v>
       </c>
       <c r="H32" t="n">
-        <v>1186.76</v>
+        <v>1020.19</v>
       </c>
       <c r="I32" t="n">
-        <v>23992.78</v>
+        <v>23016.78</v>
       </c>
       <c r="J32" t="n">
-        <v>23944.4</v>
+        <v>23842.6</v>
       </c>
       <c r="K32" t="n">
-        <v>24712.98</v>
+        <v>24358.5</v>
       </c>
       <c r="L32" t="n">
-        <v>25481.56</v>
+        <v>24874.4</v>
       </c>
       <c r="M32" t="n">
-        <v>25841.66</v>
+        <v>25545.26</v>
       </c>
       <c r="N32" t="n">
-        <v>26201.76</v>
+        <v>26216.12</v>
       </c>
       <c r="O32" t="n">
-        <v>27378.82</v>
+        <v>26577.06</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,14 +3197,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3233,55 +3219,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24532.85</v>
+        <v>25772.56</v>
       </c>
       <c r="C33" t="n">
-        <v>25429.76</v>
+        <v>26073.97</v>
       </c>
       <c r="D33" t="n">
-        <v>24409.57</v>
+        <v>25653.63</v>
       </c>
       <c r="E33" t="n">
-        <v>25116.53</v>
+        <v>25893.54</v>
       </c>
       <c r="F33" t="n">
-        <v>164.65</v>
+        <v>777.01</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0309</v>
       </c>
       <c r="H33" t="n">
-        <v>1020.19</v>
+        <v>420.34</v>
       </c>
       <c r="I33" t="n">
-        <v>23016.78</v>
+        <v>23389.38</v>
       </c>
       <c r="J33" t="n">
-        <v>23842.6</v>
+        <v>24194.77</v>
       </c>
       <c r="K33" t="n">
-        <v>24358.5</v>
+        <v>24606.43</v>
       </c>
       <c r="L33" t="n">
-        <v>24874.4</v>
+        <v>25018.1</v>
       </c>
       <c r="M33" t="n">
-        <v>25545.26</v>
+        <v>25626.62</v>
       </c>
       <c r="N33" t="n">
-        <v>26216.12</v>
+        <v>26235.15</v>
       </c>
       <c r="O33" t="n">
-        <v>26577.06</v>
+        <v>26449.95</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3292,13 +3282,15 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3320,50 +3312,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25772.56</v>
+        <v>25708.64</v>
       </c>
       <c r="C34" t="n">
-        <v>26073.97</v>
+        <v>26403.07</v>
       </c>
       <c r="D34" t="n">
-        <v>25653.63</v>
+        <v>25508.53</v>
       </c>
       <c r="E34" t="n">
-        <v>25893.54</v>
+        <v>26160.33</v>
       </c>
       <c r="F34" t="n">
-        <v>777.01</v>
+        <v>266.79</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.0103</v>
       </c>
       <c r="H34" t="n">
-        <v>420.34</v>
+        <v>894.54</v>
       </c>
       <c r="I34" t="n">
-        <v>23389.38</v>
+        <v>25233.29</v>
       </c>
       <c r="J34" t="n">
-        <v>24194.77</v>
+        <v>25488.07</v>
       </c>
       <c r="K34" t="n">
-        <v>24606.43</v>
+        <v>25683.37</v>
       </c>
       <c r="L34" t="n">
-        <v>25018.1</v>
+        <v>25878.67</v>
       </c>
       <c r="M34" t="n">
-        <v>25626.62</v>
+        <v>26103.71</v>
       </c>
       <c r="N34" t="n">
-        <v>26235.15</v>
+        <v>26328.75</v>
       </c>
       <c r="O34" t="n">
-        <v>26449.95</v>
+        <v>26494.31</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3371,10 +3363,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3384,8 +3378,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3397,57 +3393,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25708.64</v>
+        <v>26204.61</v>
       </c>
       <c r="C35" t="n">
-        <v>26403.07</v>
+        <v>26529.49</v>
       </c>
       <c r="D35" t="n">
-        <v>25508.53</v>
+        <v>25639.26</v>
       </c>
       <c r="E35" t="n">
-        <v>26160.33</v>
+        <v>25978.07</v>
       </c>
       <c r="F35" t="n">
-        <v>266.79</v>
+        <v>-182.26</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.007</v>
       </c>
       <c r="H35" t="n">
-        <v>894.54</v>
+        <v>890.23</v>
       </c>
       <c r="I35" t="n">
-        <v>25233.29</v>
+        <v>24613.99</v>
       </c>
       <c r="J35" t="n">
-        <v>25488.07</v>
+        <v>25368.05</v>
       </c>
       <c r="K35" t="n">
-        <v>25683.37</v>
+        <v>25713.06</v>
       </c>
       <c r="L35" t="n">
-        <v>25878.67</v>
+        <v>26058.06</v>
       </c>
       <c r="M35" t="n">
-        <v>26103.71</v>
+        <v>26607.6</v>
       </c>
       <c r="N35" t="n">
-        <v>26328.75</v>
+        <v>27157.14</v>
       </c>
       <c r="O35" t="n">
-        <v>26494.31</v>
+        <v>27297.61</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3462,18 +3458,14 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3492,50 +3484,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26204.61</v>
+        <v>25976.97</v>
       </c>
       <c r="C36" t="n">
-        <v>26529.49</v>
+        <v>26132.94</v>
       </c>
       <c r="D36" t="n">
-        <v>25639.26</v>
+        <v>25609.61</v>
       </c>
       <c r="E36" t="n">
-        <v>25978.07</v>
+        <v>25776.53</v>
       </c>
       <c r="F36" t="n">
-        <v>-182.26</v>
+        <v>-201.54</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0078</v>
       </c>
       <c r="H36" t="n">
-        <v>890.23</v>
+        <v>523.33</v>
       </c>
       <c r="I36" t="n">
-        <v>24613.99</v>
+        <v>24749.03</v>
       </c>
       <c r="J36" t="n">
-        <v>25368.05</v>
+        <v>25034.69</v>
       </c>
       <c r="K36" t="n">
-        <v>25713.06</v>
+        <v>25532.96</v>
       </c>
       <c r="L36" t="n">
-        <v>26058.06</v>
+        <v>26031.22</v>
       </c>
       <c r="M36" t="n">
-        <v>26607.6</v>
+        <v>26423.19</v>
       </c>
       <c r="N36" t="n">
-        <v>27157.14</v>
+        <v>26815.15</v>
       </c>
       <c r="O36" t="n">
-        <v>27297.61</v>
+        <v>27419.72</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3545,12 +3537,12 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3567,59 +3559,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25976.97</v>
+        <v>26138.34</v>
       </c>
       <c r="C37" t="n">
-        <v>26132.94</v>
+        <v>26669.26</v>
       </c>
       <c r="D37" t="n">
-        <v>25609.61</v>
+        <v>25690.36</v>
       </c>
       <c r="E37" t="n">
-        <v>25776.53</v>
+        <v>26393.71</v>
       </c>
       <c r="F37" t="n">
-        <v>-201.54</v>
+        <v>617.1799999999999</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0239</v>
       </c>
       <c r="H37" t="n">
-        <v>523.33</v>
+        <v>978.9</v>
       </c>
       <c r="I37" t="n">
-        <v>24749.03</v>
+        <v>25086.28</v>
       </c>
       <c r="J37" t="n">
-        <v>25034.69</v>
+        <v>25205.83</v>
       </c>
       <c r="K37" t="n">
-        <v>25532.96</v>
+        <v>25514.86</v>
       </c>
       <c r="L37" t="n">
-        <v>26031.22</v>
+        <v>25823.9</v>
       </c>
       <c r="M37" t="n">
-        <v>26423.19</v>
+        <v>26038.19</v>
       </c>
       <c r="N37" t="n">
-        <v>26815.15</v>
+        <v>26252.49</v>
       </c>
       <c r="O37" t="n">
-        <v>27419.72</v>
+        <v>26656.27</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3627,28 +3615,32 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3656,50 +3648,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26138.34</v>
+        <v>26310.87</v>
       </c>
       <c r="C38" t="n">
-        <v>26669.26</v>
+        <v>26844.8</v>
       </c>
       <c r="D38" t="n">
-        <v>25690.36</v>
+        <v>25847.15</v>
       </c>
       <c r="E38" t="n">
-        <v>26393.71</v>
+        <v>25962.73</v>
       </c>
       <c r="F38" t="n">
-        <v>617.1799999999999</v>
+        <v>-430.98</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0163</v>
       </c>
       <c r="H38" t="n">
-        <v>978.9</v>
+        <v>997.65</v>
       </c>
       <c r="I38" t="n">
-        <v>25086.28</v>
+        <v>24711.46</v>
       </c>
       <c r="J38" t="n">
-        <v>25205.83</v>
+        <v>25521.76</v>
       </c>
       <c r="K38" t="n">
-        <v>25514.86</v>
+        <v>25904.26</v>
       </c>
       <c r="L38" t="n">
-        <v>25823.9</v>
+        <v>26286.76</v>
       </c>
       <c r="M38" t="n">
-        <v>26038.19</v>
+        <v>26883.16</v>
       </c>
       <c r="N38" t="n">
-        <v>26252.49</v>
+        <v>27479.56</v>
       </c>
       <c r="O38" t="n">
-        <v>26656.27</v>
+        <v>27648.16</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3707,83 +3699,83 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26310.87</v>
+        <v>25838.96</v>
       </c>
       <c r="C39" t="n">
-        <v>26844.8</v>
+        <v>25845.46</v>
       </c>
       <c r="D39" t="n">
-        <v>25847.15</v>
+        <v>25341.73</v>
       </c>
       <c r="E39" t="n">
-        <v>25962.73</v>
+        <v>25606.03</v>
       </c>
       <c r="F39" t="n">
-        <v>-430.98</v>
+        <v>-356.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0137</v>
       </c>
       <c r="H39" t="n">
-        <v>997.65</v>
+        <v>503.73</v>
       </c>
       <c r="I39" t="n">
-        <v>24711.46</v>
+        <v>24849.5</v>
       </c>
       <c r="J39" t="n">
-        <v>25521.76</v>
+        <v>24773.46</v>
       </c>
       <c r="K39" t="n">
-        <v>25904.26</v>
+        <v>25463.91</v>
       </c>
       <c r="L39" t="n">
-        <v>26286.76</v>
+        <v>26154.35</v>
       </c>
       <c r="M39" t="n">
-        <v>26883.16</v>
+        <v>26461.56</v>
       </c>
       <c r="N39" t="n">
-        <v>27479.56</v>
+        <v>26768.76</v>
       </c>
       <c r="O39" t="n">
-        <v>27648.16</v>
+        <v>27842.45</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3796,7 +3788,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3817,70 +3809,74 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25838.96</v>
+        <v>25622.36</v>
       </c>
       <c r="C40" t="n">
-        <v>25845.46</v>
+        <v>25768.38</v>
       </c>
       <c r="D40" t="n">
-        <v>25341.73</v>
+        <v>24727.26</v>
       </c>
       <c r="E40" t="n">
-        <v>25606.03</v>
+        <v>25182.39</v>
       </c>
       <c r="F40" t="n">
-        <v>-356.7</v>
+        <v>-423.64</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0165</v>
       </c>
       <c r="H40" t="n">
-        <v>503.73</v>
+        <v>1041.12</v>
       </c>
       <c r="I40" t="n">
-        <v>24849.5</v>
+        <v>24838</v>
       </c>
       <c r="J40" t="n">
-        <v>24773.46</v>
+        <v>25108.52</v>
       </c>
       <c r="K40" t="n">
-        <v>25463.91</v>
+        <v>25354.16</v>
       </c>
       <c r="L40" t="n">
-        <v>26154.35</v>
+        <v>25599.81</v>
       </c>
       <c r="M40" t="n">
-        <v>26461.56</v>
+        <v>25857.89</v>
       </c>
       <c r="N40" t="n">
-        <v>26768.76</v>
+        <v>26115.98</v>
       </c>
       <c r="O40" t="n">
-        <v>27842.45</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>26349.19</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3908,73 +3904,69 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25622.36</v>
+        <v>25180.05</v>
       </c>
       <c r="C41" t="n">
-        <v>25768.38</v>
+        <v>26045.07</v>
       </c>
       <c r="D41" t="n">
-        <v>24727.26</v>
+        <v>24928.14</v>
       </c>
       <c r="E41" t="n">
-        <v>25182.39</v>
+        <v>24961.95</v>
       </c>
       <c r="F41" t="n">
-        <v>-423.64</v>
+        <v>-220.44</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0165</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>1041.12</v>
+        <v>1116.93</v>
       </c>
       <c r="I41" t="n">
-        <v>24838</v>
+        <v>23686.14</v>
       </c>
       <c r="J41" t="n">
-        <v>25108.52</v>
+        <v>24108.55</v>
       </c>
       <c r="K41" t="n">
-        <v>25354.16</v>
+        <v>24661.83</v>
       </c>
       <c r="L41" t="n">
-        <v>25599.81</v>
+        <v>25215.11</v>
       </c>
       <c r="M41" t="n">
-        <v>25857.89</v>
+        <v>25702.95</v>
       </c>
       <c r="N41" t="n">
-        <v>26115.98</v>
+        <v>26190.8</v>
       </c>
       <c r="O41" t="n">
-        <v>26349.19</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+        <v>26809.5</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3989,57 +3981,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25180.05</v>
+        <v>24582.91</v>
       </c>
       <c r="C42" t="n">
-        <v>26045.07</v>
+        <v>24837.98</v>
       </c>
       <c r="D42" t="n">
-        <v>24928.14</v>
+        <v>23999.67</v>
       </c>
       <c r="E42" t="n">
-        <v>24961.95</v>
+        <v>24718.1</v>
       </c>
       <c r="F42" t="n">
-        <v>-220.44</v>
+        <v>-243.85</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="H42" t="n">
-        <v>1116.93</v>
+        <v>838.3099999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>23686.14</v>
+        <v>23811.21</v>
       </c>
       <c r="J42" t="n">
-        <v>24108.55</v>
+        <v>23582.69</v>
       </c>
       <c r="K42" t="n">
-        <v>24661.83</v>
+        <v>24403.48</v>
       </c>
       <c r="L42" t="n">
-        <v>25215.11</v>
+        <v>25224.28</v>
       </c>
       <c r="M42" t="n">
-        <v>25702.95</v>
+        <v>25520.41</v>
       </c>
       <c r="N42" t="n">
-        <v>26190.8</v>
+        <v>25816.55</v>
       </c>
       <c r="O42" t="n">
-        <v>26809.5</v>
+        <v>27162</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4047,18 +4039,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4073,70 +4065,72 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24582.91</v>
+        <v>25001.42</v>
       </c>
       <c r="C43" t="n">
-        <v>24837.98</v>
+        <v>25047.9</v>
       </c>
       <c r="D43" t="n">
-        <v>23999.67</v>
+        <v>23749.99</v>
       </c>
       <c r="E43" t="n">
-        <v>24718.1</v>
+        <v>23924.81</v>
       </c>
       <c r="F43" t="n">
-        <v>-243.85</v>
+        <v>-793.29</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0321</v>
       </c>
       <c r="H43" t="n">
-        <v>838.3099999999999</v>
+        <v>1297.91</v>
       </c>
       <c r="I43" t="n">
-        <v>23811.21</v>
+        <v>23161.36</v>
       </c>
       <c r="J43" t="n">
-        <v>23582.69</v>
+        <v>24029.43</v>
       </c>
       <c r="K43" t="n">
-        <v>24403.48</v>
+        <v>24298.94</v>
       </c>
       <c r="L43" t="n">
-        <v>25224.28</v>
+        <v>24568.46</v>
       </c>
       <c r="M43" t="n">
-        <v>25520.41</v>
+        <v>25137.25</v>
       </c>
       <c r="N43" t="n">
-        <v>25816.55</v>
+        <v>25706.05</v>
       </c>
       <c r="O43" t="n">
-        <v>27162</v>
+        <v>25676.29</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4150,79 +4144,79 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25001.42</v>
+        <v>23811.76</v>
       </c>
       <c r="C44" t="n">
-        <v>25047.9</v>
+        <v>23863.71</v>
       </c>
       <c r="D44" t="n">
-        <v>23749.99</v>
+        <v>22518</v>
       </c>
       <c r="E44" t="n">
-        <v>23924.81</v>
+        <v>22671.86</v>
       </c>
       <c r="F44" t="n">
-        <v>-793.29</v>
+        <v>-1252.95</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0524</v>
       </c>
       <c r="H44" t="n">
-        <v>1297.91</v>
+        <v>1345.71</v>
       </c>
       <c r="I44" t="n">
-        <v>23161.36</v>
+        <v>22452.08</v>
       </c>
       <c r="J44" t="n">
-        <v>24029.43</v>
+        <v>22389.83</v>
       </c>
       <c r="K44" t="n">
-        <v>24298.94</v>
+        <v>23275.86</v>
       </c>
       <c r="L44" t="n">
-        <v>24568.46</v>
+        <v>24161.88</v>
       </c>
       <c r="M44" t="n">
-        <v>25137.25</v>
+        <v>24573.77</v>
       </c>
       <c r="N44" t="n">
-        <v>25706.05</v>
+        <v>24985.65</v>
       </c>
       <c r="O44" t="n">
-        <v>25676.29</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>26345.81</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4241,81 +4235,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23811.76</v>
+        <v>22827.65</v>
       </c>
       <c r="C45" t="n">
-        <v>23863.71</v>
+        <v>23516.7</v>
       </c>
       <c r="D45" t="n">
-        <v>22518</v>
+        <v>22685.14</v>
       </c>
       <c r="E45" t="n">
-        <v>22671.86</v>
+        <v>23350.03</v>
       </c>
       <c r="F45" t="n">
-        <v>-1252.95</v>
+        <v>678.17</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0524</v>
+        <v>0.0299</v>
       </c>
       <c r="H45" t="n">
-        <v>1345.71</v>
+        <v>831.5599999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>22452.08</v>
+        <v>21172.29</v>
       </c>
       <c r="J45" t="n">
-        <v>22389.83</v>
+        <v>21066.65</v>
       </c>
       <c r="K45" t="n">
-        <v>23275.86</v>
+        <v>21999</v>
       </c>
       <c r="L45" t="n">
-        <v>24161.88</v>
+        <v>22931.36</v>
       </c>
       <c r="M45" t="n">
-        <v>24573.77</v>
+        <v>23344.71</v>
       </c>
       <c r="N45" t="n">
-        <v>24985.65</v>
+        <v>23758.07</v>
       </c>
       <c r="O45" t="n">
-        <v>26345.81</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
+        <v>25209.42</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4327,55 +4315,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22827.65</v>
+        <v>23404.61</v>
       </c>
       <c r="C46" t="n">
-        <v>23516.7</v>
+        <v>24499.63</v>
       </c>
       <c r="D46" t="n">
-        <v>22685.14</v>
+        <v>23229.38</v>
       </c>
       <c r="E46" t="n">
-        <v>23350.03</v>
+        <v>24175.12</v>
       </c>
       <c r="F46" t="n">
-        <v>678.17</v>
+        <v>825.09</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0353</v>
       </c>
       <c r="H46" t="n">
-        <v>831.5599999999999</v>
+        <v>1270.25</v>
       </c>
       <c r="I46" t="n">
-        <v>21172.29</v>
+        <v>21853.58</v>
       </c>
       <c r="J46" t="n">
-        <v>21066.65</v>
+        <v>22643.03</v>
       </c>
       <c r="K46" t="n">
-        <v>21999</v>
+        <v>22934.25</v>
       </c>
       <c r="L46" t="n">
-        <v>22931.36</v>
+        <v>23225.47</v>
       </c>
       <c r="M46" t="n">
-        <v>23344.71</v>
+        <v>23765.81</v>
       </c>
       <c r="N46" t="n">
-        <v>23758.07</v>
+        <v>24306.14</v>
       </c>
       <c r="O46" t="n">
-        <v>25209.42</v>
+        <v>24348.26</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4386,21 +4378,25 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W46" s="11" t="inlineStr">
         <is>
@@ -4409,57 +4405,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23404.61</v>
+        <v>24157.65</v>
       </c>
       <c r="C47" t="n">
-        <v>24499.63</v>
+        <v>25221.44</v>
       </c>
       <c r="D47" t="n">
-        <v>23229.38</v>
+        <v>23902.05</v>
       </c>
       <c r="E47" t="n">
-        <v>24175.12</v>
+        <v>24562.24</v>
       </c>
       <c r="F47" t="n">
-        <v>825.09</v>
+        <v>387.12</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.016</v>
       </c>
       <c r="H47" t="n">
-        <v>1270.25</v>
+        <v>1319.39</v>
       </c>
       <c r="I47" t="n">
-        <v>21853.58</v>
+        <v>21959.13</v>
       </c>
       <c r="J47" t="n">
-        <v>22643.03</v>
+        <v>23060.18</v>
       </c>
       <c r="K47" t="n">
-        <v>22934.25</v>
+        <v>23539.99</v>
       </c>
       <c r="L47" t="n">
-        <v>23225.47</v>
+        <v>24019.81</v>
       </c>
       <c r="M47" t="n">
-        <v>23765.81</v>
+        <v>24810.24</v>
       </c>
       <c r="N47" t="n">
-        <v>24306.14</v>
+        <v>25600.68</v>
       </c>
       <c r="O47" t="n">
-        <v>24348.26</v>
+        <v>25769.88</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4470,25 +4466,21 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
@@ -4504,50 +4496,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24157.65</v>
+        <v>24835.03</v>
       </c>
       <c r="C48" t="n">
-        <v>25221.44</v>
+        <v>25267.39</v>
       </c>
       <c r="D48" t="n">
-        <v>23902.05</v>
+        <v>24756.36</v>
       </c>
       <c r="E48" t="n">
-        <v>24562.24</v>
+        <v>24963.23</v>
       </c>
       <c r="F48" t="n">
-        <v>387.12</v>
+        <v>400.99</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
       </c>
       <c r="H48" t="n">
-        <v>1319.39</v>
+        <v>511.03</v>
       </c>
       <c r="I48" t="n">
-        <v>21959.13</v>
+        <v>22582.66</v>
       </c>
       <c r="J48" t="n">
-        <v>23060.18</v>
+        <v>23243.1</v>
       </c>
       <c r="K48" t="n">
-        <v>23539.99</v>
+        <v>23902.55</v>
       </c>
       <c r="L48" t="n">
-        <v>24019.81</v>
+        <v>24561.99</v>
       </c>
       <c r="M48" t="n">
-        <v>24810.24</v>
+        <v>25221.93</v>
       </c>
       <c r="N48" t="n">
-        <v>25600.68</v>
+        <v>25881.88</v>
       </c>
       <c r="O48" t="n">
-        <v>25769.88</v>
+        <v>26540.83</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4558,7 +4550,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4588,50 +4580,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24835.03</v>
+        <v>24993.77</v>
       </c>
       <c r="C49" t="n">
-        <v>25267.39</v>
+        <v>25971.63</v>
       </c>
       <c r="D49" t="n">
-        <v>24756.36</v>
+        <v>24938.34</v>
       </c>
       <c r="E49" t="n">
-        <v>24963.23</v>
+        <v>25884.43</v>
       </c>
       <c r="F49" t="n">
-        <v>400.99</v>
+        <v>921.2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0369</v>
       </c>
       <c r="H49" t="n">
-        <v>511.03</v>
+        <v>1033.29</v>
       </c>
       <c r="I49" t="n">
-        <v>22582.66</v>
+        <v>24245.33</v>
       </c>
       <c r="J49" t="n">
-        <v>23243.1</v>
+        <v>24427.88</v>
       </c>
       <c r="K49" t="n">
-        <v>23902.55</v>
+        <v>24707.71</v>
       </c>
       <c r="L49" t="n">
-        <v>24561.99</v>
+        <v>24987.55</v>
       </c>
       <c r="M49" t="n">
-        <v>25221.93</v>
+        <v>25218.75</v>
       </c>
       <c r="N49" t="n">
-        <v>25881.88</v>
+        <v>25449.94</v>
       </c>
       <c r="O49" t="n">
-        <v>26540.83</v>
+        <v>25778.42</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4642,80 +4634,80 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24993.77</v>
+        <v>25987.31</v>
       </c>
       <c r="C50" t="n">
-        <v>25971.63</v>
+        <v>26187.57</v>
       </c>
       <c r="D50" t="n">
-        <v>24938.34</v>
+        <v>25389.42</v>
       </c>
       <c r="E50" t="n">
-        <v>25884.43</v>
+        <v>25668.03</v>
       </c>
       <c r="F50" t="n">
-        <v>921.2</v>
+        <v>-216.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0369</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>1033.29</v>
+        <v>798.15</v>
       </c>
       <c r="I50" t="n">
-        <v>24245.33</v>
+        <v>23905.05</v>
       </c>
       <c r="J50" t="n">
-        <v>24427.88</v>
+        <v>25065.86</v>
       </c>
       <c r="K50" t="n">
-        <v>24707.71</v>
+        <v>25367.78</v>
       </c>
       <c r="L50" t="n">
-        <v>24987.55</v>
+        <v>25669.71</v>
       </c>
       <c r="M50" t="n">
-        <v>25218.75</v>
+        <v>26401.08</v>
       </c>
       <c r="N50" t="n">
-        <v>25449.94</v>
+        <v>27132.44</v>
       </c>
       <c r="O50" t="n">
-        <v>25778.42</v>
+        <v>27004.92</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4728,78 +4720,76 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25987.31</v>
+        <v>25805.18</v>
       </c>
       <c r="C51" t="n">
-        <v>26187.57</v>
+        <v>26060.32</v>
       </c>
       <c r="D51" t="n">
-        <v>25389.42</v>
+        <v>25089.14</v>
       </c>
       <c r="E51" t="n">
-        <v>25668.03</v>
+        <v>25116.85</v>
       </c>
       <c r="F51" t="n">
-        <v>-216.4</v>
+        <v>-551.1799999999999</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0215</v>
       </c>
       <c r="H51" t="n">
-        <v>798.15</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>23905.05</v>
+        <v>24591.27</v>
       </c>
       <c r="J51" t="n">
-        <v>25065.86</v>
+        <v>24809.65</v>
       </c>
       <c r="K51" t="n">
-        <v>25367.78</v>
+        <v>25268.95</v>
       </c>
       <c r="L51" t="n">
-        <v>25669.71</v>
+        <v>25728.26</v>
       </c>
       <c r="M51" t="n">
-        <v>26401.08</v>
+        <v>26067.1</v>
       </c>
       <c r="N51" t="n">
-        <v>27132.44</v>
+        <v>26405.95</v>
       </c>
       <c r="O51" t="n">
-        <v>27004.92</v>
+        <v>26985.72</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4807,12 +4797,14 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4831,57 +4823,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25805.18</v>
+        <v>25303.41</v>
       </c>
       <c r="C52" t="n">
-        <v>26060.32</v>
+        <v>26009.46</v>
       </c>
       <c r="D52" t="n">
-        <v>25089.14</v>
+        <v>25240.62</v>
       </c>
       <c r="E52" t="n">
-        <v>25116.85</v>
+        <v>26009.46</v>
       </c>
       <c r="F52" t="n">
-        <v>-551.1799999999999</v>
+        <v>892.61</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0215</v>
+        <v>0.0355</v>
       </c>
       <c r="H52" t="n">
-        <v>971.1799999999999</v>
+        <v>768.84</v>
       </c>
       <c r="I52" t="n">
-        <v>24591.27</v>
+        <v>24117.96</v>
       </c>
       <c r="J52" t="n">
-        <v>24809.65</v>
+        <v>23916.73</v>
       </c>
       <c r="K52" t="n">
-        <v>25268.95</v>
+        <v>24631.26</v>
       </c>
       <c r="L52" t="n">
-        <v>25728.26</v>
+        <v>25345.79</v>
       </c>
       <c r="M52" t="n">
-        <v>26067.1</v>
+        <v>25602.44</v>
       </c>
       <c r="N52" t="n">
-        <v>26405.95</v>
+        <v>25859.09</v>
       </c>
       <c r="O52" t="n">
-        <v>26985.72</v>
+        <v>27031.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4889,22 +4881,24 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4915,81 +4909,81 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25303.41</v>
+        <v>25780.12</v>
       </c>
       <c r="C53" t="n">
-        <v>26009.46</v>
+        <v>25800.22</v>
       </c>
       <c r="D53" t="n">
-        <v>25240.62</v>
+        <v>25403.44</v>
       </c>
       <c r="E53" t="n">
-        <v>26009.46</v>
+        <v>25584.79</v>
       </c>
       <c r="F53" t="n">
-        <v>892.61</v>
+        <v>-424.67</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0355</v>
+        <v>-0.0163</v>
       </c>
       <c r="H53" t="n">
-        <v>768.84</v>
+        <v>396.78</v>
       </c>
       <c r="I53" t="n">
-        <v>24117.96</v>
+        <v>24471.78</v>
       </c>
       <c r="J53" t="n">
-        <v>23916.73</v>
+        <v>25432.83</v>
       </c>
       <c r="K53" t="n">
-        <v>24631.26</v>
+        <v>25625.04</v>
       </c>
       <c r="L53" t="n">
-        <v>25345.79</v>
+        <v>25817.25</v>
       </c>
       <c r="M53" t="n">
-        <v>25602.44</v>
+        <v>26393.88</v>
       </c>
       <c r="N53" t="n">
-        <v>25859.09</v>
+        <v>26970.51</v>
       </c>
       <c r="O53" t="n">
-        <v>27031.5</v>
+        <v>26778.3</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -5001,57 +4995,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25780.12</v>
+        <v>25420.63</v>
       </c>
       <c r="C54" t="n">
-        <v>25800.22</v>
+        <v>25791.38</v>
       </c>
       <c r="D54" t="n">
-        <v>25403.44</v>
+        <v>25008.87</v>
       </c>
       <c r="E54" t="n">
-        <v>25584.79</v>
+        <v>25650.87</v>
       </c>
       <c r="F54" t="n">
-        <v>-424.67</v>
+        <v>66.08</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0163</v>
+        <v>0.0026</v>
       </c>
       <c r="H54" t="n">
-        <v>396.78</v>
+        <v>782.51</v>
       </c>
       <c r="I54" t="n">
-        <v>24471.78</v>
+        <v>25006.66</v>
       </c>
       <c r="J54" t="n">
-        <v>25432.83</v>
+        <v>25179.49</v>
       </c>
       <c r="K54" t="n">
-        <v>25625.04</v>
+        <v>25386.4</v>
       </c>
       <c r="L54" t="n">
-        <v>25817.25</v>
+        <v>25593.31</v>
       </c>
       <c r="M54" t="n">
-        <v>26393.88</v>
+        <v>25783.18</v>
       </c>
       <c r="N54" t="n">
-        <v>26970.51</v>
+        <v>25973.05</v>
       </c>
       <c r="O54" t="n">
-        <v>26778.3</v>
+        <v>26197</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5063,16 +5057,18 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5094,57 +5090,57 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25420.63</v>
+        <v>25652.97</v>
       </c>
       <c r="C55" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D55" t="n">
-        <v>25008.87</v>
+        <v>24570.24</v>
       </c>
       <c r="E55" t="n">
-        <v>25650.87</v>
+        <v>24805.63</v>
       </c>
       <c r="F55" t="n">
-        <v>66.08</v>
+        <v>-845.24</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.033</v>
       </c>
       <c r="H55" t="n">
-        <v>782.51</v>
+        <v>1094.74</v>
       </c>
       <c r="I55" t="n">
-        <v>25006.66</v>
+        <v>24226.36</v>
       </c>
       <c r="J55" t="n">
-        <v>25179.49</v>
+        <v>24993.73</v>
       </c>
       <c r="K55" t="n">
-        <v>25386.4</v>
+        <v>25259.61</v>
       </c>
       <c r="L55" t="n">
-        <v>25593.31</v>
+        <v>25525.5</v>
       </c>
       <c r="M55" t="n">
-        <v>25783.18</v>
+        <v>26042.12</v>
       </c>
       <c r="N55" t="n">
-        <v>25973.05</v>
+        <v>26558.75</v>
       </c>
       <c r="O55" t="n">
-        <v>26197</v>
+        <v>26573.89</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -5154,13 +5150,11 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5168,81 +5162,73 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25652.97</v>
+        <v>24701.18</v>
       </c>
       <c r="C56" t="n">
-        <v>25664.98</v>
+        <v>24934.06</v>
       </c>
       <c r="D56" t="n">
-        <v>24570.24</v>
+        <v>24357.69</v>
       </c>
       <c r="E56" t="n">
-        <v>24805.63</v>
+        <v>24750.78</v>
       </c>
       <c r="F56" t="n">
-        <v>-845.24</v>
+        <v>-54.85</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.0022</v>
       </c>
       <c r="H56" t="n">
-        <v>1094.74</v>
+        <v>576.37</v>
       </c>
       <c r="I56" t="n">
-        <v>24226.36</v>
+        <v>23475.5</v>
       </c>
       <c r="J56" t="n">
-        <v>24993.73</v>
+        <v>23554.9</v>
       </c>
       <c r="K56" t="n">
-        <v>25259.61</v>
+        <v>24258.26</v>
       </c>
       <c r="L56" t="n">
-        <v>25525.5</v>
+        <v>24961.62</v>
       </c>
       <c r="M56" t="n">
-        <v>26042.12</v>
+        <v>25353</v>
       </c>
       <c r="N56" t="n">
-        <v>26558.75</v>
+        <v>25744.38</v>
       </c>
       <c r="O56" t="n">
-        <v>26573.89</v>
+        <v>26759.72</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5264,50 +5250,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24701.18</v>
+        <v>24748.45</v>
       </c>
       <c r="C57" t="n">
-        <v>24934.06</v>
+        <v>25254.11</v>
       </c>
       <c r="D57" t="n">
-        <v>24357.69</v>
+        <v>24275.56</v>
       </c>
       <c r="E57" t="n">
-        <v>24750.78</v>
+        <v>24510.09</v>
       </c>
       <c r="F57" t="n">
-        <v>-54.85</v>
+        <v>-240.69</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0097</v>
       </c>
       <c r="H57" t="n">
-        <v>576.37</v>
+        <v>978.55</v>
       </c>
       <c r="I57" t="n">
-        <v>23475.5</v>
+        <v>23781.32</v>
       </c>
       <c r="J57" t="n">
-        <v>23554.9</v>
+        <v>24226.86</v>
       </c>
       <c r="K57" t="n">
-        <v>24258.26</v>
+        <v>24462.59</v>
       </c>
       <c r="L57" t="n">
-        <v>24961.62</v>
+        <v>24698.33</v>
       </c>
       <c r="M57" t="n">
-        <v>25353</v>
+        <v>25038.96</v>
       </c>
       <c r="N57" t="n">
-        <v>25744.38</v>
+        <v>25379.6</v>
       </c>
       <c r="O57" t="n">
-        <v>26759.72</v>
+        <v>25510.43</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5315,16 +5301,20 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5337,89 +5327,9 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>24748.45</v>
-      </c>
-      <c r="C58" t="n">
-        <v>25072.25</v>
-      </c>
-      <c r="D58" t="n">
-        <v>24648.29</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24761.13</v>
-      </c>
-      <c r="F58" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="H58" t="n">
-        <v>423.96</v>
-      </c>
-      <c r="I58" t="n">
-        <v>23781.32</v>
-      </c>
-      <c r="J58" t="n">
-        <v>24226.86</v>
-      </c>
-      <c r="K58" t="n">
-        <v>24462.59</v>
-      </c>
-      <c r="L58" t="n">
-        <v>24698.33</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25038.96</v>
-      </c>
-      <c r="N58" t="n">
-        <v>25379.6</v>
-      </c>
-      <c r="O58" t="n">
-        <v>25510.43</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5333,6 +5336,90 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>24554.58</v>
+      </c>
+      <c r="C58" t="n">
+        <v>24767.22</v>
+      </c>
+      <c r="D58" t="n">
+        <v>24554.58</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>212.64</v>
+      </c>
+      <c r="I58" t="n">
+        <v>23297.01</v>
+      </c>
+      <c r="J58" t="n">
+        <v>23404.17</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24020.82</v>
+      </c>
+      <c r="L58" t="n">
+        <v>24637.46</v>
+      </c>
+      <c r="M58" t="n">
+        <v>24999.36</v>
+      </c>
+      <c r="N58" t="n">
+        <v>25361.27</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26232.66</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>776.73</v>
       </c>
       <c r="I2" t="n">
-        <v>23698.7</v>
+        <v>23797.86</v>
       </c>
       <c r="J2" t="n">
-        <v>23824.44</v>
+        <v>23948.39</v>
       </c>
       <c r="K2" t="n">
-        <v>24522.58</v>
+        <v>24572.16</v>
       </c>
       <c r="L2" t="n">
-        <v>25220.72</v>
+        <v>25195.93</v>
       </c>
       <c r="M2" t="n">
-        <v>25632.66</v>
+        <v>25583.08</v>
       </c>
       <c r="N2" t="n">
-        <v>26044.6</v>
+        <v>25970.23</v>
       </c>
       <c r="O2" t="n">
-        <v>27028.94</v>
+        <v>26830.62</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,12 +690,12 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -5349,19 +5346,19 @@
         <v>24767.22</v>
       </c>
       <c r="D58" t="n">
-        <v>24554.58</v>
+        <v>24444.15</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>24523.57</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>13.48</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0005</v>
       </c>
       <c r="H58" t="n">
-        <v>212.64</v>
+        <v>323.07</v>
       </c>
       <c r="I58" t="n">
         <v>23297.01</v>
@@ -5384,10 +5381,8 @@
       <c r="O58" t="n">
         <v>26232.66</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5395,9 +5390,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5416,7 +5411,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>776.73</v>
       </c>
       <c r="I2" t="n">
-        <v>23797.86</v>
+        <v>23963.64</v>
       </c>
       <c r="J2" t="n">
-        <v>23948.39</v>
+        <v>24155.61</v>
       </c>
       <c r="K2" t="n">
-        <v>24572.16</v>
+        <v>24655.05</v>
       </c>
       <c r="L2" t="n">
-        <v>25195.93</v>
+        <v>25154.48</v>
       </c>
       <c r="M2" t="n">
-        <v>25583.08</v>
+        <v>25500.19</v>
       </c>
       <c r="N2" t="n">
-        <v>25970.23</v>
+        <v>25845.89</v>
       </c>
       <c r="O2" t="n">
-        <v>26830.62</v>
+        <v>26499.06</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -709,11 +709,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5346,19 +5342,19 @@
         <v>24767.22</v>
       </c>
       <c r="D58" t="n">
-        <v>24444.15</v>
+        <v>24332.64</v>
       </c>
       <c r="E58" t="n">
-        <v>24523.57</v>
+        <v>24613.27</v>
       </c>
       <c r="F58" t="n">
-        <v>13.48</v>
+        <v>103.18</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0042</v>
       </c>
       <c r="H58" t="n">
-        <v>323.07</v>
+        <v>434.58</v>
       </c>
       <c r="I58" t="n">
         <v>23297.01</v>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>776.73</v>
       </c>
       <c r="I2" t="n">
-        <v>23963.64</v>
+        <v>24340.05</v>
       </c>
       <c r="J2" t="n">
-        <v>24155.61</v>
+        <v>24626.13</v>
       </c>
       <c r="K2" t="n">
-        <v>24655.05</v>
+        <v>24843.25</v>
       </c>
       <c r="L2" t="n">
-        <v>25154.48</v>
+        <v>25060.38</v>
       </c>
       <c r="M2" t="n">
-        <v>25500.19</v>
+        <v>25311.98</v>
       </c>
       <c r="N2" t="n">
-        <v>25845.89</v>
+        <v>25563.59</v>
       </c>
       <c r="O2" t="n">
-        <v>26499.06</v>
+        <v>25746.24</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,11 +698,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25508.21</v>
+        <v>25440.01</v>
       </c>
       <c r="C2" t="n">
-        <v>25789.99</v>
+        <v>26585.95</v>
       </c>
       <c r="D2" t="n">
-        <v>25013.26</v>
+        <v>25387.81</v>
       </c>
       <c r="E2" t="n">
-        <v>25417.98</v>
+        <v>26388.16</v>
       </c>
       <c r="F2" t="n">
-        <v>340.36</v>
+        <v>970.1799999999999</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0382</v>
       </c>
       <c r="H2" t="n">
-        <v>776.73</v>
+        <v>1198.14</v>
       </c>
       <c r="I2" t="n">
-        <v>24340.05</v>
+        <v>24236.53</v>
       </c>
       <c r="J2" t="n">
-        <v>24626.13</v>
+        <v>24649.43</v>
       </c>
       <c r="K2" t="n">
-        <v>24843.25</v>
+        <v>25029.62</v>
       </c>
       <c r="L2" t="n">
-        <v>25060.38</v>
+        <v>25409.8</v>
       </c>
       <c r="M2" t="n">
-        <v>25311.98</v>
+        <v>25806.35</v>
       </c>
       <c r="N2" t="n">
-        <v>25563.59</v>
+        <v>26202.89</v>
       </c>
       <c r="O2" t="n">
-        <v>25746.24</v>
+        <v>26566.72</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,17 +695,17 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -718,50 +718,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25440.01</v>
+        <v>26308.91</v>
       </c>
       <c r="C3" t="n">
-        <v>26585.95</v>
+        <v>27058.03</v>
       </c>
       <c r="D3" t="n">
-        <v>25387.81</v>
+        <v>26280.23</v>
       </c>
       <c r="E3" t="n">
-        <v>26388.16</v>
+        <v>26545.1</v>
       </c>
       <c r="F3" t="n">
-        <v>970.1799999999999</v>
+        <v>156.94</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.0059</v>
       </c>
       <c r="H3" t="n">
-        <v>1198.14</v>
+        <v>777.8</v>
       </c>
       <c r="I3" t="n">
-        <v>24236.53</v>
+        <v>24189.67</v>
       </c>
       <c r="J3" t="n">
-        <v>24649.43</v>
+        <v>25390.66</v>
       </c>
       <c r="K3" t="n">
-        <v>25029.62</v>
+        <v>25789.09</v>
       </c>
       <c r="L3" t="n">
-        <v>25409.8</v>
+        <v>26187.52</v>
       </c>
       <c r="M3" t="n">
-        <v>25806.35</v>
+        <v>26987.23</v>
       </c>
       <c r="N3" t="n">
-        <v>26202.89</v>
+        <v>27786.94</v>
       </c>
       <c r="O3" t="n">
-        <v>26566.72</v>
+        <v>27784.09</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,7 +774,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -782,15 +782,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -802,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26308.91</v>
+        <v>26459.52</v>
       </c>
       <c r="C4" t="n">
-        <v>27058.03</v>
+        <v>26640.53</v>
       </c>
       <c r="D4" t="n">
-        <v>26280.23</v>
+        <v>26003.67</v>
       </c>
       <c r="E4" t="n">
-        <v>26545.1</v>
+        <v>26128.2</v>
       </c>
       <c r="F4" t="n">
-        <v>156.94</v>
+        <v>-416.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0157</v>
       </c>
       <c r="H4" t="n">
-        <v>777.8</v>
+        <v>636.86</v>
       </c>
       <c r="I4" t="n">
-        <v>24189.67</v>
+        <v>25502.43</v>
       </c>
       <c r="J4" t="n">
-        <v>25390.66</v>
+        <v>25705.29</v>
       </c>
       <c r="K4" t="n">
-        <v>25789.09</v>
+        <v>26156.2</v>
       </c>
       <c r="L4" t="n">
-        <v>26187.52</v>
+        <v>26607.11</v>
       </c>
       <c r="M4" t="n">
-        <v>26987.23</v>
+        <v>26934</v>
       </c>
       <c r="N4" t="n">
-        <v>27786.94</v>
+        <v>27260.88</v>
       </c>
       <c r="O4" t="n">
-        <v>27784.09</v>
+        <v>27835.83</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,18 +849,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -877,55 +873,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26459.52</v>
+        <v>26321.57</v>
       </c>
       <c r="C5" t="n">
-        <v>26640.53</v>
+        <v>27381.84</v>
       </c>
       <c r="D5" t="n">
-        <v>26003.67</v>
+        <v>26321.57</v>
       </c>
       <c r="E5" t="n">
-        <v>26128.2</v>
+        <v>27140.92</v>
       </c>
       <c r="F5" t="n">
-        <v>-416.9</v>
+        <v>1012.72</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0388</v>
       </c>
       <c r="H5" t="n">
-        <v>636.86</v>
+        <v>1060.27</v>
       </c>
       <c r="I5" t="n">
-        <v>25502.43</v>
+        <v>25366.81</v>
       </c>
       <c r="J5" t="n">
-        <v>25705.29</v>
+        <v>25394.39</v>
       </c>
       <c r="K5" t="n">
-        <v>26156.2</v>
+        <v>25809.77</v>
       </c>
       <c r="L5" t="n">
-        <v>26607.11</v>
+        <v>26225.15</v>
       </c>
       <c r="M5" t="n">
-        <v>26934</v>
+        <v>26446.63</v>
       </c>
       <c r="N5" t="n">
-        <v>27260.88</v>
+        <v>26668.11</v>
       </c>
       <c r="O5" t="n">
-        <v>27835.83</v>
+        <v>27277.39</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,170 +933,174 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26321.57</v>
+        <v>27003.92</v>
       </c>
       <c r="C6" t="n">
-        <v>27381.84</v>
+        <v>27145.17</v>
       </c>
       <c r="D6" t="n">
-        <v>26321.57</v>
+        <v>26247.04</v>
       </c>
       <c r="E6" t="n">
-        <v>27140.92</v>
+        <v>26290.32</v>
       </c>
       <c r="F6" t="n">
-        <v>1012.72</v>
+        <v>-850.6</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0388</v>
+        <v>-0.0313</v>
       </c>
       <c r="H6" t="n">
-        <v>1060.27</v>
+        <v>898.13</v>
       </c>
       <c r="I6" t="n">
-        <v>25366.81</v>
+        <v>25261.3</v>
       </c>
       <c r="J6" t="n">
-        <v>25394.39</v>
+        <v>26225.26</v>
       </c>
       <c r="K6" t="n">
-        <v>25809.77</v>
+        <v>26610.79</v>
       </c>
       <c r="L6" t="n">
-        <v>26225.15</v>
+        <v>26996.31</v>
       </c>
       <c r="M6" t="n">
-        <v>26446.63</v>
+        <v>27671.05</v>
       </c>
       <c r="N6" t="n">
-        <v>26668.11</v>
+        <v>28345.8</v>
       </c>
       <c r="O6" t="n">
-        <v>27277.39</v>
+        <v>28442.11</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27003.92</v>
+        <v>25634</v>
       </c>
       <c r="C7" t="n">
-        <v>27145.17</v>
+        <v>26102.68</v>
       </c>
       <c r="D7" t="n">
-        <v>26247.04</v>
+        <v>25145.34</v>
       </c>
       <c r="E7" t="n">
-        <v>26290.32</v>
+        <v>25247.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-850.6</v>
+        <v>-1043.22</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0397</v>
       </c>
       <c r="H7" t="n">
-        <v>898.13</v>
+        <v>957.34</v>
       </c>
       <c r="I7" t="n">
-        <v>25261.3</v>
+        <v>25348.91</v>
       </c>
       <c r="J7" t="n">
-        <v>26225.26</v>
+        <v>25189.3</v>
       </c>
       <c r="K7" t="n">
-        <v>26610.79</v>
+        <v>25841.25</v>
       </c>
       <c r="L7" t="n">
-        <v>26996.31</v>
+        <v>26493.21</v>
       </c>
       <c r="M7" t="n">
-        <v>27671.05</v>
+        <v>26739.39</v>
       </c>
       <c r="N7" t="n">
-        <v>28345.8</v>
+        <v>26985.56</v>
       </c>
       <c r="O7" t="n">
-        <v>28442.11</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
+        <v>28043.3</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
@@ -1136,77 +1140,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25634</v>
+        <v>25884.46</v>
       </c>
       <c r="C8" t="n">
-        <v>26102.68</v>
+        <v>26367.35</v>
       </c>
       <c r="D8" t="n">
-        <v>25145.34</v>
+        <v>25591.66</v>
       </c>
       <c r="E8" t="n">
-        <v>25247.1</v>
+        <v>26160.15</v>
       </c>
       <c r="F8" t="n">
-        <v>-1043.22</v>
+        <v>913.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0362</v>
       </c>
       <c r="H8" t="n">
-        <v>957.34</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>25348.91</v>
+        <v>24188</v>
       </c>
       <c r="J8" t="n">
-        <v>25189.3</v>
+        <v>24101.3</v>
       </c>
       <c r="K8" t="n">
-        <v>25841.25</v>
+        <v>24768.43</v>
       </c>
       <c r="L8" t="n">
-        <v>26493.21</v>
+        <v>25435.55</v>
       </c>
       <c r="M8" t="n">
-        <v>26739.39</v>
+        <v>25725.77</v>
       </c>
       <c r="N8" t="n">
-        <v>26985.56</v>
+        <v>26015.98</v>
       </c>
       <c r="O8" t="n">
-        <v>28043.3</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>27060.02</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1215,59 +1217,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25884.46</v>
+        <v>26495.97</v>
       </c>
       <c r="C9" t="n">
-        <v>26367.35</v>
+        <v>26588.89</v>
       </c>
       <c r="D9" t="n">
-        <v>25591.66</v>
+        <v>25906.65</v>
       </c>
       <c r="E9" t="n">
-        <v>26160.15</v>
+        <v>25906.65</v>
       </c>
       <c r="F9" t="n">
-        <v>913.05</v>
+        <v>-253.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0362</v>
+        <v>-0.0097</v>
       </c>
       <c r="H9" t="n">
-        <v>775.6900000000001</v>
+        <v>682.24</v>
       </c>
       <c r="I9" t="n">
-        <v>24188</v>
+        <v>24815.97</v>
       </c>
       <c r="J9" t="n">
-        <v>24101.3</v>
+        <v>25474.78</v>
       </c>
       <c r="K9" t="n">
-        <v>24768.43</v>
+        <v>25772.31</v>
       </c>
       <c r="L9" t="n">
-        <v>25435.55</v>
+        <v>26069.83</v>
       </c>
       <c r="M9" t="n">
-        <v>25725.77</v>
+        <v>26548</v>
       </c>
       <c r="N9" t="n">
-        <v>26015.98</v>
+        <v>27026.16</v>
       </c>
       <c r="O9" t="n">
-        <v>27060.02</v>
+        <v>27143.04</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,12 +1273,14 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
@@ -1288,10 +1288,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1301,55 +1299,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26495.97</v>
+        <v>25999.17</v>
       </c>
       <c r="C10" t="n">
-        <v>26588.89</v>
+        <v>26490.71</v>
       </c>
       <c r="D10" t="n">
-        <v>25906.65</v>
+        <v>25496.13</v>
       </c>
       <c r="E10" t="n">
-        <v>25906.65</v>
+        <v>26241.83</v>
       </c>
       <c r="F10" t="n">
-        <v>-253.5</v>
+        <v>335.18</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0129</v>
       </c>
       <c r="H10" t="n">
-        <v>682.24</v>
+        <v>994.58</v>
       </c>
       <c r="I10" t="n">
-        <v>24815.97</v>
+        <v>25224.41</v>
       </c>
       <c r="J10" t="n">
-        <v>25474.78</v>
+        <v>25053.85</v>
       </c>
       <c r="K10" t="n">
-        <v>25772.31</v>
+        <v>25565.53</v>
       </c>
       <c r="L10" t="n">
-        <v>26069.83</v>
+        <v>26077.21</v>
       </c>
       <c r="M10" t="n">
-        <v>26548</v>
+        <v>26247.77</v>
       </c>
       <c r="N10" t="n">
-        <v>27026.16</v>
+        <v>26418.33</v>
       </c>
       <c r="O10" t="n">
-        <v>27143.04</v>
+        <v>27271.13</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,21 +1361,23 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1385,57 +1389,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25999.17</v>
+        <v>26319.4</v>
       </c>
       <c r="C11" t="n">
-        <v>26490.71</v>
+        <v>27188.81</v>
       </c>
       <c r="D11" t="n">
-        <v>25496.13</v>
+        <v>26302.93</v>
       </c>
       <c r="E11" t="n">
-        <v>26241.83</v>
+        <v>26572.46</v>
       </c>
       <c r="F11" t="n">
-        <v>335.18</v>
+        <v>330.63</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
       <c r="H11" t="n">
-        <v>994.58</v>
+        <v>885.88</v>
       </c>
       <c r="I11" t="n">
-        <v>25224.41</v>
+        <v>24501.55</v>
       </c>
       <c r="J11" t="n">
-        <v>25053.85</v>
+        <v>25371.45</v>
       </c>
       <c r="K11" t="n">
-        <v>25565.53</v>
+        <v>25744.54</v>
       </c>
       <c r="L11" t="n">
-        <v>26077.21</v>
+        <v>26117.63</v>
       </c>
       <c r="M11" t="n">
-        <v>26247.77</v>
+        <v>26739.12</v>
       </c>
       <c r="N11" t="n">
-        <v>26418.33</v>
+        <v>27360.61</v>
       </c>
       <c r="O11" t="n">
-        <v>27271.13</v>
+        <v>27485.29</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1443,10 +1447,8 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1458,10 +1460,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1471,88 +1471,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26319.4</v>
+        <v>26441.7</v>
       </c>
       <c r="C12" t="n">
-        <v>27188.81</v>
+        <v>26531.8</v>
       </c>
       <c r="D12" t="n">
-        <v>26302.93</v>
+        <v>25178.63</v>
       </c>
       <c r="E12" t="n">
-        <v>26572.46</v>
+        <v>25220.02</v>
       </c>
       <c r="F12" t="n">
-        <v>330.63</v>
+        <v>-1352.44</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0126</v>
+        <v>-0.0509</v>
       </c>
       <c r="H12" t="n">
-        <v>885.88</v>
+        <v>1353.17</v>
       </c>
       <c r="I12" t="n">
-        <v>24501.55</v>
+        <v>25417.05</v>
       </c>
       <c r="J12" t="n">
-        <v>25371.45</v>
+        <v>25599.88</v>
       </c>
       <c r="K12" t="n">
-        <v>25744.54</v>
+        <v>26129.52</v>
       </c>
       <c r="L12" t="n">
-        <v>26117.63</v>
+        <v>26659.17</v>
       </c>
       <c r="M12" t="n">
-        <v>26739.12</v>
+        <v>27015.4</v>
       </c>
       <c r="N12" t="n">
-        <v>27360.61</v>
+        <v>27371.64</v>
       </c>
       <c r="O12" t="n">
-        <v>27485.29</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+        <v>28074.69</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1560,74 +1560,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26441.7</v>
+        <v>25452.87</v>
       </c>
       <c r="C13" t="n">
-        <v>26531.8</v>
+        <v>26136.27</v>
       </c>
       <c r="D13" t="n">
-        <v>25178.63</v>
+        <v>25369.29</v>
       </c>
       <c r="E13" t="n">
-        <v>25220.02</v>
+        <v>25858.89</v>
       </c>
       <c r="F13" t="n">
-        <v>-1352.44</v>
+        <v>638.87</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0509</v>
+        <v>0.0253</v>
       </c>
       <c r="H13" t="n">
-        <v>1353.17</v>
+        <v>766.98</v>
       </c>
       <c r="I13" t="n">
-        <v>25417.05</v>
+        <v>23825.46</v>
       </c>
       <c r="J13" t="n">
-        <v>25599.88</v>
+        <v>23549.25</v>
       </c>
       <c r="K13" t="n">
-        <v>26129.52</v>
+        <v>24543.43</v>
       </c>
       <c r="L13" t="n">
-        <v>26659.17</v>
+        <v>25537.62</v>
       </c>
       <c r="M13" t="n">
-        <v>27015.4</v>
+        <v>25896.6</v>
       </c>
       <c r="N13" t="n">
-        <v>27371.64</v>
+        <v>26255.59</v>
       </c>
       <c r="O13" t="n">
-        <v>28074.69</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>27884.97</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1639,55 +1635,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25452.87</v>
+        <v>25945.87</v>
       </c>
       <c r="C14" t="n">
-        <v>26136.27</v>
+        <v>26264.13</v>
       </c>
       <c r="D14" t="n">
-        <v>25369.29</v>
+        <v>25649.3</v>
       </c>
       <c r="E14" t="n">
-        <v>25858.89</v>
+        <v>26085.08</v>
       </c>
       <c r="F14" t="n">
-        <v>638.87</v>
+        <v>226.19</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0253</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>766.98</v>
+        <v>614.83</v>
       </c>
       <c r="I14" t="n">
-        <v>23825.46</v>
+        <v>24602.31</v>
       </c>
       <c r="J14" t="n">
-        <v>23549.25</v>
+        <v>25144.97</v>
       </c>
       <c r="K14" t="n">
-        <v>24543.43</v>
+        <v>25475.4</v>
       </c>
       <c r="L14" t="n">
-        <v>25537.62</v>
+        <v>25805.83</v>
       </c>
       <c r="M14" t="n">
-        <v>25896.6</v>
+        <v>26242.38</v>
       </c>
       <c r="N14" t="n">
-        <v>26255.59</v>
+        <v>26678.93</v>
       </c>
       <c r="O14" t="n">
-        <v>27884.97</v>
+        <v>26903.25</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1721,76 +1721,78 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25945.87</v>
+        <v>26067.86</v>
       </c>
       <c r="C15" t="n">
-        <v>26264.13</v>
+        <v>26151.46</v>
       </c>
       <c r="D15" t="n">
-        <v>25649.3</v>
+        <v>25257.61</v>
       </c>
       <c r="E15" t="n">
-        <v>26085.08</v>
+        <v>25976.79</v>
       </c>
       <c r="F15" t="n">
-        <v>226.19</v>
+        <v>-108.29</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0042</v>
       </c>
       <c r="H15" t="n">
-        <v>614.83</v>
+        <v>893.85</v>
       </c>
       <c r="I15" t="n">
-        <v>24602.31</v>
+        <v>25034.47</v>
       </c>
       <c r="J15" t="n">
-        <v>25144.97</v>
+        <v>25534.43</v>
       </c>
       <c r="K15" t="n">
-        <v>25475.4</v>
+        <v>25777.67</v>
       </c>
       <c r="L15" t="n">
-        <v>25805.83</v>
+        <v>26020.9</v>
       </c>
       <c r="M15" t="n">
-        <v>26242.38</v>
+        <v>26392.5</v>
       </c>
       <c r="N15" t="n">
-        <v>26678.93</v>
+        <v>26764.09</v>
       </c>
       <c r="O15" t="n">
-        <v>26903.25</v>
+        <v>26878.96</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1803,59 +1805,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26067.86</v>
+        <v>25718.14</v>
       </c>
       <c r="C16" t="n">
-        <v>26151.46</v>
+        <v>25824.44</v>
       </c>
       <c r="D16" t="n">
-        <v>25257.61</v>
+        <v>25086.54</v>
       </c>
       <c r="E16" t="n">
-        <v>25976.79</v>
+        <v>25690.53</v>
       </c>
       <c r="F16" t="n">
-        <v>-108.29</v>
+        <v>-286.26</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.011</v>
       </c>
       <c r="H16" t="n">
-        <v>893.85</v>
+        <v>737.9</v>
       </c>
       <c r="I16" t="n">
-        <v>25034.47</v>
+        <v>24363.76</v>
       </c>
       <c r="J16" t="n">
-        <v>25534.43</v>
+        <v>25219.06</v>
       </c>
       <c r="K16" t="n">
-        <v>25777.67</v>
+        <v>25529.86</v>
       </c>
       <c r="L16" t="n">
-        <v>26020.9</v>
+        <v>25840.66</v>
       </c>
       <c r="M16" t="n">
-        <v>26392.5</v>
+        <v>26423.71</v>
       </c>
       <c r="N16" t="n">
-        <v>26764.09</v>
+        <v>27006.77</v>
       </c>
       <c r="O16" t="n">
-        <v>26878.96</v>
+        <v>27045.31</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1894,71 +1892,69 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25718.14</v>
+        <v>25795.94</v>
       </c>
       <c r="C17" t="n">
-        <v>25824.44</v>
+        <v>25927.66</v>
       </c>
       <c r="D17" t="n">
-        <v>25086.54</v>
+        <v>25671.33</v>
       </c>
       <c r="E17" t="n">
-        <v>25690.53</v>
+        <v>25818.93</v>
       </c>
       <c r="F17" t="n">
-        <v>-286.26</v>
+        <v>128.4</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H17" t="n">
-        <v>737.9</v>
+        <v>256.33</v>
       </c>
       <c r="I17" t="n">
-        <v>24363.76</v>
+        <v>24348.64</v>
       </c>
       <c r="J17" t="n">
-        <v>25219.06</v>
+        <v>25070.15</v>
       </c>
       <c r="K17" t="n">
-        <v>25529.86</v>
+        <v>25321.58</v>
       </c>
       <c r="L17" t="n">
-        <v>25840.66</v>
+        <v>25573.01</v>
       </c>
       <c r="M17" t="n">
-        <v>26423.71</v>
+        <v>26059.48</v>
       </c>
       <c r="N17" t="n">
-        <v>27006.77</v>
+        <v>26545.95</v>
       </c>
       <c r="O17" t="n">
-        <v>27045.31</v>
+        <v>26562.34</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1971,64 +1967,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25795.94</v>
+        <v>25928.89</v>
       </c>
       <c r="C18" t="n">
-        <v>25927.66</v>
+        <v>26345.63</v>
       </c>
       <c r="D18" t="n">
-        <v>25671.33</v>
+        <v>25554.31</v>
       </c>
       <c r="E18" t="n">
-        <v>25818.93</v>
+        <v>26338.47</v>
       </c>
       <c r="F18" t="n">
-        <v>128.4</v>
+        <v>519.54</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0201</v>
       </c>
       <c r="H18" t="n">
-        <v>256.33</v>
+        <v>791.3200000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>24348.64</v>
+        <v>25415</v>
       </c>
       <c r="J18" t="n">
-        <v>25070.15</v>
+        <v>25572.32</v>
       </c>
       <c r="K18" t="n">
-        <v>25321.58</v>
+        <v>25690.76</v>
       </c>
       <c r="L18" t="n">
-        <v>25573.01</v>
+        <v>25809.21</v>
       </c>
       <c r="M18" t="n">
-        <v>26059.48</v>
+        <v>25947.09</v>
       </c>
       <c r="N18" t="n">
-        <v>26545.95</v>
+        <v>26084.98</v>
       </c>
       <c r="O18" t="n">
-        <v>26562.34</v>
+        <v>26183.99</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
@@ -2037,90 +2041,90 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25928.89</v>
+        <v>26361.44</v>
       </c>
       <c r="C19" t="n">
-        <v>26345.63</v>
+        <v>26858.13</v>
       </c>
       <c r="D19" t="n">
-        <v>25554.31</v>
+        <v>25960.34</v>
       </c>
       <c r="E19" t="n">
-        <v>26338.47</v>
+        <v>26231.79</v>
       </c>
       <c r="F19" t="n">
-        <v>519.54</v>
+        <v>-106.68</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.0041</v>
       </c>
       <c r="H19" t="n">
-        <v>791.3200000000001</v>
+        <v>897.79</v>
       </c>
       <c r="I19" t="n">
-        <v>25415</v>
+        <v>24762.99</v>
       </c>
       <c r="J19" t="n">
-        <v>25572.32</v>
+        <v>25741.4</v>
       </c>
       <c r="K19" t="n">
-        <v>25690.76</v>
+        <v>25942.81</v>
       </c>
       <c r="L19" t="n">
-        <v>25809.21</v>
+        <v>26144.22</v>
       </c>
       <c r="M19" t="n">
-        <v>25947.09</v>
+        <v>26734.13</v>
       </c>
       <c r="N19" t="n">
-        <v>26084.98</v>
+        <v>27324.04</v>
       </c>
       <c r="O19" t="n">
-        <v>26183.99</v>
+        <v>27136.95</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2128,15 +2132,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2152,50 +2152,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26361.44</v>
+        <v>26376.84</v>
       </c>
       <c r="C20" t="n">
-        <v>26858.13</v>
+        <v>27206.84</v>
       </c>
       <c r="D20" t="n">
-        <v>25960.34</v>
+        <v>26187.76</v>
       </c>
       <c r="E20" t="n">
-        <v>26231.79</v>
+        <v>26844.96</v>
       </c>
       <c r="F20" t="n">
-        <v>-106.68</v>
+        <v>613.17</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0234</v>
       </c>
       <c r="H20" t="n">
-        <v>897.79</v>
+        <v>1019.08</v>
       </c>
       <c r="I20" t="n">
-        <v>24762.99</v>
+        <v>25062.55</v>
       </c>
       <c r="J20" t="n">
-        <v>25741.4</v>
+        <v>25245.27</v>
       </c>
       <c r="K20" t="n">
-        <v>25942.81</v>
+        <v>25782.89</v>
       </c>
       <c r="L20" t="n">
-        <v>26144.22</v>
+        <v>26320.51</v>
       </c>
       <c r="M20" t="n">
-        <v>26734.13</v>
+        <v>26680.68</v>
       </c>
       <c r="N20" t="n">
-        <v>27324.04</v>
+        <v>27040.86</v>
       </c>
       <c r="O20" t="n">
-        <v>27136.95</v>
+        <v>27755.92</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2208,16 +2208,18 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2227,59 +2229,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26376.84</v>
+        <v>26641.6</v>
       </c>
       <c r="C21" t="n">
-        <v>27206.84</v>
+        <v>26895.94</v>
       </c>
       <c r="D21" t="n">
-        <v>26187.76</v>
+        <v>26363.86</v>
       </c>
       <c r="E21" t="n">
-        <v>26844.96</v>
+        <v>26749.51</v>
       </c>
       <c r="F21" t="n">
-        <v>613.17</v>
+        <v>-95.45</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0234</v>
+        <v>-0.0036</v>
       </c>
       <c r="H21" t="n">
-        <v>1019.08</v>
+        <v>532.08</v>
       </c>
       <c r="I21" t="n">
-        <v>25062.55</v>
+        <v>25168.68</v>
       </c>
       <c r="J21" t="n">
-        <v>25245.27</v>
+        <v>25899.71</v>
       </c>
       <c r="K21" t="n">
-        <v>25782.89</v>
+        <v>26335.42</v>
       </c>
       <c r="L21" t="n">
-        <v>26320.51</v>
+        <v>26771.13</v>
       </c>
       <c r="M21" t="n">
-        <v>26680.68</v>
+        <v>27354.5</v>
       </c>
       <c r="N21" t="n">
-        <v>27040.86</v>
+        <v>27937.87</v>
       </c>
       <c r="O21" t="n">
-        <v>27755.92</v>
+        <v>28225.92</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2290,20 +2288,16 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2313,55 +2307,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26641.6</v>
+        <v>26844.04</v>
       </c>
       <c r="C22" t="n">
-        <v>26895.94</v>
+        <v>28056.1</v>
       </c>
       <c r="D22" t="n">
-        <v>26363.86</v>
+        <v>26619.83</v>
       </c>
       <c r="E22" t="n">
-        <v>26749.51</v>
+        <v>27387.11</v>
       </c>
       <c r="F22" t="n">
-        <v>-95.45</v>
+        <v>637.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0238</v>
       </c>
       <c r="H22" t="n">
-        <v>532.08</v>
+        <v>1436.27</v>
       </c>
       <c r="I22" t="n">
-        <v>25168.68</v>
+        <v>25831.78</v>
       </c>
       <c r="J22" t="n">
-        <v>25899.71</v>
+        <v>26277.23</v>
       </c>
       <c r="K22" t="n">
-        <v>26335.42</v>
+        <v>26483.47</v>
       </c>
       <c r="L22" t="n">
-        <v>26771.13</v>
+        <v>26689.7</v>
       </c>
       <c r="M22" t="n">
-        <v>27354.5</v>
+        <v>27015.55</v>
       </c>
       <c r="N22" t="n">
-        <v>27937.87</v>
+        <v>27341.4</v>
       </c>
       <c r="O22" t="n">
-        <v>28225.92</v>
+        <v>27428.02</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2372,78 +2370,80 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26844.04</v>
+        <v>27097.34</v>
       </c>
       <c r="C23" t="n">
-        <v>28056.1</v>
+        <v>27126.48</v>
       </c>
       <c r="D23" t="n">
-        <v>26619.83</v>
+        <v>26295.03</v>
       </c>
       <c r="E23" t="n">
-        <v>27387.11</v>
+        <v>26559.95</v>
       </c>
       <c r="F23" t="n">
-        <v>637.6</v>
+        <v>-827.16</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0238</v>
+        <v>-0.0302</v>
       </c>
       <c r="H23" t="n">
-        <v>1436.27</v>
+        <v>831.45</v>
       </c>
       <c r="I23" t="n">
-        <v>25831.78</v>
+        <v>25183.56</v>
       </c>
       <c r="J23" t="n">
-        <v>26277.23</v>
+        <v>25975.41</v>
       </c>
       <c r="K23" t="n">
-        <v>26483.47</v>
+        <v>26668.97</v>
       </c>
       <c r="L23" t="n">
-        <v>26689.7</v>
+        <v>27362.54</v>
       </c>
       <c r="M23" t="n">
-        <v>27015.55</v>
+        <v>28105.24</v>
       </c>
       <c r="N23" t="n">
-        <v>27341.4</v>
+        <v>28847.95</v>
       </c>
       <c r="O23" t="n">
-        <v>27428.02</v>
+        <v>29492.37</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,83 +2451,83 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27097.34</v>
+        <v>26982.49</v>
       </c>
       <c r="C24" t="n">
-        <v>27126.48</v>
+        <v>27397.65</v>
       </c>
       <c r="D24" t="n">
-        <v>26295.03</v>
+        <v>26444.46</v>
       </c>
       <c r="E24" t="n">
-        <v>26559.95</v>
+        <v>26567.12</v>
       </c>
       <c r="F24" t="n">
-        <v>-827.16</v>
+        <v>7.17</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0003</v>
       </c>
       <c r="H24" t="n">
-        <v>831.45</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>25183.56</v>
+        <v>25463.58</v>
       </c>
       <c r="J24" t="n">
-        <v>25975.41</v>
+        <v>25653.1</v>
       </c>
       <c r="K24" t="n">
-        <v>26668.97</v>
+        <v>26144.22</v>
       </c>
       <c r="L24" t="n">
-        <v>27362.54</v>
+        <v>26635.35</v>
       </c>
       <c r="M24" t="n">
-        <v>28105.24</v>
+        <v>26975.67</v>
       </c>
       <c r="N24" t="n">
-        <v>28847.95</v>
+        <v>27316</v>
       </c>
       <c r="O24" t="n">
-        <v>29492.37</v>
+        <v>27957.93</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2535,21 +2535,23 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2559,59 +2561,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26982.49</v>
+        <v>26501.2</v>
       </c>
       <c r="C25" t="n">
-        <v>27397.65</v>
+        <v>26734.41</v>
       </c>
       <c r="D25" t="n">
-        <v>26444.46</v>
+        <v>26356.96</v>
       </c>
       <c r="E25" t="n">
-        <v>26567.12</v>
+        <v>26413.35</v>
       </c>
       <c r="F25" t="n">
-        <v>7.17</v>
+        <v>-153.77</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0058</v>
       </c>
       <c r="H25" t="n">
-        <v>953.1900000000001</v>
+        <v>377.45</v>
       </c>
       <c r="I25" t="n">
-        <v>25463.58</v>
+        <v>25491.27</v>
       </c>
       <c r="J25" t="n">
-        <v>25653.1</v>
+        <v>25436.96</v>
       </c>
       <c r="K25" t="n">
-        <v>26144.22</v>
+        <v>26090.52</v>
       </c>
       <c r="L25" t="n">
-        <v>26635.35</v>
+        <v>26744.09</v>
       </c>
       <c r="M25" t="n">
-        <v>26975.67</v>
+        <v>27043.71</v>
       </c>
       <c r="N25" t="n">
-        <v>27316</v>
+        <v>27343.34</v>
       </c>
       <c r="O25" t="n">
-        <v>27957.93</v>
+        <v>28350.84</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2619,23 +2617,21 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2645,55 +2641,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26501.2</v>
+        <v>26798.97</v>
       </c>
       <c r="C26" t="n">
-        <v>26734.41</v>
+        <v>27156.28</v>
       </c>
       <c r="D26" t="n">
-        <v>26356.96</v>
+        <v>26373.01</v>
       </c>
       <c r="E26" t="n">
-        <v>26413.35</v>
+        <v>26630.54</v>
       </c>
       <c r="F26" t="n">
-        <v>-153.77</v>
+        <v>217.19</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>377.45</v>
+        <v>783.27</v>
       </c>
       <c r="I26" t="n">
-        <v>25491.27</v>
+        <v>25979.51</v>
       </c>
       <c r="J26" t="n">
-        <v>25436.96</v>
+        <v>25969.73</v>
       </c>
       <c r="K26" t="n">
-        <v>26090.52</v>
+        <v>26224.62</v>
       </c>
       <c r="L26" t="n">
-        <v>26744.09</v>
+        <v>26479.52</v>
       </c>
       <c r="M26" t="n">
-        <v>27043.71</v>
+        <v>26602.07</v>
       </c>
       <c r="N26" t="n">
-        <v>27343.34</v>
+        <v>26724.63</v>
       </c>
       <c r="O26" t="n">
-        <v>28350.84</v>
+        <v>27111.86</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2701,116 +2701,116 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26798.97</v>
+        <v>26305.58</v>
       </c>
       <c r="C27" t="n">
-        <v>27156.28</v>
+        <v>26403.85</v>
       </c>
       <c r="D27" t="n">
-        <v>26373.01</v>
+        <v>24958.43</v>
       </c>
       <c r="E27" t="n">
-        <v>26630.54</v>
+        <v>25757.29</v>
       </c>
       <c r="F27" t="n">
-        <v>217.19</v>
+        <v>-873.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="H27" t="n">
-        <v>783.27</v>
+        <v>1445.42</v>
       </c>
       <c r="I27" t="n">
-        <v>25979.51</v>
+        <v>25589.74</v>
       </c>
       <c r="J27" t="n">
-        <v>25969.73</v>
+        <v>25780.22</v>
       </c>
       <c r="K27" t="n">
-        <v>26224.62</v>
+        <v>26238.9</v>
       </c>
       <c r="L27" t="n">
-        <v>26479.52</v>
+        <v>26697.59</v>
       </c>
       <c r="M27" t="n">
-        <v>26602.07</v>
+        <v>27022.17</v>
       </c>
       <c r="N27" t="n">
-        <v>26724.63</v>
+        <v>27346.76</v>
       </c>
       <c r="O27" t="n">
-        <v>27111.86</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+        <v>27939.55</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2818,60 +2818,56 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26305.58</v>
+        <v>25075.74</v>
       </c>
       <c r="C28" t="n">
-        <v>26403.85</v>
+        <v>26149.64</v>
       </c>
       <c r="D28" t="n">
-        <v>24958.43</v>
+        <v>24906</v>
       </c>
       <c r="E28" t="n">
-        <v>25757.29</v>
+        <v>25465.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-873.25</v>
+        <v>-291.69</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0328</v>
+        <v>-0.0113</v>
       </c>
       <c r="H28" t="n">
-        <v>1445.42</v>
+        <v>1243.64</v>
       </c>
       <c r="I28" t="n">
-        <v>25589.74</v>
+        <v>23513.01</v>
       </c>
       <c r="J28" t="n">
-        <v>25780.22</v>
+        <v>24349.94</v>
       </c>
       <c r="K28" t="n">
-        <v>26238.9</v>
+        <v>25034.58</v>
       </c>
       <c r="L28" t="n">
-        <v>26697.59</v>
+        <v>25719.21</v>
       </c>
       <c r="M28" t="n">
-        <v>27022.17</v>
+        <v>26480</v>
       </c>
       <c r="N28" t="n">
-        <v>27346.76</v>
+        <v>27240.78</v>
       </c>
       <c r="O28" t="n">
-        <v>27939.55</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27849.27</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
@@ -2880,7 +2876,7 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2902,50 +2898,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25075.74</v>
+        <v>25436.27</v>
       </c>
       <c r="C29" t="n">
-        <v>26149.64</v>
+        <v>26250.14</v>
       </c>
       <c r="D29" t="n">
-        <v>24906</v>
+        <v>25121.46</v>
       </c>
       <c r="E29" t="n">
-        <v>25465.6</v>
+        <v>25277.32</v>
       </c>
       <c r="F29" t="n">
-        <v>-291.69</v>
+        <v>-188.28</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.0074</v>
       </c>
       <c r="H29" t="n">
-        <v>1243.64</v>
+        <v>1128.68</v>
       </c>
       <c r="I29" t="n">
-        <v>23513.01</v>
+        <v>23662.36</v>
       </c>
       <c r="J29" t="n">
-        <v>24349.94</v>
+        <v>24190.85</v>
       </c>
       <c r="K29" t="n">
-        <v>25034.58</v>
+        <v>24843.78</v>
       </c>
       <c r="L29" t="n">
-        <v>25719.21</v>
+        <v>25496.71</v>
       </c>
       <c r="M29" t="n">
-        <v>26480</v>
+        <v>26087.42</v>
       </c>
       <c r="N29" t="n">
-        <v>27240.78</v>
+        <v>26678.13</v>
       </c>
       <c r="O29" t="n">
-        <v>27849.27</v>
+        <v>27393.28</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2953,18 +2949,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2977,55 +2973,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25436.27</v>
+        <v>24789.14</v>
       </c>
       <c r="C30" t="n">
-        <v>26250.14</v>
+        <v>25390.3</v>
       </c>
       <c r="D30" t="n">
-        <v>25121.46</v>
+        <v>24203.54</v>
       </c>
       <c r="E30" t="n">
-        <v>25277.32</v>
+        <v>24951.88</v>
       </c>
       <c r="F30" t="n">
-        <v>-188.28</v>
+        <v>-325.44</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0129</v>
       </c>
       <c r="H30" t="n">
-        <v>1128.68</v>
+        <v>1186.76</v>
       </c>
       <c r="I30" t="n">
-        <v>23662.36</v>
+        <v>23992.78</v>
       </c>
       <c r="J30" t="n">
-        <v>24190.85</v>
+        <v>23944.4</v>
       </c>
       <c r="K30" t="n">
-        <v>24843.78</v>
+        <v>24712.98</v>
       </c>
       <c r="L30" t="n">
-        <v>25496.71</v>
+        <v>25481.56</v>
       </c>
       <c r="M30" t="n">
-        <v>26087.42</v>
+        <v>25841.66</v>
       </c>
       <c r="N30" t="n">
-        <v>26678.13</v>
+        <v>26201.76</v>
       </c>
       <c r="O30" t="n">
-        <v>27393.28</v>
+        <v>27378.82</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3033,18 +3033,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3057,59 +3057,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24789.14</v>
+        <v>24532.85</v>
       </c>
       <c r="C31" t="n">
-        <v>25390.3</v>
+        <v>25429.76</v>
       </c>
       <c r="D31" t="n">
-        <v>24203.54</v>
+        <v>24409.57</v>
       </c>
       <c r="E31" t="n">
-        <v>24951.88</v>
+        <v>25116.53</v>
       </c>
       <c r="F31" t="n">
-        <v>-325.44</v>
+        <v>164.65</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0066</v>
       </c>
       <c r="H31" t="n">
-        <v>1186.76</v>
+        <v>1020.19</v>
       </c>
       <c r="I31" t="n">
-        <v>23992.78</v>
+        <v>23016.78</v>
       </c>
       <c r="J31" t="n">
-        <v>23944.4</v>
+        <v>23842.6</v>
       </c>
       <c r="K31" t="n">
-        <v>24712.98</v>
+        <v>24358.5</v>
       </c>
       <c r="L31" t="n">
-        <v>25481.56</v>
+        <v>24874.4</v>
       </c>
       <c r="M31" t="n">
-        <v>25841.66</v>
+        <v>25545.26</v>
       </c>
       <c r="N31" t="n">
-        <v>26201.76</v>
+        <v>26216.12</v>
       </c>
       <c r="O31" t="n">
-        <v>27378.82</v>
+        <v>26577.06</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,14 +3113,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3141,55 +3135,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24532.85</v>
+        <v>25772.56</v>
       </c>
       <c r="C32" t="n">
-        <v>25429.76</v>
+        <v>26073.97</v>
       </c>
       <c r="D32" t="n">
-        <v>24409.57</v>
+        <v>25653.63</v>
       </c>
       <c r="E32" t="n">
-        <v>25116.53</v>
+        <v>25893.54</v>
       </c>
       <c r="F32" t="n">
-        <v>164.65</v>
+        <v>777.01</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0309</v>
       </c>
       <c r="H32" t="n">
-        <v>1020.19</v>
+        <v>420.34</v>
       </c>
       <c r="I32" t="n">
-        <v>23016.78</v>
+        <v>23389.38</v>
       </c>
       <c r="J32" t="n">
-        <v>23842.6</v>
+        <v>24194.77</v>
       </c>
       <c r="K32" t="n">
-        <v>24358.5</v>
+        <v>24606.43</v>
       </c>
       <c r="L32" t="n">
-        <v>24874.4</v>
+        <v>25018.1</v>
       </c>
       <c r="M32" t="n">
-        <v>25545.26</v>
+        <v>25626.62</v>
       </c>
       <c r="N32" t="n">
-        <v>26216.12</v>
+        <v>26235.15</v>
       </c>
       <c r="O32" t="n">
-        <v>26577.06</v>
+        <v>26449.95</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3202,11 +3200,13 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3228,50 +3228,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25772.56</v>
+        <v>25708.64</v>
       </c>
       <c r="C33" t="n">
-        <v>26073.97</v>
+        <v>26403.07</v>
       </c>
       <c r="D33" t="n">
-        <v>25653.63</v>
+        <v>25508.53</v>
       </c>
       <c r="E33" t="n">
-        <v>25893.54</v>
+        <v>26160.33</v>
       </c>
       <c r="F33" t="n">
-        <v>777.01</v>
+        <v>266.79</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.0103</v>
       </c>
       <c r="H33" t="n">
-        <v>420.34</v>
+        <v>894.54</v>
       </c>
       <c r="I33" t="n">
-        <v>23389.38</v>
+        <v>25233.29</v>
       </c>
       <c r="J33" t="n">
-        <v>24194.77</v>
+        <v>25488.07</v>
       </c>
       <c r="K33" t="n">
-        <v>24606.43</v>
+        <v>25683.37</v>
       </c>
       <c r="L33" t="n">
-        <v>25018.1</v>
+        <v>25878.67</v>
       </c>
       <c r="M33" t="n">
-        <v>25626.62</v>
+        <v>26103.71</v>
       </c>
       <c r="N33" t="n">
-        <v>26235.15</v>
+        <v>26328.75</v>
       </c>
       <c r="O33" t="n">
-        <v>26449.95</v>
+        <v>26494.31</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3279,8 +3279,10 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
@@ -3292,8 +3294,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3305,57 +3309,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25708.64</v>
+        <v>26204.61</v>
       </c>
       <c r="C34" t="n">
-        <v>26403.07</v>
+        <v>26529.49</v>
       </c>
       <c r="D34" t="n">
-        <v>25508.53</v>
+        <v>25639.26</v>
       </c>
       <c r="E34" t="n">
-        <v>26160.33</v>
+        <v>25978.07</v>
       </c>
       <c r="F34" t="n">
-        <v>266.79</v>
+        <v>-182.26</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.007</v>
       </c>
       <c r="H34" t="n">
-        <v>894.54</v>
+        <v>890.23</v>
       </c>
       <c r="I34" t="n">
-        <v>25233.29</v>
+        <v>24613.99</v>
       </c>
       <c r="J34" t="n">
-        <v>25488.07</v>
+        <v>25368.05</v>
       </c>
       <c r="K34" t="n">
-        <v>25683.37</v>
+        <v>25713.06</v>
       </c>
       <c r="L34" t="n">
-        <v>25878.67</v>
+        <v>26058.06</v>
       </c>
       <c r="M34" t="n">
-        <v>26103.71</v>
+        <v>26607.6</v>
       </c>
       <c r="N34" t="n">
-        <v>26328.75</v>
+        <v>27157.14</v>
       </c>
       <c r="O34" t="n">
-        <v>26494.31</v>
+        <v>27297.61</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3368,20 +3372,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3400,50 +3400,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26204.61</v>
+        <v>25976.97</v>
       </c>
       <c r="C35" t="n">
-        <v>26529.49</v>
+        <v>26132.94</v>
       </c>
       <c r="D35" t="n">
-        <v>25639.26</v>
+        <v>25609.61</v>
       </c>
       <c r="E35" t="n">
-        <v>25978.07</v>
+        <v>25776.53</v>
       </c>
       <c r="F35" t="n">
-        <v>-182.26</v>
+        <v>-201.54</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0078</v>
       </c>
       <c r="H35" t="n">
-        <v>890.23</v>
+        <v>523.33</v>
       </c>
       <c r="I35" t="n">
-        <v>24613.99</v>
+        <v>24749.03</v>
       </c>
       <c r="J35" t="n">
-        <v>25368.05</v>
+        <v>25034.69</v>
       </c>
       <c r="K35" t="n">
-        <v>25713.06</v>
+        <v>25532.96</v>
       </c>
       <c r="L35" t="n">
-        <v>26058.06</v>
+        <v>26031.22</v>
       </c>
       <c r="M35" t="n">
-        <v>26607.6</v>
+        <v>26423.19</v>
       </c>
       <c r="N35" t="n">
-        <v>27157.14</v>
+        <v>26815.15</v>
       </c>
       <c r="O35" t="n">
-        <v>27297.61</v>
+        <v>27419.72</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3475,59 +3475,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25976.97</v>
+        <v>26138.34</v>
       </c>
       <c r="C36" t="n">
-        <v>26132.94</v>
+        <v>26669.26</v>
       </c>
       <c r="D36" t="n">
-        <v>25609.61</v>
+        <v>25690.36</v>
       </c>
       <c r="E36" t="n">
-        <v>25776.53</v>
+        <v>26393.71</v>
       </c>
       <c r="F36" t="n">
-        <v>-201.54</v>
+        <v>617.1799999999999</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0239</v>
       </c>
       <c r="H36" t="n">
-        <v>523.33</v>
+        <v>978.9</v>
       </c>
       <c r="I36" t="n">
-        <v>24749.03</v>
+        <v>25086.28</v>
       </c>
       <c r="J36" t="n">
-        <v>25034.69</v>
+        <v>25205.83</v>
       </c>
       <c r="K36" t="n">
-        <v>25532.96</v>
+        <v>25514.86</v>
       </c>
       <c r="L36" t="n">
-        <v>26031.22</v>
+        <v>25823.9</v>
       </c>
       <c r="M36" t="n">
-        <v>26423.19</v>
+        <v>26038.19</v>
       </c>
       <c r="N36" t="n">
-        <v>26815.15</v>
+        <v>26252.49</v>
       </c>
       <c r="O36" t="n">
-        <v>27419.72</v>
+        <v>26656.27</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3535,28 +3531,32 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3564,50 +3564,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26138.34</v>
+        <v>26310.87</v>
       </c>
       <c r="C37" t="n">
-        <v>26669.26</v>
+        <v>26844.8</v>
       </c>
       <c r="D37" t="n">
-        <v>25690.36</v>
+        <v>25847.15</v>
       </c>
       <c r="E37" t="n">
-        <v>26393.71</v>
+        <v>25962.73</v>
       </c>
       <c r="F37" t="n">
-        <v>617.1799999999999</v>
+        <v>-430.98</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0163</v>
       </c>
       <c r="H37" t="n">
-        <v>978.9</v>
+        <v>997.65</v>
       </c>
       <c r="I37" t="n">
-        <v>25086.28</v>
+        <v>24711.46</v>
       </c>
       <c r="J37" t="n">
-        <v>25205.83</v>
+        <v>25521.76</v>
       </c>
       <c r="K37" t="n">
-        <v>25514.86</v>
+        <v>25904.26</v>
       </c>
       <c r="L37" t="n">
-        <v>25823.9</v>
+        <v>26286.76</v>
       </c>
       <c r="M37" t="n">
-        <v>26038.19</v>
+        <v>26883.16</v>
       </c>
       <c r="N37" t="n">
-        <v>26252.49</v>
+        <v>27479.56</v>
       </c>
       <c r="O37" t="n">
-        <v>26656.27</v>
+        <v>27648.16</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3615,83 +3615,83 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26310.87</v>
+        <v>25838.96</v>
       </c>
       <c r="C38" t="n">
-        <v>26844.8</v>
+        <v>25845.46</v>
       </c>
       <c r="D38" t="n">
-        <v>25847.15</v>
+        <v>25341.73</v>
       </c>
       <c r="E38" t="n">
-        <v>25962.73</v>
+        <v>25606.03</v>
       </c>
       <c r="F38" t="n">
-        <v>-430.98</v>
+        <v>-356.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0137</v>
       </c>
       <c r="H38" t="n">
-        <v>997.65</v>
+        <v>503.73</v>
       </c>
       <c r="I38" t="n">
-        <v>24711.46</v>
+        <v>24849.5</v>
       </c>
       <c r="J38" t="n">
-        <v>25521.76</v>
+        <v>24773.46</v>
       </c>
       <c r="K38" t="n">
-        <v>25904.26</v>
+        <v>25463.91</v>
       </c>
       <c r="L38" t="n">
-        <v>26286.76</v>
+        <v>26154.35</v>
       </c>
       <c r="M38" t="n">
-        <v>26883.16</v>
+        <v>26461.56</v>
       </c>
       <c r="N38" t="n">
-        <v>27479.56</v>
+        <v>26768.76</v>
       </c>
       <c r="O38" t="n">
-        <v>27648.16</v>
+        <v>27842.45</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3725,67 +3725,71 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25838.96</v>
+        <v>25622.36</v>
       </c>
       <c r="C39" t="n">
-        <v>25845.46</v>
+        <v>25768.38</v>
       </c>
       <c r="D39" t="n">
-        <v>25341.73</v>
+        <v>24727.26</v>
       </c>
       <c r="E39" t="n">
-        <v>25606.03</v>
+        <v>25182.39</v>
       </c>
       <c r="F39" t="n">
-        <v>-356.7</v>
+        <v>-423.64</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0165</v>
       </c>
       <c r="H39" t="n">
-        <v>503.73</v>
+        <v>1041.12</v>
       </c>
       <c r="I39" t="n">
-        <v>24849.5</v>
+        <v>24838</v>
       </c>
       <c r="J39" t="n">
-        <v>24773.46</v>
+        <v>25108.52</v>
       </c>
       <c r="K39" t="n">
-        <v>25463.91</v>
+        <v>25354.16</v>
       </c>
       <c r="L39" t="n">
-        <v>26154.35</v>
+        <v>25599.81</v>
       </c>
       <c r="M39" t="n">
-        <v>26461.56</v>
+        <v>25857.89</v>
       </c>
       <c r="N39" t="n">
-        <v>26768.76</v>
+        <v>26115.98</v>
       </c>
       <c r="O39" t="n">
-        <v>27842.45</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+        <v>26349.19</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
@@ -3816,73 +3820,69 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25622.36</v>
+        <v>25180.05</v>
       </c>
       <c r="C40" t="n">
-        <v>25768.38</v>
+        <v>26045.07</v>
       </c>
       <c r="D40" t="n">
-        <v>24727.26</v>
+        <v>24928.14</v>
       </c>
       <c r="E40" t="n">
-        <v>25182.39</v>
+        <v>24961.95</v>
       </c>
       <c r="F40" t="n">
-        <v>-423.64</v>
+        <v>-220.44</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0165</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>1041.12</v>
+        <v>1116.93</v>
       </c>
       <c r="I40" t="n">
-        <v>24838</v>
+        <v>23686.14</v>
       </c>
       <c r="J40" t="n">
-        <v>25108.52</v>
+        <v>24108.55</v>
       </c>
       <c r="K40" t="n">
-        <v>25354.16</v>
+        <v>24661.83</v>
       </c>
       <c r="L40" t="n">
-        <v>25599.81</v>
+        <v>25215.11</v>
       </c>
       <c r="M40" t="n">
-        <v>25857.89</v>
+        <v>25702.95</v>
       </c>
       <c r="N40" t="n">
-        <v>26115.98</v>
+        <v>26190.8</v>
       </c>
       <c r="O40" t="n">
-        <v>26349.19</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26809.5</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3897,57 +3897,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25180.05</v>
+        <v>24582.91</v>
       </c>
       <c r="C41" t="n">
-        <v>26045.07</v>
+        <v>24837.98</v>
       </c>
       <c r="D41" t="n">
-        <v>24928.14</v>
+        <v>23999.67</v>
       </c>
       <c r="E41" t="n">
-        <v>24961.95</v>
+        <v>24718.1</v>
       </c>
       <c r="F41" t="n">
-        <v>-220.44</v>
+        <v>-243.85</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="H41" t="n">
-        <v>1116.93</v>
+        <v>838.3099999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>23686.14</v>
+        <v>23811.21</v>
       </c>
       <c r="J41" t="n">
-        <v>24108.55</v>
+        <v>23582.69</v>
       </c>
       <c r="K41" t="n">
-        <v>24661.83</v>
+        <v>24403.48</v>
       </c>
       <c r="L41" t="n">
-        <v>25215.11</v>
+        <v>25224.28</v>
       </c>
       <c r="M41" t="n">
-        <v>25702.95</v>
+        <v>25520.41</v>
       </c>
       <c r="N41" t="n">
-        <v>26190.8</v>
+        <v>25816.55</v>
       </c>
       <c r="O41" t="n">
-        <v>26809.5</v>
+        <v>27162</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3955,18 +3955,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3981,67 +3981,69 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>24582.91</v>
+        <v>25001.42</v>
       </c>
       <c r="C42" t="n">
-        <v>24837.98</v>
+        <v>25047.9</v>
       </c>
       <c r="D42" t="n">
-        <v>23999.67</v>
+        <v>23749.99</v>
       </c>
       <c r="E42" t="n">
-        <v>24718.1</v>
+        <v>23924.81</v>
       </c>
       <c r="F42" t="n">
-        <v>-243.85</v>
+        <v>-793.29</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0321</v>
       </c>
       <c r="H42" t="n">
-        <v>838.3099999999999</v>
+        <v>1297.91</v>
       </c>
       <c r="I42" t="n">
-        <v>23811.21</v>
+        <v>23161.36</v>
       </c>
       <c r="J42" t="n">
-        <v>23582.69</v>
+        <v>24029.43</v>
       </c>
       <c r="K42" t="n">
-        <v>24403.48</v>
+        <v>24298.94</v>
       </c>
       <c r="L42" t="n">
-        <v>25224.28</v>
+        <v>24568.46</v>
       </c>
       <c r="M42" t="n">
-        <v>25520.41</v>
+        <v>25137.25</v>
       </c>
       <c r="N42" t="n">
-        <v>25816.55</v>
+        <v>25706.05</v>
       </c>
       <c r="O42" t="n">
-        <v>27162</v>
+        <v>25676.29</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4058,73 +4060,73 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25001.42</v>
+        <v>23811.76</v>
       </c>
       <c r="C43" t="n">
-        <v>25047.9</v>
+        <v>23863.71</v>
       </c>
       <c r="D43" t="n">
-        <v>23749.99</v>
+        <v>22518</v>
       </c>
       <c r="E43" t="n">
-        <v>23924.81</v>
+        <v>22671.86</v>
       </c>
       <c r="F43" t="n">
-        <v>-793.29</v>
+        <v>-1252.95</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0524</v>
       </c>
       <c r="H43" t="n">
-        <v>1297.91</v>
+        <v>1345.71</v>
       </c>
       <c r="I43" t="n">
-        <v>23161.36</v>
+        <v>22452.08</v>
       </c>
       <c r="J43" t="n">
-        <v>24029.43</v>
+        <v>22389.83</v>
       </c>
       <c r="K43" t="n">
-        <v>24298.94</v>
+        <v>23275.86</v>
       </c>
       <c r="L43" t="n">
-        <v>24568.46</v>
+        <v>24161.88</v>
       </c>
       <c r="M43" t="n">
-        <v>25137.25</v>
+        <v>24573.77</v>
       </c>
       <c r="N43" t="n">
-        <v>25706.05</v>
+        <v>24985.65</v>
       </c>
       <c r="O43" t="n">
-        <v>25676.29</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>26345.81</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4149,81 +4151,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23811.76</v>
+        <v>22827.65</v>
       </c>
       <c r="C44" t="n">
-        <v>23863.71</v>
+        <v>23516.7</v>
       </c>
       <c r="D44" t="n">
-        <v>22518</v>
+        <v>22685.14</v>
       </c>
       <c r="E44" t="n">
-        <v>22671.86</v>
+        <v>23350.03</v>
       </c>
       <c r="F44" t="n">
-        <v>-1252.95</v>
+        <v>678.17</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0524</v>
+        <v>0.0299</v>
       </c>
       <c r="H44" t="n">
-        <v>1345.71</v>
+        <v>831.5599999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>22452.08</v>
+        <v>21172.29</v>
       </c>
       <c r="J44" t="n">
-        <v>22389.83</v>
+        <v>21066.65</v>
       </c>
       <c r="K44" t="n">
-        <v>23275.86</v>
+        <v>21999</v>
       </c>
       <c r="L44" t="n">
-        <v>24161.88</v>
+        <v>22931.36</v>
       </c>
       <c r="M44" t="n">
-        <v>24573.77</v>
+        <v>23344.71</v>
       </c>
       <c r="N44" t="n">
-        <v>24985.65</v>
+        <v>23758.07</v>
       </c>
       <c r="O44" t="n">
-        <v>26345.81</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
+        <v>25209.42</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4235,55 +4231,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>22827.65</v>
+        <v>23404.61</v>
       </c>
       <c r="C45" t="n">
-        <v>23516.7</v>
+        <v>24499.63</v>
       </c>
       <c r="D45" t="n">
-        <v>22685.14</v>
+        <v>23229.38</v>
       </c>
       <c r="E45" t="n">
-        <v>23350.03</v>
+        <v>24175.12</v>
       </c>
       <c r="F45" t="n">
-        <v>678.17</v>
+        <v>825.09</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0353</v>
       </c>
       <c r="H45" t="n">
-        <v>831.5599999999999</v>
+        <v>1270.25</v>
       </c>
       <c r="I45" t="n">
-        <v>21172.29</v>
+        <v>21853.58</v>
       </c>
       <c r="J45" t="n">
-        <v>21066.65</v>
+        <v>22643.03</v>
       </c>
       <c r="K45" t="n">
-        <v>21999</v>
+        <v>22934.25</v>
       </c>
       <c r="L45" t="n">
-        <v>22931.36</v>
+        <v>23225.47</v>
       </c>
       <c r="M45" t="n">
-        <v>23344.71</v>
+        <v>23765.81</v>
       </c>
       <c r="N45" t="n">
-        <v>23758.07</v>
+        <v>24306.14</v>
       </c>
       <c r="O45" t="n">
-        <v>25209.42</v>
+        <v>24348.26</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4301,14 +4301,18 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
@@ -4317,57 +4321,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23404.61</v>
+        <v>24157.65</v>
       </c>
       <c r="C46" t="n">
-        <v>24499.63</v>
+        <v>25221.44</v>
       </c>
       <c r="D46" t="n">
-        <v>23229.38</v>
+        <v>23902.05</v>
       </c>
       <c r="E46" t="n">
-        <v>24175.12</v>
+        <v>24562.24</v>
       </c>
       <c r="F46" t="n">
-        <v>825.09</v>
+        <v>387.12</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.016</v>
       </c>
       <c r="H46" t="n">
-        <v>1270.25</v>
+        <v>1319.39</v>
       </c>
       <c r="I46" t="n">
-        <v>21853.58</v>
+        <v>21959.13</v>
       </c>
       <c r="J46" t="n">
-        <v>22643.03</v>
+        <v>23060.18</v>
       </c>
       <c r="K46" t="n">
-        <v>22934.25</v>
+        <v>23539.99</v>
       </c>
       <c r="L46" t="n">
-        <v>23225.47</v>
+        <v>24019.81</v>
       </c>
       <c r="M46" t="n">
-        <v>23765.81</v>
+        <v>24810.24</v>
       </c>
       <c r="N46" t="n">
-        <v>24306.14</v>
+        <v>25600.68</v>
       </c>
       <c r="O46" t="n">
-        <v>24348.26</v>
+        <v>25769.88</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4385,18 +4389,14 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="11" t="inlineStr">
         <is>
@@ -4412,50 +4412,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24157.65</v>
+        <v>24835.03</v>
       </c>
       <c r="C47" t="n">
-        <v>25221.44</v>
+        <v>25267.39</v>
       </c>
       <c r="D47" t="n">
-        <v>23902.05</v>
+        <v>24756.36</v>
       </c>
       <c r="E47" t="n">
-        <v>24562.24</v>
+        <v>24963.23</v>
       </c>
       <c r="F47" t="n">
-        <v>387.12</v>
+        <v>400.99</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
       </c>
       <c r="H47" t="n">
-        <v>1319.39</v>
+        <v>511.03</v>
       </c>
       <c r="I47" t="n">
-        <v>21959.13</v>
+        <v>22582.66</v>
       </c>
       <c r="J47" t="n">
-        <v>23060.18</v>
+        <v>23243.1</v>
       </c>
       <c r="K47" t="n">
-        <v>23539.99</v>
+        <v>23902.55</v>
       </c>
       <c r="L47" t="n">
-        <v>24019.81</v>
+        <v>24561.99</v>
       </c>
       <c r="M47" t="n">
-        <v>24810.24</v>
+        <v>25221.93</v>
       </c>
       <c r="N47" t="n">
-        <v>25600.68</v>
+        <v>25881.88</v>
       </c>
       <c r="O47" t="n">
-        <v>25769.88</v>
+        <v>26540.83</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4496,50 +4496,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24835.03</v>
+        <v>24993.77</v>
       </c>
       <c r="C48" t="n">
-        <v>25267.39</v>
+        <v>25971.63</v>
       </c>
       <c r="D48" t="n">
-        <v>24756.36</v>
+        <v>24938.34</v>
       </c>
       <c r="E48" t="n">
-        <v>24963.23</v>
+        <v>25884.43</v>
       </c>
       <c r="F48" t="n">
-        <v>400.99</v>
+        <v>921.2</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0369</v>
       </c>
       <c r="H48" t="n">
-        <v>511.03</v>
+        <v>1033.29</v>
       </c>
       <c r="I48" t="n">
-        <v>22582.66</v>
+        <v>24245.33</v>
       </c>
       <c r="J48" t="n">
-        <v>23243.1</v>
+        <v>24427.88</v>
       </c>
       <c r="K48" t="n">
-        <v>23902.55</v>
+        <v>24707.71</v>
       </c>
       <c r="L48" t="n">
-        <v>24561.99</v>
+        <v>24987.55</v>
       </c>
       <c r="M48" t="n">
-        <v>25221.93</v>
+        <v>25218.75</v>
       </c>
       <c r="N48" t="n">
-        <v>25881.88</v>
+        <v>25449.94</v>
       </c>
       <c r="O48" t="n">
-        <v>26540.83</v>
+        <v>25778.42</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4557,73 +4557,73 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24993.77</v>
+        <v>25987.31</v>
       </c>
       <c r="C49" t="n">
-        <v>25971.63</v>
+        <v>26187.57</v>
       </c>
       <c r="D49" t="n">
-        <v>24938.34</v>
+        <v>25389.42</v>
       </c>
       <c r="E49" t="n">
-        <v>25884.43</v>
+        <v>25668.03</v>
       </c>
       <c r="F49" t="n">
-        <v>921.2</v>
+        <v>-216.4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0369</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>1033.29</v>
+        <v>798.15</v>
       </c>
       <c r="I49" t="n">
-        <v>24245.33</v>
+        <v>23905.05</v>
       </c>
       <c r="J49" t="n">
-        <v>24427.88</v>
+        <v>25065.86</v>
       </c>
       <c r="K49" t="n">
-        <v>24707.71</v>
+        <v>25367.78</v>
       </c>
       <c r="L49" t="n">
-        <v>24987.55</v>
+        <v>25669.71</v>
       </c>
       <c r="M49" t="n">
-        <v>25218.75</v>
+        <v>26401.08</v>
       </c>
       <c r="N49" t="n">
-        <v>25449.94</v>
+        <v>27132.44</v>
       </c>
       <c r="O49" t="n">
-        <v>25778.42</v>
+        <v>27004.92</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4634,80 +4634,78 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25987.31</v>
+        <v>25805.18</v>
       </c>
       <c r="C50" t="n">
-        <v>26187.57</v>
+        <v>26060.32</v>
       </c>
       <c r="D50" t="n">
-        <v>25389.42</v>
+        <v>25089.14</v>
       </c>
       <c r="E50" t="n">
-        <v>25668.03</v>
+        <v>25116.85</v>
       </c>
       <c r="F50" t="n">
-        <v>-216.4</v>
+        <v>-551.1799999999999</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0215</v>
       </c>
       <c r="H50" t="n">
-        <v>798.15</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>23905.05</v>
+        <v>24591.27</v>
       </c>
       <c r="J50" t="n">
-        <v>25065.86</v>
+        <v>24809.65</v>
       </c>
       <c r="K50" t="n">
-        <v>25367.78</v>
+        <v>25268.95</v>
       </c>
       <c r="L50" t="n">
-        <v>25669.71</v>
+        <v>25728.26</v>
       </c>
       <c r="M50" t="n">
-        <v>26401.08</v>
+        <v>26067.1</v>
       </c>
       <c r="N50" t="n">
-        <v>27132.44</v>
+        <v>26405.95</v>
       </c>
       <c r="O50" t="n">
-        <v>27004.92</v>
+        <v>26985.72</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4715,12 +4713,14 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4739,57 +4739,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25805.18</v>
+        <v>25303.41</v>
       </c>
       <c r="C51" t="n">
-        <v>26060.32</v>
+        <v>26009.46</v>
       </c>
       <c r="D51" t="n">
-        <v>25089.14</v>
+        <v>25240.62</v>
       </c>
       <c r="E51" t="n">
-        <v>25116.85</v>
+        <v>26009.46</v>
       </c>
       <c r="F51" t="n">
-        <v>-551.1799999999999</v>
+        <v>892.61</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0215</v>
+        <v>0.0355</v>
       </c>
       <c r="H51" t="n">
-        <v>971.1799999999999</v>
+        <v>768.84</v>
       </c>
       <c r="I51" t="n">
-        <v>24591.27</v>
+        <v>24117.96</v>
       </c>
       <c r="J51" t="n">
-        <v>24809.65</v>
+        <v>23916.73</v>
       </c>
       <c r="K51" t="n">
-        <v>25268.95</v>
+        <v>24631.26</v>
       </c>
       <c r="L51" t="n">
-        <v>25728.26</v>
+        <v>25345.79</v>
       </c>
       <c r="M51" t="n">
-        <v>26067.1</v>
+        <v>25602.44</v>
       </c>
       <c r="N51" t="n">
-        <v>26405.95</v>
+        <v>25859.09</v>
       </c>
       <c r="O51" t="n">
-        <v>26985.72</v>
+        <v>27031.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4797,22 +4797,24 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4823,82 +4825,82 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25303.41</v>
+        <v>25780.12</v>
       </c>
       <c r="C52" t="n">
-        <v>26009.46</v>
+        <v>25800.22</v>
       </c>
       <c r="D52" t="n">
-        <v>25240.62</v>
+        <v>25403.44</v>
       </c>
       <c r="E52" t="n">
-        <v>26009.46</v>
+        <v>25584.79</v>
       </c>
       <c r="F52" t="n">
-        <v>892.61</v>
+        <v>-424.67</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0355</v>
+        <v>-0.0163</v>
       </c>
       <c r="H52" t="n">
-        <v>768.84</v>
+        <v>396.78</v>
       </c>
       <c r="I52" t="n">
-        <v>24117.96</v>
+        <v>24471.78</v>
       </c>
       <c r="J52" t="n">
-        <v>23916.73</v>
+        <v>25432.83</v>
       </c>
       <c r="K52" t="n">
-        <v>24631.26</v>
+        <v>25625.04</v>
       </c>
       <c r="L52" t="n">
-        <v>25345.79</v>
+        <v>25817.25</v>
       </c>
       <c r="M52" t="n">
-        <v>25602.44</v>
+        <v>26393.88</v>
       </c>
       <c r="N52" t="n">
-        <v>25859.09</v>
+        <v>26970.51</v>
       </c>
       <c r="O52" t="n">
-        <v>27031.5</v>
+        <v>26778.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4909,57 +4911,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25780.12</v>
+        <v>25420.63</v>
       </c>
       <c r="C53" t="n">
-        <v>25800.22</v>
+        <v>25791.38</v>
       </c>
       <c r="D53" t="n">
-        <v>25403.44</v>
+        <v>25008.87</v>
       </c>
       <c r="E53" t="n">
-        <v>25584.79</v>
+        <v>25650.87</v>
       </c>
       <c r="F53" t="n">
-        <v>-424.67</v>
+        <v>66.08</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0163</v>
+        <v>0.0026</v>
       </c>
       <c r="H53" t="n">
-        <v>396.78</v>
+        <v>782.51</v>
       </c>
       <c r="I53" t="n">
-        <v>24471.78</v>
+        <v>25006.66</v>
       </c>
       <c r="J53" t="n">
-        <v>25432.83</v>
+        <v>25179.49</v>
       </c>
       <c r="K53" t="n">
-        <v>25625.04</v>
+        <v>25386.4</v>
       </c>
       <c r="L53" t="n">
-        <v>25817.25</v>
+        <v>25593.31</v>
       </c>
       <c r="M53" t="n">
-        <v>26393.88</v>
+        <v>25783.18</v>
       </c>
       <c r="N53" t="n">
-        <v>26970.51</v>
+        <v>25973.05</v>
       </c>
       <c r="O53" t="n">
-        <v>26778.3</v>
+        <v>26197</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4971,16 +4973,18 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -5002,57 +5006,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25420.63</v>
+        <v>25652.97</v>
       </c>
       <c r="C54" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D54" t="n">
-        <v>25008.87</v>
+        <v>24570.24</v>
       </c>
       <c r="E54" t="n">
-        <v>25650.87</v>
+        <v>24805.63</v>
       </c>
       <c r="F54" t="n">
-        <v>66.08</v>
+        <v>-845.24</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.033</v>
       </c>
       <c r="H54" t="n">
-        <v>782.51</v>
+        <v>1094.74</v>
       </c>
       <c r="I54" t="n">
-        <v>25006.66</v>
+        <v>24226.36</v>
       </c>
       <c r="J54" t="n">
-        <v>25179.49</v>
+        <v>24993.73</v>
       </c>
       <c r="K54" t="n">
-        <v>25386.4</v>
+        <v>25259.61</v>
       </c>
       <c r="L54" t="n">
-        <v>25593.31</v>
+        <v>25525.5</v>
       </c>
       <c r="M54" t="n">
-        <v>25783.18</v>
+        <v>26042.12</v>
       </c>
       <c r="N54" t="n">
-        <v>25973.05</v>
+        <v>26558.75</v>
       </c>
       <c r="O54" t="n">
-        <v>26197</v>
+        <v>26573.89</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -5060,15 +5064,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5076,81 +5078,73 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25652.97</v>
+        <v>24701.18</v>
       </c>
       <c r="C55" t="n">
-        <v>25664.98</v>
+        <v>24934.06</v>
       </c>
       <c r="D55" t="n">
-        <v>24570.24</v>
+        <v>24357.69</v>
       </c>
       <c r="E55" t="n">
-        <v>24805.63</v>
+        <v>24750.78</v>
       </c>
       <c r="F55" t="n">
-        <v>-845.24</v>
+        <v>-54.85</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.0022</v>
       </c>
       <c r="H55" t="n">
-        <v>1094.74</v>
+        <v>576.37</v>
       </c>
       <c r="I55" t="n">
-        <v>24226.36</v>
+        <v>23475.5</v>
       </c>
       <c r="J55" t="n">
-        <v>24993.73</v>
+        <v>23554.9</v>
       </c>
       <c r="K55" t="n">
-        <v>25259.61</v>
+        <v>24258.26</v>
       </c>
       <c r="L55" t="n">
-        <v>25525.5</v>
+        <v>24961.62</v>
       </c>
       <c r="M55" t="n">
-        <v>26042.12</v>
+        <v>25353</v>
       </c>
       <c r="N55" t="n">
-        <v>26558.75</v>
+        <v>25744.38</v>
       </c>
       <c r="O55" t="n">
-        <v>26573.89</v>
+        <v>26759.72</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5172,50 +5166,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24701.18</v>
+        <v>24748.45</v>
       </c>
       <c r="C56" t="n">
-        <v>24934.06</v>
+        <v>25254.11</v>
       </c>
       <c r="D56" t="n">
-        <v>24357.69</v>
+        <v>24275.56</v>
       </c>
       <c r="E56" t="n">
-        <v>24750.78</v>
+        <v>24510.09</v>
       </c>
       <c r="F56" t="n">
-        <v>-54.85</v>
+        <v>-240.69</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0097</v>
       </c>
       <c r="H56" t="n">
-        <v>576.37</v>
+        <v>978.55</v>
       </c>
       <c r="I56" t="n">
-        <v>23475.5</v>
+        <v>23781.32</v>
       </c>
       <c r="J56" t="n">
-        <v>23554.9</v>
+        <v>24226.86</v>
       </c>
       <c r="K56" t="n">
-        <v>24258.26</v>
+        <v>24462.59</v>
       </c>
       <c r="L56" t="n">
-        <v>24961.62</v>
+        <v>24698.33</v>
       </c>
       <c r="M56" t="n">
-        <v>25353</v>
+        <v>25038.96</v>
       </c>
       <c r="N56" t="n">
-        <v>25744.38</v>
+        <v>25379.6</v>
       </c>
       <c r="O56" t="n">
-        <v>26759.72</v>
+        <v>25510.43</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5223,16 +5217,20 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5245,55 +5243,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24748.45</v>
+        <v>24554.58</v>
       </c>
       <c r="C57" t="n">
-        <v>25254.11</v>
+        <v>24767.22</v>
       </c>
       <c r="D57" t="n">
-        <v>24275.56</v>
+        <v>23865.33</v>
       </c>
       <c r="E57" t="n">
-        <v>24510.09</v>
+        <v>23972.29</v>
       </c>
       <c r="F57" t="n">
-        <v>-240.69</v>
+        <v>-537.8</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0219</v>
       </c>
       <c r="H57" t="n">
-        <v>978.55</v>
+        <v>901.89</v>
       </c>
       <c r="I57" t="n">
-        <v>23781.32</v>
+        <v>23297.01</v>
       </c>
       <c r="J57" t="n">
-        <v>24226.86</v>
+        <v>23404.17</v>
       </c>
       <c r="K57" t="n">
-        <v>24462.59</v>
+        <v>24020.82</v>
       </c>
       <c r="L57" t="n">
-        <v>24698.33</v>
+        <v>24637.46</v>
       </c>
       <c r="M57" t="n">
-        <v>25038.96</v>
+        <v>24999.36</v>
       </c>
       <c r="N57" t="n">
-        <v>25379.6</v>
+        <v>25361.27</v>
       </c>
       <c r="O57" t="n">
-        <v>25510.43</v>
+        <v>26232.66</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5311,10 +5313,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5327,93 +5327,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>24554.58</v>
-      </c>
-      <c r="C58" t="n">
-        <v>24767.22</v>
-      </c>
-      <c r="D58" t="n">
-        <v>24332.64</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24613.27</v>
-      </c>
-      <c r="F58" t="n">
-        <v>103.18</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="H58" t="n">
-        <v>434.58</v>
-      </c>
-      <c r="I58" t="n">
-        <v>23297.01</v>
-      </c>
-      <c r="J58" t="n">
-        <v>23404.17</v>
-      </c>
-      <c r="K58" t="n">
-        <v>24020.82</v>
-      </c>
-      <c r="L58" t="n">
-        <v>24637.46</v>
-      </c>
-      <c r="M58" t="n">
-        <v>24999.36</v>
-      </c>
-      <c r="N58" t="n">
-        <v>25361.27</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26232.66</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5329,6 +5332,86 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>23963.41</v>
+      </c>
+      <c r="C58" t="n">
+        <v>24040.34</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23835.68</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>204.66</v>
+      </c>
+      <c r="I58" t="n">
+        <v>22963.44</v>
+      </c>
+      <c r="J58" t="n">
+        <v>22898.41</v>
+      </c>
+      <c r="K58" t="n">
+        <v>23521.34</v>
+      </c>
+      <c r="L58" t="n">
+        <v>24144.28</v>
+      </c>
+      <c r="M58" t="n">
+        <v>24423.23</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24702.19</v>
+      </c>
+      <c r="O58" t="n">
+        <v>25669.11</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5342,22 +5339,22 @@
         <v>23963.41</v>
       </c>
       <c r="C58" t="n">
-        <v>24040.34</v>
+        <v>24354.11</v>
       </c>
       <c r="D58" t="n">
         <v>23835.68</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>24280.56</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>308.27</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0129</v>
       </c>
       <c r="H58" t="n">
-        <v>204.66</v>
+        <v>518.4299999999999</v>
       </c>
       <c r="I58" t="n">
         <v>22963.44</v>
@@ -5380,10 +5377,8 @@
       <c r="O58" t="n">
         <v>25669.11</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5391,9 +5386,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5410,7 +5405,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1198.14</v>
       </c>
       <c r="I2" t="n">
-        <v>24236.53</v>
+        <v>24532.07</v>
       </c>
       <c r="J2" t="n">
-        <v>24649.43</v>
+        <v>25018.85</v>
       </c>
       <c r="K2" t="n">
-        <v>25029.62</v>
+        <v>25177.39</v>
       </c>
       <c r="L2" t="n">
-        <v>25409.8</v>
+        <v>25335.92</v>
       </c>
       <c r="M2" t="n">
-        <v>25806.35</v>
+        <v>25658.58</v>
       </c>
       <c r="N2" t="n">
-        <v>26202.89</v>
+        <v>25981.23</v>
       </c>
       <c r="O2" t="n">
-        <v>26566.72</v>
+        <v>25975.64</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5345,13 +5345,13 @@
         <v>23835.68</v>
       </c>
       <c r="E58" t="n">
-        <v>24280.56</v>
+        <v>24130.5</v>
       </c>
       <c r="F58" t="n">
-        <v>308.27</v>
+        <v>158.21</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0066</v>
       </c>
       <c r="H58" t="n">
         <v>518.4299999999999</v>
@@ -5386,9 +5386,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1198.14</v>
       </c>
       <c r="I2" t="n">
-        <v>24532.07</v>
+        <v>24709.5</v>
       </c>
       <c r="J2" t="n">
-        <v>25018.85</v>
+        <v>25105.21</v>
       </c>
       <c r="K2" t="n">
-        <v>25177.39</v>
+        <v>25227.41</v>
       </c>
       <c r="L2" t="n">
-        <v>25335.92</v>
+        <v>25349.6</v>
       </c>
       <c r="M2" t="n">
-        <v>25658.58</v>
+        <v>25608.56</v>
       </c>
       <c r="N2" t="n">
-        <v>25981.23</v>
+        <v>25867.51</v>
       </c>
       <c r="O2" t="n">
-        <v>25975.64</v>
+        <v>25852.95</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5342,19 +5342,19 @@
         <v>24354.11</v>
       </c>
       <c r="D58" t="n">
-        <v>23835.68</v>
+        <v>23737.14</v>
       </c>
       <c r="E58" t="n">
-        <v>24130.5</v>
+        <v>23785.79</v>
       </c>
       <c r="F58" t="n">
-        <v>158.21</v>
+        <v>-186.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0078</v>
       </c>
       <c r="H58" t="n">
-        <v>518.4299999999999</v>
+        <v>616.97</v>
       </c>
       <c r="I58" t="n">
         <v>22963.44</v>
@@ -5383,12 +5383,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5405,11 +5407,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25440.01</v>
+        <v>26308.91</v>
       </c>
       <c r="C2" t="n">
-        <v>26585.95</v>
+        <v>27058.03</v>
       </c>
       <c r="D2" t="n">
-        <v>25387.81</v>
+        <v>26280.23</v>
       </c>
       <c r="E2" t="n">
-        <v>26388.16</v>
+        <v>26545.1</v>
       </c>
       <c r="F2" t="n">
-        <v>970.1799999999999</v>
+        <v>156.94</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.0059</v>
       </c>
       <c r="H2" t="n">
-        <v>1198.14</v>
+        <v>777.8</v>
       </c>
       <c r="I2" t="n">
-        <v>24709.5</v>
+        <v>24189.67</v>
       </c>
       <c r="J2" t="n">
-        <v>25105.21</v>
+        <v>25390.66</v>
       </c>
       <c r="K2" t="n">
-        <v>25227.41</v>
+        <v>25789.09</v>
       </c>
       <c r="L2" t="n">
-        <v>25349.6</v>
+        <v>26187.52</v>
       </c>
       <c r="M2" t="n">
-        <v>25608.56</v>
+        <v>26987.23</v>
       </c>
       <c r="N2" t="n">
-        <v>25867.51</v>
+        <v>27786.94</v>
       </c>
       <c r="O2" t="n">
-        <v>25852.95</v>
+        <v>27784.09</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,7 +690,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -698,15 +698,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -718,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26308.91</v>
+        <v>26459.52</v>
       </c>
       <c r="C3" t="n">
-        <v>27058.03</v>
+        <v>26640.53</v>
       </c>
       <c r="D3" t="n">
-        <v>26280.23</v>
+        <v>26003.67</v>
       </c>
       <c r="E3" t="n">
-        <v>26545.1</v>
+        <v>26128.2</v>
       </c>
       <c r="F3" t="n">
-        <v>156.94</v>
+        <v>-416.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0157</v>
       </c>
       <c r="H3" t="n">
-        <v>777.8</v>
+        <v>636.86</v>
       </c>
       <c r="I3" t="n">
-        <v>24189.67</v>
+        <v>25502.43</v>
       </c>
       <c r="J3" t="n">
-        <v>25390.66</v>
+        <v>25705.29</v>
       </c>
       <c r="K3" t="n">
-        <v>25789.09</v>
+        <v>26156.2</v>
       </c>
       <c r="L3" t="n">
-        <v>26187.52</v>
+        <v>26607.11</v>
       </c>
       <c r="M3" t="n">
-        <v>26987.23</v>
+        <v>26934</v>
       </c>
       <c r="N3" t="n">
-        <v>27786.94</v>
+        <v>27260.88</v>
       </c>
       <c r="O3" t="n">
-        <v>27784.09</v>
+        <v>27835.83</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,18 +765,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26459.52</v>
+        <v>26321.57</v>
       </c>
       <c r="C4" t="n">
-        <v>26640.53</v>
+        <v>27381.84</v>
       </c>
       <c r="D4" t="n">
-        <v>26003.67</v>
+        <v>26321.57</v>
       </c>
       <c r="E4" t="n">
-        <v>26128.2</v>
+        <v>27140.92</v>
       </c>
       <c r="F4" t="n">
-        <v>-416.9</v>
+        <v>1012.72</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0388</v>
       </c>
       <c r="H4" t="n">
-        <v>636.86</v>
+        <v>1060.27</v>
       </c>
       <c r="I4" t="n">
-        <v>25502.43</v>
+        <v>25366.81</v>
       </c>
       <c r="J4" t="n">
-        <v>25705.29</v>
+        <v>25394.39</v>
       </c>
       <c r="K4" t="n">
-        <v>26156.2</v>
+        <v>25809.77</v>
       </c>
       <c r="L4" t="n">
-        <v>26607.11</v>
+        <v>26225.15</v>
       </c>
       <c r="M4" t="n">
-        <v>26934</v>
+        <v>26446.63</v>
       </c>
       <c r="N4" t="n">
-        <v>27260.88</v>
+        <v>26668.11</v>
       </c>
       <c r="O4" t="n">
-        <v>27835.83</v>
+        <v>27277.39</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,170 +849,174 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26321.57</v>
+        <v>27003.92</v>
       </c>
       <c r="C5" t="n">
-        <v>27381.84</v>
+        <v>27145.17</v>
       </c>
       <c r="D5" t="n">
-        <v>26321.57</v>
+        <v>26247.04</v>
       </c>
       <c r="E5" t="n">
-        <v>27140.92</v>
+        <v>26290.32</v>
       </c>
       <c r="F5" t="n">
-        <v>1012.72</v>
+        <v>-850.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0388</v>
+        <v>-0.0313</v>
       </c>
       <c r="H5" t="n">
-        <v>1060.27</v>
+        <v>898.13</v>
       </c>
       <c r="I5" t="n">
-        <v>25366.81</v>
+        <v>25261.3</v>
       </c>
       <c r="J5" t="n">
-        <v>25394.39</v>
+        <v>26225.26</v>
       </c>
       <c r="K5" t="n">
-        <v>25809.77</v>
+        <v>26610.79</v>
       </c>
       <c r="L5" t="n">
-        <v>26225.15</v>
+        <v>26996.31</v>
       </c>
       <c r="M5" t="n">
-        <v>26446.63</v>
+        <v>27671.05</v>
       </c>
       <c r="N5" t="n">
-        <v>26668.11</v>
+        <v>28345.8</v>
       </c>
       <c r="O5" t="n">
-        <v>27277.39</v>
+        <v>28442.11</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27003.92</v>
+        <v>25634</v>
       </c>
       <c r="C6" t="n">
-        <v>27145.17</v>
+        <v>26102.68</v>
       </c>
       <c r="D6" t="n">
-        <v>26247.04</v>
+        <v>25145.34</v>
       </c>
       <c r="E6" t="n">
-        <v>26290.32</v>
+        <v>25247.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-850.6</v>
+        <v>-1043.22</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0397</v>
       </c>
       <c r="H6" t="n">
-        <v>898.13</v>
+        <v>957.34</v>
       </c>
       <c r="I6" t="n">
-        <v>25261.3</v>
+        <v>25348.91</v>
       </c>
       <c r="J6" t="n">
-        <v>26225.26</v>
+        <v>25189.3</v>
       </c>
       <c r="K6" t="n">
-        <v>26610.79</v>
+        <v>25841.25</v>
       </c>
       <c r="L6" t="n">
-        <v>26996.31</v>
+        <v>26493.21</v>
       </c>
       <c r="M6" t="n">
-        <v>27671.05</v>
+        <v>26739.39</v>
       </c>
       <c r="N6" t="n">
-        <v>28345.8</v>
+        <v>26985.56</v>
       </c>
       <c r="O6" t="n">
-        <v>28442.11</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
+        <v>28043.3</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
@@ -1052,77 +1056,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25634</v>
+        <v>25884.46</v>
       </c>
       <c r="C7" t="n">
-        <v>26102.68</v>
+        <v>26367.35</v>
       </c>
       <c r="D7" t="n">
-        <v>25145.34</v>
+        <v>25591.66</v>
       </c>
       <c r="E7" t="n">
-        <v>25247.1</v>
+        <v>26160.15</v>
       </c>
       <c r="F7" t="n">
-        <v>-1043.22</v>
+        <v>913.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0362</v>
       </c>
       <c r="H7" t="n">
-        <v>957.34</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>25348.91</v>
+        <v>24188</v>
       </c>
       <c r="J7" t="n">
-        <v>25189.3</v>
+        <v>24101.3</v>
       </c>
       <c r="K7" t="n">
-        <v>25841.25</v>
+        <v>24768.43</v>
       </c>
       <c r="L7" t="n">
-        <v>26493.21</v>
+        <v>25435.55</v>
       </c>
       <c r="M7" t="n">
-        <v>26739.39</v>
+        <v>25725.77</v>
       </c>
       <c r="N7" t="n">
-        <v>26985.56</v>
+        <v>26015.98</v>
       </c>
       <c r="O7" t="n">
-        <v>28043.3</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>27060.02</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1131,59 +1133,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25884.46</v>
+        <v>26495.97</v>
       </c>
       <c r="C8" t="n">
-        <v>26367.35</v>
+        <v>26588.89</v>
       </c>
       <c r="D8" t="n">
-        <v>25591.66</v>
+        <v>25906.65</v>
       </c>
       <c r="E8" t="n">
-        <v>26160.15</v>
+        <v>25906.65</v>
       </c>
       <c r="F8" t="n">
-        <v>913.05</v>
+        <v>-253.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0362</v>
+        <v>-0.0097</v>
       </c>
       <c r="H8" t="n">
-        <v>775.6900000000001</v>
+        <v>682.24</v>
       </c>
       <c r="I8" t="n">
-        <v>24188</v>
+        <v>24815.97</v>
       </c>
       <c r="J8" t="n">
-        <v>24101.3</v>
+        <v>25474.78</v>
       </c>
       <c r="K8" t="n">
-        <v>24768.43</v>
+        <v>25772.31</v>
       </c>
       <c r="L8" t="n">
-        <v>25435.55</v>
+        <v>26069.83</v>
       </c>
       <c r="M8" t="n">
-        <v>25725.77</v>
+        <v>26548</v>
       </c>
       <c r="N8" t="n">
-        <v>26015.98</v>
+        <v>27026.16</v>
       </c>
       <c r="O8" t="n">
-        <v>27060.02</v>
+        <v>27143.04</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,12 +1189,14 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
@@ -1204,10 +1204,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1217,55 +1215,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26495.97</v>
+        <v>25999.17</v>
       </c>
       <c r="C9" t="n">
-        <v>26588.89</v>
+        <v>26490.71</v>
       </c>
       <c r="D9" t="n">
-        <v>25906.65</v>
+        <v>25496.13</v>
       </c>
       <c r="E9" t="n">
-        <v>25906.65</v>
+        <v>26241.83</v>
       </c>
       <c r="F9" t="n">
-        <v>-253.5</v>
+        <v>335.18</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0129</v>
       </c>
       <c r="H9" t="n">
-        <v>682.24</v>
+        <v>994.58</v>
       </c>
       <c r="I9" t="n">
-        <v>24815.97</v>
+        <v>25224.41</v>
       </c>
       <c r="J9" t="n">
-        <v>25474.78</v>
+        <v>25053.85</v>
       </c>
       <c r="K9" t="n">
-        <v>25772.31</v>
+        <v>25565.53</v>
       </c>
       <c r="L9" t="n">
-        <v>26069.83</v>
+        <v>26077.21</v>
       </c>
       <c r="M9" t="n">
-        <v>26548</v>
+        <v>26247.77</v>
       </c>
       <c r="N9" t="n">
-        <v>27026.16</v>
+        <v>26418.33</v>
       </c>
       <c r="O9" t="n">
-        <v>27143.04</v>
+        <v>27271.13</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,22 +1277,24 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1301,57 +1305,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25999.17</v>
+        <v>26319.4</v>
       </c>
       <c r="C10" t="n">
-        <v>26490.71</v>
+        <v>27188.81</v>
       </c>
       <c r="D10" t="n">
-        <v>25496.13</v>
+        <v>26302.93</v>
       </c>
       <c r="E10" t="n">
-        <v>26241.83</v>
+        <v>26572.46</v>
       </c>
       <c r="F10" t="n">
-        <v>335.18</v>
+        <v>330.63</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
       <c r="H10" t="n">
-        <v>994.58</v>
+        <v>885.88</v>
       </c>
       <c r="I10" t="n">
-        <v>25224.41</v>
+        <v>24501.55</v>
       </c>
       <c r="J10" t="n">
-        <v>25053.85</v>
+        <v>25371.45</v>
       </c>
       <c r="K10" t="n">
-        <v>25565.53</v>
+        <v>25744.54</v>
       </c>
       <c r="L10" t="n">
-        <v>26077.21</v>
+        <v>26117.63</v>
       </c>
       <c r="M10" t="n">
-        <v>26247.77</v>
+        <v>26739.12</v>
       </c>
       <c r="N10" t="n">
-        <v>26418.33</v>
+        <v>27360.61</v>
       </c>
       <c r="O10" t="n">
-        <v>27271.13</v>
+        <v>27485.29</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,10 +1363,8 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
@@ -1374,10 +1376,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1387,88 +1387,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26319.4</v>
+        <v>26441.7</v>
       </c>
       <c r="C11" t="n">
-        <v>27188.81</v>
+        <v>26531.8</v>
       </c>
       <c r="D11" t="n">
-        <v>26302.93</v>
+        <v>25178.63</v>
       </c>
       <c r="E11" t="n">
-        <v>26572.46</v>
+        <v>25220.02</v>
       </c>
       <c r="F11" t="n">
-        <v>330.63</v>
+        <v>-1352.44</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0126</v>
+        <v>-0.0509</v>
       </c>
       <c r="H11" t="n">
-        <v>885.88</v>
+        <v>1353.17</v>
       </c>
       <c r="I11" t="n">
-        <v>24501.55</v>
+        <v>25417.05</v>
       </c>
       <c r="J11" t="n">
-        <v>25371.45</v>
+        <v>25599.88</v>
       </c>
       <c r="K11" t="n">
-        <v>25744.54</v>
+        <v>26129.52</v>
       </c>
       <c r="L11" t="n">
-        <v>26117.63</v>
+        <v>26659.17</v>
       </c>
       <c r="M11" t="n">
-        <v>26739.12</v>
+        <v>27015.4</v>
       </c>
       <c r="N11" t="n">
-        <v>27360.61</v>
+        <v>27371.64</v>
       </c>
       <c r="O11" t="n">
-        <v>27485.29</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+        <v>28074.69</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1476,74 +1476,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26441.7</v>
+        <v>25452.87</v>
       </c>
       <c r="C12" t="n">
-        <v>26531.8</v>
+        <v>26136.27</v>
       </c>
       <c r="D12" t="n">
-        <v>25178.63</v>
+        <v>25369.29</v>
       </c>
       <c r="E12" t="n">
-        <v>25220.02</v>
+        <v>25858.89</v>
       </c>
       <c r="F12" t="n">
-        <v>-1352.44</v>
+        <v>638.87</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0509</v>
+        <v>0.0253</v>
       </c>
       <c r="H12" t="n">
-        <v>1353.17</v>
+        <v>766.98</v>
       </c>
       <c r="I12" t="n">
-        <v>25417.05</v>
+        <v>23825.46</v>
       </c>
       <c r="J12" t="n">
-        <v>25599.88</v>
+        <v>23549.25</v>
       </c>
       <c r="K12" t="n">
-        <v>26129.52</v>
+        <v>24543.43</v>
       </c>
       <c r="L12" t="n">
-        <v>26659.17</v>
+        <v>25537.62</v>
       </c>
       <c r="M12" t="n">
-        <v>27015.4</v>
+        <v>25896.6</v>
       </c>
       <c r="N12" t="n">
-        <v>27371.64</v>
+        <v>26255.59</v>
       </c>
       <c r="O12" t="n">
-        <v>28074.69</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>27884.97</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1555,55 +1551,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25452.87</v>
+        <v>25945.87</v>
       </c>
       <c r="C13" t="n">
-        <v>26136.27</v>
+        <v>26264.13</v>
       </c>
       <c r="D13" t="n">
-        <v>25369.29</v>
+        <v>25649.3</v>
       </c>
       <c r="E13" t="n">
-        <v>25858.89</v>
+        <v>26085.08</v>
       </c>
       <c r="F13" t="n">
-        <v>638.87</v>
+        <v>226.19</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0253</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>766.98</v>
+        <v>614.83</v>
       </c>
       <c r="I13" t="n">
-        <v>23825.46</v>
+        <v>24602.31</v>
       </c>
       <c r="J13" t="n">
-        <v>23549.25</v>
+        <v>25144.97</v>
       </c>
       <c r="K13" t="n">
-        <v>24543.43</v>
+        <v>25475.4</v>
       </c>
       <c r="L13" t="n">
-        <v>25537.62</v>
+        <v>25805.83</v>
       </c>
       <c r="M13" t="n">
-        <v>25896.6</v>
+        <v>26242.38</v>
       </c>
       <c r="N13" t="n">
-        <v>26255.59</v>
+        <v>26678.93</v>
       </c>
       <c r="O13" t="n">
-        <v>27884.97</v>
+        <v>26903.25</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1637,76 +1637,78 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25945.87</v>
+        <v>26067.86</v>
       </c>
       <c r="C14" t="n">
-        <v>26264.13</v>
+        <v>26151.46</v>
       </c>
       <c r="D14" t="n">
-        <v>25649.3</v>
+        <v>25257.61</v>
       </c>
       <c r="E14" t="n">
-        <v>26085.08</v>
+        <v>25976.79</v>
       </c>
       <c r="F14" t="n">
-        <v>226.19</v>
+        <v>-108.29</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0042</v>
       </c>
       <c r="H14" t="n">
-        <v>614.83</v>
+        <v>893.85</v>
       </c>
       <c r="I14" t="n">
-        <v>24602.31</v>
+        <v>25034.47</v>
       </c>
       <c r="J14" t="n">
-        <v>25144.97</v>
+        <v>25534.43</v>
       </c>
       <c r="K14" t="n">
-        <v>25475.4</v>
+        <v>25777.67</v>
       </c>
       <c r="L14" t="n">
-        <v>25805.83</v>
+        <v>26020.9</v>
       </c>
       <c r="M14" t="n">
-        <v>26242.38</v>
+        <v>26392.5</v>
       </c>
       <c r="N14" t="n">
-        <v>26678.93</v>
+        <v>26764.09</v>
       </c>
       <c r="O14" t="n">
-        <v>26903.25</v>
+        <v>26878.96</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1719,59 +1721,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26067.86</v>
+        <v>25718.14</v>
       </c>
       <c r="C15" t="n">
-        <v>26151.46</v>
+        <v>25824.44</v>
       </c>
       <c r="D15" t="n">
-        <v>25257.61</v>
+        <v>25086.54</v>
       </c>
       <c r="E15" t="n">
-        <v>25976.79</v>
+        <v>25690.53</v>
       </c>
       <c r="F15" t="n">
-        <v>-108.29</v>
+        <v>-286.26</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.011</v>
       </c>
       <c r="H15" t="n">
-        <v>893.85</v>
+        <v>737.9</v>
       </c>
       <c r="I15" t="n">
-        <v>25034.47</v>
+        <v>24363.76</v>
       </c>
       <c r="J15" t="n">
-        <v>25534.43</v>
+        <v>25219.06</v>
       </c>
       <c r="K15" t="n">
-        <v>25777.67</v>
+        <v>25529.86</v>
       </c>
       <c r="L15" t="n">
-        <v>26020.9</v>
+        <v>25840.66</v>
       </c>
       <c r="M15" t="n">
-        <v>26392.5</v>
+        <v>26423.71</v>
       </c>
       <c r="N15" t="n">
-        <v>26764.09</v>
+        <v>27006.77</v>
       </c>
       <c r="O15" t="n">
-        <v>26878.96</v>
+        <v>27045.31</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1810,71 +1808,69 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25718.14</v>
+        <v>25795.94</v>
       </c>
       <c r="C16" t="n">
-        <v>25824.44</v>
+        <v>25927.66</v>
       </c>
       <c r="D16" t="n">
-        <v>25086.54</v>
+        <v>25671.33</v>
       </c>
       <c r="E16" t="n">
-        <v>25690.53</v>
+        <v>25818.93</v>
       </c>
       <c r="F16" t="n">
-        <v>-286.26</v>
+        <v>128.4</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H16" t="n">
-        <v>737.9</v>
+        <v>256.33</v>
       </c>
       <c r="I16" t="n">
-        <v>24363.76</v>
+        <v>24348.64</v>
       </c>
       <c r="J16" t="n">
-        <v>25219.06</v>
+        <v>25070.15</v>
       </c>
       <c r="K16" t="n">
-        <v>25529.86</v>
+        <v>25321.58</v>
       </c>
       <c r="L16" t="n">
-        <v>25840.66</v>
+        <v>25573.01</v>
       </c>
       <c r="M16" t="n">
-        <v>26423.71</v>
+        <v>26059.48</v>
       </c>
       <c r="N16" t="n">
-        <v>27006.77</v>
+        <v>26545.95</v>
       </c>
       <c r="O16" t="n">
-        <v>27045.31</v>
+        <v>26562.34</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1887,64 +1883,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25795.94</v>
+        <v>25928.89</v>
       </c>
       <c r="C17" t="n">
-        <v>25927.66</v>
+        <v>26345.63</v>
       </c>
       <c r="D17" t="n">
-        <v>25671.33</v>
+        <v>25554.31</v>
       </c>
       <c r="E17" t="n">
-        <v>25818.93</v>
+        <v>26338.47</v>
       </c>
       <c r="F17" t="n">
-        <v>128.4</v>
+        <v>519.54</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0201</v>
       </c>
       <c r="H17" t="n">
-        <v>256.33</v>
+        <v>791.3200000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>24348.64</v>
+        <v>25415</v>
       </c>
       <c r="J17" t="n">
-        <v>25070.15</v>
+        <v>25572.32</v>
       </c>
       <c r="K17" t="n">
-        <v>25321.58</v>
+        <v>25690.76</v>
       </c>
       <c r="L17" t="n">
-        <v>25573.01</v>
+        <v>25809.21</v>
       </c>
       <c r="M17" t="n">
-        <v>26059.48</v>
+        <v>25947.09</v>
       </c>
       <c r="N17" t="n">
-        <v>26545.95</v>
+        <v>26084.98</v>
       </c>
       <c r="O17" t="n">
-        <v>26562.34</v>
+        <v>26183.99</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -1953,106 +1957,102 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25928.89</v>
+        <v>26361.44</v>
       </c>
       <c r="C18" t="n">
-        <v>26345.63</v>
+        <v>26858.13</v>
       </c>
       <c r="D18" t="n">
-        <v>25554.31</v>
+        <v>25960.34</v>
       </c>
       <c r="E18" t="n">
-        <v>26338.47</v>
+        <v>26231.79</v>
       </c>
       <c r="F18" t="n">
-        <v>519.54</v>
+        <v>-106.68</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.0041</v>
       </c>
       <c r="H18" t="n">
-        <v>791.3200000000001</v>
+        <v>897.79</v>
       </c>
       <c r="I18" t="n">
-        <v>25415</v>
+        <v>24762.99</v>
       </c>
       <c r="J18" t="n">
-        <v>25572.32</v>
+        <v>25741.4</v>
       </c>
       <c r="K18" t="n">
-        <v>25690.76</v>
+        <v>25942.81</v>
       </c>
       <c r="L18" t="n">
-        <v>25809.21</v>
+        <v>26144.22</v>
       </c>
       <c r="M18" t="n">
-        <v>25947.09</v>
+        <v>26734.13</v>
       </c>
       <c r="N18" t="n">
-        <v>26084.98</v>
+        <v>27324.04</v>
       </c>
       <c r="O18" t="n">
-        <v>26183.99</v>
+        <v>27136.95</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2068,50 +2068,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26361.44</v>
+        <v>26376.84</v>
       </c>
       <c r="C19" t="n">
-        <v>26858.13</v>
+        <v>27206.84</v>
       </c>
       <c r="D19" t="n">
-        <v>25960.34</v>
+        <v>26187.76</v>
       </c>
       <c r="E19" t="n">
-        <v>26231.79</v>
+        <v>26844.96</v>
       </c>
       <c r="F19" t="n">
-        <v>-106.68</v>
+        <v>613.17</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0234</v>
       </c>
       <c r="H19" t="n">
-        <v>897.79</v>
+        <v>1019.08</v>
       </c>
       <c r="I19" t="n">
-        <v>24762.99</v>
+        <v>25062.55</v>
       </c>
       <c r="J19" t="n">
-        <v>25741.4</v>
+        <v>25245.27</v>
       </c>
       <c r="K19" t="n">
-        <v>25942.81</v>
+        <v>25782.89</v>
       </c>
       <c r="L19" t="n">
-        <v>26144.22</v>
+        <v>26320.51</v>
       </c>
       <c r="M19" t="n">
-        <v>26734.13</v>
+        <v>26680.68</v>
       </c>
       <c r="N19" t="n">
-        <v>27324.04</v>
+        <v>27040.86</v>
       </c>
       <c r="O19" t="n">
-        <v>27136.95</v>
+        <v>27755.92</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2124,17 +2124,19 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2143,59 +2145,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26376.84</v>
+        <v>26641.6</v>
       </c>
       <c r="C20" t="n">
-        <v>27206.84</v>
+        <v>26895.94</v>
       </c>
       <c r="D20" t="n">
-        <v>26187.76</v>
+        <v>26363.86</v>
       </c>
       <c r="E20" t="n">
-        <v>26844.96</v>
+        <v>26749.51</v>
       </c>
       <c r="F20" t="n">
-        <v>613.17</v>
+        <v>-95.45</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0234</v>
+        <v>-0.0036</v>
       </c>
       <c r="H20" t="n">
-        <v>1019.08</v>
+        <v>532.08</v>
       </c>
       <c r="I20" t="n">
-        <v>25062.55</v>
+        <v>25168.68</v>
       </c>
       <c r="J20" t="n">
-        <v>25245.27</v>
+        <v>25899.71</v>
       </c>
       <c r="K20" t="n">
-        <v>25782.89</v>
+        <v>26335.42</v>
       </c>
       <c r="L20" t="n">
-        <v>26320.51</v>
+        <v>26771.13</v>
       </c>
       <c r="M20" t="n">
-        <v>26680.68</v>
+        <v>27354.5</v>
       </c>
       <c r="N20" t="n">
-        <v>27040.86</v>
+        <v>27937.87</v>
       </c>
       <c r="O20" t="n">
-        <v>27755.92</v>
+        <v>28225.92</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2206,20 +2204,16 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2229,55 +2223,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26641.6</v>
+        <v>26844.04</v>
       </c>
       <c r="C21" t="n">
-        <v>26895.94</v>
+        <v>28056.1</v>
       </c>
       <c r="D21" t="n">
-        <v>26363.86</v>
+        <v>26619.83</v>
       </c>
       <c r="E21" t="n">
-        <v>26749.51</v>
+        <v>27387.11</v>
       </c>
       <c r="F21" t="n">
-        <v>-95.45</v>
+        <v>637.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0238</v>
       </c>
       <c r="H21" t="n">
-        <v>532.08</v>
+        <v>1436.27</v>
       </c>
       <c r="I21" t="n">
-        <v>25168.68</v>
+        <v>25831.78</v>
       </c>
       <c r="J21" t="n">
-        <v>25899.71</v>
+        <v>26277.23</v>
       </c>
       <c r="K21" t="n">
-        <v>26335.42</v>
+        <v>26483.47</v>
       </c>
       <c r="L21" t="n">
-        <v>26771.13</v>
+        <v>26689.7</v>
       </c>
       <c r="M21" t="n">
-        <v>27354.5</v>
+        <v>27015.55</v>
       </c>
       <c r="N21" t="n">
-        <v>27937.87</v>
+        <v>27341.4</v>
       </c>
       <c r="O21" t="n">
-        <v>28225.92</v>
+        <v>27428.02</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2288,78 +2286,80 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26844.04</v>
+        <v>27097.34</v>
       </c>
       <c r="C22" t="n">
-        <v>28056.1</v>
+        <v>27126.48</v>
       </c>
       <c r="D22" t="n">
-        <v>26619.83</v>
+        <v>26295.03</v>
       </c>
       <c r="E22" t="n">
-        <v>27387.11</v>
+        <v>26559.95</v>
       </c>
       <c r="F22" t="n">
-        <v>637.6</v>
+        <v>-827.16</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0238</v>
+        <v>-0.0302</v>
       </c>
       <c r="H22" t="n">
-        <v>1436.27</v>
+        <v>831.45</v>
       </c>
       <c r="I22" t="n">
-        <v>25831.78</v>
+        <v>25183.56</v>
       </c>
       <c r="J22" t="n">
-        <v>26277.23</v>
+        <v>25975.41</v>
       </c>
       <c r="K22" t="n">
-        <v>26483.47</v>
+        <v>26668.97</v>
       </c>
       <c r="L22" t="n">
-        <v>26689.7</v>
+        <v>27362.54</v>
       </c>
       <c r="M22" t="n">
-        <v>27015.55</v>
+        <v>28105.24</v>
       </c>
       <c r="N22" t="n">
-        <v>27341.4</v>
+        <v>28847.95</v>
       </c>
       <c r="O22" t="n">
-        <v>27428.02</v>
+        <v>29492.37</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,83 +2367,83 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27097.34</v>
+        <v>26982.49</v>
       </c>
       <c r="C23" t="n">
-        <v>27126.48</v>
+        <v>27397.65</v>
       </c>
       <c r="D23" t="n">
-        <v>26295.03</v>
+        <v>26444.46</v>
       </c>
       <c r="E23" t="n">
-        <v>26559.95</v>
+        <v>26567.12</v>
       </c>
       <c r="F23" t="n">
-        <v>-827.16</v>
+        <v>7.17</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0003</v>
       </c>
       <c r="H23" t="n">
-        <v>831.45</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>25183.56</v>
+        <v>25463.58</v>
       </c>
       <c r="J23" t="n">
-        <v>25975.41</v>
+        <v>25653.1</v>
       </c>
       <c r="K23" t="n">
-        <v>26668.97</v>
+        <v>26144.22</v>
       </c>
       <c r="L23" t="n">
-        <v>27362.54</v>
+        <v>26635.35</v>
       </c>
       <c r="M23" t="n">
-        <v>28105.24</v>
+        <v>26975.67</v>
       </c>
       <c r="N23" t="n">
-        <v>28847.95</v>
+        <v>27316</v>
       </c>
       <c r="O23" t="n">
-        <v>29492.37</v>
+        <v>27957.93</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,21 +2451,23 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2475,59 +2477,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26982.49</v>
+        <v>26501.2</v>
       </c>
       <c r="C24" t="n">
-        <v>27397.65</v>
+        <v>26734.41</v>
       </c>
       <c r="D24" t="n">
-        <v>26444.46</v>
+        <v>26356.96</v>
       </c>
       <c r="E24" t="n">
-        <v>26567.12</v>
+        <v>26413.35</v>
       </c>
       <c r="F24" t="n">
-        <v>7.17</v>
+        <v>-153.77</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0058</v>
       </c>
       <c r="H24" t="n">
-        <v>953.1900000000001</v>
+        <v>377.45</v>
       </c>
       <c r="I24" t="n">
-        <v>25463.58</v>
+        <v>25491.27</v>
       </c>
       <c r="J24" t="n">
-        <v>25653.1</v>
+        <v>25436.96</v>
       </c>
       <c r="K24" t="n">
-        <v>26144.22</v>
+        <v>26090.52</v>
       </c>
       <c r="L24" t="n">
-        <v>26635.35</v>
+        <v>26744.09</v>
       </c>
       <c r="M24" t="n">
-        <v>26975.67</v>
+        <v>27043.71</v>
       </c>
       <c r="N24" t="n">
-        <v>27316</v>
+        <v>27343.34</v>
       </c>
       <c r="O24" t="n">
-        <v>27957.93</v>
+        <v>28350.84</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2535,23 +2533,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2561,55 +2557,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26501.2</v>
+        <v>26798.97</v>
       </c>
       <c r="C25" t="n">
-        <v>26734.41</v>
+        <v>27156.28</v>
       </c>
       <c r="D25" t="n">
-        <v>26356.96</v>
+        <v>26373.01</v>
       </c>
       <c r="E25" t="n">
-        <v>26413.35</v>
+        <v>26630.54</v>
       </c>
       <c r="F25" t="n">
-        <v>-153.77</v>
+        <v>217.19</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>377.45</v>
+        <v>783.27</v>
       </c>
       <c r="I25" t="n">
-        <v>25491.27</v>
+        <v>25979.51</v>
       </c>
       <c r="J25" t="n">
-        <v>25436.96</v>
+        <v>25969.73</v>
       </c>
       <c r="K25" t="n">
-        <v>26090.52</v>
+        <v>26224.62</v>
       </c>
       <c r="L25" t="n">
-        <v>26744.09</v>
+        <v>26479.52</v>
       </c>
       <c r="M25" t="n">
-        <v>27043.71</v>
+        <v>26602.07</v>
       </c>
       <c r="N25" t="n">
-        <v>27343.34</v>
+        <v>26724.63</v>
       </c>
       <c r="O25" t="n">
-        <v>28350.84</v>
+        <v>27111.86</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2617,116 +2617,116 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26798.97</v>
+        <v>26305.58</v>
       </c>
       <c r="C26" t="n">
-        <v>27156.28</v>
+        <v>26403.85</v>
       </c>
       <c r="D26" t="n">
-        <v>26373.01</v>
+        <v>24958.43</v>
       </c>
       <c r="E26" t="n">
-        <v>26630.54</v>
+        <v>25757.29</v>
       </c>
       <c r="F26" t="n">
-        <v>217.19</v>
+        <v>-873.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="H26" t="n">
-        <v>783.27</v>
+        <v>1445.42</v>
       </c>
       <c r="I26" t="n">
-        <v>25979.51</v>
+        <v>25589.74</v>
       </c>
       <c r="J26" t="n">
-        <v>25969.73</v>
+        <v>25780.22</v>
       </c>
       <c r="K26" t="n">
-        <v>26224.62</v>
+        <v>26238.9</v>
       </c>
       <c r="L26" t="n">
-        <v>26479.52</v>
+        <v>26697.59</v>
       </c>
       <c r="M26" t="n">
-        <v>26602.07</v>
+        <v>27022.17</v>
       </c>
       <c r="N26" t="n">
-        <v>26724.63</v>
+        <v>27346.76</v>
       </c>
       <c r="O26" t="n">
-        <v>27111.86</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+        <v>27939.55</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2734,69 +2734,65 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26305.58</v>
+        <v>25075.74</v>
       </c>
       <c r="C27" t="n">
-        <v>26403.85</v>
+        <v>26149.64</v>
       </c>
       <c r="D27" t="n">
-        <v>24958.43</v>
+        <v>24906</v>
       </c>
       <c r="E27" t="n">
-        <v>25757.29</v>
+        <v>25465.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-873.25</v>
+        <v>-291.69</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0328</v>
+        <v>-0.0113</v>
       </c>
       <c r="H27" t="n">
-        <v>1445.42</v>
+        <v>1243.64</v>
       </c>
       <c r="I27" t="n">
-        <v>25589.74</v>
+        <v>23513.01</v>
       </c>
       <c r="J27" t="n">
-        <v>25780.22</v>
+        <v>24349.94</v>
       </c>
       <c r="K27" t="n">
-        <v>26238.9</v>
+        <v>25034.58</v>
       </c>
       <c r="L27" t="n">
-        <v>26697.59</v>
+        <v>25719.21</v>
       </c>
       <c r="M27" t="n">
-        <v>27022.17</v>
+        <v>26480</v>
       </c>
       <c r="N27" t="n">
-        <v>27346.76</v>
+        <v>27240.78</v>
       </c>
       <c r="O27" t="n">
-        <v>27939.55</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>27849.27</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2818,50 +2814,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25075.74</v>
+        <v>25436.27</v>
       </c>
       <c r="C28" t="n">
-        <v>26149.64</v>
+        <v>26250.14</v>
       </c>
       <c r="D28" t="n">
-        <v>24906</v>
+        <v>25121.46</v>
       </c>
       <c r="E28" t="n">
-        <v>25465.6</v>
+        <v>25277.32</v>
       </c>
       <c r="F28" t="n">
-        <v>-291.69</v>
+        <v>-188.28</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.0074</v>
       </c>
       <c r="H28" t="n">
-        <v>1243.64</v>
+        <v>1128.68</v>
       </c>
       <c r="I28" t="n">
-        <v>23513.01</v>
+        <v>23662.36</v>
       </c>
       <c r="J28" t="n">
-        <v>24349.94</v>
+        <v>24190.85</v>
       </c>
       <c r="K28" t="n">
-        <v>25034.58</v>
+        <v>24843.78</v>
       </c>
       <c r="L28" t="n">
-        <v>25719.21</v>
+        <v>25496.71</v>
       </c>
       <c r="M28" t="n">
-        <v>26480</v>
+        <v>26087.42</v>
       </c>
       <c r="N28" t="n">
-        <v>27240.78</v>
+        <v>26678.13</v>
       </c>
       <c r="O28" t="n">
-        <v>27849.27</v>
+        <v>27393.28</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2869,19 +2865,19 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2893,55 +2889,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25436.27</v>
+        <v>24789.14</v>
       </c>
       <c r="C29" t="n">
-        <v>26250.14</v>
+        <v>25390.3</v>
       </c>
       <c r="D29" t="n">
-        <v>25121.46</v>
+        <v>24203.54</v>
       </c>
       <c r="E29" t="n">
-        <v>25277.32</v>
+        <v>24951.88</v>
       </c>
       <c r="F29" t="n">
-        <v>-188.28</v>
+        <v>-325.44</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0129</v>
       </c>
       <c r="H29" t="n">
-        <v>1128.68</v>
+        <v>1186.76</v>
       </c>
       <c r="I29" t="n">
-        <v>23662.36</v>
+        <v>23992.78</v>
       </c>
       <c r="J29" t="n">
-        <v>24190.85</v>
+        <v>23944.4</v>
       </c>
       <c r="K29" t="n">
-        <v>24843.78</v>
+        <v>24712.98</v>
       </c>
       <c r="L29" t="n">
-        <v>25496.71</v>
+        <v>25481.56</v>
       </c>
       <c r="M29" t="n">
-        <v>26087.42</v>
+        <v>25841.66</v>
       </c>
       <c r="N29" t="n">
-        <v>26678.13</v>
+        <v>26201.76</v>
       </c>
       <c r="O29" t="n">
-        <v>27393.28</v>
+        <v>27378.82</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2949,18 +2949,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2973,59 +2973,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24789.14</v>
+        <v>24532.85</v>
       </c>
       <c r="C30" t="n">
-        <v>25390.3</v>
+        <v>25429.76</v>
       </c>
       <c r="D30" t="n">
-        <v>24203.54</v>
+        <v>24409.57</v>
       </c>
       <c r="E30" t="n">
-        <v>24951.88</v>
+        <v>25116.53</v>
       </c>
       <c r="F30" t="n">
-        <v>-325.44</v>
+        <v>164.65</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0066</v>
       </c>
       <c r="H30" t="n">
-        <v>1186.76</v>
+        <v>1020.19</v>
       </c>
       <c r="I30" t="n">
-        <v>23992.78</v>
+        <v>23016.78</v>
       </c>
       <c r="J30" t="n">
-        <v>23944.4</v>
+        <v>23842.6</v>
       </c>
       <c r="K30" t="n">
-        <v>24712.98</v>
+        <v>24358.5</v>
       </c>
       <c r="L30" t="n">
-        <v>25481.56</v>
+        <v>24874.4</v>
       </c>
       <c r="M30" t="n">
-        <v>25841.66</v>
+        <v>25545.26</v>
       </c>
       <c r="N30" t="n">
-        <v>26201.76</v>
+        <v>26216.12</v>
       </c>
       <c r="O30" t="n">
-        <v>27378.82</v>
+        <v>26577.06</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3033,14 +3029,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3057,55 +3051,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24532.85</v>
+        <v>25772.56</v>
       </c>
       <c r="C31" t="n">
-        <v>25429.76</v>
+        <v>26073.97</v>
       </c>
       <c r="D31" t="n">
-        <v>24409.57</v>
+        <v>25653.63</v>
       </c>
       <c r="E31" t="n">
-        <v>25116.53</v>
+        <v>25893.54</v>
       </c>
       <c r="F31" t="n">
-        <v>164.65</v>
+        <v>777.01</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0309</v>
       </c>
       <c r="H31" t="n">
-        <v>1020.19</v>
+        <v>420.34</v>
       </c>
       <c r="I31" t="n">
-        <v>23016.78</v>
+        <v>23389.38</v>
       </c>
       <c r="J31" t="n">
-        <v>23842.6</v>
+        <v>24194.77</v>
       </c>
       <c r="K31" t="n">
-        <v>24358.5</v>
+        <v>24606.43</v>
       </c>
       <c r="L31" t="n">
-        <v>24874.4</v>
+        <v>25018.1</v>
       </c>
       <c r="M31" t="n">
-        <v>25545.26</v>
+        <v>25626.62</v>
       </c>
       <c r="N31" t="n">
-        <v>26216.12</v>
+        <v>26235.15</v>
       </c>
       <c r="O31" t="n">
-        <v>26577.06</v>
+        <v>26449.95</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3118,11 +3116,13 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3144,50 +3144,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25772.56</v>
+        <v>25708.64</v>
       </c>
       <c r="C32" t="n">
-        <v>26073.97</v>
+        <v>26403.07</v>
       </c>
       <c r="D32" t="n">
-        <v>25653.63</v>
+        <v>25508.53</v>
       </c>
       <c r="E32" t="n">
-        <v>25893.54</v>
+        <v>26160.33</v>
       </c>
       <c r="F32" t="n">
-        <v>777.01</v>
+        <v>266.79</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.0103</v>
       </c>
       <c r="H32" t="n">
-        <v>420.34</v>
+        <v>894.54</v>
       </c>
       <c r="I32" t="n">
-        <v>23389.38</v>
+        <v>25233.29</v>
       </c>
       <c r="J32" t="n">
-        <v>24194.77</v>
+        <v>25488.07</v>
       </c>
       <c r="K32" t="n">
-        <v>24606.43</v>
+        <v>25683.37</v>
       </c>
       <c r="L32" t="n">
-        <v>25018.1</v>
+        <v>25878.67</v>
       </c>
       <c r="M32" t="n">
-        <v>25626.62</v>
+        <v>26103.71</v>
       </c>
       <c r="N32" t="n">
-        <v>26235.15</v>
+        <v>26328.75</v>
       </c>
       <c r="O32" t="n">
-        <v>26449.95</v>
+        <v>26494.31</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3195,8 +3195,10 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
@@ -3208,8 +3210,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3221,57 +3225,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25708.64</v>
+        <v>26204.61</v>
       </c>
       <c r="C33" t="n">
-        <v>26403.07</v>
+        <v>26529.49</v>
       </c>
       <c r="D33" t="n">
-        <v>25508.53</v>
+        <v>25639.26</v>
       </c>
       <c r="E33" t="n">
-        <v>26160.33</v>
+        <v>25978.07</v>
       </c>
       <c r="F33" t="n">
-        <v>266.79</v>
+        <v>-182.26</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.007</v>
       </c>
       <c r="H33" t="n">
-        <v>894.54</v>
+        <v>890.23</v>
       </c>
       <c r="I33" t="n">
-        <v>25233.29</v>
+        <v>24613.99</v>
       </c>
       <c r="J33" t="n">
-        <v>25488.07</v>
+        <v>25368.05</v>
       </c>
       <c r="K33" t="n">
-        <v>25683.37</v>
+        <v>25713.06</v>
       </c>
       <c r="L33" t="n">
-        <v>25878.67</v>
+        <v>26058.06</v>
       </c>
       <c r="M33" t="n">
-        <v>26103.71</v>
+        <v>26607.6</v>
       </c>
       <c r="N33" t="n">
-        <v>26328.75</v>
+        <v>27157.14</v>
       </c>
       <c r="O33" t="n">
-        <v>26494.31</v>
+        <v>27297.61</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3284,20 +3288,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3316,50 +3316,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26204.61</v>
+        <v>25976.97</v>
       </c>
       <c r="C34" t="n">
-        <v>26529.49</v>
+        <v>26132.94</v>
       </c>
       <c r="D34" t="n">
-        <v>25639.26</v>
+        <v>25609.61</v>
       </c>
       <c r="E34" t="n">
-        <v>25978.07</v>
+        <v>25776.53</v>
       </c>
       <c r="F34" t="n">
-        <v>-182.26</v>
+        <v>-201.54</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0078</v>
       </c>
       <c r="H34" t="n">
-        <v>890.23</v>
+        <v>523.33</v>
       </c>
       <c r="I34" t="n">
-        <v>24613.99</v>
+        <v>24749.03</v>
       </c>
       <c r="J34" t="n">
-        <v>25368.05</v>
+        <v>25034.69</v>
       </c>
       <c r="K34" t="n">
-        <v>25713.06</v>
+        <v>25532.96</v>
       </c>
       <c r="L34" t="n">
-        <v>26058.06</v>
+        <v>26031.22</v>
       </c>
       <c r="M34" t="n">
-        <v>26607.6</v>
+        <v>26423.19</v>
       </c>
       <c r="N34" t="n">
-        <v>27157.14</v>
+        <v>26815.15</v>
       </c>
       <c r="O34" t="n">
-        <v>27297.61</v>
+        <v>27419.72</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3369,12 +3369,12 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3391,59 +3391,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25976.97</v>
+        <v>26138.34</v>
       </c>
       <c r="C35" t="n">
-        <v>26132.94</v>
+        <v>26669.26</v>
       </c>
       <c r="D35" t="n">
-        <v>25609.61</v>
+        <v>25690.36</v>
       </c>
       <c r="E35" t="n">
-        <v>25776.53</v>
+        <v>26393.71</v>
       </c>
       <c r="F35" t="n">
-        <v>-201.54</v>
+        <v>617.1799999999999</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0239</v>
       </c>
       <c r="H35" t="n">
-        <v>523.33</v>
+        <v>978.9</v>
       </c>
       <c r="I35" t="n">
-        <v>24749.03</v>
+        <v>25086.28</v>
       </c>
       <c r="J35" t="n">
-        <v>25034.69</v>
+        <v>25205.83</v>
       </c>
       <c r="K35" t="n">
-        <v>25532.96</v>
+        <v>25514.86</v>
       </c>
       <c r="L35" t="n">
-        <v>26031.22</v>
+        <v>25823.9</v>
       </c>
       <c r="M35" t="n">
-        <v>26423.19</v>
+        <v>26038.19</v>
       </c>
       <c r="N35" t="n">
-        <v>26815.15</v>
+        <v>26252.49</v>
       </c>
       <c r="O35" t="n">
-        <v>27419.72</v>
+        <v>26656.27</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3451,28 +3447,32 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3480,50 +3480,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26138.34</v>
+        <v>26310.87</v>
       </c>
       <c r="C36" t="n">
-        <v>26669.26</v>
+        <v>26844.8</v>
       </c>
       <c r="D36" t="n">
-        <v>25690.36</v>
+        <v>25847.15</v>
       </c>
       <c r="E36" t="n">
-        <v>26393.71</v>
+        <v>25962.73</v>
       </c>
       <c r="F36" t="n">
-        <v>617.1799999999999</v>
+        <v>-430.98</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0163</v>
       </c>
       <c r="H36" t="n">
-        <v>978.9</v>
+        <v>997.65</v>
       </c>
       <c r="I36" t="n">
-        <v>25086.28</v>
+        <v>24711.46</v>
       </c>
       <c r="J36" t="n">
-        <v>25205.83</v>
+        <v>25521.76</v>
       </c>
       <c r="K36" t="n">
-        <v>25514.86</v>
+        <v>25904.26</v>
       </c>
       <c r="L36" t="n">
-        <v>25823.9</v>
+        <v>26286.76</v>
       </c>
       <c r="M36" t="n">
-        <v>26038.19</v>
+        <v>26883.16</v>
       </c>
       <c r="N36" t="n">
-        <v>26252.49</v>
+        <v>27479.56</v>
       </c>
       <c r="O36" t="n">
-        <v>26656.27</v>
+        <v>27648.16</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3531,83 +3531,83 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26310.87</v>
+        <v>25838.96</v>
       </c>
       <c r="C37" t="n">
-        <v>26844.8</v>
+        <v>25845.46</v>
       </c>
       <c r="D37" t="n">
-        <v>25847.15</v>
+        <v>25341.73</v>
       </c>
       <c r="E37" t="n">
-        <v>25962.73</v>
+        <v>25606.03</v>
       </c>
       <c r="F37" t="n">
-        <v>-430.98</v>
+        <v>-356.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0137</v>
       </c>
       <c r="H37" t="n">
-        <v>997.65</v>
+        <v>503.73</v>
       </c>
       <c r="I37" t="n">
-        <v>24711.46</v>
+        <v>24849.5</v>
       </c>
       <c r="J37" t="n">
-        <v>25521.76</v>
+        <v>24773.46</v>
       </c>
       <c r="K37" t="n">
-        <v>25904.26</v>
+        <v>25463.91</v>
       </c>
       <c r="L37" t="n">
-        <v>26286.76</v>
+        <v>26154.35</v>
       </c>
       <c r="M37" t="n">
-        <v>26883.16</v>
+        <v>26461.56</v>
       </c>
       <c r="N37" t="n">
-        <v>27479.56</v>
+        <v>26768.76</v>
       </c>
       <c r="O37" t="n">
-        <v>27648.16</v>
+        <v>27842.45</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3641,67 +3641,71 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25838.96</v>
+        <v>25622.36</v>
       </c>
       <c r="C38" t="n">
-        <v>25845.46</v>
+        <v>25768.38</v>
       </c>
       <c r="D38" t="n">
-        <v>25341.73</v>
+        <v>24727.26</v>
       </c>
       <c r="E38" t="n">
-        <v>25606.03</v>
+        <v>25182.39</v>
       </c>
       <c r="F38" t="n">
-        <v>-356.7</v>
+        <v>-423.64</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0165</v>
       </c>
       <c r="H38" t="n">
-        <v>503.73</v>
+        <v>1041.12</v>
       </c>
       <c r="I38" t="n">
-        <v>24849.5</v>
+        <v>24838</v>
       </c>
       <c r="J38" t="n">
-        <v>24773.46</v>
+        <v>25108.52</v>
       </c>
       <c r="K38" t="n">
-        <v>25463.91</v>
+        <v>25354.16</v>
       </c>
       <c r="L38" t="n">
-        <v>26154.35</v>
+        <v>25599.81</v>
       </c>
       <c r="M38" t="n">
-        <v>26461.56</v>
+        <v>25857.89</v>
       </c>
       <c r="N38" t="n">
-        <v>26768.76</v>
+        <v>26115.98</v>
       </c>
       <c r="O38" t="n">
-        <v>27842.45</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+        <v>26349.19</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
@@ -3732,74 +3736,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25622.36</v>
+        <v>25180.05</v>
       </c>
       <c r="C39" t="n">
-        <v>25768.38</v>
+        <v>26045.07</v>
       </c>
       <c r="D39" t="n">
-        <v>24727.26</v>
+        <v>24928.14</v>
       </c>
       <c r="E39" t="n">
-        <v>25182.39</v>
+        <v>24961.95</v>
       </c>
       <c r="F39" t="n">
-        <v>-423.64</v>
+        <v>-220.44</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0165</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>1041.12</v>
+        <v>1116.93</v>
       </c>
       <c r="I39" t="n">
-        <v>24838</v>
+        <v>23686.14</v>
       </c>
       <c r="J39" t="n">
-        <v>25108.52</v>
+        <v>24108.55</v>
       </c>
       <c r="K39" t="n">
-        <v>25354.16</v>
+        <v>24661.83</v>
       </c>
       <c r="L39" t="n">
-        <v>25599.81</v>
+        <v>25215.11</v>
       </c>
       <c r="M39" t="n">
-        <v>25857.89</v>
+        <v>25702.95</v>
       </c>
       <c r="N39" t="n">
-        <v>26115.98</v>
+        <v>26190.8</v>
       </c>
       <c r="O39" t="n">
-        <v>26349.19</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
+        <v>26809.5</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3813,57 +3813,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25180.05</v>
+        <v>24582.91</v>
       </c>
       <c r="C40" t="n">
-        <v>26045.07</v>
+        <v>24837.98</v>
       </c>
       <c r="D40" t="n">
-        <v>24928.14</v>
+        <v>23999.67</v>
       </c>
       <c r="E40" t="n">
-        <v>24961.95</v>
+        <v>24718.1</v>
       </c>
       <c r="F40" t="n">
-        <v>-220.44</v>
+        <v>-243.85</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="H40" t="n">
-        <v>1116.93</v>
+        <v>838.3099999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>23686.14</v>
+        <v>23811.21</v>
       </c>
       <c r="J40" t="n">
-        <v>24108.55</v>
+        <v>23582.69</v>
       </c>
       <c r="K40" t="n">
-        <v>24661.83</v>
+        <v>24403.48</v>
       </c>
       <c r="L40" t="n">
-        <v>25215.11</v>
+        <v>25224.28</v>
       </c>
       <c r="M40" t="n">
-        <v>25702.95</v>
+        <v>25520.41</v>
       </c>
       <c r="N40" t="n">
-        <v>26190.8</v>
+        <v>25816.55</v>
       </c>
       <c r="O40" t="n">
-        <v>26809.5</v>
+        <v>27162</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3871,18 +3871,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3897,67 +3897,69 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24582.91</v>
+        <v>25001.42</v>
       </c>
       <c r="C41" t="n">
-        <v>24837.98</v>
+        <v>25047.9</v>
       </c>
       <c r="D41" t="n">
-        <v>23999.67</v>
+        <v>23749.99</v>
       </c>
       <c r="E41" t="n">
-        <v>24718.1</v>
+        <v>23924.81</v>
       </c>
       <c r="F41" t="n">
-        <v>-243.85</v>
+        <v>-793.29</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0321</v>
       </c>
       <c r="H41" t="n">
-        <v>838.3099999999999</v>
+        <v>1297.91</v>
       </c>
       <c r="I41" t="n">
-        <v>23811.21</v>
+        <v>23161.36</v>
       </c>
       <c r="J41" t="n">
-        <v>23582.69</v>
+        <v>24029.43</v>
       </c>
       <c r="K41" t="n">
-        <v>24403.48</v>
+        <v>24298.94</v>
       </c>
       <c r="L41" t="n">
-        <v>25224.28</v>
+        <v>24568.46</v>
       </c>
       <c r="M41" t="n">
-        <v>25520.41</v>
+        <v>25137.25</v>
       </c>
       <c r="N41" t="n">
-        <v>25816.55</v>
+        <v>25706.05</v>
       </c>
       <c r="O41" t="n">
-        <v>27162</v>
+        <v>25676.29</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
@@ -3974,73 +3976,73 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25001.42</v>
+        <v>23811.76</v>
       </c>
       <c r="C42" t="n">
-        <v>25047.9</v>
+        <v>23863.71</v>
       </c>
       <c r="D42" t="n">
-        <v>23749.99</v>
+        <v>22518</v>
       </c>
       <c r="E42" t="n">
-        <v>23924.81</v>
+        <v>22671.86</v>
       </c>
       <c r="F42" t="n">
-        <v>-793.29</v>
+        <v>-1252.95</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0524</v>
       </c>
       <c r="H42" t="n">
-        <v>1297.91</v>
+        <v>1345.71</v>
       </c>
       <c r="I42" t="n">
-        <v>23161.36</v>
+        <v>22452.08</v>
       </c>
       <c r="J42" t="n">
-        <v>24029.43</v>
+        <v>22389.83</v>
       </c>
       <c r="K42" t="n">
-        <v>24298.94</v>
+        <v>23275.86</v>
       </c>
       <c r="L42" t="n">
-        <v>24568.46</v>
+        <v>24161.88</v>
       </c>
       <c r="M42" t="n">
-        <v>25137.25</v>
+        <v>24573.77</v>
       </c>
       <c r="N42" t="n">
-        <v>25706.05</v>
+        <v>24985.65</v>
       </c>
       <c r="O42" t="n">
-        <v>25676.29</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>26345.81</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4065,81 +4067,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23811.76</v>
+        <v>22827.65</v>
       </c>
       <c r="C43" t="n">
-        <v>23863.71</v>
+        <v>23516.7</v>
       </c>
       <c r="D43" t="n">
-        <v>22518</v>
+        <v>22685.14</v>
       </c>
       <c r="E43" t="n">
-        <v>22671.86</v>
+        <v>23350.03</v>
       </c>
       <c r="F43" t="n">
-        <v>-1252.95</v>
+        <v>678.17</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0524</v>
+        <v>0.0299</v>
       </c>
       <c r="H43" t="n">
-        <v>1345.71</v>
+        <v>831.5599999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>22452.08</v>
+        <v>21172.29</v>
       </c>
       <c r="J43" t="n">
-        <v>22389.83</v>
+        <v>21066.65</v>
       </c>
       <c r="K43" t="n">
-        <v>23275.86</v>
+        <v>21999</v>
       </c>
       <c r="L43" t="n">
-        <v>24161.88</v>
+        <v>22931.36</v>
       </c>
       <c r="M43" t="n">
-        <v>24573.77</v>
+        <v>23344.71</v>
       </c>
       <c r="N43" t="n">
-        <v>24985.65</v>
+        <v>23758.07</v>
       </c>
       <c r="O43" t="n">
-        <v>26345.81</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>25209.42</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4151,55 +4147,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22827.65</v>
+        <v>23404.61</v>
       </c>
       <c r="C44" t="n">
-        <v>23516.7</v>
+        <v>24499.63</v>
       </c>
       <c r="D44" t="n">
-        <v>22685.14</v>
+        <v>23229.38</v>
       </c>
       <c r="E44" t="n">
-        <v>23350.03</v>
+        <v>24175.12</v>
       </c>
       <c r="F44" t="n">
-        <v>678.17</v>
+        <v>825.09</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0353</v>
       </c>
       <c r="H44" t="n">
-        <v>831.5599999999999</v>
+        <v>1270.25</v>
       </c>
       <c r="I44" t="n">
-        <v>21172.29</v>
+        <v>21853.58</v>
       </c>
       <c r="J44" t="n">
-        <v>21066.65</v>
+        <v>22643.03</v>
       </c>
       <c r="K44" t="n">
-        <v>21999</v>
+        <v>22934.25</v>
       </c>
       <c r="L44" t="n">
-        <v>22931.36</v>
+        <v>23225.47</v>
       </c>
       <c r="M44" t="n">
-        <v>23344.71</v>
+        <v>23765.81</v>
       </c>
       <c r="N44" t="n">
-        <v>23758.07</v>
+        <v>24306.14</v>
       </c>
       <c r="O44" t="n">
-        <v>25209.42</v>
+        <v>24348.26</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4217,14 +4217,18 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
@@ -4233,57 +4237,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23404.61</v>
+        <v>24157.65</v>
       </c>
       <c r="C45" t="n">
-        <v>24499.63</v>
+        <v>25221.44</v>
       </c>
       <c r="D45" t="n">
-        <v>23229.38</v>
+        <v>23902.05</v>
       </c>
       <c r="E45" t="n">
-        <v>24175.12</v>
+        <v>24562.24</v>
       </c>
       <c r="F45" t="n">
-        <v>825.09</v>
+        <v>387.12</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.016</v>
       </c>
       <c r="H45" t="n">
-        <v>1270.25</v>
+        <v>1319.39</v>
       </c>
       <c r="I45" t="n">
-        <v>21853.58</v>
+        <v>21959.13</v>
       </c>
       <c r="J45" t="n">
-        <v>22643.03</v>
+        <v>23060.18</v>
       </c>
       <c r="K45" t="n">
-        <v>22934.25</v>
+        <v>23539.99</v>
       </c>
       <c r="L45" t="n">
-        <v>23225.47</v>
+        <v>24019.81</v>
       </c>
       <c r="M45" t="n">
-        <v>23765.81</v>
+        <v>24810.24</v>
       </c>
       <c r="N45" t="n">
-        <v>24306.14</v>
+        <v>25600.68</v>
       </c>
       <c r="O45" t="n">
-        <v>24348.26</v>
+        <v>25769.88</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4301,18 +4305,14 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
@@ -4328,50 +4328,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24157.65</v>
+        <v>24835.03</v>
       </c>
       <c r="C46" t="n">
-        <v>25221.44</v>
+        <v>25267.39</v>
       </c>
       <c r="D46" t="n">
-        <v>23902.05</v>
+        <v>24756.36</v>
       </c>
       <c r="E46" t="n">
-        <v>24562.24</v>
+        <v>24963.23</v>
       </c>
       <c r="F46" t="n">
-        <v>387.12</v>
+        <v>400.99</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
       </c>
       <c r="H46" t="n">
-        <v>1319.39</v>
+        <v>511.03</v>
       </c>
       <c r="I46" t="n">
-        <v>21959.13</v>
+        <v>22582.66</v>
       </c>
       <c r="J46" t="n">
-        <v>23060.18</v>
+        <v>23243.1</v>
       </c>
       <c r="K46" t="n">
-        <v>23539.99</v>
+        <v>23902.55</v>
       </c>
       <c r="L46" t="n">
-        <v>24019.81</v>
+        <v>24561.99</v>
       </c>
       <c r="M46" t="n">
-        <v>24810.24</v>
+        <v>25221.93</v>
       </c>
       <c r="N46" t="n">
-        <v>25600.68</v>
+        <v>25881.88</v>
       </c>
       <c r="O46" t="n">
-        <v>25769.88</v>
+        <v>26540.83</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4412,50 +4412,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24835.03</v>
+        <v>24993.77</v>
       </c>
       <c r="C47" t="n">
-        <v>25267.39</v>
+        <v>25971.63</v>
       </c>
       <c r="D47" t="n">
-        <v>24756.36</v>
+        <v>24938.34</v>
       </c>
       <c r="E47" t="n">
-        <v>24963.23</v>
+        <v>25884.43</v>
       </c>
       <c r="F47" t="n">
-        <v>400.99</v>
+        <v>921.2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0369</v>
       </c>
       <c r="H47" t="n">
-        <v>511.03</v>
+        <v>1033.29</v>
       </c>
       <c r="I47" t="n">
-        <v>22582.66</v>
+        <v>24245.33</v>
       </c>
       <c r="J47" t="n">
-        <v>23243.1</v>
+        <v>24427.88</v>
       </c>
       <c r="K47" t="n">
-        <v>23902.55</v>
+        <v>24707.71</v>
       </c>
       <c r="L47" t="n">
-        <v>24561.99</v>
+        <v>24987.55</v>
       </c>
       <c r="M47" t="n">
-        <v>25221.93</v>
+        <v>25218.75</v>
       </c>
       <c r="N47" t="n">
-        <v>25881.88</v>
+        <v>25449.94</v>
       </c>
       <c r="O47" t="n">
-        <v>26540.83</v>
+        <v>25778.42</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4473,73 +4473,73 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24993.77</v>
+        <v>25987.31</v>
       </c>
       <c r="C48" t="n">
-        <v>25971.63</v>
+        <v>26187.57</v>
       </c>
       <c r="D48" t="n">
-        <v>24938.34</v>
+        <v>25389.42</v>
       </c>
       <c r="E48" t="n">
-        <v>25884.43</v>
+        <v>25668.03</v>
       </c>
       <c r="F48" t="n">
-        <v>921.2</v>
+        <v>-216.4</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0369</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>1033.29</v>
+        <v>798.15</v>
       </c>
       <c r="I48" t="n">
-        <v>24245.33</v>
+        <v>23905.05</v>
       </c>
       <c r="J48" t="n">
-        <v>24427.88</v>
+        <v>25065.86</v>
       </c>
       <c r="K48" t="n">
-        <v>24707.71</v>
+        <v>25367.78</v>
       </c>
       <c r="L48" t="n">
-        <v>24987.55</v>
+        <v>25669.71</v>
       </c>
       <c r="M48" t="n">
-        <v>25218.75</v>
+        <v>26401.08</v>
       </c>
       <c r="N48" t="n">
-        <v>25449.94</v>
+        <v>27132.44</v>
       </c>
       <c r="O48" t="n">
-        <v>25778.42</v>
+        <v>27004.92</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4550,80 +4550,78 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25987.31</v>
+        <v>25805.18</v>
       </c>
       <c r="C49" t="n">
-        <v>26187.57</v>
+        <v>26060.32</v>
       </c>
       <c r="D49" t="n">
-        <v>25389.42</v>
+        <v>25089.14</v>
       </c>
       <c r="E49" t="n">
-        <v>25668.03</v>
+        <v>25116.85</v>
       </c>
       <c r="F49" t="n">
-        <v>-216.4</v>
+        <v>-551.1799999999999</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0215</v>
       </c>
       <c r="H49" t="n">
-        <v>798.15</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>23905.05</v>
+        <v>24591.27</v>
       </c>
       <c r="J49" t="n">
-        <v>25065.86</v>
+        <v>24809.65</v>
       </c>
       <c r="K49" t="n">
-        <v>25367.78</v>
+        <v>25268.95</v>
       </c>
       <c r="L49" t="n">
-        <v>25669.71</v>
+        <v>25728.26</v>
       </c>
       <c r="M49" t="n">
-        <v>26401.08</v>
+        <v>26067.1</v>
       </c>
       <c r="N49" t="n">
-        <v>27132.44</v>
+        <v>26405.95</v>
       </c>
       <c r="O49" t="n">
-        <v>27004.92</v>
+        <v>26985.72</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4631,12 +4629,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4655,57 +4655,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25805.18</v>
+        <v>25303.41</v>
       </c>
       <c r="C50" t="n">
-        <v>26060.32</v>
+        <v>26009.46</v>
       </c>
       <c r="D50" t="n">
-        <v>25089.14</v>
+        <v>25240.62</v>
       </c>
       <c r="E50" t="n">
-        <v>25116.85</v>
+        <v>26009.46</v>
       </c>
       <c r="F50" t="n">
-        <v>-551.1799999999999</v>
+        <v>892.61</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0215</v>
+        <v>0.0355</v>
       </c>
       <c r="H50" t="n">
-        <v>971.1799999999999</v>
+        <v>768.84</v>
       </c>
       <c r="I50" t="n">
-        <v>24591.27</v>
+        <v>24117.96</v>
       </c>
       <c r="J50" t="n">
-        <v>24809.65</v>
+        <v>23916.73</v>
       </c>
       <c r="K50" t="n">
-        <v>25268.95</v>
+        <v>24631.26</v>
       </c>
       <c r="L50" t="n">
-        <v>25728.26</v>
+        <v>25345.79</v>
       </c>
       <c r="M50" t="n">
-        <v>26067.1</v>
+        <v>25602.44</v>
       </c>
       <c r="N50" t="n">
-        <v>26405.95</v>
+        <v>25859.09</v>
       </c>
       <c r="O50" t="n">
-        <v>26985.72</v>
+        <v>27031.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4713,22 +4713,24 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4739,82 +4741,82 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25303.41</v>
+        <v>25780.12</v>
       </c>
       <c r="C51" t="n">
-        <v>26009.46</v>
+        <v>25800.22</v>
       </c>
       <c r="D51" t="n">
-        <v>25240.62</v>
+        <v>25403.44</v>
       </c>
       <c r="E51" t="n">
-        <v>26009.46</v>
+        <v>25584.79</v>
       </c>
       <c r="F51" t="n">
-        <v>892.61</v>
+        <v>-424.67</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0355</v>
+        <v>-0.0163</v>
       </c>
       <c r="H51" t="n">
-        <v>768.84</v>
+        <v>396.78</v>
       </c>
       <c r="I51" t="n">
-        <v>24117.96</v>
+        <v>24471.78</v>
       </c>
       <c r="J51" t="n">
-        <v>23916.73</v>
+        <v>25432.83</v>
       </c>
       <c r="K51" t="n">
-        <v>24631.26</v>
+        <v>25625.04</v>
       </c>
       <c r="L51" t="n">
-        <v>25345.79</v>
+        <v>25817.25</v>
       </c>
       <c r="M51" t="n">
-        <v>25602.44</v>
+        <v>26393.88</v>
       </c>
       <c r="N51" t="n">
-        <v>25859.09</v>
+        <v>26970.51</v>
       </c>
       <c r="O51" t="n">
-        <v>27031.5</v>
+        <v>26778.3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4825,57 +4827,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25780.12</v>
+        <v>25420.63</v>
       </c>
       <c r="C52" t="n">
-        <v>25800.22</v>
+        <v>25791.38</v>
       </c>
       <c r="D52" t="n">
-        <v>25403.44</v>
+        <v>25008.87</v>
       </c>
       <c r="E52" t="n">
-        <v>25584.79</v>
+        <v>25650.87</v>
       </c>
       <c r="F52" t="n">
-        <v>-424.67</v>
+        <v>66.08</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0163</v>
+        <v>0.0026</v>
       </c>
       <c r="H52" t="n">
-        <v>396.78</v>
+        <v>782.51</v>
       </c>
       <c r="I52" t="n">
-        <v>24471.78</v>
+        <v>25006.66</v>
       </c>
       <c r="J52" t="n">
-        <v>25432.83</v>
+        <v>25179.49</v>
       </c>
       <c r="K52" t="n">
-        <v>25625.04</v>
+        <v>25386.4</v>
       </c>
       <c r="L52" t="n">
-        <v>25817.25</v>
+        <v>25593.31</v>
       </c>
       <c r="M52" t="n">
-        <v>26393.88</v>
+        <v>25783.18</v>
       </c>
       <c r="N52" t="n">
-        <v>26970.51</v>
+        <v>25973.05</v>
       </c>
       <c r="O52" t="n">
-        <v>26778.3</v>
+        <v>26197</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4887,16 +4889,18 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4918,73 +4922,71 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25420.63</v>
+        <v>25652.97</v>
       </c>
       <c r="C53" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D53" t="n">
-        <v>25008.87</v>
+        <v>24570.24</v>
       </c>
       <c r="E53" t="n">
-        <v>25650.87</v>
+        <v>24805.63</v>
       </c>
       <c r="F53" t="n">
-        <v>66.08</v>
+        <v>-845.24</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.033</v>
       </c>
       <c r="H53" t="n">
-        <v>782.51</v>
+        <v>1094.74</v>
       </c>
       <c r="I53" t="n">
-        <v>25006.66</v>
+        <v>24226.36</v>
       </c>
       <c r="J53" t="n">
-        <v>25179.49</v>
+        <v>24993.73</v>
       </c>
       <c r="K53" t="n">
-        <v>25386.4</v>
+        <v>25259.61</v>
       </c>
       <c r="L53" t="n">
-        <v>25593.31</v>
+        <v>25525.5</v>
       </c>
       <c r="M53" t="n">
-        <v>25783.18</v>
+        <v>26042.12</v>
       </c>
       <c r="N53" t="n">
-        <v>25973.05</v>
+        <v>26558.75</v>
       </c>
       <c r="O53" t="n">
-        <v>26197</v>
+        <v>26573.89</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4992,81 +4994,73 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25652.97</v>
+        <v>24701.18</v>
       </c>
       <c r="C54" t="n">
-        <v>25664.98</v>
+        <v>24934.06</v>
       </c>
       <c r="D54" t="n">
-        <v>24570.24</v>
+        <v>24357.69</v>
       </c>
       <c r="E54" t="n">
-        <v>24805.63</v>
+        <v>24750.78</v>
       </c>
       <c r="F54" t="n">
-        <v>-845.24</v>
+        <v>-54.85</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.0022</v>
       </c>
       <c r="H54" t="n">
-        <v>1094.74</v>
+        <v>576.37</v>
       </c>
       <c r="I54" t="n">
-        <v>24226.36</v>
+        <v>23475.5</v>
       </c>
       <c r="J54" t="n">
-        <v>24993.73</v>
+        <v>23554.9</v>
       </c>
       <c r="K54" t="n">
-        <v>25259.61</v>
+        <v>24258.26</v>
       </c>
       <c r="L54" t="n">
-        <v>25525.5</v>
+        <v>24961.62</v>
       </c>
       <c r="M54" t="n">
-        <v>26042.12</v>
+        <v>25353</v>
       </c>
       <c r="N54" t="n">
-        <v>26558.75</v>
+        <v>25744.38</v>
       </c>
       <c r="O54" t="n">
-        <v>26573.89</v>
+        <v>26759.72</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5088,50 +5082,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24701.18</v>
+        <v>24748.45</v>
       </c>
       <c r="C55" t="n">
-        <v>24934.06</v>
+        <v>25254.11</v>
       </c>
       <c r="D55" t="n">
-        <v>24357.69</v>
+        <v>24275.56</v>
       </c>
       <c r="E55" t="n">
-        <v>24750.78</v>
+        <v>24510.09</v>
       </c>
       <c r="F55" t="n">
-        <v>-54.85</v>
+        <v>-240.69</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0097</v>
       </c>
       <c r="H55" t="n">
-        <v>576.37</v>
+        <v>978.55</v>
       </c>
       <c r="I55" t="n">
-        <v>23475.5</v>
+        <v>23781.32</v>
       </c>
       <c r="J55" t="n">
-        <v>23554.9</v>
+        <v>24226.86</v>
       </c>
       <c r="K55" t="n">
-        <v>24258.26</v>
+        <v>24462.59</v>
       </c>
       <c r="L55" t="n">
-        <v>24961.62</v>
+        <v>24698.33</v>
       </c>
       <c r="M55" t="n">
-        <v>25353</v>
+        <v>25038.96</v>
       </c>
       <c r="N55" t="n">
-        <v>25744.38</v>
+        <v>25379.6</v>
       </c>
       <c r="O55" t="n">
-        <v>26759.72</v>
+        <v>25510.43</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5139,16 +5133,20 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5161,55 +5159,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24748.45</v>
+        <v>24554.58</v>
       </c>
       <c r="C56" t="n">
-        <v>25254.11</v>
+        <v>24767.22</v>
       </c>
       <c r="D56" t="n">
-        <v>24275.56</v>
+        <v>23865.33</v>
       </c>
       <c r="E56" t="n">
-        <v>24510.09</v>
+        <v>23972.29</v>
       </c>
       <c r="F56" t="n">
-        <v>-240.69</v>
+        <v>-537.8</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0219</v>
       </c>
       <c r="H56" t="n">
-        <v>978.55</v>
+        <v>901.89</v>
       </c>
       <c r="I56" t="n">
-        <v>23781.32</v>
+        <v>23297.01</v>
       </c>
       <c r="J56" t="n">
-        <v>24226.86</v>
+        <v>23404.17</v>
       </c>
       <c r="K56" t="n">
-        <v>24462.59</v>
+        <v>24020.82</v>
       </c>
       <c r="L56" t="n">
-        <v>24698.33</v>
+        <v>24637.46</v>
       </c>
       <c r="M56" t="n">
-        <v>25038.96</v>
+        <v>24999.36</v>
       </c>
       <c r="N56" t="n">
-        <v>25379.6</v>
+        <v>25361.27</v>
       </c>
       <c r="O56" t="n">
-        <v>25510.43</v>
+        <v>26232.66</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5227,10 +5229,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5243,59 +5243,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24554.58</v>
+        <v>23963.41</v>
       </c>
       <c r="C57" t="n">
-        <v>24767.22</v>
+        <v>24354.11</v>
       </c>
       <c r="D57" t="n">
-        <v>23865.33</v>
+        <v>23737.14</v>
       </c>
       <c r="E57" t="n">
-        <v>23972.29</v>
+        <v>24211.35</v>
       </c>
       <c r="F57" t="n">
-        <v>-537.8</v>
+        <v>239.06</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0219</v>
+        <v>0.01</v>
       </c>
       <c r="H57" t="n">
-        <v>901.89</v>
+        <v>616.97</v>
       </c>
       <c r="I57" t="n">
-        <v>23297.01</v>
+        <v>22963.44</v>
       </c>
       <c r="J57" t="n">
-        <v>23404.17</v>
+        <v>22898.41</v>
       </c>
       <c r="K57" t="n">
-        <v>24020.82</v>
+        <v>23521.34</v>
       </c>
       <c r="L57" t="n">
-        <v>24637.46</v>
+        <v>24144.28</v>
       </c>
       <c r="M57" t="n">
-        <v>24999.36</v>
+        <v>24423.23</v>
       </c>
       <c r="N57" t="n">
-        <v>25361.27</v>
+        <v>24702.19</v>
       </c>
       <c r="O57" t="n">
-        <v>26232.66</v>
+        <v>25669.11</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5303,14 +5299,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5327,87 +5321,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>23963.41</v>
-      </c>
-      <c r="C58" t="n">
-        <v>24354.11</v>
-      </c>
-      <c r="D58" t="n">
-        <v>23737.14</v>
-      </c>
-      <c r="E58" t="n">
-        <v>23785.79</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-186.5</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0078</v>
-      </c>
-      <c r="H58" t="n">
-        <v>616.97</v>
-      </c>
-      <c r="I58" t="n">
-        <v>22963.44</v>
-      </c>
-      <c r="J58" t="n">
-        <v>22898.41</v>
-      </c>
-      <c r="K58" t="n">
-        <v>23521.34</v>
-      </c>
-      <c r="L58" t="n">
-        <v>24144.28</v>
-      </c>
-      <c r="M58" t="n">
-        <v>24423.23</v>
-      </c>
-      <c r="N58" t="n">
-        <v>24702.19</v>
-      </c>
-      <c r="O58" t="n">
-        <v>25669.11</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5327,6 +5330,90 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>24434.93</v>
+      </c>
+      <c r="C58" t="n">
+        <v>24434.93</v>
+      </c>
+      <c r="D58" t="n">
+        <v>24434.93</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>23120.17</v>
+      </c>
+      <c r="J58" t="n">
+        <v>23677.24</v>
+      </c>
+      <c r="K58" t="n">
+        <v>23902.87</v>
+      </c>
+      <c r="L58" t="n">
+        <v>24128.49</v>
+      </c>
+      <c r="M58" t="n">
+        <v>24519.83</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24911.18</v>
+      </c>
+      <c r="O58" t="n">
+        <v>24971.08</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>777.8</v>
       </c>
       <c r="I2" t="n">
-        <v>24189.67</v>
+        <v>24764.61</v>
       </c>
       <c r="J2" t="n">
-        <v>25390.66</v>
+        <v>25606.26</v>
       </c>
       <c r="K2" t="n">
-        <v>25789.09</v>
+        <v>25932.83</v>
       </c>
       <c r="L2" t="n">
-        <v>26187.52</v>
+        <v>26259.39</v>
       </c>
       <c r="M2" t="n">
-        <v>26987.23</v>
+        <v>26843.5</v>
       </c>
       <c r="N2" t="n">
-        <v>27786.94</v>
+        <v>27427.6</v>
       </c>
       <c r="O2" t="n">
-        <v>27784.09</v>
+        <v>27496.62</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5340,22 +5337,22 @@
         <v>24434.93</v>
       </c>
       <c r="C58" t="n">
-        <v>24434.93</v>
+        <v>24455.95</v>
       </c>
       <c r="D58" t="n">
-        <v>24434.93</v>
+        <v>24193.3</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>24271.2</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>59.85</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0025</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>262.65</v>
       </c>
       <c r="I58" t="n">
         <v>23120.17</v>
@@ -5378,10 +5375,8 @@
       <c r="O58" t="n">
         <v>24971.08</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5389,9 +5384,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5410,7 +5405,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>777.8</v>
       </c>
       <c r="I2" t="n">
-        <v>24764.61</v>
+        <v>25171.99</v>
       </c>
       <c r="J2" t="n">
-        <v>25606.26</v>
+        <v>25759.03</v>
       </c>
       <c r="K2" t="n">
-        <v>25932.83</v>
+        <v>26034.67</v>
       </c>
       <c r="L2" t="n">
-        <v>26259.39</v>
+        <v>26310.31</v>
       </c>
       <c r="M2" t="n">
-        <v>26843.5</v>
+        <v>26741.65</v>
       </c>
       <c r="N2" t="n">
-        <v>27427.6</v>
+        <v>27172.99</v>
       </c>
       <c r="O2" t="n">
-        <v>27496.62</v>
+        <v>27292.93</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,12 +690,12 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -5340,19 +5340,19 @@
         <v>24455.95</v>
       </c>
       <c r="D58" t="n">
-        <v>24193.3</v>
+        <v>23987.77</v>
       </c>
       <c r="E58" t="n">
-        <v>24271.2</v>
+        <v>24345.22</v>
       </c>
       <c r="F58" t="n">
-        <v>59.85</v>
+        <v>133.87</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0055</v>
       </c>
       <c r="H58" t="n">
-        <v>262.65</v>
+        <v>468.18</v>
       </c>
       <c r="I58" t="n">
         <v>23120.17</v>
@@ -5386,11 +5386,13 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5337,22 +5337,22 @@
         <v>24434.93</v>
       </c>
       <c r="C58" t="n">
-        <v>24455.95</v>
+        <v>24524.63</v>
       </c>
       <c r="D58" t="n">
         <v>23987.77</v>
       </c>
       <c r="E58" t="n">
-        <v>24345.22</v>
+        <v>24314.17</v>
       </c>
       <c r="F58" t="n">
-        <v>133.87</v>
+        <v>102.82</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0042</v>
       </c>
       <c r="H58" t="n">
-        <v>468.18</v>
+        <v>536.86</v>
       </c>
       <c r="I58" t="n">
         <v>23120.17</v>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>777.8</v>
       </c>
       <c r="I2" t="n">
-        <v>25171.99</v>
+        <v>26073.37</v>
       </c>
       <c r="J2" t="n">
-        <v>25759.03</v>
+        <v>26097.05</v>
       </c>
       <c r="K2" t="n">
-        <v>26034.67</v>
+        <v>26260.02</v>
       </c>
       <c r="L2" t="n">
-        <v>26310.31</v>
+        <v>26422.98</v>
       </c>
       <c r="M2" t="n">
-        <v>26741.65</v>
+        <v>26516.3</v>
       </c>
       <c r="N2" t="n">
-        <v>27172.99</v>
+        <v>26609.63</v>
       </c>
       <c r="O2" t="n">
-        <v>27292.93</v>
+        <v>26842.24</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,18 +698,26 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5340,19 +5348,19 @@
         <v>24524.63</v>
       </c>
       <c r="D58" t="n">
-        <v>23987.77</v>
+        <v>23945.84</v>
       </c>
       <c r="E58" t="n">
-        <v>24314.17</v>
+        <v>24062.72</v>
       </c>
       <c r="F58" t="n">
-        <v>102.82</v>
+        <v>-148.63</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0061</v>
       </c>
       <c r="H58" t="n">
-        <v>536.86</v>
+        <v>578.79</v>
       </c>
       <c r="I58" t="n">
         <v>23120.17</v>
@@ -5384,9 +5392,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5407,7 +5415,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26308.91</v>
+        <v>26459.52</v>
       </c>
       <c r="C2" t="n">
-        <v>27058.03</v>
+        <v>26640.53</v>
       </c>
       <c r="D2" t="n">
-        <v>26280.23</v>
+        <v>26003.67</v>
       </c>
       <c r="E2" t="n">
-        <v>26545.1</v>
+        <v>26128.2</v>
       </c>
       <c r="F2" t="n">
-        <v>156.94</v>
+        <v>-416.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0157</v>
       </c>
       <c r="H2" t="n">
-        <v>777.8</v>
+        <v>636.86</v>
       </c>
       <c r="I2" t="n">
-        <v>26073.37</v>
+        <v>25502.43</v>
       </c>
       <c r="J2" t="n">
-        <v>26097.05</v>
+        <v>25705.29</v>
       </c>
       <c r="K2" t="n">
-        <v>26260.02</v>
+        <v>26156.2</v>
       </c>
       <c r="L2" t="n">
-        <v>26422.98</v>
+        <v>26607.11</v>
       </c>
       <c r="M2" t="n">
-        <v>26516.3</v>
+        <v>26934</v>
       </c>
       <c r="N2" t="n">
-        <v>26609.63</v>
+        <v>27260.88</v>
       </c>
       <c r="O2" t="n">
-        <v>26842.24</v>
+        <v>27835.83</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,28 +685,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -715,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26459.52</v>
+        <v>26321.57</v>
       </c>
       <c r="C3" t="n">
-        <v>26640.53</v>
+        <v>27381.84</v>
       </c>
       <c r="D3" t="n">
-        <v>26003.67</v>
+        <v>26321.57</v>
       </c>
       <c r="E3" t="n">
-        <v>26128.2</v>
+        <v>27140.92</v>
       </c>
       <c r="F3" t="n">
-        <v>-416.9</v>
+        <v>1012.72</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0388</v>
       </c>
       <c r="H3" t="n">
-        <v>636.86</v>
+        <v>1060.27</v>
       </c>
       <c r="I3" t="n">
-        <v>25502.43</v>
+        <v>25366.81</v>
       </c>
       <c r="J3" t="n">
-        <v>25705.29</v>
+        <v>25394.39</v>
       </c>
       <c r="K3" t="n">
-        <v>26156.2</v>
+        <v>25809.77</v>
       </c>
       <c r="L3" t="n">
-        <v>26607.11</v>
+        <v>26225.15</v>
       </c>
       <c r="M3" t="n">
-        <v>26934</v>
+        <v>26446.63</v>
       </c>
       <c r="N3" t="n">
-        <v>27260.88</v>
+        <v>26668.11</v>
       </c>
       <c r="O3" t="n">
-        <v>27835.83</v>
+        <v>27277.39</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,170 +769,174 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
-      </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26321.57</v>
+        <v>27003.92</v>
       </c>
       <c r="C4" t="n">
-        <v>27381.84</v>
+        <v>27145.17</v>
       </c>
       <c r="D4" t="n">
-        <v>26321.57</v>
+        <v>26247.04</v>
       </c>
       <c r="E4" t="n">
-        <v>27140.92</v>
+        <v>26290.32</v>
       </c>
       <c r="F4" t="n">
-        <v>1012.72</v>
+        <v>-850.6</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0388</v>
+        <v>-0.0313</v>
       </c>
       <c r="H4" t="n">
-        <v>1060.27</v>
+        <v>898.13</v>
       </c>
       <c r="I4" t="n">
-        <v>25366.81</v>
+        <v>25261.3</v>
       </c>
       <c r="J4" t="n">
-        <v>25394.39</v>
+        <v>26225.26</v>
       </c>
       <c r="K4" t="n">
-        <v>25809.77</v>
+        <v>26610.79</v>
       </c>
       <c r="L4" t="n">
-        <v>26225.15</v>
+        <v>26996.31</v>
       </c>
       <c r="M4" t="n">
-        <v>26446.63</v>
+        <v>27671.05</v>
       </c>
       <c r="N4" t="n">
-        <v>26668.11</v>
+        <v>28345.8</v>
       </c>
       <c r="O4" t="n">
-        <v>27277.39</v>
+        <v>28442.11</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27003.92</v>
+        <v>25634</v>
       </c>
       <c r="C5" t="n">
-        <v>27145.17</v>
+        <v>26102.68</v>
       </c>
       <c r="D5" t="n">
-        <v>26247.04</v>
+        <v>25145.34</v>
       </c>
       <c r="E5" t="n">
-        <v>26290.32</v>
+        <v>25247.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-850.6</v>
+        <v>-1043.22</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0397</v>
       </c>
       <c r="H5" t="n">
-        <v>898.13</v>
+        <v>957.34</v>
       </c>
       <c r="I5" t="n">
-        <v>25261.3</v>
+        <v>25348.91</v>
       </c>
       <c r="J5" t="n">
-        <v>26225.26</v>
+        <v>25189.3</v>
       </c>
       <c r="K5" t="n">
-        <v>26610.79</v>
+        <v>25841.25</v>
       </c>
       <c r="L5" t="n">
-        <v>26996.31</v>
+        <v>26493.21</v>
       </c>
       <c r="M5" t="n">
-        <v>27671.05</v>
+        <v>26739.39</v>
       </c>
       <c r="N5" t="n">
-        <v>28345.8</v>
+        <v>26985.56</v>
       </c>
       <c r="O5" t="n">
-        <v>28442.11</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
+        <v>28043.3</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -976,77 +976,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25634</v>
+        <v>25884.46</v>
       </c>
       <c r="C6" t="n">
-        <v>26102.68</v>
+        <v>26367.35</v>
       </c>
       <c r="D6" t="n">
-        <v>25145.34</v>
+        <v>25591.66</v>
       </c>
       <c r="E6" t="n">
-        <v>25247.1</v>
+        <v>26160.15</v>
       </c>
       <c r="F6" t="n">
-        <v>-1043.22</v>
+        <v>913.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0362</v>
       </c>
       <c r="H6" t="n">
-        <v>957.34</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>25348.91</v>
+        <v>24188</v>
       </c>
       <c r="J6" t="n">
-        <v>25189.3</v>
+        <v>24101.3</v>
       </c>
       <c r="K6" t="n">
-        <v>25841.25</v>
+        <v>24768.43</v>
       </c>
       <c r="L6" t="n">
-        <v>26493.21</v>
+        <v>25435.55</v>
       </c>
       <c r="M6" t="n">
-        <v>26739.39</v>
+        <v>25725.77</v>
       </c>
       <c r="N6" t="n">
-        <v>26985.56</v>
+        <v>26015.98</v>
       </c>
       <c r="O6" t="n">
-        <v>28043.3</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>27060.02</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1055,59 +1053,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25884.46</v>
+        <v>26495.97</v>
       </c>
       <c r="C7" t="n">
-        <v>26367.35</v>
+        <v>26588.89</v>
       </c>
       <c r="D7" t="n">
-        <v>25591.66</v>
+        <v>25906.65</v>
       </c>
       <c r="E7" t="n">
-        <v>26160.15</v>
+        <v>25906.65</v>
       </c>
       <c r="F7" t="n">
-        <v>913.05</v>
+        <v>-253.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0362</v>
+        <v>-0.0097</v>
       </c>
       <c r="H7" t="n">
-        <v>775.6900000000001</v>
+        <v>682.24</v>
       </c>
       <c r="I7" t="n">
-        <v>24188</v>
+        <v>24815.97</v>
       </c>
       <c r="J7" t="n">
-        <v>24101.3</v>
+        <v>25474.78</v>
       </c>
       <c r="K7" t="n">
-        <v>24768.43</v>
+        <v>25772.31</v>
       </c>
       <c r="L7" t="n">
-        <v>25435.55</v>
+        <v>26069.83</v>
       </c>
       <c r="M7" t="n">
-        <v>25725.77</v>
+        <v>26548</v>
       </c>
       <c r="N7" t="n">
-        <v>26015.98</v>
+        <v>27026.16</v>
       </c>
       <c r="O7" t="n">
-        <v>27060.02</v>
+        <v>27143.04</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1115,12 +1109,14 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1128,10 +1124,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1141,55 +1135,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26495.97</v>
+        <v>25999.17</v>
       </c>
       <c r="C8" t="n">
-        <v>26588.89</v>
+        <v>26490.71</v>
       </c>
       <c r="D8" t="n">
-        <v>25906.65</v>
+        <v>25496.13</v>
       </c>
       <c r="E8" t="n">
-        <v>25906.65</v>
+        <v>26241.83</v>
       </c>
       <c r="F8" t="n">
-        <v>-253.5</v>
+        <v>335.18</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0129</v>
       </c>
       <c r="H8" t="n">
-        <v>682.24</v>
+        <v>994.58</v>
       </c>
       <c r="I8" t="n">
-        <v>24815.97</v>
+        <v>25224.41</v>
       </c>
       <c r="J8" t="n">
-        <v>25474.78</v>
+        <v>25053.85</v>
       </c>
       <c r="K8" t="n">
-        <v>25772.31</v>
+        <v>25565.53</v>
       </c>
       <c r="L8" t="n">
-        <v>26069.83</v>
+        <v>26077.21</v>
       </c>
       <c r="M8" t="n">
-        <v>26548</v>
+        <v>26247.77</v>
       </c>
       <c r="N8" t="n">
-        <v>27026.16</v>
+        <v>26418.33</v>
       </c>
       <c r="O8" t="n">
-        <v>27143.04</v>
+        <v>27271.13</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1199,22 +1197,24 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1225,57 +1225,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25999.17</v>
+        <v>26319.4</v>
       </c>
       <c r="C9" t="n">
-        <v>26490.71</v>
+        <v>27188.81</v>
       </c>
       <c r="D9" t="n">
-        <v>25496.13</v>
+        <v>26302.93</v>
       </c>
       <c r="E9" t="n">
-        <v>26241.83</v>
+        <v>26572.46</v>
       </c>
       <c r="F9" t="n">
-        <v>335.18</v>
+        <v>330.63</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
       <c r="H9" t="n">
-        <v>994.58</v>
+        <v>885.88</v>
       </c>
       <c r="I9" t="n">
-        <v>25224.41</v>
+        <v>24501.55</v>
       </c>
       <c r="J9" t="n">
-        <v>25053.85</v>
+        <v>25371.45</v>
       </c>
       <c r="K9" t="n">
-        <v>25565.53</v>
+        <v>25744.54</v>
       </c>
       <c r="L9" t="n">
-        <v>26077.21</v>
+        <v>26117.63</v>
       </c>
       <c r="M9" t="n">
-        <v>26247.77</v>
+        <v>26739.12</v>
       </c>
       <c r="N9" t="n">
-        <v>26418.33</v>
+        <v>27360.61</v>
       </c>
       <c r="O9" t="n">
-        <v>27271.13</v>
+        <v>27485.29</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1283,12 +1283,10 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1298,10 +1296,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1311,78 +1307,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26319.4</v>
+        <v>26441.7</v>
       </c>
       <c r="C10" t="n">
-        <v>27188.81</v>
+        <v>26531.8</v>
       </c>
       <c r="D10" t="n">
-        <v>26302.93</v>
+        <v>25178.63</v>
       </c>
       <c r="E10" t="n">
-        <v>26572.46</v>
+        <v>25220.02</v>
       </c>
       <c r="F10" t="n">
-        <v>330.63</v>
+        <v>-1352.44</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0126</v>
+        <v>-0.0509</v>
       </c>
       <c r="H10" t="n">
-        <v>885.88</v>
+        <v>1353.17</v>
       </c>
       <c r="I10" t="n">
-        <v>24501.55</v>
+        <v>25417.05</v>
       </c>
       <c r="J10" t="n">
-        <v>25371.45</v>
+        <v>25599.88</v>
       </c>
       <c r="K10" t="n">
-        <v>25744.54</v>
+        <v>26129.52</v>
       </c>
       <c r="L10" t="n">
-        <v>26117.63</v>
+        <v>26659.17</v>
       </c>
       <c r="M10" t="n">
-        <v>26739.12</v>
+        <v>27015.4</v>
       </c>
       <c r="N10" t="n">
-        <v>27360.61</v>
+        <v>27371.64</v>
       </c>
       <c r="O10" t="n">
-        <v>27485.29</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+        <v>28074.69</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1390,9 +1386,9 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1400,74 +1396,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26441.7</v>
+        <v>25452.87</v>
       </c>
       <c r="C11" t="n">
-        <v>26531.8</v>
+        <v>26136.27</v>
       </c>
       <c r="D11" t="n">
-        <v>25178.63</v>
+        <v>25369.29</v>
       </c>
       <c r="E11" t="n">
-        <v>25220.02</v>
+        <v>25858.89</v>
       </c>
       <c r="F11" t="n">
-        <v>-1352.44</v>
+        <v>638.87</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0509</v>
+        <v>0.0253</v>
       </c>
       <c r="H11" t="n">
-        <v>1353.17</v>
+        <v>766.98</v>
       </c>
       <c r="I11" t="n">
-        <v>25417.05</v>
+        <v>23825.46</v>
       </c>
       <c r="J11" t="n">
-        <v>25599.88</v>
+        <v>23549.25</v>
       </c>
       <c r="K11" t="n">
-        <v>26129.52</v>
+        <v>24543.43</v>
       </c>
       <c r="L11" t="n">
-        <v>26659.17</v>
+        <v>25537.62</v>
       </c>
       <c r="M11" t="n">
-        <v>27015.4</v>
+        <v>25896.6</v>
       </c>
       <c r="N11" t="n">
-        <v>27371.64</v>
+        <v>26255.59</v>
       </c>
       <c r="O11" t="n">
-        <v>28074.69</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>27884.97</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1479,55 +1471,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25452.87</v>
+        <v>25945.87</v>
       </c>
       <c r="C12" t="n">
-        <v>26136.27</v>
+        <v>26264.13</v>
       </c>
       <c r="D12" t="n">
-        <v>25369.29</v>
+        <v>25649.3</v>
       </c>
       <c r="E12" t="n">
-        <v>25858.89</v>
+        <v>26085.08</v>
       </c>
       <c r="F12" t="n">
-        <v>638.87</v>
+        <v>226.19</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0253</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>766.98</v>
+        <v>614.83</v>
       </c>
       <c r="I12" t="n">
-        <v>23825.46</v>
+        <v>24602.31</v>
       </c>
       <c r="J12" t="n">
-        <v>23549.25</v>
+        <v>25144.97</v>
       </c>
       <c r="K12" t="n">
-        <v>24543.43</v>
+        <v>25475.4</v>
       </c>
       <c r="L12" t="n">
-        <v>25537.62</v>
+        <v>25805.83</v>
       </c>
       <c r="M12" t="n">
-        <v>25896.6</v>
+        <v>26242.38</v>
       </c>
       <c r="N12" t="n">
-        <v>26255.59</v>
+        <v>26678.93</v>
       </c>
       <c r="O12" t="n">
-        <v>27884.97</v>
+        <v>26903.25</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1538,7 +1534,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1561,76 +1557,78 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25945.87</v>
+        <v>26067.86</v>
       </c>
       <c r="C13" t="n">
-        <v>26264.13</v>
+        <v>26151.46</v>
       </c>
       <c r="D13" t="n">
-        <v>25649.3</v>
+        <v>25257.61</v>
       </c>
       <c r="E13" t="n">
-        <v>26085.08</v>
+        <v>25976.79</v>
       </c>
       <c r="F13" t="n">
-        <v>226.19</v>
+        <v>-108.29</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0042</v>
       </c>
       <c r="H13" t="n">
-        <v>614.83</v>
+        <v>893.85</v>
       </c>
       <c r="I13" t="n">
-        <v>24602.31</v>
+        <v>25034.47</v>
       </c>
       <c r="J13" t="n">
-        <v>25144.97</v>
+        <v>25534.43</v>
       </c>
       <c r="K13" t="n">
-        <v>25475.4</v>
+        <v>25777.67</v>
       </c>
       <c r="L13" t="n">
-        <v>25805.83</v>
+        <v>26020.9</v>
       </c>
       <c r="M13" t="n">
-        <v>26242.38</v>
+        <v>26392.5</v>
       </c>
       <c r="N13" t="n">
-        <v>26678.93</v>
+        <v>26764.09</v>
       </c>
       <c r="O13" t="n">
-        <v>26903.25</v>
+        <v>26878.96</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1643,59 +1641,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26067.86</v>
+        <v>25718.14</v>
       </c>
       <c r="C14" t="n">
-        <v>26151.46</v>
+        <v>25824.44</v>
       </c>
       <c r="D14" t="n">
-        <v>25257.61</v>
+        <v>25086.54</v>
       </c>
       <c r="E14" t="n">
-        <v>25976.79</v>
+        <v>25690.53</v>
       </c>
       <c r="F14" t="n">
-        <v>-108.29</v>
+        <v>-286.26</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.011</v>
       </c>
       <c r="H14" t="n">
-        <v>893.85</v>
+        <v>737.9</v>
       </c>
       <c r="I14" t="n">
-        <v>25034.47</v>
+        <v>24363.76</v>
       </c>
       <c r="J14" t="n">
-        <v>25534.43</v>
+        <v>25219.06</v>
       </c>
       <c r="K14" t="n">
-        <v>25777.67</v>
+        <v>25529.86</v>
       </c>
       <c r="L14" t="n">
-        <v>26020.9</v>
+        <v>25840.66</v>
       </c>
       <c r="M14" t="n">
-        <v>26392.5</v>
+        <v>26423.71</v>
       </c>
       <c r="N14" t="n">
-        <v>26764.09</v>
+        <v>27006.77</v>
       </c>
       <c r="O14" t="n">
-        <v>26878.96</v>
+        <v>27045.31</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1710,7 +1704,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1734,71 +1728,69 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25718.14</v>
+        <v>25795.94</v>
       </c>
       <c r="C15" t="n">
-        <v>25824.44</v>
+        <v>25927.66</v>
       </c>
       <c r="D15" t="n">
-        <v>25086.54</v>
+        <v>25671.33</v>
       </c>
       <c r="E15" t="n">
-        <v>25690.53</v>
+        <v>25818.93</v>
       </c>
       <c r="F15" t="n">
-        <v>-286.26</v>
+        <v>128.4</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H15" t="n">
-        <v>737.9</v>
+        <v>256.33</v>
       </c>
       <c r="I15" t="n">
-        <v>24363.76</v>
+        <v>24348.64</v>
       </c>
       <c r="J15" t="n">
-        <v>25219.06</v>
+        <v>25070.15</v>
       </c>
       <c r="K15" t="n">
-        <v>25529.86</v>
+        <v>25321.58</v>
       </c>
       <c r="L15" t="n">
-        <v>25840.66</v>
+        <v>25573.01</v>
       </c>
       <c r="M15" t="n">
-        <v>26423.71</v>
+        <v>26059.48</v>
       </c>
       <c r="N15" t="n">
-        <v>27006.77</v>
+        <v>26545.95</v>
       </c>
       <c r="O15" t="n">
-        <v>27045.31</v>
+        <v>26562.34</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1811,172 +1803,176 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25795.94</v>
+        <v>25928.89</v>
       </c>
       <c r="C16" t="n">
-        <v>25927.66</v>
+        <v>26345.63</v>
       </c>
       <c r="D16" t="n">
-        <v>25671.33</v>
+        <v>25554.31</v>
       </c>
       <c r="E16" t="n">
-        <v>25818.93</v>
+        <v>26338.47</v>
       </c>
       <c r="F16" t="n">
-        <v>128.4</v>
+        <v>519.54</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0201</v>
       </c>
       <c r="H16" t="n">
-        <v>256.33</v>
+        <v>791.3200000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>24348.64</v>
+        <v>25415</v>
       </c>
       <c r="J16" t="n">
-        <v>25070.15</v>
+        <v>25572.32</v>
       </c>
       <c r="K16" t="n">
-        <v>25321.58</v>
+        <v>25690.76</v>
       </c>
       <c r="L16" t="n">
-        <v>25573.01</v>
+        <v>25809.21</v>
       </c>
       <c r="M16" t="n">
-        <v>26059.48</v>
+        <v>25947.09</v>
       </c>
       <c r="N16" t="n">
-        <v>26545.95</v>
+        <v>26084.98</v>
       </c>
       <c r="O16" t="n">
-        <v>26562.34</v>
+        <v>26183.99</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25928.89</v>
+        <v>26361.44</v>
       </c>
       <c r="C17" t="n">
-        <v>26345.63</v>
+        <v>26858.13</v>
       </c>
       <c r="D17" t="n">
-        <v>25554.31</v>
+        <v>25960.34</v>
       </c>
       <c r="E17" t="n">
-        <v>26338.47</v>
+        <v>26231.79</v>
       </c>
       <c r="F17" t="n">
-        <v>519.54</v>
+        <v>-106.68</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.0041</v>
       </c>
       <c r="H17" t="n">
-        <v>791.3200000000001</v>
+        <v>897.79</v>
       </c>
       <c r="I17" t="n">
-        <v>25415</v>
+        <v>24762.99</v>
       </c>
       <c r="J17" t="n">
-        <v>25572.32</v>
+        <v>25741.4</v>
       </c>
       <c r="K17" t="n">
-        <v>25690.76</v>
+        <v>25942.81</v>
       </c>
       <c r="L17" t="n">
-        <v>25809.21</v>
+        <v>26144.22</v>
       </c>
       <c r="M17" t="n">
-        <v>25947.09</v>
+        <v>26734.13</v>
       </c>
       <c r="N17" t="n">
-        <v>26084.98</v>
+        <v>27324.04</v>
       </c>
       <c r="O17" t="n">
-        <v>26183.99</v>
+        <v>27136.95</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1992,50 +1988,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26361.44</v>
+        <v>26376.84</v>
       </c>
       <c r="C18" t="n">
-        <v>26858.13</v>
+        <v>27206.84</v>
       </c>
       <c r="D18" t="n">
-        <v>25960.34</v>
+        <v>26187.76</v>
       </c>
       <c r="E18" t="n">
-        <v>26231.79</v>
+        <v>26844.96</v>
       </c>
       <c r="F18" t="n">
-        <v>-106.68</v>
+        <v>613.17</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0234</v>
       </c>
       <c r="H18" t="n">
-        <v>897.79</v>
+        <v>1019.08</v>
       </c>
       <c r="I18" t="n">
-        <v>24762.99</v>
+        <v>25062.55</v>
       </c>
       <c r="J18" t="n">
-        <v>25741.4</v>
+        <v>25245.27</v>
       </c>
       <c r="K18" t="n">
-        <v>25942.81</v>
+        <v>25782.89</v>
       </c>
       <c r="L18" t="n">
-        <v>26144.22</v>
+        <v>26320.51</v>
       </c>
       <c r="M18" t="n">
-        <v>26734.13</v>
+        <v>26680.68</v>
       </c>
       <c r="N18" t="n">
-        <v>27324.04</v>
+        <v>27040.86</v>
       </c>
       <c r="O18" t="n">
-        <v>27136.95</v>
+        <v>27755.92</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2046,19 +2042,21 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2067,59 +2065,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26376.84</v>
+        <v>26641.6</v>
       </c>
       <c r="C19" t="n">
-        <v>27206.84</v>
+        <v>26895.94</v>
       </c>
       <c r="D19" t="n">
-        <v>26187.76</v>
+        <v>26363.86</v>
       </c>
       <c r="E19" t="n">
-        <v>26844.96</v>
+        <v>26749.51</v>
       </c>
       <c r="F19" t="n">
-        <v>613.17</v>
+        <v>-95.45</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0234</v>
+        <v>-0.0036</v>
       </c>
       <c r="H19" t="n">
-        <v>1019.08</v>
+        <v>532.08</v>
       </c>
       <c r="I19" t="n">
-        <v>25062.55</v>
+        <v>25168.68</v>
       </c>
       <c r="J19" t="n">
-        <v>25245.27</v>
+        <v>25899.71</v>
       </c>
       <c r="K19" t="n">
-        <v>25782.89</v>
+        <v>26335.42</v>
       </c>
       <c r="L19" t="n">
-        <v>26320.51</v>
+        <v>26771.13</v>
       </c>
       <c r="M19" t="n">
-        <v>26680.68</v>
+        <v>27354.5</v>
       </c>
       <c r="N19" t="n">
-        <v>27040.86</v>
+        <v>27937.87</v>
       </c>
       <c r="O19" t="n">
-        <v>27755.92</v>
+        <v>28225.92</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2132,18 +2126,14 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2153,55 +2143,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26641.6</v>
+        <v>26844.04</v>
       </c>
       <c r="C20" t="n">
-        <v>26895.94</v>
+        <v>28056.1</v>
       </c>
       <c r="D20" t="n">
-        <v>26363.86</v>
+        <v>26619.83</v>
       </c>
       <c r="E20" t="n">
-        <v>26749.51</v>
+        <v>27387.11</v>
       </c>
       <c r="F20" t="n">
-        <v>-95.45</v>
+        <v>637.6</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0238</v>
       </c>
       <c r="H20" t="n">
-        <v>532.08</v>
+        <v>1436.27</v>
       </c>
       <c r="I20" t="n">
-        <v>25168.68</v>
+        <v>25831.78</v>
       </c>
       <c r="J20" t="n">
-        <v>25899.71</v>
+        <v>26277.23</v>
       </c>
       <c r="K20" t="n">
-        <v>26335.42</v>
+        <v>26483.47</v>
       </c>
       <c r="L20" t="n">
-        <v>26771.13</v>
+        <v>26689.7</v>
       </c>
       <c r="M20" t="n">
-        <v>27354.5</v>
+        <v>27015.55</v>
       </c>
       <c r="N20" t="n">
-        <v>27937.87</v>
+        <v>27341.4</v>
       </c>
       <c r="O20" t="n">
-        <v>28225.92</v>
+        <v>27428.02</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2214,76 +2208,78 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26844.04</v>
+        <v>27097.34</v>
       </c>
       <c r="C21" t="n">
-        <v>28056.1</v>
+        <v>27126.48</v>
       </c>
       <c r="D21" t="n">
-        <v>26619.83</v>
+        <v>26295.03</v>
       </c>
       <c r="E21" t="n">
-        <v>27387.11</v>
+        <v>26559.95</v>
       </c>
       <c r="F21" t="n">
-        <v>637.6</v>
+        <v>-827.16</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0238</v>
+        <v>-0.0302</v>
       </c>
       <c r="H21" t="n">
-        <v>1436.27</v>
+        <v>831.45</v>
       </c>
       <c r="I21" t="n">
-        <v>25831.78</v>
+        <v>25183.56</v>
       </c>
       <c r="J21" t="n">
-        <v>26277.23</v>
+        <v>25975.41</v>
       </c>
       <c r="K21" t="n">
-        <v>26483.47</v>
+        <v>26668.97</v>
       </c>
       <c r="L21" t="n">
-        <v>26689.7</v>
+        <v>27362.54</v>
       </c>
       <c r="M21" t="n">
-        <v>27015.55</v>
+        <v>28105.24</v>
       </c>
       <c r="N21" t="n">
-        <v>27341.4</v>
+        <v>28847.95</v>
       </c>
       <c r="O21" t="n">
-        <v>27428.02</v>
+        <v>29492.37</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2291,83 +2287,83 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27097.34</v>
+        <v>26982.49</v>
       </c>
       <c r="C22" t="n">
-        <v>27126.48</v>
+        <v>27397.65</v>
       </c>
       <c r="D22" t="n">
-        <v>26295.03</v>
+        <v>26444.46</v>
       </c>
       <c r="E22" t="n">
-        <v>26559.95</v>
+        <v>26567.12</v>
       </c>
       <c r="F22" t="n">
-        <v>-827.16</v>
+        <v>7.17</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0003</v>
       </c>
       <c r="H22" t="n">
-        <v>831.45</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>25183.56</v>
+        <v>25463.58</v>
       </c>
       <c r="J22" t="n">
-        <v>25975.41</v>
+        <v>25653.1</v>
       </c>
       <c r="K22" t="n">
-        <v>26668.97</v>
+        <v>26144.22</v>
       </c>
       <c r="L22" t="n">
-        <v>27362.54</v>
+        <v>26635.35</v>
       </c>
       <c r="M22" t="n">
-        <v>28105.24</v>
+        <v>26975.67</v>
       </c>
       <c r="N22" t="n">
-        <v>28847.95</v>
+        <v>27316</v>
       </c>
       <c r="O22" t="n">
-        <v>29492.37</v>
+        <v>27957.93</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2375,21 +2371,23 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2399,59 +2397,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26982.49</v>
+        <v>26501.2</v>
       </c>
       <c r="C23" t="n">
-        <v>27397.65</v>
+        <v>26734.41</v>
       </c>
       <c r="D23" t="n">
-        <v>26444.46</v>
+        <v>26356.96</v>
       </c>
       <c r="E23" t="n">
-        <v>26567.12</v>
+        <v>26413.35</v>
       </c>
       <c r="F23" t="n">
-        <v>7.17</v>
+        <v>-153.77</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0058</v>
       </c>
       <c r="H23" t="n">
-        <v>953.1900000000001</v>
+        <v>377.45</v>
       </c>
       <c r="I23" t="n">
-        <v>25463.58</v>
+        <v>25491.27</v>
       </c>
       <c r="J23" t="n">
-        <v>25653.1</v>
+        <v>25436.96</v>
       </c>
       <c r="K23" t="n">
-        <v>26144.22</v>
+        <v>26090.52</v>
       </c>
       <c r="L23" t="n">
-        <v>26635.35</v>
+        <v>26744.09</v>
       </c>
       <c r="M23" t="n">
-        <v>26975.67</v>
+        <v>27043.71</v>
       </c>
       <c r="N23" t="n">
-        <v>27316</v>
+        <v>27343.34</v>
       </c>
       <c r="O23" t="n">
-        <v>27957.93</v>
+        <v>28350.84</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2459,23 +2453,21 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2485,55 +2477,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26501.2</v>
+        <v>26798.97</v>
       </c>
       <c r="C24" t="n">
-        <v>26734.41</v>
+        <v>27156.28</v>
       </c>
       <c r="D24" t="n">
-        <v>26356.96</v>
+        <v>26373.01</v>
       </c>
       <c r="E24" t="n">
-        <v>26413.35</v>
+        <v>26630.54</v>
       </c>
       <c r="F24" t="n">
-        <v>-153.77</v>
+        <v>217.19</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>377.45</v>
+        <v>783.27</v>
       </c>
       <c r="I24" t="n">
-        <v>25491.27</v>
+        <v>25979.51</v>
       </c>
       <c r="J24" t="n">
-        <v>25436.96</v>
+        <v>25969.73</v>
       </c>
       <c r="K24" t="n">
-        <v>26090.52</v>
+        <v>26224.62</v>
       </c>
       <c r="L24" t="n">
-        <v>26744.09</v>
+        <v>26479.52</v>
       </c>
       <c r="M24" t="n">
-        <v>27043.71</v>
+        <v>26602.07</v>
       </c>
       <c r="N24" t="n">
-        <v>27343.34</v>
+        <v>26724.63</v>
       </c>
       <c r="O24" t="n">
-        <v>28350.84</v>
+        <v>27111.86</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2541,116 +2537,116 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26798.97</v>
+        <v>26305.58</v>
       </c>
       <c r="C25" t="n">
-        <v>27156.28</v>
+        <v>26403.85</v>
       </c>
       <c r="D25" t="n">
-        <v>26373.01</v>
+        <v>24958.43</v>
       </c>
       <c r="E25" t="n">
-        <v>26630.54</v>
+        <v>25757.29</v>
       </c>
       <c r="F25" t="n">
-        <v>217.19</v>
+        <v>-873.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="H25" t="n">
-        <v>783.27</v>
+        <v>1445.42</v>
       </c>
       <c r="I25" t="n">
-        <v>25979.51</v>
+        <v>25589.74</v>
       </c>
       <c r="J25" t="n">
-        <v>25969.73</v>
+        <v>25780.22</v>
       </c>
       <c r="K25" t="n">
-        <v>26224.62</v>
+        <v>26238.9</v>
       </c>
       <c r="L25" t="n">
-        <v>26479.52</v>
+        <v>26697.59</v>
       </c>
       <c r="M25" t="n">
-        <v>26602.07</v>
+        <v>27022.17</v>
       </c>
       <c r="N25" t="n">
-        <v>26724.63</v>
+        <v>27346.76</v>
       </c>
       <c r="O25" t="n">
-        <v>27111.86</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>27939.55</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2658,69 +2654,65 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26305.58</v>
+        <v>25075.74</v>
       </c>
       <c r="C26" t="n">
-        <v>26403.85</v>
+        <v>26149.64</v>
       </c>
       <c r="D26" t="n">
-        <v>24958.43</v>
+        <v>24906</v>
       </c>
       <c r="E26" t="n">
-        <v>25757.29</v>
+        <v>25465.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-873.25</v>
+        <v>-291.69</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0328</v>
+        <v>-0.0113</v>
       </c>
       <c r="H26" t="n">
-        <v>1445.42</v>
+        <v>1243.64</v>
       </c>
       <c r="I26" t="n">
-        <v>25589.74</v>
+        <v>23513.01</v>
       </c>
       <c r="J26" t="n">
-        <v>25780.22</v>
+        <v>24349.94</v>
       </c>
       <c r="K26" t="n">
-        <v>26238.9</v>
+        <v>25034.58</v>
       </c>
       <c r="L26" t="n">
-        <v>26697.59</v>
+        <v>25719.21</v>
       </c>
       <c r="M26" t="n">
-        <v>27022.17</v>
+        <v>26480</v>
       </c>
       <c r="N26" t="n">
-        <v>27346.76</v>
+        <v>27240.78</v>
       </c>
       <c r="O26" t="n">
-        <v>27939.55</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>27849.27</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2742,50 +2734,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25075.74</v>
+        <v>25436.27</v>
       </c>
       <c r="C27" t="n">
-        <v>26149.64</v>
+        <v>26250.14</v>
       </c>
       <c r="D27" t="n">
-        <v>24906</v>
+        <v>25121.46</v>
       </c>
       <c r="E27" t="n">
-        <v>25465.6</v>
+        <v>25277.32</v>
       </c>
       <c r="F27" t="n">
-        <v>-291.69</v>
+        <v>-188.28</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.0074</v>
       </c>
       <c r="H27" t="n">
-        <v>1243.64</v>
+        <v>1128.68</v>
       </c>
       <c r="I27" t="n">
-        <v>23513.01</v>
+        <v>23662.36</v>
       </c>
       <c r="J27" t="n">
-        <v>24349.94</v>
+        <v>24190.85</v>
       </c>
       <c r="K27" t="n">
-        <v>25034.58</v>
+        <v>24843.78</v>
       </c>
       <c r="L27" t="n">
-        <v>25719.21</v>
+        <v>25496.71</v>
       </c>
       <c r="M27" t="n">
-        <v>26480</v>
+        <v>26087.42</v>
       </c>
       <c r="N27" t="n">
-        <v>27240.78</v>
+        <v>26678.13</v>
       </c>
       <c r="O27" t="n">
-        <v>27849.27</v>
+        <v>27393.28</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2793,19 +2785,19 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2817,55 +2809,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25436.27</v>
+        <v>24789.14</v>
       </c>
       <c r="C28" t="n">
-        <v>26250.14</v>
+        <v>25390.3</v>
       </c>
       <c r="D28" t="n">
-        <v>25121.46</v>
+        <v>24203.54</v>
       </c>
       <c r="E28" t="n">
-        <v>25277.32</v>
+        <v>24951.88</v>
       </c>
       <c r="F28" t="n">
-        <v>-188.28</v>
+        <v>-325.44</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0129</v>
       </c>
       <c r="H28" t="n">
-        <v>1128.68</v>
+        <v>1186.76</v>
       </c>
       <c r="I28" t="n">
-        <v>23662.36</v>
+        <v>23992.78</v>
       </c>
       <c r="J28" t="n">
-        <v>24190.85</v>
+        <v>23944.4</v>
       </c>
       <c r="K28" t="n">
-        <v>24843.78</v>
+        <v>24712.98</v>
       </c>
       <c r="L28" t="n">
-        <v>25496.71</v>
+        <v>25481.56</v>
       </c>
       <c r="M28" t="n">
-        <v>26087.42</v>
+        <v>25841.66</v>
       </c>
       <c r="N28" t="n">
-        <v>26678.13</v>
+        <v>26201.76</v>
       </c>
       <c r="O28" t="n">
-        <v>27393.28</v>
+        <v>27378.82</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2873,18 +2869,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2897,59 +2893,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24789.14</v>
+        <v>24532.85</v>
       </c>
       <c r="C29" t="n">
-        <v>25390.3</v>
+        <v>25429.76</v>
       </c>
       <c r="D29" t="n">
-        <v>24203.54</v>
+        <v>24409.57</v>
       </c>
       <c r="E29" t="n">
-        <v>24951.88</v>
+        <v>25116.53</v>
       </c>
       <c r="F29" t="n">
-        <v>-325.44</v>
+        <v>164.65</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0066</v>
       </c>
       <c r="H29" t="n">
-        <v>1186.76</v>
+        <v>1020.19</v>
       </c>
       <c r="I29" t="n">
-        <v>23992.78</v>
+        <v>23016.78</v>
       </c>
       <c r="J29" t="n">
-        <v>23944.4</v>
+        <v>23842.6</v>
       </c>
       <c r="K29" t="n">
-        <v>24712.98</v>
+        <v>24358.5</v>
       </c>
       <c r="L29" t="n">
-        <v>25481.56</v>
+        <v>24874.4</v>
       </c>
       <c r="M29" t="n">
-        <v>25841.66</v>
+        <v>25545.26</v>
       </c>
       <c r="N29" t="n">
-        <v>26201.76</v>
+        <v>26216.12</v>
       </c>
       <c r="O29" t="n">
-        <v>27378.82</v>
+        <v>26577.06</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2957,14 +2949,12 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2981,55 +2971,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24532.85</v>
+        <v>25772.56</v>
       </c>
       <c r="C30" t="n">
-        <v>25429.76</v>
+        <v>26073.97</v>
       </c>
       <c r="D30" t="n">
-        <v>24409.57</v>
+        <v>25653.63</v>
       </c>
       <c r="E30" t="n">
-        <v>25116.53</v>
+        <v>25893.54</v>
       </c>
       <c r="F30" t="n">
-        <v>164.65</v>
+        <v>777.01</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0309</v>
       </c>
       <c r="H30" t="n">
-        <v>1020.19</v>
+        <v>420.34</v>
       </c>
       <c r="I30" t="n">
-        <v>23016.78</v>
+        <v>23389.38</v>
       </c>
       <c r="J30" t="n">
-        <v>23842.6</v>
+        <v>24194.77</v>
       </c>
       <c r="K30" t="n">
-        <v>24358.5</v>
+        <v>24606.43</v>
       </c>
       <c r="L30" t="n">
-        <v>24874.4</v>
+        <v>25018.1</v>
       </c>
       <c r="M30" t="n">
-        <v>25545.26</v>
+        <v>25626.62</v>
       </c>
       <c r="N30" t="n">
-        <v>26216.12</v>
+        <v>26235.15</v>
       </c>
       <c r="O30" t="n">
-        <v>26577.06</v>
+        <v>26449.95</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3040,13 +3034,15 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3068,50 +3064,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25772.56</v>
+        <v>25708.64</v>
       </c>
       <c r="C31" t="n">
-        <v>26073.97</v>
+        <v>26403.07</v>
       </c>
       <c r="D31" t="n">
-        <v>25653.63</v>
+        <v>25508.53</v>
       </c>
       <c r="E31" t="n">
-        <v>25893.54</v>
+        <v>26160.33</v>
       </c>
       <c r="F31" t="n">
-        <v>777.01</v>
+        <v>266.79</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.0103</v>
       </c>
       <c r="H31" t="n">
-        <v>420.34</v>
+        <v>894.54</v>
       </c>
       <c r="I31" t="n">
-        <v>23389.38</v>
+        <v>25233.29</v>
       </c>
       <c r="J31" t="n">
-        <v>24194.77</v>
+        <v>25488.07</v>
       </c>
       <c r="K31" t="n">
-        <v>24606.43</v>
+        <v>25683.37</v>
       </c>
       <c r="L31" t="n">
-        <v>25018.1</v>
+        <v>25878.67</v>
       </c>
       <c r="M31" t="n">
-        <v>25626.62</v>
+        <v>26103.71</v>
       </c>
       <c r="N31" t="n">
-        <v>26235.15</v>
+        <v>26328.75</v>
       </c>
       <c r="O31" t="n">
-        <v>26449.95</v>
+        <v>26494.31</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3119,10 +3115,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3132,8 +3130,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3145,57 +3145,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25708.64</v>
+        <v>26204.61</v>
       </c>
       <c r="C32" t="n">
-        <v>26403.07</v>
+        <v>26529.49</v>
       </c>
       <c r="D32" t="n">
-        <v>25508.53</v>
+        <v>25639.26</v>
       </c>
       <c r="E32" t="n">
-        <v>26160.33</v>
+        <v>25978.07</v>
       </c>
       <c r="F32" t="n">
-        <v>266.79</v>
+        <v>-182.26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.007</v>
       </c>
       <c r="H32" t="n">
-        <v>894.54</v>
+        <v>890.23</v>
       </c>
       <c r="I32" t="n">
-        <v>25233.29</v>
+        <v>24613.99</v>
       </c>
       <c r="J32" t="n">
-        <v>25488.07</v>
+        <v>25368.05</v>
       </c>
       <c r="K32" t="n">
-        <v>25683.37</v>
+        <v>25713.06</v>
       </c>
       <c r="L32" t="n">
-        <v>25878.67</v>
+        <v>26058.06</v>
       </c>
       <c r="M32" t="n">
-        <v>26103.71</v>
+        <v>26607.6</v>
       </c>
       <c r="N32" t="n">
-        <v>26328.75</v>
+        <v>27157.14</v>
       </c>
       <c r="O32" t="n">
-        <v>26494.31</v>
+        <v>27297.61</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3210,18 +3210,14 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3240,50 +3236,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26204.61</v>
+        <v>25976.97</v>
       </c>
       <c r="C33" t="n">
-        <v>26529.49</v>
+        <v>26132.94</v>
       </c>
       <c r="D33" t="n">
-        <v>25639.26</v>
+        <v>25609.61</v>
       </c>
       <c r="E33" t="n">
-        <v>25978.07</v>
+        <v>25776.53</v>
       </c>
       <c r="F33" t="n">
-        <v>-182.26</v>
+        <v>-201.54</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0078</v>
       </c>
       <c r="H33" t="n">
-        <v>890.23</v>
+        <v>523.33</v>
       </c>
       <c r="I33" t="n">
-        <v>24613.99</v>
+        <v>24749.03</v>
       </c>
       <c r="J33" t="n">
-        <v>25368.05</v>
+        <v>25034.69</v>
       </c>
       <c r="K33" t="n">
-        <v>25713.06</v>
+        <v>25532.96</v>
       </c>
       <c r="L33" t="n">
-        <v>26058.06</v>
+        <v>26031.22</v>
       </c>
       <c r="M33" t="n">
-        <v>26607.6</v>
+        <v>26423.19</v>
       </c>
       <c r="N33" t="n">
-        <v>27157.14</v>
+        <v>26815.15</v>
       </c>
       <c r="O33" t="n">
-        <v>27297.61</v>
+        <v>27419.72</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3293,12 +3289,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3315,59 +3311,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25976.97</v>
+        <v>26138.34</v>
       </c>
       <c r="C34" t="n">
-        <v>26132.94</v>
+        <v>26669.26</v>
       </c>
       <c r="D34" t="n">
-        <v>25609.61</v>
+        <v>25690.36</v>
       </c>
       <c r="E34" t="n">
-        <v>25776.53</v>
+        <v>26393.71</v>
       </c>
       <c r="F34" t="n">
-        <v>-201.54</v>
+        <v>617.1799999999999</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0239</v>
       </c>
       <c r="H34" t="n">
-        <v>523.33</v>
+        <v>978.9</v>
       </c>
       <c r="I34" t="n">
-        <v>24749.03</v>
+        <v>25086.28</v>
       </c>
       <c r="J34" t="n">
-        <v>25034.69</v>
+        <v>25205.83</v>
       </c>
       <c r="K34" t="n">
-        <v>25532.96</v>
+        <v>25514.86</v>
       </c>
       <c r="L34" t="n">
-        <v>26031.22</v>
+        <v>25823.9</v>
       </c>
       <c r="M34" t="n">
-        <v>26423.19</v>
+        <v>26038.19</v>
       </c>
       <c r="N34" t="n">
-        <v>26815.15</v>
+        <v>26252.49</v>
       </c>
       <c r="O34" t="n">
-        <v>27419.72</v>
+        <v>26656.27</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3375,28 +3367,32 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3404,50 +3400,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26138.34</v>
+        <v>26310.87</v>
       </c>
       <c r="C35" t="n">
-        <v>26669.26</v>
+        <v>26844.8</v>
       </c>
       <c r="D35" t="n">
-        <v>25690.36</v>
+        <v>25847.15</v>
       </c>
       <c r="E35" t="n">
-        <v>26393.71</v>
+        <v>25962.73</v>
       </c>
       <c r="F35" t="n">
-        <v>617.1799999999999</v>
+        <v>-430.98</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0163</v>
       </c>
       <c r="H35" t="n">
-        <v>978.9</v>
+        <v>997.65</v>
       </c>
       <c r="I35" t="n">
-        <v>25086.28</v>
+        <v>24711.46</v>
       </c>
       <c r="J35" t="n">
-        <v>25205.83</v>
+        <v>25521.76</v>
       </c>
       <c r="K35" t="n">
-        <v>25514.86</v>
+        <v>25904.26</v>
       </c>
       <c r="L35" t="n">
-        <v>25823.9</v>
+        <v>26286.76</v>
       </c>
       <c r="M35" t="n">
-        <v>26038.19</v>
+        <v>26883.16</v>
       </c>
       <c r="N35" t="n">
-        <v>26252.49</v>
+        <v>27479.56</v>
       </c>
       <c r="O35" t="n">
-        <v>26656.27</v>
+        <v>27648.16</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3455,83 +3451,83 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26310.87</v>
+        <v>25838.96</v>
       </c>
       <c r="C36" t="n">
-        <v>26844.8</v>
+        <v>25845.46</v>
       </c>
       <c r="D36" t="n">
-        <v>25847.15</v>
+        <v>25341.73</v>
       </c>
       <c r="E36" t="n">
-        <v>25962.73</v>
+        <v>25606.03</v>
       </c>
       <c r="F36" t="n">
-        <v>-430.98</v>
+        <v>-356.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0137</v>
       </c>
       <c r="H36" t="n">
-        <v>997.65</v>
+        <v>503.73</v>
       </c>
       <c r="I36" t="n">
-        <v>24711.46</v>
+        <v>24849.5</v>
       </c>
       <c r="J36" t="n">
-        <v>25521.76</v>
+        <v>24773.46</v>
       </c>
       <c r="K36" t="n">
-        <v>25904.26</v>
+        <v>25463.91</v>
       </c>
       <c r="L36" t="n">
-        <v>26286.76</v>
+        <v>26154.35</v>
       </c>
       <c r="M36" t="n">
-        <v>26883.16</v>
+        <v>26461.56</v>
       </c>
       <c r="N36" t="n">
-        <v>27479.56</v>
+        <v>26768.76</v>
       </c>
       <c r="O36" t="n">
-        <v>27648.16</v>
+        <v>27842.45</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3544,7 +3540,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3565,70 +3561,74 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25838.96</v>
+        <v>25622.36</v>
       </c>
       <c r="C37" t="n">
-        <v>25845.46</v>
+        <v>25768.38</v>
       </c>
       <c r="D37" t="n">
-        <v>25341.73</v>
+        <v>24727.26</v>
       </c>
       <c r="E37" t="n">
-        <v>25606.03</v>
+        <v>25182.39</v>
       </c>
       <c r="F37" t="n">
-        <v>-356.7</v>
+        <v>-423.64</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0165</v>
       </c>
       <c r="H37" t="n">
-        <v>503.73</v>
+        <v>1041.12</v>
       </c>
       <c r="I37" t="n">
-        <v>24849.5</v>
+        <v>24838</v>
       </c>
       <c r="J37" t="n">
-        <v>24773.46</v>
+        <v>25108.52</v>
       </c>
       <c r="K37" t="n">
-        <v>25463.91</v>
+        <v>25354.16</v>
       </c>
       <c r="L37" t="n">
-        <v>26154.35</v>
+        <v>25599.81</v>
       </c>
       <c r="M37" t="n">
-        <v>26461.56</v>
+        <v>25857.89</v>
       </c>
       <c r="N37" t="n">
-        <v>26768.76</v>
+        <v>26115.98</v>
       </c>
       <c r="O37" t="n">
-        <v>27842.45</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>26349.19</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3656,74 +3656,70 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25622.36</v>
+        <v>25180.05</v>
       </c>
       <c r="C38" t="n">
-        <v>25768.38</v>
+        <v>26045.07</v>
       </c>
       <c r="D38" t="n">
-        <v>24727.26</v>
+        <v>24928.14</v>
       </c>
       <c r="E38" t="n">
-        <v>25182.39</v>
+        <v>24961.95</v>
       </c>
       <c r="F38" t="n">
-        <v>-423.64</v>
+        <v>-220.44</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0165</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>1041.12</v>
+        <v>1116.93</v>
       </c>
       <c r="I38" t="n">
-        <v>24838</v>
+        <v>23686.14</v>
       </c>
       <c r="J38" t="n">
-        <v>25108.52</v>
+        <v>24108.55</v>
       </c>
       <c r="K38" t="n">
-        <v>25354.16</v>
+        <v>24661.83</v>
       </c>
       <c r="L38" t="n">
-        <v>25599.81</v>
+        <v>25215.11</v>
       </c>
       <c r="M38" t="n">
-        <v>25857.89</v>
+        <v>25702.95</v>
       </c>
       <c r="N38" t="n">
-        <v>26115.98</v>
+        <v>26190.8</v>
       </c>
       <c r="O38" t="n">
-        <v>26349.19</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
+        <v>26809.5</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3737,57 +3733,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25180.05</v>
+        <v>24582.91</v>
       </c>
       <c r="C39" t="n">
-        <v>26045.07</v>
+        <v>24837.98</v>
       </c>
       <c r="D39" t="n">
-        <v>24928.14</v>
+        <v>23999.67</v>
       </c>
       <c r="E39" t="n">
-        <v>24961.95</v>
+        <v>24718.1</v>
       </c>
       <c r="F39" t="n">
-        <v>-220.44</v>
+        <v>-243.85</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="H39" t="n">
-        <v>1116.93</v>
+        <v>838.3099999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>23686.14</v>
+        <v>23811.21</v>
       </c>
       <c r="J39" t="n">
-        <v>24108.55</v>
+        <v>23582.69</v>
       </c>
       <c r="K39" t="n">
-        <v>24661.83</v>
+        <v>24403.48</v>
       </c>
       <c r="L39" t="n">
-        <v>25215.11</v>
+        <v>25224.28</v>
       </c>
       <c r="M39" t="n">
-        <v>25702.95</v>
+        <v>25520.41</v>
       </c>
       <c r="N39" t="n">
-        <v>26190.8</v>
+        <v>25816.55</v>
       </c>
       <c r="O39" t="n">
-        <v>26809.5</v>
+        <v>27162</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3795,18 +3791,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3821,70 +3817,72 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24582.91</v>
+        <v>25001.42</v>
       </c>
       <c r="C40" t="n">
-        <v>24837.98</v>
+        <v>25047.9</v>
       </c>
       <c r="D40" t="n">
-        <v>23999.67</v>
+        <v>23749.99</v>
       </c>
       <c r="E40" t="n">
-        <v>24718.1</v>
+        <v>23924.81</v>
       </c>
       <c r="F40" t="n">
-        <v>-243.85</v>
+        <v>-793.29</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0321</v>
       </c>
       <c r="H40" t="n">
-        <v>838.3099999999999</v>
+        <v>1297.91</v>
       </c>
       <c r="I40" t="n">
-        <v>23811.21</v>
+        <v>23161.36</v>
       </c>
       <c r="J40" t="n">
-        <v>23582.69</v>
+        <v>24029.43</v>
       </c>
       <c r="K40" t="n">
-        <v>24403.48</v>
+        <v>24298.94</v>
       </c>
       <c r="L40" t="n">
-        <v>25224.28</v>
+        <v>24568.46</v>
       </c>
       <c r="M40" t="n">
-        <v>25520.41</v>
+        <v>25137.25</v>
       </c>
       <c r="N40" t="n">
-        <v>25816.55</v>
+        <v>25706.05</v>
       </c>
       <c r="O40" t="n">
-        <v>27162</v>
+        <v>25676.29</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3898,79 +3896,79 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25001.42</v>
+        <v>23811.76</v>
       </c>
       <c r="C41" t="n">
-        <v>25047.9</v>
+        <v>23863.71</v>
       </c>
       <c r="D41" t="n">
-        <v>23749.99</v>
+        <v>22518</v>
       </c>
       <c r="E41" t="n">
-        <v>23924.81</v>
+        <v>22671.86</v>
       </c>
       <c r="F41" t="n">
-        <v>-793.29</v>
+        <v>-1252.95</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0524</v>
       </c>
       <c r="H41" t="n">
-        <v>1297.91</v>
+        <v>1345.71</v>
       </c>
       <c r="I41" t="n">
-        <v>23161.36</v>
+        <v>22452.08</v>
       </c>
       <c r="J41" t="n">
-        <v>24029.43</v>
+        <v>22389.83</v>
       </c>
       <c r="K41" t="n">
-        <v>24298.94</v>
+        <v>23275.86</v>
       </c>
       <c r="L41" t="n">
-        <v>24568.46</v>
+        <v>24161.88</v>
       </c>
       <c r="M41" t="n">
-        <v>25137.25</v>
+        <v>24573.77</v>
       </c>
       <c r="N41" t="n">
-        <v>25706.05</v>
+        <v>24985.65</v>
       </c>
       <c r="O41" t="n">
-        <v>25676.29</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>26345.81</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3989,81 +3987,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>23811.76</v>
+        <v>22827.65</v>
       </c>
       <c r="C42" t="n">
-        <v>23863.71</v>
+        <v>23516.7</v>
       </c>
       <c r="D42" t="n">
-        <v>22518</v>
+        <v>22685.14</v>
       </c>
       <c r="E42" t="n">
-        <v>22671.86</v>
+        <v>23350.03</v>
       </c>
       <c r="F42" t="n">
-        <v>-1252.95</v>
+        <v>678.17</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0524</v>
+        <v>0.0299</v>
       </c>
       <c r="H42" t="n">
-        <v>1345.71</v>
+        <v>831.5599999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>22452.08</v>
+        <v>21172.29</v>
       </c>
       <c r="J42" t="n">
-        <v>22389.83</v>
+        <v>21066.65</v>
       </c>
       <c r="K42" t="n">
-        <v>23275.86</v>
+        <v>21999</v>
       </c>
       <c r="L42" t="n">
-        <v>24161.88</v>
+        <v>22931.36</v>
       </c>
       <c r="M42" t="n">
-        <v>24573.77</v>
+        <v>23344.71</v>
       </c>
       <c r="N42" t="n">
-        <v>24985.65</v>
+        <v>23758.07</v>
       </c>
       <c r="O42" t="n">
-        <v>26345.81</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
+        <v>25209.42</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4075,55 +4067,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22827.65</v>
+        <v>23404.61</v>
       </c>
       <c r="C43" t="n">
-        <v>23516.7</v>
+        <v>24499.63</v>
       </c>
       <c r="D43" t="n">
-        <v>22685.14</v>
+        <v>23229.38</v>
       </c>
       <c r="E43" t="n">
-        <v>23350.03</v>
+        <v>24175.12</v>
       </c>
       <c r="F43" t="n">
-        <v>678.17</v>
+        <v>825.09</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0353</v>
       </c>
       <c r="H43" t="n">
-        <v>831.5599999999999</v>
+        <v>1270.25</v>
       </c>
       <c r="I43" t="n">
-        <v>21172.29</v>
+        <v>21853.58</v>
       </c>
       <c r="J43" t="n">
-        <v>21066.65</v>
+        <v>22643.03</v>
       </c>
       <c r="K43" t="n">
-        <v>21999</v>
+        <v>22934.25</v>
       </c>
       <c r="L43" t="n">
-        <v>22931.36</v>
+        <v>23225.47</v>
       </c>
       <c r="M43" t="n">
-        <v>23344.71</v>
+        <v>23765.81</v>
       </c>
       <c r="N43" t="n">
-        <v>23758.07</v>
+        <v>24306.14</v>
       </c>
       <c r="O43" t="n">
-        <v>25209.42</v>
+        <v>24348.26</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4134,21 +4130,25 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
@@ -4157,57 +4157,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23404.61</v>
+        <v>24157.65</v>
       </c>
       <c r="C44" t="n">
-        <v>24499.63</v>
+        <v>25221.44</v>
       </c>
       <c r="D44" t="n">
-        <v>23229.38</v>
+        <v>23902.05</v>
       </c>
       <c r="E44" t="n">
-        <v>24175.12</v>
+        <v>24562.24</v>
       </c>
       <c r="F44" t="n">
-        <v>825.09</v>
+        <v>387.12</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.016</v>
       </c>
       <c r="H44" t="n">
-        <v>1270.25</v>
+        <v>1319.39</v>
       </c>
       <c r="I44" t="n">
-        <v>21853.58</v>
+        <v>21959.13</v>
       </c>
       <c r="J44" t="n">
-        <v>22643.03</v>
+        <v>23060.18</v>
       </c>
       <c r="K44" t="n">
-        <v>22934.25</v>
+        <v>23539.99</v>
       </c>
       <c r="L44" t="n">
-        <v>23225.47</v>
+        <v>24019.81</v>
       </c>
       <c r="M44" t="n">
-        <v>23765.81</v>
+        <v>24810.24</v>
       </c>
       <c r="N44" t="n">
-        <v>24306.14</v>
+        <v>25600.68</v>
       </c>
       <c r="O44" t="n">
-        <v>24348.26</v>
+        <v>25769.88</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4218,25 +4218,21 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
@@ -4252,50 +4248,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>24157.65</v>
+        <v>24835.03</v>
       </c>
       <c r="C45" t="n">
-        <v>25221.44</v>
+        <v>25267.39</v>
       </c>
       <c r="D45" t="n">
-        <v>23902.05</v>
+        <v>24756.36</v>
       </c>
       <c r="E45" t="n">
-        <v>24562.24</v>
+        <v>24963.23</v>
       </c>
       <c r="F45" t="n">
-        <v>387.12</v>
+        <v>400.99</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
       </c>
       <c r="H45" t="n">
-        <v>1319.39</v>
+        <v>511.03</v>
       </c>
       <c r="I45" t="n">
-        <v>21959.13</v>
+        <v>22582.66</v>
       </c>
       <c r="J45" t="n">
-        <v>23060.18</v>
+        <v>23243.1</v>
       </c>
       <c r="K45" t="n">
-        <v>23539.99</v>
+        <v>23902.55</v>
       </c>
       <c r="L45" t="n">
-        <v>24019.81</v>
+        <v>24561.99</v>
       </c>
       <c r="M45" t="n">
-        <v>24810.24</v>
+        <v>25221.93</v>
       </c>
       <c r="N45" t="n">
-        <v>25600.68</v>
+        <v>25881.88</v>
       </c>
       <c r="O45" t="n">
-        <v>25769.88</v>
+        <v>26540.83</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4306,7 +4302,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4336,50 +4332,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24835.03</v>
+        <v>24993.77</v>
       </c>
       <c r="C46" t="n">
-        <v>25267.39</v>
+        <v>25971.63</v>
       </c>
       <c r="D46" t="n">
-        <v>24756.36</v>
+        <v>24938.34</v>
       </c>
       <c r="E46" t="n">
-        <v>24963.23</v>
+        <v>25884.43</v>
       </c>
       <c r="F46" t="n">
-        <v>400.99</v>
+        <v>921.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0369</v>
       </c>
       <c r="H46" t="n">
-        <v>511.03</v>
+        <v>1033.29</v>
       </c>
       <c r="I46" t="n">
-        <v>22582.66</v>
+        <v>24245.33</v>
       </c>
       <c r="J46" t="n">
-        <v>23243.1</v>
+        <v>24427.88</v>
       </c>
       <c r="K46" t="n">
-        <v>23902.55</v>
+        <v>24707.71</v>
       </c>
       <c r="L46" t="n">
-        <v>24561.99</v>
+        <v>24987.55</v>
       </c>
       <c r="M46" t="n">
-        <v>25221.93</v>
+        <v>25218.75</v>
       </c>
       <c r="N46" t="n">
-        <v>25881.88</v>
+        <v>25449.94</v>
       </c>
       <c r="O46" t="n">
-        <v>26540.83</v>
+        <v>25778.42</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4390,80 +4386,80 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24993.77</v>
+        <v>25987.31</v>
       </c>
       <c r="C47" t="n">
-        <v>25971.63</v>
+        <v>26187.57</v>
       </c>
       <c r="D47" t="n">
-        <v>24938.34</v>
+        <v>25389.42</v>
       </c>
       <c r="E47" t="n">
-        <v>25884.43</v>
+        <v>25668.03</v>
       </c>
       <c r="F47" t="n">
-        <v>921.2</v>
+        <v>-216.4</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0369</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>1033.29</v>
+        <v>798.15</v>
       </c>
       <c r="I47" t="n">
-        <v>24245.33</v>
+        <v>23905.05</v>
       </c>
       <c r="J47" t="n">
-        <v>24427.88</v>
+        <v>25065.86</v>
       </c>
       <c r="K47" t="n">
-        <v>24707.71</v>
+        <v>25367.78</v>
       </c>
       <c r="L47" t="n">
-        <v>24987.55</v>
+        <v>25669.71</v>
       </c>
       <c r="M47" t="n">
-        <v>25218.75</v>
+        <v>26401.08</v>
       </c>
       <c r="N47" t="n">
-        <v>25449.94</v>
+        <v>27132.44</v>
       </c>
       <c r="O47" t="n">
-        <v>25778.42</v>
+        <v>27004.92</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4476,78 +4472,76 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25987.31</v>
+        <v>25805.18</v>
       </c>
       <c r="C48" t="n">
-        <v>26187.57</v>
+        <v>26060.32</v>
       </c>
       <c r="D48" t="n">
-        <v>25389.42</v>
+        <v>25089.14</v>
       </c>
       <c r="E48" t="n">
-        <v>25668.03</v>
+        <v>25116.85</v>
       </c>
       <c r="F48" t="n">
-        <v>-216.4</v>
+        <v>-551.1799999999999</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0215</v>
       </c>
       <c r="H48" t="n">
-        <v>798.15</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>23905.05</v>
+        <v>24591.27</v>
       </c>
       <c r="J48" t="n">
-        <v>25065.86</v>
+        <v>24809.65</v>
       </c>
       <c r="K48" t="n">
-        <v>25367.78</v>
+        <v>25268.95</v>
       </c>
       <c r="L48" t="n">
-        <v>25669.71</v>
+        <v>25728.26</v>
       </c>
       <c r="M48" t="n">
-        <v>26401.08</v>
+        <v>26067.1</v>
       </c>
       <c r="N48" t="n">
-        <v>27132.44</v>
+        <v>26405.95</v>
       </c>
       <c r="O48" t="n">
-        <v>27004.92</v>
+        <v>26985.72</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4555,12 +4549,14 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4579,57 +4575,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25805.18</v>
+        <v>25303.41</v>
       </c>
       <c r="C49" t="n">
-        <v>26060.32</v>
+        <v>26009.46</v>
       </c>
       <c r="D49" t="n">
-        <v>25089.14</v>
+        <v>25240.62</v>
       </c>
       <c r="E49" t="n">
-        <v>25116.85</v>
+        <v>26009.46</v>
       </c>
       <c r="F49" t="n">
-        <v>-551.1799999999999</v>
+        <v>892.61</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0215</v>
+        <v>0.0355</v>
       </c>
       <c r="H49" t="n">
-        <v>971.1799999999999</v>
+        <v>768.84</v>
       </c>
       <c r="I49" t="n">
-        <v>24591.27</v>
+        <v>24117.96</v>
       </c>
       <c r="J49" t="n">
-        <v>24809.65</v>
+        <v>23916.73</v>
       </c>
       <c r="K49" t="n">
-        <v>25268.95</v>
+        <v>24631.26</v>
       </c>
       <c r="L49" t="n">
-        <v>25728.26</v>
+        <v>25345.79</v>
       </c>
       <c r="M49" t="n">
-        <v>26067.1</v>
+        <v>25602.44</v>
       </c>
       <c r="N49" t="n">
-        <v>26405.95</v>
+        <v>25859.09</v>
       </c>
       <c r="O49" t="n">
-        <v>26985.72</v>
+        <v>27031.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4637,22 +4633,24 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4663,81 +4661,81 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25303.41</v>
+        <v>25780.12</v>
       </c>
       <c r="C50" t="n">
-        <v>26009.46</v>
+        <v>25800.22</v>
       </c>
       <c r="D50" t="n">
-        <v>25240.62</v>
+        <v>25403.44</v>
       </c>
       <c r="E50" t="n">
-        <v>26009.46</v>
+        <v>25584.79</v>
       </c>
       <c r="F50" t="n">
-        <v>892.61</v>
+        <v>-424.67</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0355</v>
+        <v>-0.0163</v>
       </c>
       <c r="H50" t="n">
-        <v>768.84</v>
+        <v>396.78</v>
       </c>
       <c r="I50" t="n">
-        <v>24117.96</v>
+        <v>24471.78</v>
       </c>
       <c r="J50" t="n">
-        <v>23916.73</v>
+        <v>25432.83</v>
       </c>
       <c r="K50" t="n">
-        <v>24631.26</v>
+        <v>25625.04</v>
       </c>
       <c r="L50" t="n">
-        <v>25345.79</v>
+        <v>25817.25</v>
       </c>
       <c r="M50" t="n">
-        <v>25602.44</v>
+        <v>26393.88</v>
       </c>
       <c r="N50" t="n">
-        <v>25859.09</v>
+        <v>26970.51</v>
       </c>
       <c r="O50" t="n">
-        <v>27031.5</v>
+        <v>26778.3</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4749,57 +4747,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25780.12</v>
+        <v>25420.63</v>
       </c>
       <c r="C51" t="n">
-        <v>25800.22</v>
+        <v>25791.38</v>
       </c>
       <c r="D51" t="n">
-        <v>25403.44</v>
+        <v>25008.87</v>
       </c>
       <c r="E51" t="n">
-        <v>25584.79</v>
+        <v>25650.87</v>
       </c>
       <c r="F51" t="n">
-        <v>-424.67</v>
+        <v>66.08</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0163</v>
+        <v>0.0026</v>
       </c>
       <c r="H51" t="n">
-        <v>396.78</v>
+        <v>782.51</v>
       </c>
       <c r="I51" t="n">
-        <v>24471.78</v>
+        <v>25006.66</v>
       </c>
       <c r="J51" t="n">
-        <v>25432.83</v>
+        <v>25179.49</v>
       </c>
       <c r="K51" t="n">
-        <v>25625.04</v>
+        <v>25386.4</v>
       </c>
       <c r="L51" t="n">
-        <v>25817.25</v>
+        <v>25593.31</v>
       </c>
       <c r="M51" t="n">
-        <v>26393.88</v>
+        <v>25783.18</v>
       </c>
       <c r="N51" t="n">
-        <v>26970.51</v>
+        <v>25973.05</v>
       </c>
       <c r="O51" t="n">
-        <v>26778.3</v>
+        <v>26197</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4811,16 +4809,18 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4842,73 +4842,71 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25420.63</v>
+        <v>25652.97</v>
       </c>
       <c r="C52" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D52" t="n">
-        <v>25008.87</v>
+        <v>24570.24</v>
       </c>
       <c r="E52" t="n">
-        <v>25650.87</v>
+        <v>24805.63</v>
       </c>
       <c r="F52" t="n">
-        <v>66.08</v>
+        <v>-845.24</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.033</v>
       </c>
       <c r="H52" t="n">
-        <v>782.51</v>
+        <v>1094.74</v>
       </c>
       <c r="I52" t="n">
-        <v>25006.66</v>
+        <v>24226.36</v>
       </c>
       <c r="J52" t="n">
-        <v>25179.49</v>
+        <v>24993.73</v>
       </c>
       <c r="K52" t="n">
-        <v>25386.4</v>
+        <v>25259.61</v>
       </c>
       <c r="L52" t="n">
-        <v>25593.31</v>
+        <v>25525.5</v>
       </c>
       <c r="M52" t="n">
-        <v>25783.18</v>
+        <v>26042.12</v>
       </c>
       <c r="N52" t="n">
-        <v>25973.05</v>
+        <v>26558.75</v>
       </c>
       <c r="O52" t="n">
-        <v>26197</v>
+        <v>26573.89</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4916,81 +4914,73 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25652.97</v>
+        <v>24701.18</v>
       </c>
       <c r="C53" t="n">
-        <v>25664.98</v>
+        <v>24934.06</v>
       </c>
       <c r="D53" t="n">
-        <v>24570.24</v>
+        <v>24357.69</v>
       </c>
       <c r="E53" t="n">
-        <v>24805.63</v>
+        <v>24750.78</v>
       </c>
       <c r="F53" t="n">
-        <v>-845.24</v>
+        <v>-54.85</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.0022</v>
       </c>
       <c r="H53" t="n">
-        <v>1094.74</v>
+        <v>576.37</v>
       </c>
       <c r="I53" t="n">
-        <v>24226.36</v>
+        <v>23475.5</v>
       </c>
       <c r="J53" t="n">
-        <v>24993.73</v>
+        <v>23554.9</v>
       </c>
       <c r="K53" t="n">
-        <v>25259.61</v>
+        <v>24258.26</v>
       </c>
       <c r="L53" t="n">
-        <v>25525.5</v>
+        <v>24961.62</v>
       </c>
       <c r="M53" t="n">
-        <v>26042.12</v>
+        <v>25353</v>
       </c>
       <c r="N53" t="n">
-        <v>26558.75</v>
+        <v>25744.38</v>
       </c>
       <c r="O53" t="n">
-        <v>26573.89</v>
+        <v>26759.72</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -5012,50 +5002,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24701.18</v>
+        <v>24748.45</v>
       </c>
       <c r="C54" t="n">
-        <v>24934.06</v>
+        <v>25254.11</v>
       </c>
       <c r="D54" t="n">
-        <v>24357.69</v>
+        <v>24275.56</v>
       </c>
       <c r="E54" t="n">
-        <v>24750.78</v>
+        <v>24510.09</v>
       </c>
       <c r="F54" t="n">
-        <v>-54.85</v>
+        <v>-240.69</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0097</v>
       </c>
       <c r="H54" t="n">
-        <v>576.37</v>
+        <v>978.55</v>
       </c>
       <c r="I54" t="n">
-        <v>23475.5</v>
+        <v>23781.32</v>
       </c>
       <c r="J54" t="n">
-        <v>23554.9</v>
+        <v>24226.86</v>
       </c>
       <c r="K54" t="n">
-        <v>24258.26</v>
+        <v>24462.59</v>
       </c>
       <c r="L54" t="n">
-        <v>24961.62</v>
+        <v>24698.33</v>
       </c>
       <c r="M54" t="n">
-        <v>25353</v>
+        <v>25038.96</v>
       </c>
       <c r="N54" t="n">
-        <v>25744.38</v>
+        <v>25379.6</v>
       </c>
       <c r="O54" t="n">
-        <v>26759.72</v>
+        <v>25510.43</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5063,16 +5053,20 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5085,55 +5079,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24748.45</v>
+        <v>24554.58</v>
       </c>
       <c r="C55" t="n">
-        <v>25254.11</v>
+        <v>24767.22</v>
       </c>
       <c r="D55" t="n">
-        <v>24275.56</v>
+        <v>23865.33</v>
       </c>
       <c r="E55" t="n">
-        <v>24510.09</v>
+        <v>23972.29</v>
       </c>
       <c r="F55" t="n">
-        <v>-240.69</v>
+        <v>-537.8</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0219</v>
       </c>
       <c r="H55" t="n">
-        <v>978.55</v>
+        <v>901.89</v>
       </c>
       <c r="I55" t="n">
-        <v>23781.32</v>
+        <v>23297.01</v>
       </c>
       <c r="J55" t="n">
-        <v>24226.86</v>
+        <v>23404.17</v>
       </c>
       <c r="K55" t="n">
-        <v>24462.59</v>
+        <v>24020.82</v>
       </c>
       <c r="L55" t="n">
-        <v>24698.33</v>
+        <v>24637.46</v>
       </c>
       <c r="M55" t="n">
-        <v>25038.96</v>
+        <v>24999.36</v>
       </c>
       <c r="N55" t="n">
-        <v>25379.6</v>
+        <v>25361.27</v>
       </c>
       <c r="O55" t="n">
-        <v>25510.43</v>
+        <v>26232.66</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5146,15 +5144,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5167,59 +5163,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24554.58</v>
+        <v>23963.41</v>
       </c>
       <c r="C56" t="n">
-        <v>24767.22</v>
+        <v>24354.11</v>
       </c>
       <c r="D56" t="n">
-        <v>23865.33</v>
+        <v>23737.14</v>
       </c>
       <c r="E56" t="n">
-        <v>23972.29</v>
+        <v>24211.35</v>
       </c>
       <c r="F56" t="n">
-        <v>-537.8</v>
+        <v>239.06</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0219</v>
+        <v>0.01</v>
       </c>
       <c r="H56" t="n">
-        <v>901.89</v>
+        <v>616.97</v>
       </c>
       <c r="I56" t="n">
-        <v>23297.01</v>
+        <v>22963.44</v>
       </c>
       <c r="J56" t="n">
-        <v>23404.17</v>
+        <v>22898.41</v>
       </c>
       <c r="K56" t="n">
-        <v>24020.82</v>
+        <v>23521.34</v>
       </c>
       <c r="L56" t="n">
-        <v>24637.46</v>
+        <v>24144.28</v>
       </c>
       <c r="M56" t="n">
-        <v>24999.36</v>
+        <v>24423.23</v>
       </c>
       <c r="N56" t="n">
-        <v>25361.27</v>
+        <v>24702.19</v>
       </c>
       <c r="O56" t="n">
-        <v>26232.66</v>
+        <v>25669.11</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5227,14 +5219,12 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5251,55 +5241,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23963.41</v>
+        <v>24434.93</v>
       </c>
       <c r="C57" t="n">
-        <v>24354.11</v>
+        <v>24524.63</v>
       </c>
       <c r="D57" t="n">
-        <v>23737.14</v>
+        <v>23945.84</v>
       </c>
       <c r="E57" t="n">
-        <v>24211.35</v>
+        <v>24186.83</v>
       </c>
       <c r="F57" t="n">
-        <v>239.06</v>
+        <v>-24.52</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="H57" t="n">
-        <v>616.97</v>
+        <v>578.79</v>
       </c>
       <c r="I57" t="n">
-        <v>22963.44</v>
+        <v>23120.17</v>
       </c>
       <c r="J57" t="n">
-        <v>22898.41</v>
+        <v>23677.24</v>
       </c>
       <c r="K57" t="n">
-        <v>23521.34</v>
+        <v>23902.87</v>
       </c>
       <c r="L57" t="n">
-        <v>24144.28</v>
+        <v>24128.49</v>
       </c>
       <c r="M57" t="n">
-        <v>24423.23</v>
+        <v>24519.83</v>
       </c>
       <c r="N57" t="n">
-        <v>24702.19</v>
+        <v>24911.18</v>
       </c>
       <c r="O57" t="n">
-        <v>25669.11</v>
+        <v>24971.08</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5310,13 +5304,15 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5330,90 +5326,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>24434.93</v>
-      </c>
-      <c r="C58" t="n">
-        <v>24524.63</v>
-      </c>
-      <c r="D58" t="n">
-        <v>23945.84</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24062.72</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-148.63</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0061</v>
-      </c>
-      <c r="H58" t="n">
-        <v>578.79</v>
-      </c>
-      <c r="I58" t="n">
-        <v>23120.17</v>
-      </c>
-      <c r="J58" t="n">
-        <v>23677.24</v>
-      </c>
-      <c r="K58" t="n">
-        <v>23902.87</v>
-      </c>
-      <c r="L58" t="n">
-        <v>24128.49</v>
-      </c>
-      <c r="M58" t="n">
-        <v>24519.83</v>
-      </c>
-      <c r="N58" t="n">
-        <v>24911.18</v>
-      </c>
-      <c r="O58" t="n">
-        <v>24971.08</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>636.86</v>
       </c>
       <c r="I2" t="n">
-        <v>25502.43</v>
+        <v>25586.13</v>
       </c>
       <c r="J2" t="n">
-        <v>25705.29</v>
+        <v>25736.67</v>
       </c>
       <c r="K2" t="n">
-        <v>26156.2</v>
+        <v>26177.12</v>
       </c>
       <c r="L2" t="n">
-        <v>26607.11</v>
+        <v>26617.58</v>
       </c>
       <c r="M2" t="n">
-        <v>26934</v>
+        <v>26913.07</v>
       </c>
       <c r="N2" t="n">
-        <v>27260.88</v>
+        <v>27208.57</v>
       </c>
       <c r="O2" t="n">
-        <v>27835.83</v>
+        <v>27793.98</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5331,6 +5334,90 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>23990.05</v>
+      </c>
+      <c r="C58" t="n">
+        <v>23990.05</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23990.05</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>23367.05</v>
+      </c>
+      <c r="J58" t="n">
+        <v>23583.84</v>
+      </c>
+      <c r="K58" t="n">
+        <v>23897.43</v>
+      </c>
+      <c r="L58" t="n">
+        <v>24211.03</v>
+      </c>
+      <c r="M58" t="n">
+        <v>24476.23</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24741.42</v>
+      </c>
+      <c r="O58" t="n">
+        <v>25103.42</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5344,22 +5341,22 @@
         <v>23990.05</v>
       </c>
       <c r="C58" t="n">
-        <v>23990.05</v>
+        <v>24035</v>
       </c>
       <c r="D58" t="n">
-        <v>23990.05</v>
+        <v>23846.99</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>23867.74</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-319.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0132</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>188.01</v>
       </c>
       <c r="I58" t="n">
         <v>23367.05</v>
@@ -5382,20 +5379,20 @@
       <c r="O58" t="n">
         <v>25103.42</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5412,11 +5409,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -5341,22 +5341,22 @@
         <v>23990.05</v>
       </c>
       <c r="C58" t="n">
-        <v>24035</v>
+        <v>24139.11</v>
       </c>
       <c r="D58" t="n">
-        <v>23846.99</v>
+        <v>23620.1</v>
       </c>
       <c r="E58" t="n">
-        <v>23867.74</v>
+        <v>23651.87</v>
       </c>
       <c r="F58" t="n">
-        <v>-319.09</v>
+        <v>-534.96</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0132</v>
+        <v>-0.0221</v>
       </c>
       <c r="H58" t="n">
-        <v>188.01</v>
+        <v>519.01</v>
       </c>
       <c r="I58" t="n">
         <v>23367.05</v>
@@ -5382,12 +5382,14 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,35 +659,39 @@
         <v>636.86</v>
       </c>
       <c r="I2" t="n">
-        <v>25586.13</v>
+        <v>26190.58</v>
       </c>
       <c r="J2" t="n">
-        <v>25736.67</v>
+        <v>26331.18</v>
       </c>
       <c r="K2" t="n">
-        <v>26177.12</v>
+        <v>26433.33</v>
       </c>
       <c r="L2" t="n">
-        <v>26617.58</v>
+        <v>26535.49</v>
       </c>
       <c r="M2" t="n">
-        <v>26913.07</v>
+        <v>26656.87</v>
       </c>
       <c r="N2" t="n">
-        <v>27208.57</v>
+        <v>26778.24</v>
       </c>
       <c r="O2" t="n">
-        <v>27793.98</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>26861.17</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -706,12 +710,12 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -792,7 +796,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -874,7 +878,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -962,7 +966,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1048,7 +1052,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1130,7 +1134,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1218,7 +1222,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1302,7 +1306,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1386,7 +1390,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1466,7 +1470,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1550,7 +1554,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1636,7 +1640,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1718,7 +1722,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1798,7 +1802,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1890,7 +1894,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1974,7 +1978,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2060,7 +2064,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2138,7 +2142,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2226,7 +2230,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2306,7 +2310,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2392,7 +2396,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2472,7 +2476,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2560,7 +2564,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2644,7 +2648,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2724,7 +2728,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2804,7 +2808,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2888,7 +2892,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2966,7 +2970,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3050,7 +3054,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3138,7 +3142,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3222,7 +3226,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3306,7 +3310,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3390,7 +3394,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3470,7 +3474,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3554,7 +3558,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3642,7 +3646,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3726,7 +3730,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3810,7 +3814,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3896,7 +3900,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3982,7 +3986,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4062,7 +4066,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4150,7 +4154,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4234,7 +4238,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4318,7 +4322,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4406,7 +4410,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4484,7 +4488,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4568,7 +4572,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4654,7 +4658,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4740,7 +4744,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4828,7 +4832,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4914,7 +4918,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4992,7 +4996,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5074,7 +5078,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5158,7 +5162,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5236,7 +5240,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5320,7 +5324,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5344,19 +5348,19 @@
         <v>24139.11</v>
       </c>
       <c r="D58" t="n">
-        <v>23620.1</v>
+        <v>22879.11</v>
       </c>
       <c r="E58" t="n">
-        <v>23651.87</v>
+        <v>22934.68</v>
       </c>
       <c r="F58" t="n">
-        <v>-534.96</v>
+        <v>-1252.15</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0221</v>
+        <v>-0.0518</v>
       </c>
       <c r="H58" t="n">
-        <v>519.01</v>
+        <v>1260</v>
       </c>
       <c r="I58" t="n">
         <v>23367.05</v>
@@ -5379,12 +5383,14 @@
       <c r="O58" t="n">
         <v>25103.42</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -5406,7 +5412,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,225 +634,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26459.52</v>
+        <v>26321.57</v>
       </c>
       <c r="C2" t="n">
-        <v>26640.53</v>
+        <v>27381.84</v>
       </c>
       <c r="D2" t="n">
-        <v>26003.67</v>
+        <v>26321.57</v>
       </c>
       <c r="E2" t="n">
-        <v>26128.2</v>
+        <v>27140.92</v>
       </c>
       <c r="F2" t="n">
-        <v>-416.9</v>
+        <v>1012.72</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0388</v>
       </c>
       <c r="H2" t="n">
-        <v>636.86</v>
+        <v>1060.27</v>
       </c>
       <c r="I2" t="n">
-        <v>26190.58</v>
+        <v>25366.81</v>
       </c>
       <c r="J2" t="n">
-        <v>26331.18</v>
+        <v>25394.39</v>
       </c>
       <c r="K2" t="n">
-        <v>26433.33</v>
+        <v>25809.77</v>
       </c>
       <c r="L2" t="n">
-        <v>26535.49</v>
+        <v>26225.15</v>
       </c>
       <c r="M2" t="n">
-        <v>26656.87</v>
+        <v>26446.63</v>
       </c>
       <c r="N2" t="n">
-        <v>26778.24</v>
+        <v>26668.11</v>
       </c>
       <c r="O2" t="n">
-        <v>26861.17</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>27277.39</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26321.57</v>
+        <v>27003.92</v>
       </c>
       <c r="C3" t="n">
-        <v>27381.84</v>
+        <v>27145.17</v>
       </c>
       <c r="D3" t="n">
-        <v>26321.57</v>
+        <v>26247.04</v>
       </c>
       <c r="E3" t="n">
-        <v>27140.92</v>
+        <v>26290.32</v>
       </c>
       <c r="F3" t="n">
-        <v>1012.72</v>
+        <v>-850.6</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0388</v>
+        <v>-0.0313</v>
       </c>
       <c r="H3" t="n">
-        <v>1060.27</v>
+        <v>898.13</v>
       </c>
       <c r="I3" t="n">
-        <v>25366.81</v>
+        <v>25261.3</v>
       </c>
       <c r="J3" t="n">
-        <v>25394.39</v>
+        <v>26225.26</v>
       </c>
       <c r="K3" t="n">
-        <v>25809.77</v>
+        <v>26610.79</v>
       </c>
       <c r="L3" t="n">
-        <v>26225.15</v>
+        <v>26996.31</v>
       </c>
       <c r="M3" t="n">
-        <v>26446.63</v>
+        <v>27671.05</v>
       </c>
       <c r="N3" t="n">
-        <v>26668.11</v>
+        <v>28345.8</v>
       </c>
       <c r="O3" t="n">
-        <v>27277.39</v>
+        <v>28442.11</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W3" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27003.92</v>
+        <v>25634</v>
       </c>
       <c r="C4" t="n">
-        <v>27145.17</v>
+        <v>26102.68</v>
       </c>
       <c r="D4" t="n">
-        <v>26247.04</v>
+        <v>25145.34</v>
       </c>
       <c r="E4" t="n">
-        <v>26290.32</v>
+        <v>25247.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-850.6</v>
+        <v>-1043.22</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0397</v>
       </c>
       <c r="H4" t="n">
-        <v>898.13</v>
+        <v>957.34</v>
       </c>
       <c r="I4" t="n">
-        <v>25261.3</v>
+        <v>25348.91</v>
       </c>
       <c r="J4" t="n">
-        <v>26225.26</v>
+        <v>25189.3</v>
       </c>
       <c r="K4" t="n">
-        <v>26610.79</v>
+        <v>25841.25</v>
       </c>
       <c r="L4" t="n">
-        <v>26996.31</v>
+        <v>26493.21</v>
       </c>
       <c r="M4" t="n">
-        <v>27671.05</v>
+        <v>26739.39</v>
       </c>
       <c r="N4" t="n">
-        <v>28345.8</v>
+        <v>26985.56</v>
       </c>
       <c r="O4" t="n">
-        <v>28442.11</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
+        <v>28043.3</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -878,7 +878,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -892,138 +892,132 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25634</v>
+        <v>25884.46</v>
       </c>
       <c r="C5" t="n">
-        <v>26102.68</v>
+        <v>26367.35</v>
       </c>
       <c r="D5" t="n">
-        <v>25145.34</v>
+        <v>25591.66</v>
       </c>
       <c r="E5" t="n">
-        <v>25247.1</v>
+        <v>26160.15</v>
       </c>
       <c r="F5" t="n">
-        <v>-1043.22</v>
+        <v>913.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0362</v>
       </c>
       <c r="H5" t="n">
-        <v>957.34</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>25348.91</v>
+        <v>24188</v>
       </c>
       <c r="J5" t="n">
-        <v>25189.3</v>
+        <v>24101.3</v>
       </c>
       <c r="K5" t="n">
-        <v>25841.25</v>
+        <v>24768.43</v>
       </c>
       <c r="L5" t="n">
-        <v>26493.21</v>
+        <v>25435.55</v>
       </c>
       <c r="M5" t="n">
-        <v>26739.39</v>
+        <v>25725.77</v>
       </c>
       <c r="N5" t="n">
-        <v>26985.56</v>
+        <v>26015.98</v>
       </c>
       <c r="O5" t="n">
-        <v>28043.3</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
+        <v>27060.02</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25884.46</v>
+        <v>26495.97</v>
       </c>
       <c r="C6" t="n">
-        <v>26367.35</v>
+        <v>26588.89</v>
       </c>
       <c r="D6" t="n">
-        <v>25591.66</v>
+        <v>25906.65</v>
       </c>
       <c r="E6" t="n">
-        <v>26160.15</v>
+        <v>25906.65</v>
       </c>
       <c r="F6" t="n">
-        <v>913.05</v>
+        <v>-253.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0362</v>
+        <v>-0.0097</v>
       </c>
       <c r="H6" t="n">
-        <v>775.6900000000001</v>
+        <v>682.24</v>
       </c>
       <c r="I6" t="n">
-        <v>24188</v>
+        <v>24815.97</v>
       </c>
       <c r="J6" t="n">
-        <v>24101.3</v>
+        <v>25474.78</v>
       </c>
       <c r="K6" t="n">
-        <v>24768.43</v>
+        <v>25772.31</v>
       </c>
       <c r="L6" t="n">
-        <v>25435.55</v>
+        <v>26069.83</v>
       </c>
       <c r="M6" t="n">
-        <v>25725.77</v>
+        <v>26548</v>
       </c>
       <c r="N6" t="n">
-        <v>26015.98</v>
+        <v>27026.16</v>
       </c>
       <c r="O6" t="n">
-        <v>27060.02</v>
+        <v>27143.04</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1031,12 +1025,14 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
@@ -1044,68 +1040,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26495.97</v>
+        <v>25999.17</v>
       </c>
       <c r="C7" t="n">
-        <v>26588.89</v>
+        <v>26490.71</v>
       </c>
       <c r="D7" t="n">
-        <v>25906.65</v>
+        <v>25496.13</v>
       </c>
       <c r="E7" t="n">
-        <v>25906.65</v>
+        <v>26241.83</v>
       </c>
       <c r="F7" t="n">
-        <v>-253.5</v>
+        <v>335.18</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0129</v>
       </c>
       <c r="H7" t="n">
-        <v>682.24</v>
+        <v>994.58</v>
       </c>
       <c r="I7" t="n">
-        <v>24815.97</v>
+        <v>25224.41</v>
       </c>
       <c r="J7" t="n">
-        <v>25474.78</v>
+        <v>25053.85</v>
       </c>
       <c r="K7" t="n">
-        <v>25772.31</v>
+        <v>25565.53</v>
       </c>
       <c r="L7" t="n">
-        <v>26069.83</v>
+        <v>26077.21</v>
       </c>
       <c r="M7" t="n">
-        <v>26548</v>
+        <v>26247.77</v>
       </c>
       <c r="N7" t="n">
-        <v>27026.16</v>
+        <v>26418.33</v>
       </c>
       <c r="O7" t="n">
-        <v>27143.04</v>
+        <v>27271.13</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1115,83 +1113,85 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25999.17</v>
+        <v>26319.4</v>
       </c>
       <c r="C8" t="n">
-        <v>26490.71</v>
+        <v>27188.81</v>
       </c>
       <c r="D8" t="n">
-        <v>25496.13</v>
+        <v>26302.93</v>
       </c>
       <c r="E8" t="n">
-        <v>26241.83</v>
+        <v>26572.46</v>
       </c>
       <c r="F8" t="n">
-        <v>335.18</v>
+        <v>330.63</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
       <c r="H8" t="n">
-        <v>994.58</v>
+        <v>885.88</v>
       </c>
       <c r="I8" t="n">
-        <v>25224.41</v>
+        <v>24501.55</v>
       </c>
       <c r="J8" t="n">
-        <v>25053.85</v>
+        <v>25371.45</v>
       </c>
       <c r="K8" t="n">
-        <v>25565.53</v>
+        <v>25744.54</v>
       </c>
       <c r="L8" t="n">
-        <v>26077.21</v>
+        <v>26117.63</v>
       </c>
       <c r="M8" t="n">
-        <v>26247.77</v>
+        <v>26739.12</v>
       </c>
       <c r="N8" t="n">
-        <v>26418.33</v>
+        <v>27360.61</v>
       </c>
       <c r="O8" t="n">
-        <v>27271.13</v>
+        <v>27485.29</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1199,12 +1199,10 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1214,91 +1212,89 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26319.4</v>
+        <v>26441.7</v>
       </c>
       <c r="C9" t="n">
-        <v>27188.81</v>
+        <v>26531.8</v>
       </c>
       <c r="D9" t="n">
-        <v>26302.93</v>
+        <v>25178.63</v>
       </c>
       <c r="E9" t="n">
-        <v>26572.46</v>
+        <v>25220.02</v>
       </c>
       <c r="F9" t="n">
-        <v>330.63</v>
+        <v>-1352.44</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0126</v>
+        <v>-0.0509</v>
       </c>
       <c r="H9" t="n">
-        <v>885.88</v>
+        <v>1353.17</v>
       </c>
       <c r="I9" t="n">
-        <v>24501.55</v>
+        <v>25417.05</v>
       </c>
       <c r="J9" t="n">
-        <v>25371.45</v>
+        <v>25599.88</v>
       </c>
       <c r="K9" t="n">
-        <v>25744.54</v>
+        <v>26129.52</v>
       </c>
       <c r="L9" t="n">
-        <v>26117.63</v>
+        <v>26659.17</v>
       </c>
       <c r="M9" t="n">
-        <v>26739.12</v>
+        <v>27015.4</v>
       </c>
       <c r="N9" t="n">
-        <v>27360.61</v>
+        <v>27371.64</v>
       </c>
       <c r="O9" t="n">
-        <v>27485.29</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>28074.69</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1308,7 +1304,7 @@
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1316,134 +1312,134 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26441.7</v>
+        <v>25452.87</v>
       </c>
       <c r="C10" t="n">
-        <v>26531.8</v>
+        <v>26136.27</v>
       </c>
       <c r="D10" t="n">
-        <v>25178.63</v>
+        <v>25369.29</v>
       </c>
       <c r="E10" t="n">
-        <v>25220.02</v>
+        <v>25858.89</v>
       </c>
       <c r="F10" t="n">
-        <v>-1352.44</v>
+        <v>638.87</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0509</v>
+        <v>0.0253</v>
       </c>
       <c r="H10" t="n">
-        <v>1353.17</v>
+        <v>766.98</v>
       </c>
       <c r="I10" t="n">
-        <v>25417.05</v>
+        <v>23825.46</v>
       </c>
       <c r="J10" t="n">
-        <v>25599.88</v>
+        <v>23549.25</v>
       </c>
       <c r="K10" t="n">
-        <v>26129.52</v>
+        <v>24543.43</v>
       </c>
       <c r="L10" t="n">
-        <v>26659.17</v>
+        <v>25537.62</v>
       </c>
       <c r="M10" t="n">
-        <v>27015.4</v>
+        <v>25896.6</v>
       </c>
       <c r="N10" t="n">
-        <v>27371.64</v>
+        <v>26255.59</v>
       </c>
       <c r="O10" t="n">
-        <v>28074.69</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>27884.97</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25452.87</v>
+        <v>25945.87</v>
       </c>
       <c r="C11" t="n">
-        <v>26136.27</v>
+        <v>26264.13</v>
       </c>
       <c r="D11" t="n">
-        <v>25369.29</v>
+        <v>25649.3</v>
       </c>
       <c r="E11" t="n">
-        <v>25858.89</v>
+        <v>26085.08</v>
       </c>
       <c r="F11" t="n">
-        <v>638.87</v>
+        <v>226.19</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0253</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>766.98</v>
+        <v>614.83</v>
       </c>
       <c r="I11" t="n">
-        <v>23825.46</v>
+        <v>24602.31</v>
       </c>
       <c r="J11" t="n">
-        <v>23549.25</v>
+        <v>25144.97</v>
       </c>
       <c r="K11" t="n">
-        <v>24543.43</v>
+        <v>25475.4</v>
       </c>
       <c r="L11" t="n">
-        <v>25537.62</v>
+        <v>25805.83</v>
       </c>
       <c r="M11" t="n">
-        <v>25896.6</v>
+        <v>26242.38</v>
       </c>
       <c r="N11" t="n">
-        <v>26255.59</v>
+        <v>26678.93</v>
       </c>
       <c r="O11" t="n">
-        <v>27884.97</v>
+        <v>26903.25</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1454,7 +1450,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1470,83 +1466,85 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25945.87</v>
+        <v>26067.86</v>
       </c>
       <c r="C12" t="n">
-        <v>26264.13</v>
+        <v>26151.46</v>
       </c>
       <c r="D12" t="n">
-        <v>25649.3</v>
+        <v>25257.61</v>
       </c>
       <c r="E12" t="n">
-        <v>26085.08</v>
+        <v>25976.79</v>
       </c>
       <c r="F12" t="n">
-        <v>226.19</v>
+        <v>-108.29</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0042</v>
       </c>
       <c r="H12" t="n">
-        <v>614.83</v>
+        <v>893.85</v>
       </c>
       <c r="I12" t="n">
-        <v>24602.31</v>
+        <v>25034.47</v>
       </c>
       <c r="J12" t="n">
-        <v>25144.97</v>
+        <v>25534.43</v>
       </c>
       <c r="K12" t="n">
-        <v>25475.4</v>
+        <v>25777.67</v>
       </c>
       <c r="L12" t="n">
-        <v>25805.83</v>
+        <v>26020.9</v>
       </c>
       <c r="M12" t="n">
-        <v>26242.38</v>
+        <v>26392.5</v>
       </c>
       <c r="N12" t="n">
-        <v>26678.93</v>
+        <v>26764.09</v>
       </c>
       <c r="O12" t="n">
-        <v>26903.25</v>
+        <v>26878.96</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1554,64 +1552,60 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26067.86</v>
+        <v>25718.14</v>
       </c>
       <c r="C13" t="n">
-        <v>26151.46</v>
+        <v>25824.44</v>
       </c>
       <c r="D13" t="n">
-        <v>25257.61</v>
+        <v>25086.54</v>
       </c>
       <c r="E13" t="n">
-        <v>25976.79</v>
+        <v>25690.53</v>
       </c>
       <c r="F13" t="n">
-        <v>-108.29</v>
+        <v>-286.26</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.011</v>
       </c>
       <c r="H13" t="n">
-        <v>893.85</v>
+        <v>737.9</v>
       </c>
       <c r="I13" t="n">
-        <v>25034.47</v>
+        <v>24363.76</v>
       </c>
       <c r="J13" t="n">
-        <v>25534.43</v>
+        <v>25219.06</v>
       </c>
       <c r="K13" t="n">
-        <v>25777.67</v>
+        <v>25529.86</v>
       </c>
       <c r="L13" t="n">
-        <v>26020.9</v>
+        <v>25840.66</v>
       </c>
       <c r="M13" t="n">
-        <v>26392.5</v>
+        <v>26423.71</v>
       </c>
       <c r="N13" t="n">
-        <v>26764.09</v>
+        <v>27006.77</v>
       </c>
       <c r="O13" t="n">
-        <v>26878.96</v>
+        <v>27045.31</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1626,7 +1620,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1640,7 +1634,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1650,71 +1644,69 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25718.14</v>
+        <v>25795.94</v>
       </c>
       <c r="C14" t="n">
-        <v>25824.44</v>
+        <v>25927.66</v>
       </c>
       <c r="D14" t="n">
-        <v>25086.54</v>
+        <v>25671.33</v>
       </c>
       <c r="E14" t="n">
-        <v>25690.53</v>
+        <v>25818.93</v>
       </c>
       <c r="F14" t="n">
-        <v>-286.26</v>
+        <v>128.4</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H14" t="n">
-        <v>737.9</v>
+        <v>256.33</v>
       </c>
       <c r="I14" t="n">
-        <v>24363.76</v>
+        <v>24348.64</v>
       </c>
       <c r="J14" t="n">
-        <v>25219.06</v>
+        <v>25070.15</v>
       </c>
       <c r="K14" t="n">
-        <v>25529.86</v>
+        <v>25321.58</v>
       </c>
       <c r="L14" t="n">
-        <v>25840.66</v>
+        <v>25573.01</v>
       </c>
       <c r="M14" t="n">
-        <v>26423.71</v>
+        <v>26059.48</v>
       </c>
       <c r="N14" t="n">
-        <v>27006.77</v>
+        <v>26545.95</v>
       </c>
       <c r="O14" t="n">
-        <v>27045.31</v>
+        <v>26562.34</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1722,161 +1714,169 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25795.94</v>
+        <v>25928.89</v>
       </c>
       <c r="C15" t="n">
-        <v>25927.66</v>
+        <v>26345.63</v>
       </c>
       <c r="D15" t="n">
-        <v>25671.33</v>
+        <v>25554.31</v>
       </c>
       <c r="E15" t="n">
-        <v>25818.93</v>
+        <v>26338.47</v>
       </c>
       <c r="F15" t="n">
-        <v>128.4</v>
+        <v>519.54</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0201</v>
       </c>
       <c r="H15" t="n">
-        <v>256.33</v>
+        <v>791.3200000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>24348.64</v>
+        <v>25415</v>
       </c>
       <c r="J15" t="n">
-        <v>25070.15</v>
+        <v>25572.32</v>
       </c>
       <c r="K15" t="n">
-        <v>25321.58</v>
+        <v>25690.76</v>
       </c>
       <c r="L15" t="n">
-        <v>25573.01</v>
+        <v>25809.21</v>
       </c>
       <c r="M15" t="n">
-        <v>26059.48</v>
+        <v>25947.09</v>
       </c>
       <c r="N15" t="n">
-        <v>26545.95</v>
+        <v>26084.98</v>
       </c>
       <c r="O15" t="n">
-        <v>26562.34</v>
+        <v>26183.99</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25928.89</v>
+        <v>26361.44</v>
       </c>
       <c r="C16" t="n">
-        <v>26345.63</v>
+        <v>26858.13</v>
       </c>
       <c r="D16" t="n">
-        <v>25554.31</v>
+        <v>25960.34</v>
       </c>
       <c r="E16" t="n">
-        <v>26338.47</v>
+        <v>26231.79</v>
       </c>
       <c r="F16" t="n">
-        <v>519.54</v>
+        <v>-106.68</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.0041</v>
       </c>
       <c r="H16" t="n">
-        <v>791.3200000000001</v>
+        <v>897.79</v>
       </c>
       <c r="I16" t="n">
-        <v>25415</v>
+        <v>24762.99</v>
       </c>
       <c r="J16" t="n">
-        <v>25572.32</v>
+        <v>25741.4</v>
       </c>
       <c r="K16" t="n">
-        <v>25690.76</v>
+        <v>25942.81</v>
       </c>
       <c r="L16" t="n">
-        <v>25809.21</v>
+        <v>26144.22</v>
       </c>
       <c r="M16" t="n">
-        <v>25947.09</v>
+        <v>26734.13</v>
       </c>
       <c r="N16" t="n">
-        <v>26084.98</v>
+        <v>27324.04</v>
       </c>
       <c r="O16" t="n">
-        <v>26183.99</v>
+        <v>27136.95</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1884,17 +1884,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1908,50 +1904,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26361.44</v>
+        <v>26376.84</v>
       </c>
       <c r="C17" t="n">
-        <v>26858.13</v>
+        <v>27206.84</v>
       </c>
       <c r="D17" t="n">
-        <v>25960.34</v>
+        <v>26187.76</v>
       </c>
       <c r="E17" t="n">
-        <v>26231.79</v>
+        <v>26844.96</v>
       </c>
       <c r="F17" t="n">
-        <v>-106.68</v>
+        <v>613.17</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0234</v>
       </c>
       <c r="H17" t="n">
-        <v>897.79</v>
+        <v>1019.08</v>
       </c>
       <c r="I17" t="n">
-        <v>24762.99</v>
+        <v>25062.55</v>
       </c>
       <c r="J17" t="n">
-        <v>25741.4</v>
+        <v>25245.27</v>
       </c>
       <c r="K17" t="n">
-        <v>25942.81</v>
+        <v>25782.89</v>
       </c>
       <c r="L17" t="n">
-        <v>26144.22</v>
+        <v>26320.51</v>
       </c>
       <c r="M17" t="n">
-        <v>26734.13</v>
+        <v>26680.68</v>
       </c>
       <c r="N17" t="n">
-        <v>27324.04</v>
+        <v>27040.86</v>
       </c>
       <c r="O17" t="n">
-        <v>27136.95</v>
+        <v>27755.92</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1962,80 +1958,78 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26376.84</v>
+        <v>26641.6</v>
       </c>
       <c r="C18" t="n">
-        <v>27206.84</v>
+        <v>26895.94</v>
       </c>
       <c r="D18" t="n">
-        <v>26187.76</v>
+        <v>26363.86</v>
       </c>
       <c r="E18" t="n">
-        <v>26844.96</v>
+        <v>26749.51</v>
       </c>
       <c r="F18" t="n">
-        <v>613.17</v>
+        <v>-95.45</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0234</v>
+        <v>-0.0036</v>
       </c>
       <c r="H18" t="n">
-        <v>1019.08</v>
+        <v>532.08</v>
       </c>
       <c r="I18" t="n">
-        <v>25062.55</v>
+        <v>25168.68</v>
       </c>
       <c r="J18" t="n">
-        <v>25245.27</v>
+        <v>25899.71</v>
       </c>
       <c r="K18" t="n">
-        <v>25782.89</v>
+        <v>26335.42</v>
       </c>
       <c r="L18" t="n">
-        <v>26320.51</v>
+        <v>26771.13</v>
       </c>
       <c r="M18" t="n">
-        <v>26680.68</v>
+        <v>27354.5</v>
       </c>
       <c r="N18" t="n">
-        <v>27040.86</v>
+        <v>27937.87</v>
       </c>
       <c r="O18" t="n">
-        <v>27755.92</v>
+        <v>28225.92</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2048,76 +2042,76 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26641.6</v>
+        <v>26844.04</v>
       </c>
       <c r="C19" t="n">
-        <v>26895.94</v>
+        <v>28056.1</v>
       </c>
       <c r="D19" t="n">
-        <v>26363.86</v>
+        <v>26619.83</v>
       </c>
       <c r="E19" t="n">
-        <v>26749.51</v>
+        <v>27387.11</v>
       </c>
       <c r="F19" t="n">
-        <v>-95.45</v>
+        <v>637.6</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0238</v>
       </c>
       <c r="H19" t="n">
-        <v>532.08</v>
+        <v>1436.27</v>
       </c>
       <c r="I19" t="n">
-        <v>25168.68</v>
+        <v>25831.78</v>
       </c>
       <c r="J19" t="n">
-        <v>25899.71</v>
+        <v>26277.23</v>
       </c>
       <c r="K19" t="n">
-        <v>26335.42</v>
+        <v>26483.47</v>
       </c>
       <c r="L19" t="n">
-        <v>26771.13</v>
+        <v>26689.7</v>
       </c>
       <c r="M19" t="n">
-        <v>27354.5</v>
+        <v>27015.55</v>
       </c>
       <c r="N19" t="n">
-        <v>27937.87</v>
+        <v>27341.4</v>
       </c>
       <c r="O19" t="n">
-        <v>28225.92</v>
+        <v>27428.02</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2130,76 +2124,78 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26844.04</v>
+        <v>27097.34</v>
       </c>
       <c r="C20" t="n">
-        <v>28056.1</v>
+        <v>27126.48</v>
       </c>
       <c r="D20" t="n">
-        <v>26619.83</v>
+        <v>26295.03</v>
       </c>
       <c r="E20" t="n">
-        <v>27387.11</v>
+        <v>26559.95</v>
       </c>
       <c r="F20" t="n">
-        <v>637.6</v>
+        <v>-827.16</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0238</v>
+        <v>-0.0302</v>
       </c>
       <c r="H20" t="n">
-        <v>1436.27</v>
+        <v>831.45</v>
       </c>
       <c r="I20" t="n">
-        <v>25831.78</v>
+        <v>25183.56</v>
       </c>
       <c r="J20" t="n">
-        <v>26277.23</v>
+        <v>25975.41</v>
       </c>
       <c r="K20" t="n">
-        <v>26483.47</v>
+        <v>26668.97</v>
       </c>
       <c r="L20" t="n">
-        <v>26689.7</v>
+        <v>27362.54</v>
       </c>
       <c r="M20" t="n">
-        <v>27015.55</v>
+        <v>28105.24</v>
       </c>
       <c r="N20" t="n">
-        <v>27341.4</v>
+        <v>28847.95</v>
       </c>
       <c r="O20" t="n">
-        <v>27428.02</v>
+        <v>29492.37</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2207,83 +2203,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27097.34</v>
+        <v>26982.49</v>
       </c>
       <c r="C21" t="n">
-        <v>27126.48</v>
+        <v>27397.65</v>
       </c>
       <c r="D21" t="n">
-        <v>26295.03</v>
+        <v>26444.46</v>
       </c>
       <c r="E21" t="n">
-        <v>26559.95</v>
+        <v>26567.12</v>
       </c>
       <c r="F21" t="n">
-        <v>-827.16</v>
+        <v>7.17</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0003</v>
       </c>
       <c r="H21" t="n">
-        <v>831.45</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>25183.56</v>
+        <v>25463.58</v>
       </c>
       <c r="J21" t="n">
-        <v>25975.41</v>
+        <v>25653.1</v>
       </c>
       <c r="K21" t="n">
-        <v>26668.97</v>
+        <v>26144.22</v>
       </c>
       <c r="L21" t="n">
-        <v>27362.54</v>
+        <v>26635.35</v>
       </c>
       <c r="M21" t="n">
-        <v>28105.24</v>
+        <v>26975.67</v>
       </c>
       <c r="N21" t="n">
-        <v>28847.95</v>
+        <v>27316</v>
       </c>
       <c r="O21" t="n">
-        <v>29492.37</v>
+        <v>27957.93</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2291,83 +2287,81 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26982.49</v>
+        <v>26501.2</v>
       </c>
       <c r="C22" t="n">
-        <v>27397.65</v>
+        <v>26734.41</v>
       </c>
       <c r="D22" t="n">
-        <v>26444.46</v>
+        <v>26356.96</v>
       </c>
       <c r="E22" t="n">
-        <v>26567.12</v>
+        <v>26413.35</v>
       </c>
       <c r="F22" t="n">
-        <v>7.17</v>
+        <v>-153.77</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0058</v>
       </c>
       <c r="H22" t="n">
-        <v>953.1900000000001</v>
+        <v>377.45</v>
       </c>
       <c r="I22" t="n">
-        <v>25463.58</v>
+        <v>25491.27</v>
       </c>
       <c r="J22" t="n">
-        <v>25653.1</v>
+        <v>25436.96</v>
       </c>
       <c r="K22" t="n">
-        <v>26144.22</v>
+        <v>26090.52</v>
       </c>
       <c r="L22" t="n">
-        <v>26635.35</v>
+        <v>26744.09</v>
       </c>
       <c r="M22" t="n">
-        <v>26975.67</v>
+        <v>27043.71</v>
       </c>
       <c r="N22" t="n">
-        <v>27316</v>
+        <v>27343.34</v>
       </c>
       <c r="O22" t="n">
-        <v>27957.93</v>
+        <v>28350.84</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2375,81 +2369,83 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26501.2</v>
+        <v>26798.97</v>
       </c>
       <c r="C23" t="n">
-        <v>26734.41</v>
+        <v>27156.28</v>
       </c>
       <c r="D23" t="n">
-        <v>26356.96</v>
+        <v>26373.01</v>
       </c>
       <c r="E23" t="n">
-        <v>26413.35</v>
+        <v>26630.54</v>
       </c>
       <c r="F23" t="n">
-        <v>-153.77</v>
+        <v>217.19</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>377.45</v>
+        <v>783.27</v>
       </c>
       <c r="I23" t="n">
-        <v>25491.27</v>
+        <v>25979.51</v>
       </c>
       <c r="J23" t="n">
-        <v>25436.96</v>
+        <v>25969.73</v>
       </c>
       <c r="K23" t="n">
-        <v>26090.52</v>
+        <v>26224.62</v>
       </c>
       <c r="L23" t="n">
-        <v>26744.09</v>
+        <v>26479.52</v>
       </c>
       <c r="M23" t="n">
-        <v>27043.71</v>
+        <v>26602.07</v>
       </c>
       <c r="N23" t="n">
-        <v>27343.34</v>
+        <v>26724.63</v>
       </c>
       <c r="O23" t="n">
-        <v>28350.84</v>
+        <v>27111.86</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2457,116 +2453,116 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26798.97</v>
+        <v>26305.58</v>
       </c>
       <c r="C24" t="n">
-        <v>27156.28</v>
+        <v>26403.85</v>
       </c>
       <c r="D24" t="n">
-        <v>26373.01</v>
+        <v>24958.43</v>
       </c>
       <c r="E24" t="n">
-        <v>26630.54</v>
+        <v>25757.29</v>
       </c>
       <c r="F24" t="n">
-        <v>217.19</v>
+        <v>-873.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="H24" t="n">
-        <v>783.27</v>
+        <v>1445.42</v>
       </c>
       <c r="I24" t="n">
-        <v>25979.51</v>
+        <v>25589.74</v>
       </c>
       <c r="J24" t="n">
-        <v>25969.73</v>
+        <v>25780.22</v>
       </c>
       <c r="K24" t="n">
-        <v>26224.62</v>
+        <v>26238.9</v>
       </c>
       <c r="L24" t="n">
-        <v>26479.52</v>
+        <v>26697.59</v>
       </c>
       <c r="M24" t="n">
-        <v>26602.07</v>
+        <v>27022.17</v>
       </c>
       <c r="N24" t="n">
-        <v>26724.63</v>
+        <v>27346.76</v>
       </c>
       <c r="O24" t="n">
-        <v>27111.86</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>27939.55</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2574,69 +2570,65 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26305.58</v>
+        <v>25075.74</v>
       </c>
       <c r="C25" t="n">
-        <v>26403.85</v>
+        <v>26149.64</v>
       </c>
       <c r="D25" t="n">
-        <v>24958.43</v>
+        <v>24906</v>
       </c>
       <c r="E25" t="n">
-        <v>25757.29</v>
+        <v>25465.6</v>
       </c>
       <c r="F25" t="n">
-        <v>-873.25</v>
+        <v>-291.69</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0328</v>
+        <v>-0.0113</v>
       </c>
       <c r="H25" t="n">
-        <v>1445.42</v>
+        <v>1243.64</v>
       </c>
       <c r="I25" t="n">
-        <v>25589.74</v>
+        <v>23513.01</v>
       </c>
       <c r="J25" t="n">
-        <v>25780.22</v>
+        <v>24349.94</v>
       </c>
       <c r="K25" t="n">
-        <v>26238.9</v>
+        <v>25034.58</v>
       </c>
       <c r="L25" t="n">
-        <v>26697.59</v>
+        <v>25719.21</v>
       </c>
       <c r="M25" t="n">
-        <v>27022.17</v>
+        <v>26480</v>
       </c>
       <c r="N25" t="n">
-        <v>27346.76</v>
+        <v>27240.78</v>
       </c>
       <c r="O25" t="n">
-        <v>27939.55</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27849.27</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2648,7 +2640,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2658,50 +2650,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25075.74</v>
+        <v>25436.27</v>
       </c>
       <c r="C26" t="n">
-        <v>26149.64</v>
+        <v>26250.14</v>
       </c>
       <c r="D26" t="n">
-        <v>24906</v>
+        <v>25121.46</v>
       </c>
       <c r="E26" t="n">
-        <v>25465.6</v>
+        <v>25277.32</v>
       </c>
       <c r="F26" t="n">
-        <v>-291.69</v>
+        <v>-188.28</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.0074</v>
       </c>
       <c r="H26" t="n">
-        <v>1243.64</v>
+        <v>1128.68</v>
       </c>
       <c r="I26" t="n">
-        <v>23513.01</v>
+        <v>23662.36</v>
       </c>
       <c r="J26" t="n">
-        <v>24349.94</v>
+        <v>24190.85</v>
       </c>
       <c r="K26" t="n">
-        <v>25034.58</v>
+        <v>24843.78</v>
       </c>
       <c r="L26" t="n">
-        <v>25719.21</v>
+        <v>25496.71</v>
       </c>
       <c r="M26" t="n">
-        <v>26480</v>
+        <v>26087.42</v>
       </c>
       <c r="N26" t="n">
-        <v>27240.78</v>
+        <v>26678.13</v>
       </c>
       <c r="O26" t="n">
-        <v>27849.27</v>
+        <v>27393.28</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2709,18 +2701,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2728,60 +2720,64 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25436.27</v>
+        <v>24789.14</v>
       </c>
       <c r="C27" t="n">
-        <v>26250.14</v>
+        <v>25390.3</v>
       </c>
       <c r="D27" t="n">
-        <v>25121.46</v>
+        <v>24203.54</v>
       </c>
       <c r="E27" t="n">
-        <v>25277.32</v>
+        <v>24951.88</v>
       </c>
       <c r="F27" t="n">
-        <v>-188.28</v>
+        <v>-325.44</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0129</v>
       </c>
       <c r="H27" t="n">
-        <v>1128.68</v>
+        <v>1186.76</v>
       </c>
       <c r="I27" t="n">
-        <v>23662.36</v>
+        <v>23992.78</v>
       </c>
       <c r="J27" t="n">
-        <v>24190.85</v>
+        <v>23944.4</v>
       </c>
       <c r="K27" t="n">
-        <v>24843.78</v>
+        <v>24712.98</v>
       </c>
       <c r="L27" t="n">
-        <v>25496.71</v>
+        <v>25481.56</v>
       </c>
       <c r="M27" t="n">
-        <v>26087.42</v>
+        <v>25841.66</v>
       </c>
       <c r="N27" t="n">
-        <v>26678.13</v>
+        <v>26201.76</v>
       </c>
       <c r="O27" t="n">
-        <v>27393.28</v>
+        <v>27378.82</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2789,18 +2785,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2808,64 +2804,60 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24789.14</v>
+        <v>24532.85</v>
       </c>
       <c r="C28" t="n">
-        <v>25390.3</v>
+        <v>25429.76</v>
       </c>
       <c r="D28" t="n">
-        <v>24203.54</v>
+        <v>24409.57</v>
       </c>
       <c r="E28" t="n">
-        <v>24951.88</v>
+        <v>25116.53</v>
       </c>
       <c r="F28" t="n">
-        <v>-325.44</v>
+        <v>164.65</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0066</v>
       </c>
       <c r="H28" t="n">
-        <v>1186.76</v>
+        <v>1020.19</v>
       </c>
       <c r="I28" t="n">
-        <v>23992.78</v>
+        <v>23016.78</v>
       </c>
       <c r="J28" t="n">
-        <v>23944.4</v>
+        <v>23842.6</v>
       </c>
       <c r="K28" t="n">
-        <v>24712.98</v>
+        <v>24358.5</v>
       </c>
       <c r="L28" t="n">
-        <v>25481.56</v>
+        <v>24874.4</v>
       </c>
       <c r="M28" t="n">
-        <v>25841.66</v>
+        <v>25545.26</v>
       </c>
       <c r="N28" t="n">
-        <v>26201.76</v>
+        <v>26216.12</v>
       </c>
       <c r="O28" t="n">
-        <v>27378.82</v>
+        <v>26577.06</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2873,14 +2865,12 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2892,60 +2882,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24532.85</v>
+        <v>25772.56</v>
       </c>
       <c r="C29" t="n">
-        <v>25429.76</v>
+        <v>26073.97</v>
       </c>
       <c r="D29" t="n">
-        <v>24409.57</v>
+        <v>25653.63</v>
       </c>
       <c r="E29" t="n">
-        <v>25116.53</v>
+        <v>25893.54</v>
       </c>
       <c r="F29" t="n">
-        <v>164.65</v>
+        <v>777.01</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0309</v>
       </c>
       <c r="H29" t="n">
-        <v>1020.19</v>
+        <v>420.34</v>
       </c>
       <c r="I29" t="n">
-        <v>23016.78</v>
+        <v>23389.38</v>
       </c>
       <c r="J29" t="n">
-        <v>23842.6</v>
+        <v>24194.77</v>
       </c>
       <c r="K29" t="n">
-        <v>24358.5</v>
+        <v>24606.43</v>
       </c>
       <c r="L29" t="n">
-        <v>24874.4</v>
+        <v>25018.1</v>
       </c>
       <c r="M29" t="n">
-        <v>25545.26</v>
+        <v>25626.62</v>
       </c>
       <c r="N29" t="n">
-        <v>26216.12</v>
+        <v>26235.15</v>
       </c>
       <c r="O29" t="n">
-        <v>26577.06</v>
+        <v>26449.95</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2956,13 +2950,15 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2970,7 +2966,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2984,50 +2980,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25772.56</v>
+        <v>25708.64</v>
       </c>
       <c r="C30" t="n">
-        <v>26073.97</v>
+        <v>26403.07</v>
       </c>
       <c r="D30" t="n">
-        <v>25653.63</v>
+        <v>25508.53</v>
       </c>
       <c r="E30" t="n">
-        <v>25893.54</v>
+        <v>26160.33</v>
       </c>
       <c r="F30" t="n">
-        <v>777.01</v>
+        <v>266.79</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.0103</v>
       </c>
       <c r="H30" t="n">
-        <v>420.34</v>
+        <v>894.54</v>
       </c>
       <c r="I30" t="n">
-        <v>23389.38</v>
+        <v>25233.29</v>
       </c>
       <c r="J30" t="n">
-        <v>24194.77</v>
+        <v>25488.07</v>
       </c>
       <c r="K30" t="n">
-        <v>24606.43</v>
+        <v>25683.37</v>
       </c>
       <c r="L30" t="n">
-        <v>25018.1</v>
+        <v>25878.67</v>
       </c>
       <c r="M30" t="n">
-        <v>25626.62</v>
+        <v>26103.71</v>
       </c>
       <c r="N30" t="n">
-        <v>26235.15</v>
+        <v>26328.75</v>
       </c>
       <c r="O30" t="n">
-        <v>26449.95</v>
+        <v>26494.31</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3035,10 +3031,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3048,70 +3046,72 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25708.64</v>
+        <v>26204.61</v>
       </c>
       <c r="C31" t="n">
-        <v>26403.07</v>
+        <v>26529.49</v>
       </c>
       <c r="D31" t="n">
-        <v>25508.53</v>
+        <v>25639.26</v>
       </c>
       <c r="E31" t="n">
-        <v>26160.33</v>
+        <v>25978.07</v>
       </c>
       <c r="F31" t="n">
-        <v>266.79</v>
+        <v>-182.26</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.007</v>
       </c>
       <c r="H31" t="n">
-        <v>894.54</v>
+        <v>890.23</v>
       </c>
       <c r="I31" t="n">
-        <v>25233.29</v>
+        <v>24613.99</v>
       </c>
       <c r="J31" t="n">
-        <v>25488.07</v>
+        <v>25368.05</v>
       </c>
       <c r="K31" t="n">
-        <v>25683.37</v>
+        <v>25713.06</v>
       </c>
       <c r="L31" t="n">
-        <v>25878.67</v>
+        <v>26058.06</v>
       </c>
       <c r="M31" t="n">
-        <v>26103.71</v>
+        <v>26607.6</v>
       </c>
       <c r="N31" t="n">
-        <v>26328.75</v>
+        <v>27157.14</v>
       </c>
       <c r="O31" t="n">
-        <v>26494.31</v>
+        <v>27297.61</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3126,23 +3126,19 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3156,50 +3152,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26204.61</v>
+        <v>25976.97</v>
       </c>
       <c r="C32" t="n">
-        <v>26529.49</v>
+        <v>26132.94</v>
       </c>
       <c r="D32" t="n">
-        <v>25639.26</v>
+        <v>25609.61</v>
       </c>
       <c r="E32" t="n">
-        <v>25978.07</v>
+        <v>25776.53</v>
       </c>
       <c r="F32" t="n">
-        <v>-182.26</v>
+        <v>-201.54</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0078</v>
       </c>
       <c r="H32" t="n">
-        <v>890.23</v>
+        <v>523.33</v>
       </c>
       <c r="I32" t="n">
-        <v>24613.99</v>
+        <v>24749.03</v>
       </c>
       <c r="J32" t="n">
-        <v>25368.05</v>
+        <v>25034.69</v>
       </c>
       <c r="K32" t="n">
-        <v>25713.06</v>
+        <v>25532.96</v>
       </c>
       <c r="L32" t="n">
-        <v>26058.06</v>
+        <v>26031.22</v>
       </c>
       <c r="M32" t="n">
-        <v>26607.6</v>
+        <v>26423.19</v>
       </c>
       <c r="N32" t="n">
-        <v>27157.14</v>
+        <v>26815.15</v>
       </c>
       <c r="O32" t="n">
-        <v>27297.61</v>
+        <v>27419.72</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,12 +3205,12 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3226,64 +3222,60 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25976.97</v>
+        <v>26138.34</v>
       </c>
       <c r="C33" t="n">
-        <v>26132.94</v>
+        <v>26669.26</v>
       </c>
       <c r="D33" t="n">
-        <v>25609.61</v>
+        <v>25690.36</v>
       </c>
       <c r="E33" t="n">
-        <v>25776.53</v>
+        <v>26393.71</v>
       </c>
       <c r="F33" t="n">
-        <v>-201.54</v>
+        <v>617.1799999999999</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0239</v>
       </c>
       <c r="H33" t="n">
-        <v>523.33</v>
+        <v>978.9</v>
       </c>
       <c r="I33" t="n">
-        <v>24749.03</v>
+        <v>25086.28</v>
       </c>
       <c r="J33" t="n">
-        <v>25034.69</v>
+        <v>25205.83</v>
       </c>
       <c r="K33" t="n">
-        <v>25532.96</v>
+        <v>25514.86</v>
       </c>
       <c r="L33" t="n">
-        <v>26031.22</v>
+        <v>25823.9</v>
       </c>
       <c r="M33" t="n">
-        <v>26423.19</v>
+        <v>26038.19</v>
       </c>
       <c r="N33" t="n">
-        <v>26815.15</v>
+        <v>26252.49</v>
       </c>
       <c r="O33" t="n">
-        <v>27419.72</v>
+        <v>26656.27</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,28 +3283,32 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3320,50 +3316,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26138.34</v>
+        <v>26310.87</v>
       </c>
       <c r="C34" t="n">
-        <v>26669.26</v>
+        <v>26844.8</v>
       </c>
       <c r="D34" t="n">
-        <v>25690.36</v>
+        <v>25847.15</v>
       </c>
       <c r="E34" t="n">
-        <v>26393.71</v>
+        <v>25962.73</v>
       </c>
       <c r="F34" t="n">
-        <v>617.1799999999999</v>
+        <v>-430.98</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0163</v>
       </c>
       <c r="H34" t="n">
-        <v>978.9</v>
+        <v>997.65</v>
       </c>
       <c r="I34" t="n">
-        <v>25086.28</v>
+        <v>24711.46</v>
       </c>
       <c r="J34" t="n">
-        <v>25205.83</v>
+        <v>25521.76</v>
       </c>
       <c r="K34" t="n">
-        <v>25514.86</v>
+        <v>25904.26</v>
       </c>
       <c r="L34" t="n">
-        <v>25823.9</v>
+        <v>26286.76</v>
       </c>
       <c r="M34" t="n">
-        <v>26038.19</v>
+        <v>26883.16</v>
       </c>
       <c r="N34" t="n">
-        <v>26252.49</v>
+        <v>27479.56</v>
       </c>
       <c r="O34" t="n">
-        <v>26656.27</v>
+        <v>27648.16</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3371,83 +3367,83 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26310.87</v>
+        <v>25838.96</v>
       </c>
       <c r="C35" t="n">
-        <v>26844.8</v>
+        <v>25845.46</v>
       </c>
       <c r="D35" t="n">
-        <v>25847.15</v>
+        <v>25341.73</v>
       </c>
       <c r="E35" t="n">
-        <v>25962.73</v>
+        <v>25606.03</v>
       </c>
       <c r="F35" t="n">
-        <v>-430.98</v>
+        <v>-356.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0137</v>
       </c>
       <c r="H35" t="n">
-        <v>997.65</v>
+        <v>503.73</v>
       </c>
       <c r="I35" t="n">
-        <v>24711.46</v>
+        <v>24849.5</v>
       </c>
       <c r="J35" t="n">
-        <v>25521.76</v>
+        <v>24773.46</v>
       </c>
       <c r="K35" t="n">
-        <v>25904.26</v>
+        <v>25463.91</v>
       </c>
       <c r="L35" t="n">
-        <v>26286.76</v>
+        <v>26154.35</v>
       </c>
       <c r="M35" t="n">
-        <v>26883.16</v>
+        <v>26461.56</v>
       </c>
       <c r="N35" t="n">
-        <v>27479.56</v>
+        <v>26768.76</v>
       </c>
       <c r="O35" t="n">
-        <v>27648.16</v>
+        <v>27842.45</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3460,7 +3456,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3474,77 +3470,81 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25838.96</v>
+        <v>25622.36</v>
       </c>
       <c r="C36" t="n">
-        <v>25845.46</v>
+        <v>25768.38</v>
       </c>
       <c r="D36" t="n">
-        <v>25341.73</v>
+        <v>24727.26</v>
       </c>
       <c r="E36" t="n">
-        <v>25606.03</v>
+        <v>25182.39</v>
       </c>
       <c r="F36" t="n">
-        <v>-356.7</v>
+        <v>-423.64</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0165</v>
       </c>
       <c r="H36" t="n">
-        <v>503.73</v>
+        <v>1041.12</v>
       </c>
       <c r="I36" t="n">
-        <v>24849.5</v>
+        <v>24838</v>
       </c>
       <c r="J36" t="n">
-        <v>24773.46</v>
+        <v>25108.52</v>
       </c>
       <c r="K36" t="n">
-        <v>25463.91</v>
+        <v>25354.16</v>
       </c>
       <c r="L36" t="n">
-        <v>26154.35</v>
+        <v>25599.81</v>
       </c>
       <c r="M36" t="n">
-        <v>26461.56</v>
+        <v>25857.89</v>
       </c>
       <c r="N36" t="n">
-        <v>26768.76</v>
+        <v>26115.98</v>
       </c>
       <c r="O36" t="n">
-        <v>27842.45</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+        <v>26349.19</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3558,7 +3558,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3572,73 +3572,69 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25622.36</v>
+        <v>25180.05</v>
       </c>
       <c r="C37" t="n">
-        <v>25768.38</v>
+        <v>26045.07</v>
       </c>
       <c r="D37" t="n">
-        <v>24727.26</v>
+        <v>24928.14</v>
       </c>
       <c r="E37" t="n">
-        <v>25182.39</v>
+        <v>24961.95</v>
       </c>
       <c r="F37" t="n">
-        <v>-423.64</v>
+        <v>-220.44</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0165</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>1041.12</v>
+        <v>1116.93</v>
       </c>
       <c r="I37" t="n">
-        <v>24838</v>
+        <v>23686.14</v>
       </c>
       <c r="J37" t="n">
-        <v>25108.52</v>
+        <v>24108.55</v>
       </c>
       <c r="K37" t="n">
-        <v>25354.16</v>
+        <v>24661.83</v>
       </c>
       <c r="L37" t="n">
-        <v>25599.81</v>
+        <v>25215.11</v>
       </c>
       <c r="M37" t="n">
-        <v>25857.89</v>
+        <v>25702.95</v>
       </c>
       <c r="N37" t="n">
-        <v>26115.98</v>
+        <v>26190.8</v>
       </c>
       <c r="O37" t="n">
-        <v>26349.19</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+        <v>26809.5</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3646,64 +3642,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25180.05</v>
+        <v>24582.91</v>
       </c>
       <c r="C38" t="n">
-        <v>26045.07</v>
+        <v>24837.98</v>
       </c>
       <c r="D38" t="n">
-        <v>24928.14</v>
+        <v>23999.67</v>
       </c>
       <c r="E38" t="n">
-        <v>24961.95</v>
+        <v>24718.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-220.44</v>
+        <v>-243.85</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="H38" t="n">
-        <v>1116.93</v>
+        <v>838.3099999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>23686.14</v>
+        <v>23811.21</v>
       </c>
       <c r="J38" t="n">
-        <v>24108.55</v>
+        <v>23582.69</v>
       </c>
       <c r="K38" t="n">
-        <v>24661.83</v>
+        <v>24403.48</v>
       </c>
       <c r="L38" t="n">
-        <v>25215.11</v>
+        <v>25224.28</v>
       </c>
       <c r="M38" t="n">
-        <v>25702.95</v>
+        <v>25520.41</v>
       </c>
       <c r="N38" t="n">
-        <v>26190.8</v>
+        <v>25816.55</v>
       </c>
       <c r="O38" t="n">
-        <v>26809.5</v>
+        <v>27162</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3711,18 +3707,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3730,77 +3726,79 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24582.91</v>
+        <v>25001.42</v>
       </c>
       <c r="C39" t="n">
-        <v>24837.98</v>
+        <v>25047.9</v>
       </c>
       <c r="D39" t="n">
-        <v>23999.67</v>
+        <v>23749.99</v>
       </c>
       <c r="E39" t="n">
-        <v>24718.1</v>
+        <v>23924.81</v>
       </c>
       <c r="F39" t="n">
-        <v>-243.85</v>
+        <v>-793.29</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0321</v>
       </c>
       <c r="H39" t="n">
-        <v>838.3099999999999</v>
+        <v>1297.91</v>
       </c>
       <c r="I39" t="n">
-        <v>23811.21</v>
+        <v>23161.36</v>
       </c>
       <c r="J39" t="n">
-        <v>23582.69</v>
+        <v>24029.43</v>
       </c>
       <c r="K39" t="n">
-        <v>24403.48</v>
+        <v>24298.94</v>
       </c>
       <c r="L39" t="n">
-        <v>25224.28</v>
+        <v>24568.46</v>
       </c>
       <c r="M39" t="n">
-        <v>25520.41</v>
+        <v>25137.25</v>
       </c>
       <c r="N39" t="n">
-        <v>25816.55</v>
+        <v>25706.05</v>
       </c>
       <c r="O39" t="n">
-        <v>27162</v>
+        <v>25676.29</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3816,77 +3814,77 @@
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25001.42</v>
+        <v>23811.76</v>
       </c>
       <c r="C40" t="n">
-        <v>25047.9</v>
+        <v>23863.71</v>
       </c>
       <c r="D40" t="n">
-        <v>23749.99</v>
+        <v>22518</v>
       </c>
       <c r="E40" t="n">
-        <v>23924.81</v>
+        <v>22671.86</v>
       </c>
       <c r="F40" t="n">
-        <v>-793.29</v>
+        <v>-1252.95</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0524</v>
       </c>
       <c r="H40" t="n">
-        <v>1297.91</v>
+        <v>1345.71</v>
       </c>
       <c r="I40" t="n">
-        <v>23161.36</v>
+        <v>22452.08</v>
       </c>
       <c r="J40" t="n">
-        <v>24029.43</v>
+        <v>22389.83</v>
       </c>
       <c r="K40" t="n">
-        <v>24298.94</v>
+        <v>23275.86</v>
       </c>
       <c r="L40" t="n">
-        <v>24568.46</v>
+        <v>24161.88</v>
       </c>
       <c r="M40" t="n">
-        <v>25137.25</v>
+        <v>24573.77</v>
       </c>
       <c r="N40" t="n">
-        <v>25706.05</v>
+        <v>24985.65</v>
       </c>
       <c r="O40" t="n">
-        <v>25676.29</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>26345.81</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3900,146 +3898,144 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23811.76</v>
+        <v>22827.65</v>
       </c>
       <c r="C41" t="n">
-        <v>23863.71</v>
+        <v>23516.7</v>
       </c>
       <c r="D41" t="n">
-        <v>22518</v>
+        <v>22685.14</v>
       </c>
       <c r="E41" t="n">
-        <v>22671.86</v>
+        <v>23350.03</v>
       </c>
       <c r="F41" t="n">
-        <v>-1252.95</v>
+        <v>678.17</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0524</v>
+        <v>0.0299</v>
       </c>
       <c r="H41" t="n">
-        <v>1345.71</v>
+        <v>831.5599999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>22452.08</v>
+        <v>21172.29</v>
       </c>
       <c r="J41" t="n">
-        <v>22389.83</v>
+        <v>21066.65</v>
       </c>
       <c r="K41" t="n">
-        <v>23275.86</v>
+        <v>21999</v>
       </c>
       <c r="L41" t="n">
-        <v>24161.88</v>
+        <v>22931.36</v>
       </c>
       <c r="M41" t="n">
-        <v>24573.77</v>
+        <v>23344.71</v>
       </c>
       <c r="N41" t="n">
-        <v>24985.65</v>
+        <v>23758.07</v>
       </c>
       <c r="O41" t="n">
-        <v>26345.81</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
+        <v>25209.42</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>22827.65</v>
+        <v>23404.61</v>
       </c>
       <c r="C42" t="n">
-        <v>23516.7</v>
+        <v>24499.63</v>
       </c>
       <c r="D42" t="n">
-        <v>22685.14</v>
+        <v>23229.38</v>
       </c>
       <c r="E42" t="n">
-        <v>23350.03</v>
+        <v>24175.12</v>
       </c>
       <c r="F42" t="n">
-        <v>678.17</v>
+        <v>825.09</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0353</v>
       </c>
       <c r="H42" t="n">
-        <v>831.5599999999999</v>
+        <v>1270.25</v>
       </c>
       <c r="I42" t="n">
-        <v>21172.29</v>
+        <v>21853.58</v>
       </c>
       <c r="J42" t="n">
-        <v>21066.65</v>
+        <v>22643.03</v>
       </c>
       <c r="K42" t="n">
-        <v>21999</v>
+        <v>22934.25</v>
       </c>
       <c r="L42" t="n">
-        <v>22931.36</v>
+        <v>23225.47</v>
       </c>
       <c r="M42" t="n">
-        <v>23344.71</v>
+        <v>23765.81</v>
       </c>
       <c r="N42" t="n">
-        <v>23758.07</v>
+        <v>24306.14</v>
       </c>
       <c r="O42" t="n">
-        <v>25209.42</v>
+        <v>24348.26</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4050,80 +4046,84 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23404.61</v>
+        <v>24157.65</v>
       </c>
       <c r="C43" t="n">
-        <v>24499.63</v>
+        <v>25221.44</v>
       </c>
       <c r="D43" t="n">
-        <v>23229.38</v>
+        <v>23902.05</v>
       </c>
       <c r="E43" t="n">
-        <v>24175.12</v>
+        <v>24562.24</v>
       </c>
       <c r="F43" t="n">
-        <v>825.09</v>
+        <v>387.12</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.016</v>
       </c>
       <c r="H43" t="n">
-        <v>1270.25</v>
+        <v>1319.39</v>
       </c>
       <c r="I43" t="n">
-        <v>21853.58</v>
+        <v>21959.13</v>
       </c>
       <c r="J43" t="n">
-        <v>22643.03</v>
+        <v>23060.18</v>
       </c>
       <c r="K43" t="n">
-        <v>22934.25</v>
+        <v>23539.99</v>
       </c>
       <c r="L43" t="n">
-        <v>23225.47</v>
+        <v>24019.81</v>
       </c>
       <c r="M43" t="n">
-        <v>23765.81</v>
+        <v>24810.24</v>
       </c>
       <c r="N43" t="n">
-        <v>24306.14</v>
+        <v>25600.68</v>
       </c>
       <c r="O43" t="n">
-        <v>24348.26</v>
+        <v>25769.88</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4134,27 +4134,23 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4168,50 +4164,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24157.65</v>
+        <v>24835.03</v>
       </c>
       <c r="C44" t="n">
-        <v>25221.44</v>
+        <v>25267.39</v>
       </c>
       <c r="D44" t="n">
-        <v>23902.05</v>
+        <v>24756.36</v>
       </c>
       <c r="E44" t="n">
-        <v>24562.24</v>
+        <v>24963.23</v>
       </c>
       <c r="F44" t="n">
-        <v>387.12</v>
+        <v>400.99</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
       </c>
       <c r="H44" t="n">
-        <v>1319.39</v>
+        <v>511.03</v>
       </c>
       <c r="I44" t="n">
-        <v>21959.13</v>
+        <v>22582.66</v>
       </c>
       <c r="J44" t="n">
-        <v>23060.18</v>
+        <v>23243.1</v>
       </c>
       <c r="K44" t="n">
-        <v>23539.99</v>
+        <v>23902.55</v>
       </c>
       <c r="L44" t="n">
-        <v>24019.81</v>
+        <v>24561.99</v>
       </c>
       <c r="M44" t="n">
-        <v>24810.24</v>
+        <v>25221.93</v>
       </c>
       <c r="N44" t="n">
-        <v>25600.68</v>
+        <v>25881.88</v>
       </c>
       <c r="O44" t="n">
-        <v>25769.88</v>
+        <v>26540.83</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4222,7 +4218,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4238,7 +4234,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4252,50 +4248,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>24835.03</v>
+        <v>24993.77</v>
       </c>
       <c r="C45" t="n">
-        <v>25267.39</v>
+        <v>25971.63</v>
       </c>
       <c r="D45" t="n">
-        <v>24756.36</v>
+        <v>24938.34</v>
       </c>
       <c r="E45" t="n">
-        <v>24963.23</v>
+        <v>25884.43</v>
       </c>
       <c r="F45" t="n">
-        <v>400.99</v>
+        <v>921.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0369</v>
       </c>
       <c r="H45" t="n">
-        <v>511.03</v>
+        <v>1033.29</v>
       </c>
       <c r="I45" t="n">
-        <v>22582.66</v>
+        <v>24245.33</v>
       </c>
       <c r="J45" t="n">
-        <v>23243.1</v>
+        <v>24427.88</v>
       </c>
       <c r="K45" t="n">
-        <v>23902.55</v>
+        <v>24707.71</v>
       </c>
       <c r="L45" t="n">
-        <v>24561.99</v>
+        <v>24987.55</v>
       </c>
       <c r="M45" t="n">
-        <v>25221.93</v>
+        <v>25218.75</v>
       </c>
       <c r="N45" t="n">
-        <v>25881.88</v>
+        <v>25449.94</v>
       </c>
       <c r="O45" t="n">
-        <v>26540.83</v>
+        <v>25778.42</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4306,80 +4302,80 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24993.77</v>
+        <v>25987.31</v>
       </c>
       <c r="C46" t="n">
-        <v>25971.63</v>
+        <v>26187.57</v>
       </c>
       <c r="D46" t="n">
-        <v>24938.34</v>
+        <v>25389.42</v>
       </c>
       <c r="E46" t="n">
-        <v>25884.43</v>
+        <v>25668.03</v>
       </c>
       <c r="F46" t="n">
-        <v>921.2</v>
+        <v>-216.4</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0369</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>1033.29</v>
+        <v>798.15</v>
       </c>
       <c r="I46" t="n">
-        <v>24245.33</v>
+        <v>23905.05</v>
       </c>
       <c r="J46" t="n">
-        <v>24427.88</v>
+        <v>25065.86</v>
       </c>
       <c r="K46" t="n">
-        <v>24707.71</v>
+        <v>25367.78</v>
       </c>
       <c r="L46" t="n">
-        <v>24987.55</v>
+        <v>25669.71</v>
       </c>
       <c r="M46" t="n">
-        <v>25218.75</v>
+        <v>26401.08</v>
       </c>
       <c r="N46" t="n">
-        <v>25449.94</v>
+        <v>27132.44</v>
       </c>
       <c r="O46" t="n">
-        <v>25778.42</v>
+        <v>27004.92</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4392,78 +4388,76 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25987.31</v>
+        <v>25805.18</v>
       </c>
       <c r="C47" t="n">
-        <v>26187.57</v>
+        <v>26060.32</v>
       </c>
       <c r="D47" t="n">
-        <v>25389.42</v>
+        <v>25089.14</v>
       </c>
       <c r="E47" t="n">
-        <v>25668.03</v>
+        <v>25116.85</v>
       </c>
       <c r="F47" t="n">
-        <v>-216.4</v>
+        <v>-551.1799999999999</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0215</v>
       </c>
       <c r="H47" t="n">
-        <v>798.15</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>23905.05</v>
+        <v>24591.27</v>
       </c>
       <c r="J47" t="n">
-        <v>25065.86</v>
+        <v>24809.65</v>
       </c>
       <c r="K47" t="n">
-        <v>25367.78</v>
+        <v>25268.95</v>
       </c>
       <c r="L47" t="n">
-        <v>25669.71</v>
+        <v>25728.26</v>
       </c>
       <c r="M47" t="n">
-        <v>26401.08</v>
+        <v>26067.1</v>
       </c>
       <c r="N47" t="n">
-        <v>27132.44</v>
+        <v>26405.95</v>
       </c>
       <c r="O47" t="n">
-        <v>27004.92</v>
+        <v>26985.72</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4471,12 +4465,14 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4488,64 +4484,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25805.18</v>
+        <v>25303.41</v>
       </c>
       <c r="C48" t="n">
-        <v>26060.32</v>
+        <v>26009.46</v>
       </c>
       <c r="D48" t="n">
-        <v>25089.14</v>
+        <v>25240.62</v>
       </c>
       <c r="E48" t="n">
-        <v>25116.85</v>
+        <v>26009.46</v>
       </c>
       <c r="F48" t="n">
-        <v>-551.1799999999999</v>
+        <v>892.61</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0215</v>
+        <v>0.0355</v>
       </c>
       <c r="H48" t="n">
-        <v>971.1799999999999</v>
+        <v>768.84</v>
       </c>
       <c r="I48" t="n">
-        <v>24591.27</v>
+        <v>24117.96</v>
       </c>
       <c r="J48" t="n">
-        <v>24809.65</v>
+        <v>23916.73</v>
       </c>
       <c r="K48" t="n">
-        <v>25268.95</v>
+        <v>24631.26</v>
       </c>
       <c r="L48" t="n">
-        <v>25728.26</v>
+        <v>25345.79</v>
       </c>
       <c r="M48" t="n">
-        <v>26067.1</v>
+        <v>25602.44</v>
       </c>
       <c r="N48" t="n">
-        <v>26405.95</v>
+        <v>25859.09</v>
       </c>
       <c r="O48" t="n">
-        <v>26985.72</v>
+        <v>27031.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4553,169 +4549,171 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25303.41</v>
+        <v>25780.12</v>
       </c>
       <c r="C49" t="n">
-        <v>26009.46</v>
+        <v>25800.22</v>
       </c>
       <c r="D49" t="n">
-        <v>25240.62</v>
+        <v>25403.44</v>
       </c>
       <c r="E49" t="n">
-        <v>26009.46</v>
+        <v>25584.79</v>
       </c>
       <c r="F49" t="n">
-        <v>892.61</v>
+        <v>-424.67</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0355</v>
+        <v>-0.0163</v>
       </c>
       <c r="H49" t="n">
-        <v>768.84</v>
+        <v>396.78</v>
       </c>
       <c r="I49" t="n">
-        <v>24117.96</v>
+        <v>24471.78</v>
       </c>
       <c r="J49" t="n">
-        <v>23916.73</v>
+        <v>25432.83</v>
       </c>
       <c r="K49" t="n">
-        <v>24631.26</v>
+        <v>25625.04</v>
       </c>
       <c r="L49" t="n">
-        <v>25345.79</v>
+        <v>25817.25</v>
       </c>
       <c r="M49" t="n">
-        <v>25602.44</v>
+        <v>26393.88</v>
       </c>
       <c r="N49" t="n">
-        <v>25859.09</v>
+        <v>26970.51</v>
       </c>
       <c r="O49" t="n">
-        <v>27031.5</v>
+        <v>26778.3</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25780.12</v>
+        <v>25420.63</v>
       </c>
       <c r="C50" t="n">
-        <v>25800.22</v>
+        <v>25791.38</v>
       </c>
       <c r="D50" t="n">
-        <v>25403.44</v>
+        <v>25008.87</v>
       </c>
       <c r="E50" t="n">
-        <v>25584.79</v>
+        <v>25650.87</v>
       </c>
       <c r="F50" t="n">
-        <v>-424.67</v>
+        <v>66.08</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0163</v>
+        <v>0.0026</v>
       </c>
       <c r="H50" t="n">
-        <v>396.78</v>
+        <v>782.51</v>
       </c>
       <c r="I50" t="n">
-        <v>24471.78</v>
+        <v>25006.66</v>
       </c>
       <c r="J50" t="n">
-        <v>25432.83</v>
+        <v>25179.49</v>
       </c>
       <c r="K50" t="n">
-        <v>25625.04</v>
+        <v>25386.4</v>
       </c>
       <c r="L50" t="n">
-        <v>25817.25</v>
+        <v>25593.31</v>
       </c>
       <c r="M50" t="n">
-        <v>26393.88</v>
+        <v>25783.18</v>
       </c>
       <c r="N50" t="n">
-        <v>26970.51</v>
+        <v>25973.05</v>
       </c>
       <c r="O50" t="n">
-        <v>26778.3</v>
+        <v>26197</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4727,16 +4725,18 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4744,7 +4744,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4758,57 +4758,57 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25420.63</v>
+        <v>25652.97</v>
       </c>
       <c r="C51" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D51" t="n">
-        <v>25008.87</v>
+        <v>24570.24</v>
       </c>
       <c r="E51" t="n">
-        <v>25650.87</v>
+        <v>24805.63</v>
       </c>
       <c r="F51" t="n">
-        <v>66.08</v>
+        <v>-845.24</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.033</v>
       </c>
       <c r="H51" t="n">
-        <v>782.51</v>
+        <v>1094.74</v>
       </c>
       <c r="I51" t="n">
-        <v>25006.66</v>
+        <v>24226.36</v>
       </c>
       <c r="J51" t="n">
-        <v>25179.49</v>
+        <v>24993.73</v>
       </c>
       <c r="K51" t="n">
-        <v>25386.4</v>
+        <v>25259.61</v>
       </c>
       <c r="L51" t="n">
-        <v>25593.31</v>
+        <v>25525.5</v>
       </c>
       <c r="M51" t="n">
-        <v>25783.18</v>
+        <v>26042.12</v>
       </c>
       <c r="N51" t="n">
-        <v>25973.05</v>
+        <v>26558.75</v>
       </c>
       <c r="O51" t="n">
-        <v>26197</v>
+        <v>26573.89</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4818,13 +4818,11 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4834,79 +4832,71 @@
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25652.97</v>
+        <v>24701.18</v>
       </c>
       <c r="C52" t="n">
-        <v>25664.98</v>
+        <v>24934.06</v>
       </c>
       <c r="D52" t="n">
-        <v>24570.24</v>
+        <v>24357.69</v>
       </c>
       <c r="E52" t="n">
-        <v>24805.63</v>
+        <v>24750.78</v>
       </c>
       <c r="F52" t="n">
-        <v>-845.24</v>
+        <v>-54.85</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.0022</v>
       </c>
       <c r="H52" t="n">
-        <v>1094.74</v>
+        <v>576.37</v>
       </c>
       <c r="I52" t="n">
-        <v>24226.36</v>
+        <v>23475.5</v>
       </c>
       <c r="J52" t="n">
-        <v>24993.73</v>
+        <v>23554.9</v>
       </c>
       <c r="K52" t="n">
-        <v>25259.61</v>
+        <v>24258.26</v>
       </c>
       <c r="L52" t="n">
-        <v>25525.5</v>
+        <v>24961.62</v>
       </c>
       <c r="M52" t="n">
-        <v>26042.12</v>
+        <v>25353</v>
       </c>
       <c r="N52" t="n">
-        <v>26558.75</v>
+        <v>25744.38</v>
       </c>
       <c r="O52" t="n">
-        <v>26573.89</v>
+        <v>26759.72</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4918,7 +4908,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4928,50 +4918,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24701.18</v>
+        <v>24748.45</v>
       </c>
       <c r="C53" t="n">
-        <v>24934.06</v>
+        <v>25254.11</v>
       </c>
       <c r="D53" t="n">
-        <v>24357.69</v>
+        <v>24275.56</v>
       </c>
       <c r="E53" t="n">
-        <v>24750.78</v>
+        <v>24510.09</v>
       </c>
       <c r="F53" t="n">
-        <v>-54.85</v>
+        <v>-240.69</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0097</v>
       </c>
       <c r="H53" t="n">
-        <v>576.37</v>
+        <v>978.55</v>
       </c>
       <c r="I53" t="n">
-        <v>23475.5</v>
+        <v>23781.32</v>
       </c>
       <c r="J53" t="n">
-        <v>23554.9</v>
+        <v>24226.86</v>
       </c>
       <c r="K53" t="n">
-        <v>24258.26</v>
+        <v>24462.59</v>
       </c>
       <c r="L53" t="n">
-        <v>24961.62</v>
+        <v>24698.33</v>
       </c>
       <c r="M53" t="n">
-        <v>25353</v>
+        <v>25038.96</v>
       </c>
       <c r="N53" t="n">
-        <v>25744.38</v>
+        <v>25379.6</v>
       </c>
       <c r="O53" t="n">
-        <v>26759.72</v>
+        <v>25510.43</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4979,16 +4969,20 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4996,60 +4990,64 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24748.45</v>
+        <v>24554.58</v>
       </c>
       <c r="C54" t="n">
-        <v>25254.11</v>
+        <v>24767.22</v>
       </c>
       <c r="D54" t="n">
-        <v>24275.56</v>
+        <v>23865.33</v>
       </c>
       <c r="E54" t="n">
-        <v>24510.09</v>
+        <v>23972.29</v>
       </c>
       <c r="F54" t="n">
-        <v>-240.69</v>
+        <v>-537.8</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0219</v>
       </c>
       <c r="H54" t="n">
-        <v>978.55</v>
+        <v>901.89</v>
       </c>
       <c r="I54" t="n">
-        <v>23781.32</v>
+        <v>23297.01</v>
       </c>
       <c r="J54" t="n">
-        <v>24226.86</v>
+        <v>23404.17</v>
       </c>
       <c r="K54" t="n">
-        <v>24462.59</v>
+        <v>24020.82</v>
       </c>
       <c r="L54" t="n">
-        <v>24698.33</v>
+        <v>24637.46</v>
       </c>
       <c r="M54" t="n">
-        <v>25038.96</v>
+        <v>24999.36</v>
       </c>
       <c r="N54" t="n">
-        <v>25379.6</v>
+        <v>25361.27</v>
       </c>
       <c r="O54" t="n">
-        <v>25510.43</v>
+        <v>26232.66</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5062,15 +5060,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5078,64 +5074,60 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24554.58</v>
+        <v>23963.41</v>
       </c>
       <c r="C55" t="n">
-        <v>24767.22</v>
+        <v>24354.11</v>
       </c>
       <c r="D55" t="n">
-        <v>23865.33</v>
+        <v>23737.14</v>
       </c>
       <c r="E55" t="n">
-        <v>23972.29</v>
+        <v>24211.35</v>
       </c>
       <c r="F55" t="n">
-        <v>-537.8</v>
+        <v>239.06</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0219</v>
+        <v>0.01</v>
       </c>
       <c r="H55" t="n">
-        <v>901.89</v>
+        <v>616.97</v>
       </c>
       <c r="I55" t="n">
-        <v>23297.01</v>
+        <v>22963.44</v>
       </c>
       <c r="J55" t="n">
-        <v>23404.17</v>
+        <v>22898.41</v>
       </c>
       <c r="K55" t="n">
-        <v>24020.82</v>
+        <v>23521.34</v>
       </c>
       <c r="L55" t="n">
-        <v>24637.46</v>
+        <v>24144.28</v>
       </c>
       <c r="M55" t="n">
-        <v>24999.36</v>
+        <v>24423.23</v>
       </c>
       <c r="N55" t="n">
-        <v>25361.27</v>
+        <v>24702.19</v>
       </c>
       <c r="O55" t="n">
-        <v>26232.66</v>
+        <v>25669.11</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5143,14 +5135,12 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5162,60 +5152,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23963.41</v>
+        <v>24434.93</v>
       </c>
       <c r="C56" t="n">
-        <v>24354.11</v>
+        <v>24524.63</v>
       </c>
       <c r="D56" t="n">
-        <v>23737.14</v>
+        <v>23945.84</v>
       </c>
       <c r="E56" t="n">
-        <v>24211.35</v>
+        <v>24186.83</v>
       </c>
       <c r="F56" t="n">
-        <v>239.06</v>
+        <v>-24.52</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="H56" t="n">
-        <v>616.97</v>
+        <v>578.79</v>
       </c>
       <c r="I56" t="n">
-        <v>22963.44</v>
+        <v>23120.17</v>
       </c>
       <c r="J56" t="n">
-        <v>22898.41</v>
+        <v>23677.24</v>
       </c>
       <c r="K56" t="n">
-        <v>23521.34</v>
+        <v>23902.87</v>
       </c>
       <c r="L56" t="n">
-        <v>24144.28</v>
+        <v>24128.49</v>
       </c>
       <c r="M56" t="n">
-        <v>24423.23</v>
+        <v>24519.83</v>
       </c>
       <c r="N56" t="n">
-        <v>24702.19</v>
+        <v>24911.18</v>
       </c>
       <c r="O56" t="n">
-        <v>25669.11</v>
+        <v>24971.08</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5226,13 +5220,15 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5240,83 +5236,87 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24434.93</v>
+        <v>23990.05</v>
       </c>
       <c r="C57" t="n">
-        <v>24524.63</v>
+        <v>24139.11</v>
       </c>
       <c r="D57" t="n">
-        <v>23945.84</v>
+        <v>22803.77</v>
       </c>
       <c r="E57" t="n">
-        <v>24186.83</v>
+        <v>23093.37</v>
       </c>
       <c r="F57" t="n">
-        <v>-24.52</v>
+        <v>-1093.46</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0452</v>
       </c>
       <c r="H57" t="n">
-        <v>578.79</v>
+        <v>1335.34</v>
       </c>
       <c r="I57" t="n">
-        <v>23120.17</v>
+        <v>23367.05</v>
       </c>
       <c r="J57" t="n">
-        <v>23677.24</v>
+        <v>23583.84</v>
       </c>
       <c r="K57" t="n">
-        <v>23902.87</v>
+        <v>23897.43</v>
       </c>
       <c r="L57" t="n">
-        <v>24128.49</v>
+        <v>24211.03</v>
       </c>
       <c r="M57" t="n">
-        <v>24519.83</v>
+        <v>24476.23</v>
       </c>
       <c r="N57" t="n">
-        <v>24911.18</v>
+        <v>24741.42</v>
       </c>
       <c r="O57" t="n">
-        <v>24971.08</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+        <v>25103.42</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5324,100 +5324,12 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>23990.05</v>
-      </c>
-      <c r="C58" t="n">
-        <v>24139.11</v>
-      </c>
-      <c r="D58" t="n">
-        <v>22879.11</v>
-      </c>
-      <c r="E58" t="n">
-        <v>22934.68</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-1252.15</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0518</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1260</v>
-      </c>
-      <c r="I58" t="n">
-        <v>23367.05</v>
-      </c>
-      <c r="J58" t="n">
-        <v>23583.84</v>
-      </c>
-      <c r="K58" t="n">
-        <v>23897.43</v>
-      </c>
-      <c r="L58" t="n">
-        <v>24211.03</v>
-      </c>
-      <c r="M58" t="n">
-        <v>24476.23</v>
-      </c>
-      <c r="N58" t="n">
-        <v>24741.42</v>
-      </c>
-      <c r="O58" t="n">
-        <v>25103.42</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5331,6 +5331,88 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>23156.96</v>
+      </c>
+      <c r="C58" t="n">
+        <v>23259.13</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23009.79</v>
+      </c>
+      <c r="E58" t="n">
+        <v>23211.81</v>
+      </c>
+      <c r="F58" t="n">
+        <v>118.44</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="H58" t="n">
+        <v>249.34</v>
+      </c>
+      <c r="I58" t="n">
+        <v>21468.43</v>
+      </c>
+      <c r="J58" t="n">
+        <v>21568.99</v>
+      </c>
+      <c r="K58" t="n">
+        <v>22425.7</v>
+      </c>
+      <c r="L58" t="n">
+        <v>23282.4</v>
+      </c>
+      <c r="M58" t="n">
+        <v>23761.04</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24239.67</v>
+      </c>
+      <c r="O58" t="n">
+        <v>25474.45</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1060.27</v>
       </c>
       <c r="I2" t="n">
-        <v>25366.81</v>
+        <v>25473.99</v>
       </c>
       <c r="J2" t="n">
-        <v>25394.39</v>
+        <v>25434.58</v>
       </c>
       <c r="K2" t="n">
-        <v>25809.77</v>
+        <v>25836.56</v>
       </c>
       <c r="L2" t="n">
-        <v>26225.15</v>
+        <v>26238.55</v>
       </c>
       <c r="M2" t="n">
-        <v>26446.63</v>
+        <v>26419.83</v>
       </c>
       <c r="N2" t="n">
-        <v>26668.11</v>
+        <v>26601.12</v>
       </c>
       <c r="O2" t="n">
-        <v>27277.39</v>
+        <v>27223.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5341,22 +5341,22 @@
         <v>23156.96</v>
       </c>
       <c r="C58" t="n">
-        <v>23259.13</v>
+        <v>23313.92</v>
       </c>
       <c r="D58" t="n">
-        <v>23009.79</v>
+        <v>22983.99</v>
       </c>
       <c r="E58" t="n">
-        <v>23211.81</v>
+        <v>23041.32</v>
       </c>
       <c r="F58" t="n">
-        <v>118.44</v>
+        <v>-52.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0023</v>
       </c>
       <c r="H58" t="n">
-        <v>249.34</v>
+        <v>329.93</v>
       </c>
       <c r="I58" t="n">
         <v>21468.43</v>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1060.27</v>
       </c>
       <c r="I2" t="n">
-        <v>25473.99</v>
+        <v>25505.33</v>
       </c>
       <c r="J2" t="n">
-        <v>25434.58</v>
+        <v>25446.33</v>
       </c>
       <c r="K2" t="n">
-        <v>25836.56</v>
+        <v>25844.4</v>
       </c>
       <c r="L2" t="n">
-        <v>26238.55</v>
+        <v>26242.46</v>
       </c>
       <c r="M2" t="n">
-        <v>26419.83</v>
+        <v>26412</v>
       </c>
       <c r="N2" t="n">
-        <v>26601.12</v>
+        <v>26581.53</v>
       </c>
       <c r="O2" t="n">
-        <v>27223.8</v>
+        <v>27208.13</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5347,13 +5347,13 @@
         <v>22983.99</v>
       </c>
       <c r="E58" t="n">
-        <v>23041.32</v>
+        <v>23094.83</v>
       </c>
       <c r="F58" t="n">
-        <v>-52.05</v>
+        <v>1.46</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0001</v>
       </c>
       <c r="H58" t="n">
         <v>329.93</v>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1060.27</v>
       </c>
       <c r="I2" t="n">
-        <v>25505.33</v>
+        <v>25739.81</v>
       </c>
       <c r="J2" t="n">
-        <v>25446.33</v>
+        <v>25739.43</v>
       </c>
       <c r="K2" t="n">
-        <v>25844.4</v>
+        <v>25961.64</v>
       </c>
       <c r="L2" t="n">
-        <v>26242.46</v>
+        <v>26183.84</v>
       </c>
       <c r="M2" t="n">
-        <v>26412</v>
+        <v>26294.76</v>
       </c>
       <c r="N2" t="n">
-        <v>26581.53</v>
+        <v>26405.67</v>
       </c>
       <c r="O2" t="n">
-        <v>27208.13</v>
+        <v>26739.17</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5344,19 +5344,19 @@
         <v>23313.92</v>
       </c>
       <c r="D58" t="n">
-        <v>22983.99</v>
+        <v>22928.27</v>
       </c>
       <c r="E58" t="n">
-        <v>23094.83</v>
+        <v>22958.65</v>
       </c>
       <c r="F58" t="n">
-        <v>1.46</v>
+        <v>-134.72</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0058</v>
       </c>
       <c r="H58" t="n">
-        <v>329.93</v>
+        <v>385.65</v>
       </c>
       <c r="I58" t="n">
         <v>21468.43</v>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_weekly.xlsx
+++ b/three_gate/analysis/HSI_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,137 +634,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26321.57</v>
+        <v>27003.92</v>
       </c>
       <c r="C2" t="n">
-        <v>27381.84</v>
+        <v>27145.17</v>
       </c>
       <c r="D2" t="n">
-        <v>26321.57</v>
+        <v>26247.04</v>
       </c>
       <c r="E2" t="n">
-        <v>27140.92</v>
+        <v>26290.32</v>
       </c>
       <c r="F2" t="n">
-        <v>1012.72</v>
+        <v>-850.6</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0388</v>
+        <v>-0.0313</v>
       </c>
       <c r="H2" t="n">
-        <v>1060.27</v>
+        <v>898.13</v>
       </c>
       <c r="I2" t="n">
-        <v>25739.81</v>
+        <v>25261.3</v>
       </c>
       <c r="J2" t="n">
-        <v>25739.43</v>
+        <v>26225.26</v>
       </c>
       <c r="K2" t="n">
-        <v>25961.64</v>
+        <v>26610.79</v>
       </c>
       <c r="L2" t="n">
-        <v>26183.84</v>
+        <v>26996.31</v>
       </c>
       <c r="M2" t="n">
-        <v>26294.76</v>
+        <v>27671.05</v>
       </c>
       <c r="N2" t="n">
-        <v>26405.67</v>
+        <v>28345.8</v>
       </c>
       <c r="O2" t="n">
-        <v>26739.17</v>
+        <v>28442.11</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27003.92</v>
+        <v>25634</v>
       </c>
       <c r="C3" t="n">
-        <v>27145.17</v>
+        <v>26102.68</v>
       </c>
       <c r="D3" t="n">
-        <v>26247.04</v>
+        <v>25145.34</v>
       </c>
       <c r="E3" t="n">
-        <v>26290.32</v>
+        <v>25247.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-850.6</v>
+        <v>-1043.22</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0397</v>
       </c>
       <c r="H3" t="n">
-        <v>898.13</v>
+        <v>957.34</v>
       </c>
       <c r="I3" t="n">
-        <v>25261.3</v>
+        <v>25348.91</v>
       </c>
       <c r="J3" t="n">
-        <v>26225.26</v>
+        <v>25189.3</v>
       </c>
       <c r="K3" t="n">
-        <v>26610.79</v>
+        <v>25841.25</v>
       </c>
       <c r="L3" t="n">
-        <v>26996.31</v>
+        <v>26493.21</v>
       </c>
       <c r="M3" t="n">
-        <v>27671.05</v>
+        <v>26739.39</v>
       </c>
       <c r="N3" t="n">
-        <v>28345.8</v>
+        <v>26985.56</v>
       </c>
       <c r="O3" t="n">
-        <v>28442.11</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
+        <v>28043.3</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
@@ -776,7 +780,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -804,77 +808,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25634</v>
+        <v>25884.46</v>
       </c>
       <c r="C4" t="n">
-        <v>26102.68</v>
+        <v>26367.35</v>
       </c>
       <c r="D4" t="n">
-        <v>25145.34</v>
+        <v>25591.66</v>
       </c>
       <c r="E4" t="n">
-        <v>25247.1</v>
+        <v>26160.15</v>
       </c>
       <c r="F4" t="n">
-        <v>-1043.22</v>
+        <v>913.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0362</v>
       </c>
       <c r="H4" t="n">
-        <v>957.34</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>25348.91</v>
+        <v>24188</v>
       </c>
       <c r="J4" t="n">
-        <v>25189.3</v>
+        <v>24101.3</v>
       </c>
       <c r="K4" t="n">
-        <v>25841.25</v>
+        <v>24768.43</v>
       </c>
       <c r="L4" t="n">
-        <v>26493.21</v>
+        <v>25435.55</v>
       </c>
       <c r="M4" t="n">
-        <v>26739.39</v>
+        <v>25725.77</v>
       </c>
       <c r="N4" t="n">
-        <v>26985.56</v>
+        <v>26015.98</v>
       </c>
       <c r="O4" t="n">
-        <v>28043.3</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>27060.02</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -883,59 +885,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25884.46</v>
+        <v>26495.97</v>
       </c>
       <c r="C5" t="n">
-        <v>26367.35</v>
+        <v>26588.89</v>
       </c>
       <c r="D5" t="n">
-        <v>25591.66</v>
+        <v>25906.65</v>
       </c>
       <c r="E5" t="n">
-        <v>26160.15</v>
+        <v>25906.65</v>
       </c>
       <c r="F5" t="n">
-        <v>913.05</v>
+        <v>-253.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0362</v>
+        <v>-0.0097</v>
       </c>
       <c r="H5" t="n">
-        <v>775.6900000000001</v>
+        <v>682.24</v>
       </c>
       <c r="I5" t="n">
-        <v>24188</v>
+        <v>24815.97</v>
       </c>
       <c r="J5" t="n">
-        <v>24101.3</v>
+        <v>25474.78</v>
       </c>
       <c r="K5" t="n">
-        <v>24768.43</v>
+        <v>25772.31</v>
       </c>
       <c r="L5" t="n">
-        <v>25435.55</v>
+        <v>26069.83</v>
       </c>
       <c r="M5" t="n">
-        <v>25725.77</v>
+        <v>26548</v>
       </c>
       <c r="N5" t="n">
-        <v>26015.98</v>
+        <v>27026.16</v>
       </c>
       <c r="O5" t="n">
-        <v>27060.02</v>
+        <v>27143.04</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -943,12 +941,14 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -956,10 +956,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -969,55 +967,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26495.97</v>
+        <v>25999.17</v>
       </c>
       <c r="C6" t="n">
-        <v>26588.89</v>
+        <v>26490.71</v>
       </c>
       <c r="D6" t="n">
-        <v>25906.65</v>
+        <v>25496.13</v>
       </c>
       <c r="E6" t="n">
-        <v>25906.65</v>
+        <v>26241.83</v>
       </c>
       <c r="F6" t="n">
-        <v>-253.5</v>
+        <v>335.18</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0129</v>
       </c>
       <c r="H6" t="n">
-        <v>682.24</v>
+        <v>994.58</v>
       </c>
       <c r="I6" t="n">
-        <v>24815.97</v>
+        <v>25224.41</v>
       </c>
       <c r="J6" t="n">
-        <v>25474.78</v>
+        <v>25053.85</v>
       </c>
       <c r="K6" t="n">
-        <v>25772.31</v>
+        <v>25565.53</v>
       </c>
       <c r="L6" t="n">
-        <v>26069.83</v>
+        <v>26077.21</v>
       </c>
       <c r="M6" t="n">
-        <v>26548</v>
+        <v>26247.77</v>
       </c>
       <c r="N6" t="n">
-        <v>27026.16</v>
+        <v>26418.33</v>
       </c>
       <c r="O6" t="n">
-        <v>27143.04</v>
+        <v>27271.13</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1027,22 +1029,24 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1053,57 +1057,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25999.17</v>
+        <v>26319.4</v>
       </c>
       <c r="C7" t="n">
-        <v>26490.71</v>
+        <v>27188.81</v>
       </c>
       <c r="D7" t="n">
-        <v>25496.13</v>
+        <v>26302.93</v>
       </c>
       <c r="E7" t="n">
-        <v>26241.83</v>
+        <v>26572.46</v>
       </c>
       <c r="F7" t="n">
-        <v>335.18</v>
+        <v>330.63</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
       <c r="H7" t="n">
-        <v>994.58</v>
+        <v>885.88</v>
       </c>
       <c r="I7" t="n">
-        <v>25224.41</v>
+        <v>24501.55</v>
       </c>
       <c r="J7" t="n">
-        <v>25053.85</v>
+        <v>25371.45</v>
       </c>
       <c r="K7" t="n">
-        <v>25565.53</v>
+        <v>25744.54</v>
       </c>
       <c r="L7" t="n">
-        <v>26077.21</v>
+        <v>26117.63</v>
       </c>
       <c r="M7" t="n">
-        <v>26247.77</v>
+        <v>26739.12</v>
       </c>
       <c r="N7" t="n">
-        <v>26418.33</v>
+        <v>27360.61</v>
       </c>
       <c r="O7" t="n">
-        <v>27271.13</v>
+        <v>27485.29</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,12 +1115,10 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1126,10 +1128,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1139,78 +1139,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26319.4</v>
+        <v>26441.7</v>
       </c>
       <c r="C8" t="n">
-        <v>27188.81</v>
+        <v>26531.8</v>
       </c>
       <c r="D8" t="n">
-        <v>26302.93</v>
+        <v>25178.63</v>
       </c>
       <c r="E8" t="n">
-        <v>26572.46</v>
+        <v>25220.02</v>
       </c>
       <c r="F8" t="n">
-        <v>330.63</v>
+        <v>-1352.44</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0126</v>
+        <v>-0.0509</v>
       </c>
       <c r="H8" t="n">
-        <v>885.88</v>
+        <v>1353.17</v>
       </c>
       <c r="I8" t="n">
-        <v>24501.55</v>
+        <v>25417.05</v>
       </c>
       <c r="J8" t="n">
-        <v>25371.45</v>
+        <v>25599.88</v>
       </c>
       <c r="K8" t="n">
-        <v>25744.54</v>
+        <v>26129.52</v>
       </c>
       <c r="L8" t="n">
-        <v>26117.63</v>
+        <v>26659.17</v>
       </c>
       <c r="M8" t="n">
-        <v>26739.12</v>
+        <v>27015.4</v>
       </c>
       <c r="N8" t="n">
-        <v>27360.61</v>
+        <v>27371.64</v>
       </c>
       <c r="O8" t="n">
-        <v>27485.29</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>28074.69</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1218,9 +1218,9 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1228,74 +1228,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26441.7</v>
+        <v>25452.87</v>
       </c>
       <c r="C9" t="n">
-        <v>26531.8</v>
+        <v>26136.27</v>
       </c>
       <c r="D9" t="n">
-        <v>25178.63</v>
+        <v>25369.29</v>
       </c>
       <c r="E9" t="n">
-        <v>25220.02</v>
+        <v>25858.89</v>
       </c>
       <c r="F9" t="n">
-        <v>-1352.44</v>
+        <v>638.87</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0509</v>
+        <v>0.0253</v>
       </c>
       <c r="H9" t="n">
-        <v>1353.17</v>
+        <v>766.98</v>
       </c>
       <c r="I9" t="n">
-        <v>25417.05</v>
+        <v>23825.46</v>
       </c>
       <c r="J9" t="n">
-        <v>25599.88</v>
+        <v>23549.25</v>
       </c>
       <c r="K9" t="n">
-        <v>26129.52</v>
+        <v>24543.43</v>
       </c>
       <c r="L9" t="n">
-        <v>26659.17</v>
+        <v>25537.62</v>
       </c>
       <c r="M9" t="n">
-        <v>27015.4</v>
+        <v>25896.6</v>
       </c>
       <c r="N9" t="n">
-        <v>27371.64</v>
+        <v>26255.59</v>
       </c>
       <c r="O9" t="n">
-        <v>28074.69</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>27884.97</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1307,55 +1303,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25452.87</v>
+        <v>25945.87</v>
       </c>
       <c r="C10" t="n">
-        <v>26136.27</v>
+        <v>26264.13</v>
       </c>
       <c r="D10" t="n">
-        <v>25369.29</v>
+        <v>25649.3</v>
       </c>
       <c r="E10" t="n">
-        <v>25858.89</v>
+        <v>26085.08</v>
       </c>
       <c r="F10" t="n">
-        <v>638.87</v>
+        <v>226.19</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0253</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>766.98</v>
+        <v>614.83</v>
       </c>
       <c r="I10" t="n">
-        <v>23825.46</v>
+        <v>24602.31</v>
       </c>
       <c r="J10" t="n">
-        <v>23549.25</v>
+        <v>25144.97</v>
       </c>
       <c r="K10" t="n">
-        <v>24543.43</v>
+        <v>25475.4</v>
       </c>
       <c r="L10" t="n">
-        <v>25537.62</v>
+        <v>25805.83</v>
       </c>
       <c r="M10" t="n">
-        <v>25896.6</v>
+        <v>26242.38</v>
       </c>
       <c r="N10" t="n">
-        <v>26255.59</v>
+        <v>26678.93</v>
       </c>
       <c r="O10" t="n">
-        <v>27884.97</v>
+        <v>26903.25</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1366,7 +1366,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1389,76 +1389,78 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25945.87</v>
+        <v>26067.86</v>
       </c>
       <c r="C11" t="n">
-        <v>26264.13</v>
+        <v>26151.46</v>
       </c>
       <c r="D11" t="n">
-        <v>25649.3</v>
+        <v>25257.61</v>
       </c>
       <c r="E11" t="n">
-        <v>26085.08</v>
+        <v>25976.79</v>
       </c>
       <c r="F11" t="n">
-        <v>226.19</v>
+        <v>-108.29</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0042</v>
       </c>
       <c r="H11" t="n">
-        <v>614.83</v>
+        <v>893.85</v>
       </c>
       <c r="I11" t="n">
-        <v>24602.31</v>
+        <v>25034.47</v>
       </c>
       <c r="J11" t="n">
-        <v>25144.97</v>
+        <v>25534.43</v>
       </c>
       <c r="K11" t="n">
-        <v>25475.4</v>
+        <v>25777.67</v>
       </c>
       <c r="L11" t="n">
-        <v>25805.83</v>
+        <v>26020.9</v>
       </c>
       <c r="M11" t="n">
-        <v>26242.38</v>
+        <v>26392.5</v>
       </c>
       <c r="N11" t="n">
-        <v>26678.93</v>
+        <v>26764.09</v>
       </c>
       <c r="O11" t="n">
-        <v>26903.25</v>
+        <v>26878.96</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1471,59 +1473,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26067.86</v>
+        <v>25718.14</v>
       </c>
       <c r="C12" t="n">
-        <v>26151.46</v>
+        <v>25824.44</v>
       </c>
       <c r="D12" t="n">
-        <v>25257.61</v>
+        <v>25086.54</v>
       </c>
       <c r="E12" t="n">
-        <v>25976.79</v>
+        <v>25690.53</v>
       </c>
       <c r="F12" t="n">
-        <v>-108.29</v>
+        <v>-286.26</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.011</v>
       </c>
       <c r="H12" t="n">
-        <v>893.85</v>
+        <v>737.9</v>
       </c>
       <c r="I12" t="n">
-        <v>25034.47</v>
+        <v>24363.76</v>
       </c>
       <c r="J12" t="n">
-        <v>25534.43</v>
+        <v>25219.06</v>
       </c>
       <c r="K12" t="n">
-        <v>25777.67</v>
+        <v>25529.86</v>
       </c>
       <c r="L12" t="n">
-        <v>26020.9</v>
+        <v>25840.66</v>
       </c>
       <c r="M12" t="n">
-        <v>26392.5</v>
+        <v>26423.71</v>
       </c>
       <c r="N12" t="n">
-        <v>26764.09</v>
+        <v>27006.77</v>
       </c>
       <c r="O12" t="n">
-        <v>26878.96</v>
+        <v>27045.31</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1538,7 +1536,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1562,71 +1560,69 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25718.14</v>
+        <v>25795.94</v>
       </c>
       <c r="C13" t="n">
-        <v>25824.44</v>
+        <v>25927.66</v>
       </c>
       <c r="D13" t="n">
-        <v>25086.54</v>
+        <v>25671.33</v>
       </c>
       <c r="E13" t="n">
-        <v>25690.53</v>
+        <v>25818.93</v>
       </c>
       <c r="F13" t="n">
-        <v>-286.26</v>
+        <v>128.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H13" t="n">
-        <v>737.9</v>
+        <v>256.33</v>
       </c>
       <c r="I13" t="n">
-        <v>24363.76</v>
+        <v>24348.64</v>
       </c>
       <c r="J13" t="n">
-        <v>25219.06</v>
+        <v>25070.15</v>
       </c>
       <c r="K13" t="n">
-        <v>25529.86</v>
+        <v>25321.58</v>
       </c>
       <c r="L13" t="n">
-        <v>25840.66</v>
+        <v>25573.01</v>
       </c>
       <c r="M13" t="n">
-        <v>26423.71</v>
+        <v>26059.48</v>
       </c>
       <c r="N13" t="n">
-        <v>27006.77</v>
+        <v>26545.95</v>
       </c>
       <c r="O13" t="n">
-        <v>27045.31</v>
+        <v>26562.34</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1639,172 +1635,176 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25795.94</v>
+        <v>25928.89</v>
       </c>
       <c r="C14" t="n">
-        <v>25927.66</v>
+        <v>26345.63</v>
       </c>
       <c r="D14" t="n">
-        <v>25671.33</v>
+        <v>25554.31</v>
       </c>
       <c r="E14" t="n">
-        <v>25818.93</v>
+        <v>26338.47</v>
       </c>
       <c r="F14" t="n">
-        <v>128.4</v>
+        <v>519.54</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0201</v>
       </c>
       <c r="H14" t="n">
-        <v>256.33</v>
+        <v>791.3200000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>24348.64</v>
+        <v>25415</v>
       </c>
       <c r="J14" t="n">
-        <v>25070.15</v>
+        <v>25572.32</v>
       </c>
       <c r="K14" t="n">
-        <v>25321.58</v>
+        <v>25690.76</v>
       </c>
       <c r="L14" t="n">
-        <v>25573.01</v>
+        <v>25809.21</v>
       </c>
       <c r="M14" t="n">
-        <v>26059.48</v>
+        <v>25947.09</v>
       </c>
       <c r="N14" t="n">
-        <v>26545.95</v>
+        <v>26084.98</v>
       </c>
       <c r="O14" t="n">
-        <v>26562.34</v>
+        <v>26183.99</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25928.89</v>
+        <v>26361.44</v>
       </c>
       <c r="C15" t="n">
-        <v>26345.63</v>
+        <v>26858.13</v>
       </c>
       <c r="D15" t="n">
-        <v>25554.31</v>
+        <v>25960.34</v>
       </c>
       <c r="E15" t="n">
-        <v>26338.47</v>
+        <v>26231.79</v>
       </c>
       <c r="F15" t="n">
-        <v>519.54</v>
+        <v>-106.68</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.0041</v>
       </c>
       <c r="H15" t="n">
-        <v>791.3200000000001</v>
+        <v>897.79</v>
       </c>
       <c r="I15" t="n">
-        <v>25415</v>
+        <v>24762.99</v>
       </c>
       <c r="J15" t="n">
-        <v>25572.32</v>
+        <v>25741.4</v>
       </c>
       <c r="K15" t="n">
-        <v>25690.76</v>
+        <v>25942.81</v>
       </c>
       <c r="L15" t="n">
-        <v>25809.21</v>
+        <v>26144.22</v>
       </c>
       <c r="M15" t="n">
-        <v>25947.09</v>
+        <v>26734.13</v>
       </c>
       <c r="N15" t="n">
-        <v>26084.98</v>
+        <v>27324.04</v>
       </c>
       <c r="O15" t="n">
-        <v>26183.99</v>
+        <v>27136.95</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1820,50 +1820,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26361.44</v>
+        <v>26376.84</v>
       </c>
       <c r="C16" t="n">
-        <v>26858.13</v>
+        <v>27206.84</v>
       </c>
       <c r="D16" t="n">
-        <v>25960.34</v>
+        <v>26187.76</v>
       </c>
       <c r="E16" t="n">
-        <v>26231.79</v>
+        <v>26844.96</v>
       </c>
       <c r="F16" t="n">
-        <v>-106.68</v>
+        <v>613.17</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0234</v>
       </c>
       <c r="H16" t="n">
-        <v>897.79</v>
+        <v>1019.08</v>
       </c>
       <c r="I16" t="n">
-        <v>24762.99</v>
+        <v>25062.55</v>
       </c>
       <c r="J16" t="n">
-        <v>25741.4</v>
+        <v>25245.27</v>
       </c>
       <c r="K16" t="n">
-        <v>25942.81</v>
+        <v>25782.89</v>
       </c>
       <c r="L16" t="n">
-        <v>26144.22</v>
+        <v>26320.51</v>
       </c>
       <c r="M16" t="n">
-        <v>26734.13</v>
+        <v>26680.68</v>
       </c>
       <c r="N16" t="n">
-        <v>27324.04</v>
+        <v>27040.86</v>
       </c>
       <c r="O16" t="n">
-        <v>27136.95</v>
+        <v>27755.92</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1874,19 +1874,21 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1895,59 +1897,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26376.84</v>
+        <v>26641.6</v>
       </c>
       <c r="C17" t="n">
-        <v>27206.84</v>
+        <v>26895.94</v>
       </c>
       <c r="D17" t="n">
-        <v>26187.76</v>
+        <v>26363.86</v>
       </c>
       <c r="E17" t="n">
-        <v>26844.96</v>
+        <v>26749.51</v>
       </c>
       <c r="F17" t="n">
-        <v>613.17</v>
+        <v>-95.45</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0234</v>
+        <v>-0.0036</v>
       </c>
       <c r="H17" t="n">
-        <v>1019.08</v>
+        <v>532.08</v>
       </c>
       <c r="I17" t="n">
-        <v>25062.55</v>
+        <v>25168.68</v>
       </c>
       <c r="J17" t="n">
-        <v>25245.27</v>
+        <v>25899.71</v>
       </c>
       <c r="K17" t="n">
-        <v>25782.89</v>
+        <v>26335.42</v>
       </c>
       <c r="L17" t="n">
-        <v>26320.51</v>
+        <v>26771.13</v>
       </c>
       <c r="M17" t="n">
-        <v>26680.68</v>
+        <v>27354.5</v>
       </c>
       <c r="N17" t="n">
-        <v>27040.86</v>
+        <v>27937.87</v>
       </c>
       <c r="O17" t="n">
-        <v>27755.92</v>
+        <v>28225.92</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1960,18 +1958,14 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1981,55 +1975,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26641.6</v>
+        <v>26844.04</v>
       </c>
       <c r="C18" t="n">
-        <v>26895.94</v>
+        <v>28056.1</v>
       </c>
       <c r="D18" t="n">
-        <v>26363.86</v>
+        <v>26619.83</v>
       </c>
       <c r="E18" t="n">
-        <v>26749.51</v>
+        <v>27387.11</v>
       </c>
       <c r="F18" t="n">
-        <v>-95.45</v>
+        <v>637.6</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0238</v>
       </c>
       <c r="H18" t="n">
-        <v>532.08</v>
+        <v>1436.27</v>
       </c>
       <c r="I18" t="n">
-        <v>25168.68</v>
+        <v>25831.78</v>
       </c>
       <c r="J18" t="n">
-        <v>25899.71</v>
+        <v>26277.23</v>
       </c>
       <c r="K18" t="n">
-        <v>26335.42</v>
+        <v>26483.47</v>
       </c>
       <c r="L18" t="n">
-        <v>26771.13</v>
+        <v>26689.7</v>
       </c>
       <c r="M18" t="n">
-        <v>27354.5</v>
+        <v>27015.55</v>
       </c>
       <c r="N18" t="n">
-        <v>27937.87</v>
+        <v>27341.4</v>
       </c>
       <c r="O18" t="n">
-        <v>28225.92</v>
+        <v>27428.02</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2042,76 +2040,78 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26844.04</v>
+        <v>27097.34</v>
       </c>
       <c r="C19" t="n">
-        <v>28056.1</v>
+        <v>27126.48</v>
       </c>
       <c r="D19" t="n">
-        <v>26619.83</v>
+        <v>26295.03</v>
       </c>
       <c r="E19" t="n">
-        <v>27387.11</v>
+        <v>26559.95</v>
       </c>
       <c r="F19" t="n">
-        <v>637.6</v>
+        <v>-827.16</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0238</v>
+        <v>-0.0302</v>
       </c>
       <c r="H19" t="n">
-        <v>1436.27</v>
+        <v>831.45</v>
       </c>
       <c r="I19" t="n">
-        <v>25831.78</v>
+        <v>25183.56</v>
       </c>
       <c r="J19" t="n">
-        <v>26277.23</v>
+        <v>25975.41</v>
       </c>
       <c r="K19" t="n">
-        <v>26483.47</v>
+        <v>26668.97</v>
       </c>
       <c r="L19" t="n">
-        <v>26689.7</v>
+        <v>27362.54</v>
       </c>
       <c r="M19" t="n">
-        <v>27015.55</v>
+        <v>28105.24</v>
       </c>
       <c r="N19" t="n">
-        <v>27341.4</v>
+        <v>28847.95</v>
       </c>
       <c r="O19" t="n">
-        <v>27428.02</v>
+        <v>29492.37</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2119,83 +2119,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27097.34</v>
+        <v>26982.49</v>
       </c>
       <c r="C20" t="n">
-        <v>27126.48</v>
+        <v>27397.65</v>
       </c>
       <c r="D20" t="n">
-        <v>26295.03</v>
+        <v>26444.46</v>
       </c>
       <c r="E20" t="n">
-        <v>26559.95</v>
+        <v>26567.12</v>
       </c>
       <c r="F20" t="n">
-        <v>-827.16</v>
+        <v>7.17</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0003</v>
       </c>
       <c r="H20" t="n">
-        <v>831.45</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>25183.56</v>
+        <v>25463.58</v>
       </c>
       <c r="J20" t="n">
-        <v>25975.41</v>
+        <v>25653.1</v>
       </c>
       <c r="K20" t="n">
-        <v>26668.97</v>
+        <v>26144.22</v>
       </c>
       <c r="L20" t="n">
-        <v>27362.54</v>
+        <v>26635.35</v>
       </c>
       <c r="M20" t="n">
-        <v>28105.24</v>
+        <v>26975.67</v>
       </c>
       <c r="N20" t="n">
-        <v>28847.95</v>
+        <v>27316</v>
       </c>
       <c r="O20" t="n">
-        <v>29492.37</v>
+        <v>27957.93</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2203,21 +2203,23 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2227,59 +2229,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26982.49</v>
+        <v>26501.2</v>
       </c>
       <c r="C21" t="n">
-        <v>27397.65</v>
+        <v>26734.41</v>
       </c>
       <c r="D21" t="n">
-        <v>26444.46</v>
+        <v>26356.96</v>
       </c>
       <c r="E21" t="n">
-        <v>26567.12</v>
+        <v>26413.35</v>
       </c>
       <c r="F21" t="n">
-        <v>7.17</v>
+        <v>-153.77</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0058</v>
       </c>
       <c r="H21" t="n">
-        <v>953.1900000000001</v>
+        <v>377.45</v>
       </c>
       <c r="I21" t="n">
-        <v>25463.58</v>
+        <v>25491.27</v>
       </c>
       <c r="J21" t="n">
-        <v>25653.1</v>
+        <v>25436.96</v>
       </c>
       <c r="K21" t="n">
-        <v>26144.22</v>
+        <v>26090.52</v>
       </c>
       <c r="L21" t="n">
-        <v>26635.35</v>
+        <v>26744.09</v>
       </c>
       <c r="M21" t="n">
-        <v>26975.67</v>
+        <v>27043.71</v>
       </c>
       <c r="N21" t="n">
-        <v>27316</v>
+        <v>27343.34</v>
       </c>
       <c r="O21" t="n">
-        <v>27957.93</v>
+        <v>28350.84</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2287,23 +2285,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2313,55 +2309,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26501.2</v>
+        <v>26798.97</v>
       </c>
       <c r="C22" t="n">
-        <v>26734.41</v>
+        <v>27156.28</v>
       </c>
       <c r="D22" t="n">
-        <v>26356.96</v>
+        <v>26373.01</v>
       </c>
       <c r="E22" t="n">
-        <v>26413.35</v>
+        <v>26630.54</v>
       </c>
       <c r="F22" t="n">
-        <v>-153.77</v>
+        <v>217.19</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>377.45</v>
+        <v>783.27</v>
       </c>
       <c r="I22" t="n">
-        <v>25491.27</v>
+        <v>25979.51</v>
       </c>
       <c r="J22" t="n">
-        <v>25436.96</v>
+        <v>25969.73</v>
       </c>
       <c r="K22" t="n">
-        <v>26090.52</v>
+        <v>26224.62</v>
       </c>
       <c r="L22" t="n">
-        <v>26744.09</v>
+        <v>26479.52</v>
       </c>
       <c r="M22" t="n">
-        <v>27043.71</v>
+        <v>26602.07</v>
       </c>
       <c r="N22" t="n">
-        <v>27343.34</v>
+        <v>26724.63</v>
       </c>
       <c r="O22" t="n">
-        <v>28350.84</v>
+        <v>27111.86</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2369,116 +2369,116 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26798.97</v>
+        <v>26305.58</v>
       </c>
       <c r="C23" t="n">
-        <v>27156.28</v>
+        <v>26403.85</v>
       </c>
       <c r="D23" t="n">
-        <v>26373.01</v>
+        <v>24958.43</v>
       </c>
       <c r="E23" t="n">
-        <v>26630.54</v>
+        <v>25757.29</v>
       </c>
       <c r="F23" t="n">
-        <v>217.19</v>
+        <v>-873.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="H23" t="n">
-        <v>783.27</v>
+        <v>1445.42</v>
       </c>
       <c r="I23" t="n">
-        <v>25979.51</v>
+        <v>25589.74</v>
       </c>
       <c r="J23" t="n">
-        <v>25969.73</v>
+        <v>25780.22</v>
       </c>
       <c r="K23" t="n">
-        <v>26224.62</v>
+        <v>26238.9</v>
       </c>
       <c r="L23" t="n">
-        <v>26479.52</v>
+        <v>26697.59</v>
       </c>
       <c r="M23" t="n">
-        <v>26602.07</v>
+        <v>27022.17</v>
       </c>
       <c r="N23" t="n">
-        <v>26724.63</v>
+        <v>27346.76</v>
       </c>
       <c r="O23" t="n">
-        <v>27111.86</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>27939.55</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2486,69 +2486,65 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26305.58</v>
+        <v>25075.74</v>
       </c>
       <c r="C24" t="n">
-        <v>26403.85</v>
+        <v>26149.64</v>
       </c>
       <c r="D24" t="n">
-        <v>24958.43</v>
+        <v>24906</v>
       </c>
       <c r="E24" t="n">
-        <v>25757.29</v>
+        <v>25465.6</v>
       </c>
       <c r="F24" t="n">
-        <v>-873.25</v>
+        <v>-291.69</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0328</v>
+        <v>-0.0113</v>
       </c>
       <c r="H24" t="n">
-        <v>1445.42</v>
+        <v>1243.64</v>
       </c>
       <c r="I24" t="n">
-        <v>25589.74</v>
+        <v>23513.01</v>
       </c>
       <c r="J24" t="n">
-        <v>25780.22</v>
+        <v>24349.94</v>
       </c>
       <c r="K24" t="n">
-        <v>26238.9</v>
+        <v>25034.58</v>
       </c>
       <c r="L24" t="n">
-        <v>26697.59</v>
+        <v>25719.21</v>
       </c>
       <c r="M24" t="n">
-        <v>27022.17</v>
+        <v>26480</v>
       </c>
       <c r="N24" t="n">
-        <v>27346.76</v>
+        <v>27240.78</v>
       </c>
       <c r="O24" t="n">
-        <v>27939.55</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>27849.27</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2570,50 +2566,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25075.74</v>
+        <v>25436.27</v>
       </c>
       <c r="C25" t="n">
-        <v>26149.64</v>
+        <v>26250.14</v>
       </c>
       <c r="D25" t="n">
-        <v>24906</v>
+        <v>25121.46</v>
       </c>
       <c r="E25" t="n">
-        <v>25465.6</v>
+        <v>25277.32</v>
       </c>
       <c r="F25" t="n">
-        <v>-291.69</v>
+        <v>-188.28</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.0074</v>
       </c>
       <c r="H25" t="n">
-        <v>1243.64</v>
+        <v>1128.68</v>
       </c>
       <c r="I25" t="n">
-        <v>23513.01</v>
+        <v>23662.36</v>
       </c>
       <c r="J25" t="n">
-        <v>24349.94</v>
+        <v>24190.85</v>
       </c>
       <c r="K25" t="n">
-        <v>25034.58</v>
+        <v>24843.78</v>
       </c>
       <c r="L25" t="n">
-        <v>25719.21</v>
+        <v>25496.71</v>
       </c>
       <c r="M25" t="n">
-        <v>26480</v>
+        <v>26087.42</v>
       </c>
       <c r="N25" t="n">
-        <v>27240.78</v>
+        <v>26678.13</v>
       </c>
       <c r="O25" t="n">
-        <v>27849.27</v>
+        <v>27393.28</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2621,19 +2617,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2645,55 +2641,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25436.27</v>
+        <v>24789.14</v>
       </c>
       <c r="C26" t="n">
-        <v>26250.14</v>
+        <v>25390.3</v>
       </c>
       <c r="D26" t="n">
-        <v>25121.46</v>
+        <v>24203.54</v>
       </c>
       <c r="E26" t="n">
-        <v>25277.32</v>
+        <v>24951.88</v>
       </c>
       <c r="F26" t="n">
-        <v>-188.28</v>
+        <v>-325.44</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0129</v>
       </c>
       <c r="H26" t="n">
-        <v>1128.68</v>
+        <v>1186.76</v>
       </c>
       <c r="I26" t="n">
-        <v>23662.36</v>
+        <v>23992.78</v>
       </c>
       <c r="J26" t="n">
-        <v>24190.85</v>
+        <v>23944.4</v>
       </c>
       <c r="K26" t="n">
-        <v>24843.78</v>
+        <v>24712.98</v>
       </c>
       <c r="L26" t="n">
-        <v>25496.71</v>
+        <v>25481.56</v>
       </c>
       <c r="M26" t="n">
-        <v>26087.42</v>
+        <v>25841.66</v>
       </c>
       <c r="N26" t="n">
-        <v>26678.13</v>
+        <v>26201.76</v>
       </c>
       <c r="O26" t="n">
-        <v>27393.28</v>
+        <v>27378.82</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2701,18 +2701,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2725,59 +2725,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24789.14</v>
+        <v>24532.85</v>
       </c>
       <c r="C27" t="n">
-        <v>25390.3</v>
+        <v>25429.76</v>
       </c>
       <c r="D27" t="n">
-        <v>24203.54</v>
+        <v>24409.57</v>
       </c>
       <c r="E27" t="n">
-        <v>24951.88</v>
+        <v>25116.53</v>
       </c>
       <c r="F27" t="n">
-        <v>-325.44</v>
+        <v>164.65</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0066</v>
       </c>
       <c r="H27" t="n">
-        <v>1186.76</v>
+        <v>1020.19</v>
       </c>
       <c r="I27" t="n">
-        <v>23992.78</v>
+        <v>23016.78</v>
       </c>
       <c r="J27" t="n">
-        <v>23944.4</v>
+        <v>23842.6</v>
       </c>
       <c r="K27" t="n">
-        <v>24712.98</v>
+        <v>24358.5</v>
       </c>
       <c r="L27" t="n">
-        <v>25481.56</v>
+        <v>24874.4</v>
       </c>
       <c r="M27" t="n">
-        <v>25841.66</v>
+        <v>25545.26</v>
       </c>
       <c r="N27" t="n">
-        <v>26201.76</v>
+        <v>26216.12</v>
       </c>
       <c r="O27" t="n">
-        <v>27378.82</v>
+        <v>26577.06</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2785,14 +2781,12 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2809,55 +2803,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24532.85</v>
+        <v>25772.56</v>
       </c>
       <c r="C28" t="n">
-        <v>25429.76</v>
+        <v>26073.97</v>
       </c>
       <c r="D28" t="n">
-        <v>24409.57</v>
+        <v>25653.63</v>
       </c>
       <c r="E28" t="n">
-        <v>25116.53</v>
+        <v>25893.54</v>
       </c>
       <c r="F28" t="n">
-        <v>164.65</v>
+        <v>777.01</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0309</v>
       </c>
       <c r="H28" t="n">
-        <v>1020.19</v>
+        <v>420.34</v>
       </c>
       <c r="I28" t="n">
-        <v>23016.78</v>
+        <v>23389.38</v>
       </c>
       <c r="J28" t="n">
-        <v>23842.6</v>
+        <v>24194.77</v>
       </c>
       <c r="K28" t="n">
-        <v>24358.5</v>
+        <v>24606.43</v>
       </c>
       <c r="L28" t="n">
-        <v>24874.4</v>
+        <v>25018.1</v>
       </c>
       <c r="M28" t="n">
-        <v>25545.26</v>
+        <v>25626.62</v>
       </c>
       <c r="N28" t="n">
-        <v>26216.12</v>
+        <v>26235.15</v>
       </c>
       <c r="O28" t="n">
-        <v>26577.06</v>
+        <v>26449.95</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2868,13 +2866,15 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2896,50 +2896,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25772.56</v>
+        <v>25708.64</v>
       </c>
       <c r="C29" t="n">
-        <v>26073.97</v>
+        <v>26403.07</v>
       </c>
       <c r="D29" t="n">
-        <v>25653.63</v>
+        <v>25508.53</v>
       </c>
       <c r="E29" t="n">
-        <v>25893.54</v>
+        <v>26160.33</v>
       </c>
       <c r="F29" t="n">
-        <v>777.01</v>
+        <v>266.79</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.0103</v>
       </c>
       <c r="H29" t="n">
-        <v>420.34</v>
+        <v>894.54</v>
       </c>
       <c r="I29" t="n">
-        <v>23389.38</v>
+        <v>25233.29</v>
       </c>
       <c r="J29" t="n">
-        <v>24194.77</v>
+        <v>25488.07</v>
       </c>
       <c r="K29" t="n">
-        <v>24606.43</v>
+        <v>25683.37</v>
       </c>
       <c r="L29" t="n">
-        <v>25018.1</v>
+        <v>25878.67</v>
       </c>
       <c r="M29" t="n">
-        <v>25626.62</v>
+        <v>26103.71</v>
       </c>
       <c r="N29" t="n">
-        <v>26235.15</v>
+        <v>26328.75</v>
       </c>
       <c r="O29" t="n">
-        <v>26449.95</v>
+        <v>26494.31</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2947,10 +2947,12 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2960,8 +2962,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2973,57 +2977,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25708.64</v>
+        <v>26204.61</v>
       </c>
       <c r="C30" t="n">
-        <v>26403.07</v>
+        <v>26529.49</v>
       </c>
       <c r="D30" t="n">
-        <v>25508.53</v>
+        <v>25639.26</v>
       </c>
       <c r="E30" t="n">
-        <v>26160.33</v>
+        <v>25978.07</v>
       </c>
       <c r="F30" t="n">
-        <v>266.79</v>
+        <v>-182.26</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.007</v>
       </c>
       <c r="H30" t="n">
-        <v>894.54</v>
+        <v>890.23</v>
       </c>
       <c r="I30" t="n">
-        <v>25233.29</v>
+        <v>24613.99</v>
       </c>
       <c r="J30" t="n">
-        <v>25488.07</v>
+        <v>25368.05</v>
       </c>
       <c r="K30" t="n">
-        <v>25683.37</v>
+        <v>25713.06</v>
       </c>
       <c r="L30" t="n">
-        <v>25878.67</v>
+        <v>26058.06</v>
       </c>
       <c r="M30" t="n">
-        <v>26103.71</v>
+        <v>26607.6</v>
       </c>
       <c r="N30" t="n">
-        <v>26328.75</v>
+        <v>27157.14</v>
       </c>
       <c r="O30" t="n">
-        <v>26494.31</v>
+        <v>27297.61</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3038,18 +3042,14 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3068,50 +3068,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26204.61</v>
+        <v>25976.97</v>
       </c>
       <c r="C31" t="n">
-        <v>26529.49</v>
+        <v>26132.94</v>
       </c>
       <c r="D31" t="n">
-        <v>25639.26</v>
+        <v>25609.61</v>
       </c>
       <c r="E31" t="n">
-        <v>25978.07</v>
+        <v>25776.53</v>
       </c>
       <c r="F31" t="n">
-        <v>-182.26</v>
+        <v>-201.54</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0078</v>
       </c>
       <c r="H31" t="n">
-        <v>890.23</v>
+        <v>523.33</v>
       </c>
       <c r="I31" t="n">
-        <v>24613.99</v>
+        <v>24749.03</v>
       </c>
       <c r="J31" t="n">
-        <v>25368.05</v>
+        <v>25034.69</v>
       </c>
       <c r="K31" t="n">
-        <v>25713.06</v>
+        <v>25532.96</v>
       </c>
       <c r="L31" t="n">
-        <v>26058.06</v>
+        <v>26031.22</v>
       </c>
       <c r="M31" t="n">
-        <v>26607.6</v>
+        <v>26423.19</v>
       </c>
       <c r="N31" t="n">
-        <v>27157.14</v>
+        <v>26815.15</v>
       </c>
       <c r="O31" t="n">
-        <v>27297.61</v>
+        <v>27419.72</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3143,59 +3143,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25976.97</v>
+        <v>26138.34</v>
       </c>
       <c r="C32" t="n">
-        <v>26132.94</v>
+        <v>26669.26</v>
       </c>
       <c r="D32" t="n">
-        <v>25609.61</v>
+        <v>25690.36</v>
       </c>
       <c r="E32" t="n">
-        <v>25776.53</v>
+        <v>26393.71</v>
       </c>
       <c r="F32" t="n">
-        <v>-201.54</v>
+        <v>617.1799999999999</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0239</v>
       </c>
       <c r="H32" t="n">
-        <v>523.33</v>
+        <v>978.9</v>
       </c>
       <c r="I32" t="n">
-        <v>24749.03</v>
+        <v>25086.28</v>
       </c>
       <c r="J32" t="n">
-        <v>25034.69</v>
+        <v>25205.83</v>
       </c>
       <c r="K32" t="n">
-        <v>25532.96</v>
+        <v>25514.86</v>
       </c>
       <c r="L32" t="n">
-        <v>26031.22</v>
+        <v>25823.9</v>
       </c>
       <c r="M32" t="n">
-        <v>26423.19</v>
+        <v>26038.19</v>
       </c>
       <c r="N32" t="n">
-        <v>26815.15</v>
+        <v>26252.49</v>
       </c>
       <c r="O32" t="n">
-        <v>27419.72</v>
+        <v>26656.27</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3203,28 +3199,32 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3232,50 +3232,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26138.34</v>
+        <v>26310.87</v>
       </c>
       <c r="C33" t="n">
-        <v>26669.26</v>
+        <v>26844.8</v>
       </c>
       <c r="D33" t="n">
-        <v>25690.36</v>
+        <v>25847.15</v>
       </c>
       <c r="E33" t="n">
-        <v>26393.71</v>
+        <v>25962.73</v>
       </c>
       <c r="F33" t="n">
-        <v>617.1799999999999</v>
+        <v>-430.98</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0163</v>
       </c>
       <c r="H33" t="n">
-        <v>978.9</v>
+        <v>997.65</v>
       </c>
       <c r="I33" t="n">
-        <v>25086.28</v>
+        <v>24711.46</v>
       </c>
       <c r="J33" t="n">
-        <v>25205.83</v>
+        <v>25521.76</v>
       </c>
       <c r="K33" t="n">
-        <v>25514.86</v>
+        <v>25904.26</v>
       </c>
       <c r="L33" t="n">
-        <v>25823.9</v>
+        <v>26286.76</v>
       </c>
       <c r="M33" t="n">
-        <v>26038.19</v>
+        <v>26883.16</v>
       </c>
       <c r="N33" t="n">
-        <v>26252.49</v>
+        <v>27479.56</v>
       </c>
       <c r="O33" t="n">
-        <v>26656.27</v>
+        <v>27648.16</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3283,83 +3283,83 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26310.87</v>
+        <v>25838.96</v>
       </c>
       <c r="C34" t="n">
-        <v>26844.8</v>
+        <v>25845.46</v>
       </c>
       <c r="D34" t="n">
-        <v>25847.15</v>
+        <v>25341.73</v>
       </c>
       <c r="E34" t="n">
-        <v>25962.73</v>
+        <v>25606.03</v>
       </c>
       <c r="F34" t="n">
-        <v>-430.98</v>
+        <v>-356.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0137</v>
       </c>
       <c r="H34" t="n">
-        <v>997.65</v>
+        <v>503.73</v>
       </c>
       <c r="I34" t="n">
-        <v>24711.46</v>
+        <v>24849.5</v>
       </c>
       <c r="J34" t="n">
-        <v>25521.76</v>
+        <v>24773.46</v>
       </c>
       <c r="K34" t="n">
-        <v>25904.26</v>
+        <v>25463.91</v>
       </c>
       <c r="L34" t="n">
-        <v>26286.76</v>
+        <v>26154.35</v>
       </c>
       <c r="M34" t="n">
-        <v>26883.16</v>
+        <v>26461.56</v>
       </c>
       <c r="N34" t="n">
-        <v>27479.56</v>
+        <v>26768.76</v>
       </c>
       <c r="O34" t="n">
-        <v>27648.16</v>
+        <v>27842.45</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3372,7 +3372,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3393,70 +3393,74 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25838.96</v>
+        <v>25622.36</v>
       </c>
       <c r="C35" t="n">
-        <v>25845.46</v>
+        <v>25768.38</v>
       </c>
       <c r="D35" t="n">
-        <v>25341.73</v>
+        <v>24727.26</v>
       </c>
       <c r="E35" t="n">
-        <v>25606.03</v>
+        <v>25182.39</v>
       </c>
       <c r="F35" t="n">
-        <v>-356.7</v>
+        <v>-423.64</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0165</v>
       </c>
       <c r="H35" t="n">
-        <v>503.73</v>
+        <v>1041.12</v>
       </c>
       <c r="I35" t="n">
-        <v>24849.5</v>
+        <v>24838</v>
       </c>
       <c r="J35" t="n">
-        <v>24773.46</v>
+        <v>25108.52</v>
       </c>
       <c r="K35" t="n">
-        <v>25463.91</v>
+        <v>25354.16</v>
       </c>
       <c r="L35" t="n">
-        <v>26154.35</v>
+        <v>25599.81</v>
       </c>
       <c r="M35" t="n">
-        <v>26461.56</v>
+        <v>25857.89</v>
       </c>
       <c r="N35" t="n">
-        <v>26768.76</v>
+        <v>26115.98</v>
       </c>
       <c r="O35" t="n">
-        <v>27842.45</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+        <v>26349.19</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3484,74 +3488,70 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25622.36</v>
+        <v>25180.05</v>
       </c>
       <c r="C36" t="n">
-        <v>25768.38</v>
+        <v>26045.07</v>
       </c>
       <c r="D36" t="n">
-        <v>24727.26</v>
+        <v>24928.14</v>
       </c>
       <c r="E36" t="n">
-        <v>25182.39</v>
+        <v>24961.95</v>
       </c>
       <c r="F36" t="n">
-        <v>-423.64</v>
+        <v>-220.44</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0165</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>1041.12</v>
+        <v>1116.93</v>
       </c>
       <c r="I36" t="n">
-        <v>24838</v>
+        <v>23686.14</v>
       </c>
       <c r="J36" t="n">
-        <v>25108.52</v>
+        <v>24108.55</v>
       </c>
       <c r="K36" t="n">
-        <v>25354.16</v>
+        <v>24661.83</v>
       </c>
       <c r="L36" t="n">
-        <v>25599.81</v>
+        <v>25215.11</v>
       </c>
       <c r="M36" t="n">
-        <v>25857.89</v>
+        <v>25702.95</v>
       </c>
       <c r="N36" t="n">
-        <v>26115.98</v>
+        <v>26190.8</v>
       </c>
       <c r="O36" t="n">
-        <v>26349.19</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
+        <v>26809.5</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3565,57 +3565,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25180.05</v>
+        <v>24582.91</v>
       </c>
       <c r="C37" t="n">
-        <v>26045.07</v>
+        <v>24837.98</v>
       </c>
       <c r="D37" t="n">
-        <v>24928.14</v>
+        <v>23999.67</v>
       </c>
       <c r="E37" t="n">
-        <v>24961.95</v>
+        <v>24718.1</v>
       </c>
       <c r="F37" t="n">
-        <v>-220.44</v>
+        <v>-243.85</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="H37" t="n">
-        <v>1116.93</v>
+        <v>838.3099999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>23686.14</v>
+        <v>23811.21</v>
       </c>
       <c r="J37" t="n">
-        <v>24108.55</v>
+        <v>23582.69</v>
       </c>
       <c r="K37" t="n">
-        <v>24661.83</v>
+        <v>24403.48</v>
       </c>
       <c r="L37" t="n">
-        <v>25215.11</v>
+        <v>25224.28</v>
       </c>
       <c r="M37" t="n">
-        <v>25702.95</v>
+        <v>25520.41</v>
       </c>
       <c r="N37" t="n">
-        <v>26190.8</v>
+        <v>25816.55</v>
       </c>
       <c r="O37" t="n">
-        <v>26809.5</v>
+        <v>27162</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3623,18 +3623,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3649,70 +3649,72 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24582.91</v>
+        <v>25001.42</v>
       </c>
       <c r="C38" t="n">
-        <v>24837.98</v>
+        <v>25047.9</v>
       </c>
       <c r="D38" t="n">
-        <v>23999.67</v>
+        <v>23749.99</v>
       </c>
       <c r="E38" t="n">
-        <v>24718.1</v>
+        <v>23924.81</v>
       </c>
       <c r="F38" t="n">
-        <v>-243.85</v>
+        <v>-793.29</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0321</v>
       </c>
       <c r="H38" t="n">
-        <v>838.3099999999999</v>
+        <v>1297.91</v>
       </c>
       <c r="I38" t="n">
-        <v>23811.21</v>
+        <v>23161.36</v>
       </c>
       <c r="J38" t="n">
-        <v>23582.69</v>
+        <v>24029.43</v>
       </c>
       <c r="K38" t="n">
-        <v>24403.48</v>
+        <v>24298.94</v>
       </c>
       <c r="L38" t="n">
-        <v>25224.28</v>
+        <v>24568.46</v>
       </c>
       <c r="M38" t="n">
-        <v>25520.41</v>
+        <v>25137.25</v>
       </c>
       <c r="N38" t="n">
-        <v>25816.55</v>
+        <v>25706.05</v>
       </c>
       <c r="O38" t="n">
-        <v>27162</v>
+        <v>25676.29</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3726,79 +3728,79 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25001.42</v>
+        <v>23811.76</v>
       </c>
       <c r="C39" t="n">
-        <v>25047.9</v>
+        <v>23863.71</v>
       </c>
       <c r="D39" t="n">
-        <v>23749.99</v>
+        <v>22518</v>
       </c>
       <c r="E39" t="n">
-        <v>23924.81</v>
+        <v>22671.86</v>
       </c>
       <c r="F39" t="n">
-        <v>-793.29</v>
+        <v>-1252.95</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0524</v>
       </c>
       <c r="H39" t="n">
-        <v>1297.91</v>
+        <v>1345.71</v>
       </c>
       <c r="I39" t="n">
-        <v>23161.36</v>
+        <v>22452.08</v>
       </c>
       <c r="J39" t="n">
-        <v>24029.43</v>
+        <v>22389.83</v>
       </c>
       <c r="K39" t="n">
-        <v>24298.94</v>
+        <v>23275.86</v>
       </c>
       <c r="L39" t="n">
-        <v>24568.46</v>
+        <v>24161.88</v>
       </c>
       <c r="M39" t="n">
-        <v>25137.25</v>
+        <v>24573.77</v>
       </c>
       <c r="N39" t="n">
-        <v>25706.05</v>
+        <v>24985.65</v>
       </c>
       <c r="O39" t="n">
-        <v>25676.29</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>26345.81</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3817,81 +3819,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23811.76</v>
+        <v>22827.65</v>
       </c>
       <c r="C40" t="n">
-        <v>23863.71</v>
+        <v>23516.7</v>
       </c>
       <c r="D40" t="n">
-        <v>22518</v>
+        <v>22685.14</v>
       </c>
       <c r="E40" t="n">
-        <v>22671.86</v>
+        <v>23350.03</v>
       </c>
       <c r="F40" t="n">
-        <v>-1252.95</v>
+        <v>678.17</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0524</v>
+        <v>0.0299</v>
       </c>
       <c r="H40" t="n">
-        <v>1345.71</v>
+        <v>831.5599999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>22452.08</v>
+        <v>21172.29</v>
       </c>
       <c r="J40" t="n">
-        <v>22389.83</v>
+        <v>21066.65</v>
       </c>
       <c r="K40" t="n">
-        <v>23275.86</v>
+        <v>21999</v>
       </c>
       <c r="L40" t="n">
-        <v>24161.88</v>
+        <v>22931.36</v>
       </c>
       <c r="M40" t="n">
-        <v>24573.77</v>
+        <v>23344.71</v>
       </c>
       <c r="N40" t="n">
-        <v>24985.65</v>
+        <v>23758.07</v>
       </c>
       <c r="O40" t="n">
-        <v>26345.81</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
+        <v>25209.42</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3903,55 +3899,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>22827.65</v>
+        <v>23404.61</v>
       </c>
       <c r="C41" t="n">
-        <v>23516.7</v>
+        <v>24499.63</v>
       </c>
       <c r="D41" t="n">
-        <v>22685.14</v>
+        <v>23229.38</v>
       </c>
       <c r="E41" t="n">
-        <v>23350.03</v>
+        <v>24175.12</v>
       </c>
       <c r="F41" t="n">
-        <v>678.17</v>
+        <v>825.09</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0353</v>
       </c>
       <c r="H41" t="n">
-        <v>831.5599999999999</v>
+        <v>1270.25</v>
       </c>
       <c r="I41" t="n">
-        <v>21172.29</v>
+        <v>21853.58</v>
       </c>
       <c r="J41" t="n">
-        <v>21066.65</v>
+        <v>22643.03</v>
       </c>
       <c r="K41" t="n">
-        <v>21999</v>
+        <v>22934.25</v>
       </c>
       <c r="L41" t="n">
-        <v>22931.36</v>
+        <v>23225.47</v>
       </c>
       <c r="M41" t="n">
-        <v>23344.71</v>
+        <v>23765.81</v>
       </c>
       <c r="N41" t="n">
-        <v>23758.07</v>
+        <v>24306.14</v>
       </c>
       <c r="O41" t="n">
-        <v>25209.42</v>
+        <v>24348.26</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3962,21 +3962,25 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W41" s="11" t="inlineStr">
         <is>
@@ -3985,57 +3989,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>23404.61</v>
+        <v>24157.65</v>
       </c>
       <c r="C42" t="n">
-        <v>24499.63</v>
+        <v>25221.44</v>
       </c>
       <c r="D42" t="n">
-        <v>23229.38</v>
+        <v>23902.05</v>
       </c>
       <c r="E42" t="n">
-        <v>24175.12</v>
+        <v>24562.24</v>
       </c>
       <c r="F42" t="n">
-        <v>825.09</v>
+        <v>387.12</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.016</v>
       </c>
       <c r="H42" t="n">
-        <v>1270.25</v>
+        <v>1319.39</v>
       </c>
       <c r="I42" t="n">
-        <v>21853.58</v>
+        <v>21959.13</v>
       </c>
       <c r="J42" t="n">
-        <v>22643.03</v>
+        <v>23060.18</v>
       </c>
       <c r="K42" t="n">
-        <v>22934.25</v>
+        <v>23539.99</v>
       </c>
       <c r="L42" t="n">
-        <v>23225.47</v>
+        <v>24019.81</v>
       </c>
       <c r="M42" t="n">
-        <v>23765.81</v>
+        <v>24810.24</v>
       </c>
       <c r="N42" t="n">
-        <v>24306.14</v>
+        <v>25600.68</v>
       </c>
       <c r="O42" t="n">
-        <v>24348.26</v>
+        <v>25769.88</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4046,25 +4050,21 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
@@ -4080,50 +4080,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24157.65</v>
+        <v>24835.03</v>
       </c>
       <c r="C43" t="n">
-        <v>25221.44</v>
+        <v>25267.39</v>
       </c>
       <c r="D43" t="n">
-        <v>23902.05</v>
+        <v>24756.36</v>
       </c>
       <c r="E43" t="n">
-        <v>24562.24</v>
+        <v>24963.23</v>
       </c>
       <c r="F43" t="n">
-        <v>387.12</v>
+        <v>400.99</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
       </c>
       <c r="H43" t="n">
-        <v>1319.39</v>
+        <v>511.03</v>
       </c>
       <c r="I43" t="n">
-        <v>21959.13</v>
+        <v>22582.66</v>
       </c>
       <c r="J43" t="n">
-        <v>23060.18</v>
+        <v>23243.1</v>
       </c>
       <c r="K43" t="n">
-        <v>23539.99</v>
+        <v>23902.55</v>
       </c>
       <c r="L43" t="n">
-        <v>24019.81</v>
+        <v>24561.99</v>
       </c>
       <c r="M43" t="n">
-        <v>24810.24</v>
+        <v>25221.93</v>
       </c>
       <c r="N43" t="n">
-        <v>25600.68</v>
+        <v>25881.88</v>
       </c>
       <c r="O43" t="n">
-        <v>25769.88</v>
+        <v>26540.83</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4134,7 +4134,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4164,50 +4164,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24835.03</v>
+        <v>24993.77</v>
       </c>
       <c r="C44" t="n">
-        <v>25267.39</v>
+        <v>25971.63</v>
       </c>
       <c r="D44" t="n">
-        <v>24756.36</v>
+        <v>24938.34</v>
       </c>
       <c r="E44" t="n">
-        <v>24963.23</v>
+        <v>25884.43</v>
       </c>
       <c r="F44" t="n">
-        <v>400.99</v>
+        <v>921.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0369</v>
       </c>
       <c r="H44" t="n">
-        <v>511.03</v>
+        <v>1033.29</v>
       </c>
       <c r="I44" t="n">
-        <v>22582.66</v>
+        <v>24245.33</v>
       </c>
       <c r="J44" t="n">
-        <v>23243.1</v>
+        <v>24427.88</v>
       </c>
       <c r="K44" t="n">
-        <v>23902.55</v>
+        <v>24707.71</v>
       </c>
       <c r="L44" t="n">
-        <v>24561.99</v>
+        <v>24987.55</v>
       </c>
       <c r="M44" t="n">
-        <v>25221.93</v>
+        <v>25218.75</v>
       </c>
       <c r="N44" t="n">
-        <v>25881.88</v>
+        <v>25449.94</v>
       </c>
       <c r="O44" t="n">
-        <v>26540.83</v>
+        <v>25778.42</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4218,80 +4218,80 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>24993.77</v>
+        <v>25987.31</v>
       </c>
       <c r="C45" t="n">
-        <v>25971.63</v>
+        <v>26187.57</v>
       </c>
       <c r="D45" t="n">
-        <v>24938.34</v>
+        <v>25389.42</v>
       </c>
       <c r="E45" t="n">
-        <v>25884.43</v>
+        <v>25668.03</v>
       </c>
       <c r="F45" t="n">
-        <v>921.2</v>
+        <v>-216.4</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0369</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>1033.29</v>
+        <v>798.15</v>
       </c>
       <c r="I45" t="n">
-        <v>24245.33</v>
+        <v>23905.05</v>
       </c>
       <c r="J45" t="n">
-        <v>24427.88</v>
+        <v>25065.86</v>
       </c>
       <c r="K45" t="n">
-        <v>24707.71</v>
+        <v>25367.78</v>
       </c>
       <c r="L45" t="n">
-        <v>24987.55</v>
+        <v>25669.71</v>
       </c>
       <c r="M45" t="n">
-        <v>25218.75</v>
+        <v>26401.08</v>
       </c>
       <c r="N45" t="n">
-        <v>25449.94</v>
+        <v>27132.44</v>
       </c>
       <c r="O45" t="n">
-        <v>25778.42</v>
+        <v>27004.92</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4304,78 +4304,76 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25987.31</v>
+        <v>25805.18</v>
       </c>
       <c r="C46" t="n">
-        <v>26187.57</v>
+        <v>26060.32</v>
       </c>
       <c r="D46" t="n">
-        <v>25389.42</v>
+        <v>25089.14</v>
       </c>
       <c r="E46" t="n">
-        <v>25668.03</v>
+        <v>25116.85</v>
       </c>
       <c r="F46" t="n">
-        <v>-216.4</v>
+        <v>-551.1799999999999</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0215</v>
       </c>
       <c r="H46" t="n">
-        <v>798.15</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>23905.05</v>
+        <v>24591.27</v>
       </c>
       <c r="J46" t="n">
-        <v>25065.86</v>
+        <v>24809.65</v>
       </c>
       <c r="K46" t="n">
-        <v>25367.78</v>
+        <v>25268.95</v>
       </c>
       <c r="L46" t="n">
-        <v>25669.71</v>
+        <v>25728.26</v>
       </c>
       <c r="M46" t="n">
-        <v>26401.08</v>
+        <v>26067.1</v>
       </c>
       <c r="N46" t="n">
-        <v>27132.44</v>
+        <v>26405.95</v>
       </c>
       <c r="O46" t="n">
-        <v>27004.92</v>
+        <v>26985.72</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4383,12 +4381,14 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4407,57 +4407,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25805.18</v>
+        <v>25303.41</v>
       </c>
       <c r="C47" t="n">
-        <v>26060.32</v>
+        <v>26009.46</v>
       </c>
       <c r="D47" t="n">
-        <v>25089.14</v>
+        <v>25240.62</v>
       </c>
       <c r="E47" t="n">
-        <v>25116.85</v>
+        <v>26009.46</v>
       </c>
       <c r="F47" t="n">
-        <v>-551.1799999999999</v>
+        <v>892.61</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0215</v>
+        <v>0.0355</v>
       </c>
       <c r="H47" t="n">
-        <v>971.1799999999999</v>
+        <v>768.84</v>
       </c>
       <c r="I47" t="n">
-        <v>24591.27</v>
+        <v>24117.96</v>
       </c>
       <c r="J47" t="n">
-        <v>24809.65</v>
+        <v>23916.73</v>
       </c>
       <c r="K47" t="n">
-        <v>25268.95</v>
+        <v>24631.26</v>
       </c>
       <c r="L47" t="n">
-        <v>25728.26</v>
+        <v>25345.79</v>
       </c>
       <c r="M47" t="n">
-        <v>26067.1</v>
+        <v>25602.44</v>
       </c>
       <c r="N47" t="n">
-        <v>26405.95</v>
+        <v>25859.09</v>
       </c>
       <c r="O47" t="n">
-        <v>26985.72</v>
+        <v>27031.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4465,22 +4465,24 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4491,81 +4493,81 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25303.41</v>
+        <v>25780.12</v>
       </c>
       <c r="C48" t="n">
-        <v>26009.46</v>
+        <v>25800.22</v>
       </c>
       <c r="D48" t="n">
-        <v>25240.62</v>
+        <v>25403.44</v>
       </c>
       <c r="E48" t="n">
-        <v>26009.46</v>
+        <v>25584.79</v>
       </c>
       <c r="F48" t="n">
-        <v>892.61</v>
+        <v>-424.67</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0355</v>
+        <v>-0.0163</v>
       </c>
       <c r="H48" t="n">
-        <v>768.84</v>
+        <v>396.78</v>
       </c>
       <c r="I48" t="n">
-        <v>24117.96</v>
+        <v>24471.78</v>
       </c>
       <c r="J48" t="n">
-        <v>23916.73</v>
+        <v>25432.83</v>
       </c>
       <c r="K48" t="n">
-        <v>24631.26</v>
+        <v>25625.04</v>
       </c>
       <c r="L48" t="n">
-        <v>25345.79</v>
+        <v>25817.25</v>
       </c>
       <c r="M48" t="n">
-        <v>25602.44</v>
+        <v>26393.88</v>
       </c>
       <c r="N48" t="n">
-        <v>25859.09</v>
+        <v>26970.51</v>
       </c>
       <c r="O48" t="n">
-        <v>27031.5</v>
+        <v>26778.3</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4577,57 +4579,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25780.12</v>
+        <v>25420.63</v>
       </c>
       <c r="C49" t="n">
-        <v>25800.22</v>
+        <v>25791.38</v>
       </c>
       <c r="D49" t="n">
-        <v>25403.44</v>
+        <v>25008.87</v>
       </c>
       <c r="E49" t="n">
-        <v>25584.79</v>
+        <v>25650.87</v>
       </c>
       <c r="F49" t="n">
-        <v>-424.67</v>
+        <v>66.08</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0163</v>
+        <v>0.0026</v>
       </c>
       <c r="H49" t="n">
-        <v>396.78</v>
+        <v>782.51</v>
       </c>
       <c r="I49" t="n">
-        <v>24471.78</v>
+        <v>25006.66</v>
       </c>
       <c r="J49" t="n">
-        <v>25432.83</v>
+        <v>25179.49</v>
       </c>
       <c r="K49" t="n">
-        <v>25625.04</v>
+        <v>25386.4</v>
       </c>
       <c r="L49" t="n">
-        <v>25817.25</v>
+        <v>25593.31</v>
       </c>
       <c r="M49" t="n">
-        <v>26393.88</v>
+        <v>25783.18</v>
       </c>
       <c r="N49" t="n">
-        <v>26970.51</v>
+        <v>25973.05</v>
       </c>
       <c r="O49" t="n">
-        <v>26778.3</v>
+        <v>26197</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4639,16 +4641,18 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4670,73 +4674,71 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25420.63</v>
+        <v>25652.97</v>
       </c>
       <c r="C50" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D50" t="n">
-        <v>25008.87</v>
+        <v>24570.24</v>
       </c>
       <c r="E50" t="n">
-        <v>25650.87</v>
+        <v>24805.63</v>
       </c>
       <c r="F50" t="n">
-        <v>66.08</v>
+        <v>-845.24</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.033</v>
       </c>
       <c r="H50" t="n">
-        <v>782.51</v>
+        <v>1094.74</v>
       </c>
       <c r="I50" t="n">
-        <v>25006.66</v>
+        <v>24226.36</v>
       </c>
       <c r="J50" t="n">
-        <v>25179.49</v>
+        <v>24993.73</v>
       </c>
       <c r="K50" t="n">
-        <v>25386.4</v>
+        <v>25259.61</v>
       </c>
       <c r="L50" t="n">
-        <v>25593.31</v>
+        <v>25525.5</v>
       </c>
       <c r="M50" t="n">
-        <v>25783.18</v>
+        <v>26042.12</v>
       </c>
       <c r="N50" t="n">
-        <v>25973.05</v>
+        <v>26558.75</v>
       </c>
       <c r="O50" t="n">
-        <v>26197</v>
+        <v>26573.89</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4744,81 +4746,73 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25652.97</v>
+        <v>24701.18</v>
       </c>
       <c r="C51" t="n">
-        <v>25664.98</v>
+        <v>24934.06</v>
       </c>
       <c r="D51" t="n">
-        <v>24570.24</v>
+        <v>24357.69</v>
       </c>
       <c r="E51" t="n">
-        <v>24805.63</v>
+        <v>24750.78</v>
       </c>
       <c r="F51" t="n">
-        <v>-845.24</v>
+        <v>-54.85</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.0022</v>
       </c>
       <c r="H51" t="n">
-        <v>1094.74</v>
+        <v>576.37</v>
       </c>
       <c r="I51" t="n">
-        <v>24226.36</v>
+        <v>23475.5</v>
       </c>
       <c r="J51" t="n">
-        <v>24993.73</v>
+        <v>23554.9</v>
       </c>
       <c r="K51" t="n">
-        <v>25259.61</v>
+        <v>24258.26</v>
       </c>
       <c r="L51" t="n">
-        <v>25525.5</v>
+        <v>24961.62</v>
       </c>
       <c r="M51" t="n">
-        <v>26042.12</v>
+        <v>25353</v>
       </c>
       <c r="N51" t="n">
-        <v>26558.75</v>
+        <v>25744.38</v>
       </c>
       <c r="O51" t="n">
-        <v>26573.89</v>
+        <v>26759.72</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4840,50 +4834,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24701.18</v>
+        <v>24748.45</v>
       </c>
       <c r="C52" t="n">
-        <v>24934.06</v>
+        <v>25254.11</v>
       </c>
       <c r="D52" t="n">
-        <v>24357.69</v>
+        <v>24275.56</v>
       </c>
       <c r="E52" t="n">
-        <v>24750.78</v>
+        <v>24510.09</v>
       </c>
       <c r="F52" t="n">
-        <v>-54.85</v>
+        <v>-240.69</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0097</v>
       </c>
       <c r="H52" t="n">
-        <v>576.37</v>
+        <v>978.55</v>
       </c>
       <c r="I52" t="n">
-        <v>23475.5</v>
+        <v>23781.32</v>
       </c>
       <c r="J52" t="n">
-        <v>23554.9</v>
+        <v>24226.86</v>
       </c>
       <c r="K52" t="n">
-        <v>24258.26</v>
+        <v>24462.59</v>
       </c>
       <c r="L52" t="n">
-        <v>24961.62</v>
+        <v>24698.33</v>
       </c>
       <c r="M52" t="n">
-        <v>25353</v>
+        <v>25038.96</v>
       </c>
       <c r="N52" t="n">
-        <v>25744.38</v>
+        <v>25379.6</v>
       </c>
       <c r="O52" t="n">
-        <v>26759.72</v>
+        <v>25510.43</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4891,16 +4885,20 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4913,55 +4911,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24748.45</v>
+        <v>24554.58</v>
       </c>
       <c r="C53" t="n">
-        <v>25254.11</v>
+        <v>24767.22</v>
       </c>
       <c r="D53" t="n">
-        <v>24275.56</v>
+        <v>23865.33</v>
       </c>
       <c r="E53" t="n">
-        <v>24510.09</v>
+        <v>23972.29</v>
       </c>
       <c r="F53" t="n">
-        <v>-240.69</v>
+        <v>-537.8</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0219</v>
       </c>
       <c r="H53" t="n">
-        <v>978.55</v>
+        <v>901.89</v>
       </c>
       <c r="I53" t="n">
-        <v>23781.32</v>
+        <v>23297.01</v>
       </c>
       <c r="J53" t="n">
-        <v>24226.86</v>
+        <v>23404.17</v>
       </c>
       <c r="K53" t="n">
-        <v>24462.59</v>
+        <v>24020.82</v>
       </c>
       <c r="L53" t="n">
-        <v>24698.33</v>
+        <v>24637.46</v>
       </c>
       <c r="M53" t="n">
-        <v>25038.96</v>
+        <v>24999.36</v>
       </c>
       <c r="N53" t="n">
-        <v>25379.6</v>
+        <v>25361.27</v>
       </c>
       <c r="O53" t="n">
-        <v>25510.43</v>
+        <v>26232.66</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4974,15 +4976,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4995,59 +4995,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24554.58</v>
+        <v>23963.41</v>
       </c>
       <c r="C54" t="n">
-        <v>24767.22</v>
+        <v>24354.11</v>
       </c>
       <c r="D54" t="n">
-        <v>23865.33</v>
+        <v>23737.14</v>
       </c>
       <c r="E54" t="n">
-        <v>23972.29</v>
+        <v>24211.35</v>
       </c>
       <c r="F54" t="n">
-        <v>-537.8</v>
+        <v>239.06</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0219</v>
+        <v>0.01</v>
       </c>
       <c r="H54" t="n">
-        <v>901.89</v>
+        <v>616.97</v>
       </c>
       <c r="I54" t="n">
-        <v>23297.01</v>
+        <v>22963.44</v>
       </c>
       <c r="J54" t="n">
-        <v>23404.17</v>
+        <v>22898.41</v>
       </c>
       <c r="K54" t="n">
-        <v>24020.82</v>
+        <v>23521.34</v>
       </c>
       <c r="L54" t="n">
-        <v>24637.46</v>
+        <v>24144.28</v>
       </c>
       <c r="M54" t="n">
-        <v>24999.36</v>
+        <v>24423.23</v>
       </c>
       <c r="N54" t="n">
-        <v>25361.27</v>
+        <v>24702.19</v>
       </c>
       <c r="O54" t="n">
-        <v>26232.66</v>
+        <v>25669.11</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5055,14 +5051,12 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5079,55 +5073,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23963.41</v>
+        <v>24434.93</v>
       </c>
       <c r="C55" t="n">
-        <v>24354.11</v>
+        <v>24524.63</v>
       </c>
       <c r="D55" t="n">
-        <v>23737.14</v>
+        <v>23945.84</v>
       </c>
       <c r="E55" t="n">
-        <v>24211.35</v>
+        <v>24186.83</v>
       </c>
       <c r="F55" t="n">
-        <v>239.06</v>
+        <v>-24.52</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="H55" t="n">
-        <v>616.97</v>
+        <v>578.79</v>
       </c>
       <c r="I55" t="n">
-        <v>22963.44</v>
+        <v>23120.17</v>
       </c>
       <c r="J55" t="n">
-        <v>22898.41</v>
+        <v>23677.24</v>
       </c>
       <c r="K55" t="n">
-        <v>23521.34</v>
+        <v>23902.87</v>
       </c>
       <c r="L55" t="n">
-        <v>24144.28</v>
+        <v>24128.49</v>
       </c>
       <c r="M55" t="n">
-        <v>24423.23</v>
+        <v>24519.83</v>
       </c>
       <c r="N55" t="n">
-        <v>24702.19</v>
+        <v>24911.18</v>
       </c>
       <c r="O55" t="n">
-        <v>25669.11</v>
+        <v>24971.08</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5138,13 +5136,15 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5159,76 +5159,80 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24434.93</v>
+        <v>23990.05</v>
       </c>
       <c r="C56" t="n">
-        <v>24524.63</v>
+        <v>24139.11</v>
       </c>
       <c r="D56" t="n">
-        <v>23945.84</v>
+        <v>22803.77</v>
       </c>
       <c r="E56" t="n">
-        <v>24186.83</v>
+        <v>23093.37</v>
       </c>
       <c r="F56" t="n">
-        <v>-24.52</v>
+        <v>-1093.46</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0452</v>
       </c>
       <c r="H56" t="n">
-        <v>578.79</v>
+        <v>1335.34</v>
       </c>
       <c r="I56" t="n">
-        <v>23120.17</v>
+        <v>23367.05</v>
       </c>
       <c r="J56" t="n">
-        <v>23677.24</v>
+        <v>23583.84</v>
       </c>
       <c r="K56" t="n">
-        <v>23902.87</v>
+        <v>23897.43</v>
       </c>
       <c r="L56" t="n">
-        <v>24128.49</v>
+        <v>24211.03</v>
       </c>
       <c r="M56" t="n">
-        <v>24519.83</v>
+        <v>24476.23</v>
       </c>
       <c r="N56" t="n">
-        <v>24911.18</v>
+        <v>24741.42</v>
       </c>
       <c r="O56" t="n">
-        <v>24971.08</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+        <v>25103.42</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5241,78 +5245,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23990.05</v>
+        <v>23156.96</v>
       </c>
       <c r="C57" t="n">
-        <v>24139.11</v>
+        <v>23400.02</v>
       </c>
       <c r="D57" t="n">
-        <v>22803.77</v>
+        <v>22928.27</v>
       </c>
       <c r="E57" t="n">
-        <v>23093.37</v>
+        <v>23294.42</v>
       </c>
       <c r="F57" t="n">
-        <v>-1093.46</v>
+        <v>201.05</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0452</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>1335.34</v>
+        <v>471.75</v>
       </c>
       <c r="I57" t="n">
-        <v>23367.05</v>
+        <v>21468.43</v>
       </c>
       <c r="J57" t="n">
-        <v>23583.84</v>
+        <v>21568.99</v>
       </c>
       <c r="K57" t="n">
-        <v>23897.43</v>
+        <v>22425.7</v>
       </c>
       <c r="L57" t="n">
-        <v>24211.03</v>
+        <v>23282.4</v>
       </c>
       <c r="M57" t="n">
-        <v>24476.23</v>
+        <v>23761.04</v>
       </c>
       <c r="N57" t="n">
-        <v>24741.42</v>
+        <v>24239.67</v>
       </c>
       <c r="O57" t="n">
-        <v>25103.42</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>25474.45</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5329,87 +5323,9 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>23156.96</v>
-      </c>
-      <c r="C58" t="n">
-        <v>23313.92</v>
-      </c>
-      <c r="D58" t="n">
-        <v>22928.27</v>
-      </c>
-      <c r="E58" t="n">
-        <v>22958.65</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-134.72</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0058</v>
-      </c>
-      <c r="H58" t="n">
-        <v>385.65</v>
-      </c>
-      <c r="I58" t="n">
-        <v>21468.43</v>
-      </c>
-      <c r="J58" t="n">
-        <v>21568.99</v>
-      </c>
-      <c r="K58" t="n">
-        <v>22425.7</v>
-      </c>
-      <c r="L58" t="n">
-        <v>23282.4</v>
-      </c>
-      <c r="M58" t="n">
-        <v>23761.04</v>
-      </c>
-      <c r="N58" t="n">
-        <v>24239.67</v>
-      </c>
-      <c r="O58" t="n">
-        <v>25474.45</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
